--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>10508</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>16279</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>7.69000005722046</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>24893</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>7.57000017166138</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>57291</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>7.57000017166138</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>7.6100001335144</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>51814</v>
+        <v>31053</v>
       </c>
       <c r="C2715" t="n">
-        <v>7.92000007629395</v>
+        <v>7.92999982833862</v>
       </c>
       <c r="D2715" t="n">
-        <v>7.78000020980835</v>
+        <v>7.69999980926514</v>
       </c>
       <c r="E2715" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F2715" t="n">
         <v>7.88000011444092</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>7.90999984741211</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>57951</v>
+        <v>51814</v>
       </c>
       <c r="C2716" t="n">
-        <v>7.8600001335144</v>
+        <v>7.92000007629395</v>
       </c>
       <c r="D2716" t="n">
-        <v>7.57999992370605</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="E2716" t="n">
-        <v>7.8600001335144</v>
+        <v>7.88000011444092</v>
       </c>
       <c r="F2716" t="n">
-        <v>7.6100001335144</v>
+        <v>7.90999984741211</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>24543</v>
+        <v>57951</v>
       </c>
       <c r="C2717" t="n">
-        <v>7.78000020980835</v>
+        <v>7.8600001335144</v>
       </c>
       <c r="D2717" t="n">
-        <v>7.59000015258789</v>
+        <v>7.57999992370605</v>
       </c>
       <c r="E2717" t="n">
-        <v>7.65999984741211</v>
+        <v>7.8600001335144</v>
       </c>
       <c r="F2717" t="n">
-        <v>7.65999984741211</v>
+        <v>7.6100001335144</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>39683</v>
+        <v>24543</v>
       </c>
       <c r="C2718" t="n">
-        <v>7.71000003814697</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="D2718" t="n">
-        <v>7.57999992370605</v>
+        <v>7.59000015258789</v>
       </c>
       <c r="E2718" t="n">
-        <v>7.67999982833862</v>
+        <v>7.65999984741211</v>
       </c>
       <c r="F2718" t="n">
-        <v>7.61999988555908</v>
+        <v>7.65999984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>10508</v>
+        <v>39683</v>
       </c>
       <c r="C2719" t="n">
-        <v>7.67999982833862</v>
+        <v>7.71000003814697</v>
       </c>
       <c r="D2719" t="n">
         <v>7.57999992370605</v>
       </c>
       <c r="E2719" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="F2719" t="n">
         <v>7.61999988555908</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>7.57999992370605</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>16279</v>
+        <v>10508</v>
       </c>
       <c r="C2720" t="n">
-        <v>7.69000005722046</v>
+        <v>7.67999982833862</v>
       </c>
       <c r="D2720" t="n">
-        <v>7.51999998092651</v>
+        <v>7.57999992370605</v>
       </c>
       <c r="E2720" t="n">
-        <v>7.51999998092651</v>
+        <v>7.61999988555908</v>
       </c>
       <c r="F2720" t="n">
-        <v>7.59999990463257</v>
+        <v>7.57999992370605</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,13 +62934,13 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>24893</v>
+        <v>16279</v>
       </c>
       <c r="C2721" t="n">
-        <v>7.61999988555908</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="D2721" t="n">
         <v>7.51999998092651</v>
@@ -62949,7 +62949,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="F2721" t="n">
-        <v>7.57000017166138</v>
+        <v>7.59999990463257</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>57291</v>
+        <v>24893</v>
       </c>
       <c r="C2722" t="n">
-        <v>7.69999980926514</v>
+        <v>7.61999988555908</v>
       </c>
       <c r="D2722" t="n">
-        <v>7.5</v>
+        <v>7.51999998092651</v>
       </c>
       <c r="E2722" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2722" t="n">
         <v>7.57000017166138</v>
       </c>
-      <c r="F2722" t="n">
-        <v>7.6100001335144</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>73933</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>7.73000001907349</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349234104156</v>
+        <v>1.89349222183228</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853262901306</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612635612488</v>
+        <v>1.80612623691559</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139402866364</v>
+        <v>1.63139390945435</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71371972560883</v>
+        <v>1.71371984481812</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754970550537</v>
+        <v>1.56754958629608</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314003944397</v>
+        <v>1.43314015865326</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.40877842903137</v>
+        <v>1.40877854824066</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>1.50370514392853</v>
+        <v>1.50370502471924</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54570806026459</v>
+        <v>1.54570817947388</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525700569153</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G26" t="n">
-        <v>1.342414021492</v>
+        <v>1.34241390228271</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995969295502</v>
+        <v>1.13995957374573</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G30" t="n">
-        <v>1.1693617105484</v>
+        <v>1.16936159133911</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204330444336</v>
+        <v>1.19204342365265</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35333454608917</v>
+        <v>1.35333442687988</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>1.43650054931641</v>
+        <v>1.43650043010712</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G39" t="n">
-        <v>1.44742131233215</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G40" t="n">
-        <v>1.44742131233215</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254241466522</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126575469971</v>
+        <v>1.51126563549042</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G45" t="n">
-        <v>1.54570806026459</v>
+        <v>1.54570817947388</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G47" t="n">
-        <v>1.50874531269073</v>
+        <v>1.50874543190002</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.4801834821701</v>
+        <v>1.48018336296082</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586945056915</v>
+        <v>1.56586933135986</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G58" t="n">
-        <v>1.58183062076569</v>
+        <v>1.5818305015564</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G59" t="n">
-        <v>1.55578875541687</v>
+        <v>1.55578863620758</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690390586853</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G63" t="n">
-        <v>1.45078146457672</v>
+        <v>1.45078134536743</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994139671326</v>
+        <v>1.44994115829468</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30965161323547</v>
+        <v>1.30965149402618</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G70" t="n">
-        <v>1.41465890407562</v>
+        <v>1.41465878486633</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>1.44742131233215</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847023010254</v>
+        <v>1.57847034931183</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830883979797</v>
+        <v>1.55830895900726</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G77" t="n">
-        <v>1.57427000999451</v>
+        <v>1.57426989078522</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.60787236690521</v>
+        <v>1.6078724861145</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646743297577</v>
+        <v>1.53646731376648</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>1.50370514392853</v>
+        <v>1.50370502471924</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574117660522</v>
+        <v>1.44574093818665</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G89" t="n">
-        <v>1.41213870048523</v>
+        <v>1.41213858127594</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>1.43650054931641</v>
+        <v>1.43650043010712</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.42809975147247</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G97" t="n">
-        <v>1.49110436439514</v>
+        <v>1.49110424518585</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.48270356655121</v>
+        <v>1.4827036857605</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278426170349</v>
+        <v>1.49278438091278</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G103" t="n">
-        <v>1.49866473674774</v>
+        <v>1.49866461753845</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51798605918884</v>
+        <v>1.51798617839813</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126575469971</v>
+        <v>1.51126563549042</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690390586853</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G110" t="n">
-        <v>1.46338212490082</v>
+        <v>1.4633823633194</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.54150784015656</v>
+        <v>1.54150772094727</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614465236664</v>
+        <v>1.49614453315735</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457832813263</v>
+        <v>1.40457820892334</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577405452728</v>
+        <v>1.34577417373657</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G117" t="n">
-        <v>1.35669493675232</v>
+        <v>1.35669481754303</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205812454224</v>
+        <v>1.40205788612366</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G120" t="n">
-        <v>1.42809975147247</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G123" t="n">
-        <v>1.43734049797058</v>
+        <v>1.43734037876129</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G127" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537057876587</v>
+        <v>1.29537069797516</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G134" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G139" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35081458091736</v>
+        <v>1.35081446170807</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G153" t="n">
-        <v>1.33737349510193</v>
+        <v>1.33737361431122</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G154" t="n">
-        <v>1.32309257984161</v>
+        <v>1.32309246063232</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.32309257984161</v>
+        <v>1.32309246063232</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G163" t="n">
-        <v>1.2609281539917</v>
+        <v>1.26092803478241</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680862903595</v>
+        <v>1.26680850982666</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545127391815</v>
+        <v>1.30545115470886</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30293095111847</v>
+        <v>1.30293107032776</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29201030731201</v>
+        <v>1.29201018810272</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G168" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813286781311</v>
+        <v>1.32813274860382</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713140964508</v>
+        <v>1.30713129043579</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29621064662933</v>
+        <v>1.29621052742004</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265598773956</v>
+        <v>1.37265586853027</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G180" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G181" t="n">
-        <v>1.35081458091736</v>
+        <v>1.35081446170807</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33989381790161</v>
+        <v>1.33989369869232</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477259635925</v>
+        <v>1.32477271556854</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G187" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G192" t="n">
-        <v>1.36929559707642</v>
+        <v>1.36929571628571</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.37685632705688</v>
+        <v>1.3768562078476</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G194" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G195" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525700569153</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.625</v>
       </c>
       <c r="G198" t="n">
-        <v>1.36509537696838</v>
+        <v>1.36509549617767</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105666637421</v>
+        <v>1.38105642795563</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881142616272</v>
+        <v>1.30881154537201</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G203" t="n">
-        <v>1.3163720369339</v>
+        <v>1.31637215614319</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G211" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G215" t="n">
-        <v>1.27856922149658</v>
+        <v>1.27856934070587</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G217" t="n">
-        <v>1.27184891700745</v>
+        <v>1.27184903621674</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G222" t="n">
-        <v>1.17944252490997</v>
+        <v>1.17944264411926</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367574214935</v>
+        <v>1.08367562294006</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G229" t="n">
-        <v>1.09543657302856</v>
+        <v>1.09543669223785</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115565776825</v>
+        <v>1.08115553855896</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.0803154706955</v>
+        <v>1.08031535148621</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.0635142326355</v>
+        <v>1.06351435184479</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>1.058473944664</v>
+        <v>1.05847406387329</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.03915250301361</v>
+        <v>1.03915274143219</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G242" t="n">
-        <v>1.12651884555817</v>
+        <v>1.12651860713959</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.12567865848541</v>
+        <v>1.1256787776947</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.12567865848541</v>
+        <v>1.1256787776947</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584016799927</v>
+        <v>1.14584004878998</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G247" t="n">
-        <v>1.16768169403076</v>
+        <v>1.16768157482147</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.16180109977722</v>
+        <v>1.16180121898651</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348123550415</v>
+        <v>1.16348135471344</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364274501801</v>
+        <v>1.18364286422729</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501480102539</v>
+        <v>1.3550146818161</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G264" t="n">
-        <v>1.31469178199768</v>
+        <v>1.31469202041626</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377113819122</v>
+        <v>1.3037713766098</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G269" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832713603973</v>
+        <v>1.24832725524902</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.18868315219879</v>
+        <v>1.1886830329895</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448269367218</v>
+        <v>1.18448281288147</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G284" t="n">
-        <v>1.18784296512604</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104184627533</v>
+        <v>1.17104196548462</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.38900005817413</v>
       </c>
       <c r="G287" t="n">
-        <v>1.1668416261673</v>
+        <v>1.16684150695801</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G289" t="n">
-        <v>1.17776226997375</v>
+        <v>1.17776238918304</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G290" t="n">
-        <v>1.1693617105484</v>
+        <v>1.16936159133911</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G291" t="n">
-        <v>1.17860233783722</v>
+        <v>1.17860245704651</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G295" t="n">
-        <v>1.15088057518005</v>
+        <v>1.15088045597076</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424048900604</v>
+        <v>1.15424072742462</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G298" t="n">
-        <v>1.16516137123108</v>
+        <v>1.16516149044037</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740649223328</v>
+        <v>1.23740637302399</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236632347107</v>
+        <v>1.23236620426178</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G311" t="n">
-        <v>1.18784296512604</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G316" t="n">
-        <v>1.17860233783722</v>
+        <v>1.17860245704651</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.21052467823029</v>
+        <v>1.210524559021</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G323" t="n">
-        <v>1.25000727176666</v>
+        <v>1.25000739097595</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688932418823</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688932418823</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.26596856117249</v>
+        <v>1.2659684419632</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320615291595</v>
+        <v>1.23320627212524</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908662796021</v>
+        <v>1.23908674716949</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G337" t="n">
-        <v>1.22564566135406</v>
+        <v>1.22564578056335</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488640785217</v>
+        <v>1.23488628864288</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664711952209</v>
+        <v>1.24664723873138</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G345" t="n">
-        <v>1.30293095111847</v>
+        <v>1.30293107032776</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G347" t="n">
-        <v>1.29789066314697</v>
+        <v>1.29789078235626</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G350" t="n">
-        <v>1.29705083370209</v>
+        <v>1.29705059528351</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890682220459</v>
+        <v>1.52890694141388</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690390586853</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G360" t="n">
-        <v>1.46002209186554</v>
+        <v>1.46002221107483</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>1.45498168468475</v>
+        <v>1.45498180389404</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.38861703872681</v>
+        <v>1.38861691951752</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.625</v>
       </c>
       <c r="G367" t="n">
-        <v>1.36509537696838</v>
+        <v>1.36509549617767</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G368" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173534393311</v>
+        <v>1.36173522472382</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G370" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G376" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G382" t="n">
-        <v>1.35081458091736</v>
+        <v>1.35081446170807</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G383" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G387" t="n">
-        <v>1.4297798871994</v>
+        <v>1.42978000640869</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297876834869</v>
+        <v>1.41297888755798</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G394" t="n">
-        <v>1.44406080245972</v>
+        <v>1.44406092166901</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.42809975147247</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>1.41213870048523</v>
+        <v>1.41213858127594</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.42809975147247</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G399" t="n">
-        <v>1.4297798871994</v>
+        <v>1.42978000640869</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G404" t="n">
-        <v>1.46338212490082</v>
+        <v>1.4633823633194</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G405" t="n">
-        <v>1.43734049797058</v>
+        <v>1.43734037876129</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918190479279</v>
+        <v>1.45918202400208</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.53310716152191</v>
+        <v>1.5331072807312</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G412" t="n">
-        <v>1.48774385452271</v>
+        <v>1.48774397373199</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>1.44742131233215</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574117660522</v>
+        <v>1.44574093818665</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238078594208</v>
+        <v>1.44238090515137</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G428" t="n">
-        <v>1.43398022651672</v>
+        <v>1.43398034572601</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.4415408372879</v>
+        <v>1.44154071807861</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842265129089</v>
+        <v>1.46842277050018</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254241466522</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531928539276</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.80108606815338</v>
+        <v>1.8010858297348</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G446" t="n">
-        <v>1.78428483009338</v>
+        <v>1.78428471088409</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G447" t="n">
-        <v>2.08502602577209</v>
+        <v>2.08502578735352</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717527389526</v>
+        <v>1.93717551231384</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429965019226</v>
+        <v>1.99429953098297</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.94053566455841</v>
+        <v>1.94053554534912</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013195037842</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.9875785112381</v>
+        <v>1.98757874965668</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229649543762</v>
+        <v>1.95229625701904</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476923942566</v>
+        <v>1.84476912021637</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>1.85652983188629</v>
+        <v>1.856529712677</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100513458252</v>
+        <v>1.79100501537323</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165069580078</v>
+        <v>1.87165093421936</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.86493051052094</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.00438022613525</v>
+        <v>2.0043797492981</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.9489358663559</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581791877747</v>
+        <v>1.97581803798676</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341188430786</v>
+        <v>1.88341200351715</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308874607086</v>
+        <v>1.84308886528015</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316967964172</v>
+        <v>1.85316956043243</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G480" t="n">
-        <v>1.66751658916473</v>
+        <v>1.66751670837402</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879324913025</v>
+        <v>1.61879312992096</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.64651501178741</v>
+        <v>1.6465151309967</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G484" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G485" t="n">
-        <v>1.58855092525482</v>
+        <v>1.58855104446411</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326867103577</v>
+        <v>1.55326855182648</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G490" t="n">
-        <v>1.50874531269073</v>
+        <v>1.50874543190002</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G491" t="n">
-        <v>1.54570806026459</v>
+        <v>1.54570817947388</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54150784015656</v>
+        <v>1.54150772094727</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>1.59695172309875</v>
+        <v>1.59695160388947</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.61291265487671</v>
+        <v>1.612912774086</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811445236206</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531928539276</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507696151733</v>
+        <v>1.67507708072662</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299346923828</v>
+        <v>1.62299335002899</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451209545135</v>
+        <v>1.60451221466064</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459279060364</v>
+        <v>1.61459290981293</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811445236206</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887394428253</v>
+        <v>1.62887382507324</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62467348575592</v>
+        <v>1.62467360496521</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090973854065</v>
+        <v>1.57090985774994</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535204410553</v>
+        <v>1.60535228252411</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G515" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323555469513</v>
+        <v>1.65323567390442</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171704769135</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851792812347</v>
+        <v>1.68851804733276</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G524" t="n">
-        <v>1.71792006492615</v>
+        <v>1.71792018413544</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>1.873330950737</v>
+        <v>1.87333106994629</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>1.82292759418488</v>
+        <v>1.8229273557663</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013195037842</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G530" t="n">
-        <v>1.86493051052094</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.75992321968079</v>
+        <v>1.75992298126221</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152254104614</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152254104614</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G543" t="n">
-        <v>1.77252376079559</v>
+        <v>1.77252388000488</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.7935254573822</v>
+        <v>1.79352533817291</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.72632074356079</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G551" t="n">
-        <v>1.75572264194489</v>
+        <v>1.75572276115417</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472142219543</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72632074356079</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171704769135</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011736869812</v>
+        <v>1.68011748790741</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472142219543</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G564" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>1.82292759418488</v>
+        <v>1.8229273557663</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872689723969</v>
+        <v>1.81872713565826</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.125</v>
       </c>
       <c r="G572" t="n">
-        <v>1.78512465953827</v>
+        <v>1.78512477874756</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>1.76832365989685</v>
+        <v>1.76832354068756</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>1.78092455863953</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.7935254573822</v>
+        <v>1.79352533817291</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>1.78092455863953</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872689723969</v>
+        <v>1.81872713565826</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192601680756</v>
+        <v>1.80192589759827</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G582" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113388538361</v>
+        <v>1.91113364696503</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013195037842</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.9489358663559</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853262901306</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373430728912</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373430728912</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253858089447</v>
+        <v>1.98253834247589</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993768215179</v>
+        <v>1.96993780136108</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>1.97833800315857</v>
+        <v>1.97833847999573</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>2.04554271697998</v>
+        <v>2.04554319381714</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093902111053</v>
+        <v>1.99093914031982</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>2.116947889328</v>
+        <v>2.11694812774658</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.2639582157135</v>
+        <v>2.26395845413208</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935463905334</v>
+        <v>2.20935440063477</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935463905334</v>
+        <v>2.20935440063477</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214992523193</v>
+        <v>2.14214968681335</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G608" t="n">
-        <v>2.2345564365387</v>
+        <v>2.23455619812012</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>2.2135546207428</v>
+        <v>2.21355509757996</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.410968542099</v>
+        <v>2.41096830368042</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177573204041</v>
+        <v>2.51177549362183</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>2.4949746131897</v>
+        <v>2.49497437477112</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>2.62938356399536</v>
+        <v>2.62938404083252</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67978763580322</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099794387817</v>
+        <v>2.83099770545959</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059411048889</v>
+        <v>2.78059434890747</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00321006774902</v>
+        <v>3.00320982933044</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661767959595</v>
+        <v>3.11661791801453</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.15442085266113</v>
+        <v>3.15442061424255</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10821723937988</v>
+        <v>3.10821747779846</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16282105445862</v>
+        <v>3.1628212928772</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803743362427</v>
+        <v>3.39803767204285</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703585624695</v>
+        <v>3.37703609466553</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G642" t="n">
-        <v>3.40223789215088</v>
+        <v>3.40223813056946</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446483612061</v>
+        <v>3.78446435928345</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827651977539</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887354850769</v>
+        <v>3.91887378692627</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927738189697</v>
+        <v>3.96927666664124</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887354850769</v>
+        <v>3.91887378692627</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226777076721</v>
+        <v>3.82226729393005</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746861457825</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545159339905</v>
+        <v>3.59545111656189</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.7970654964447</v>
+        <v>3.79706525802612</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.12048768997192</v>
+        <v>4.12048816680908</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>4.1498908996582</v>
+        <v>4.14988994598389</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.4775128364563</v>
+        <v>4.47751331329346</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G665" t="n">
-        <v>4.43550968170166</v>
+        <v>4.43551015853882</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>4.60352230072021</v>
+        <v>4.60352182388306</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>4.7967357635498</v>
+        <v>4.79673480987549</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>4.6539249420166</v>
+        <v>4.65392541885376</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.821937084198</v>
+        <v>4.82193660736084</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553932189941</v>
+        <v>4.85553979873657</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074159622192</v>
+        <v>4.88074064254761</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>4.67072677612305</v>
+        <v>4.67072629928589</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.7043285369873</v>
+        <v>4.70432901382446</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G681" t="n">
-        <v>4.73793077468872</v>
+        <v>4.73793125152588</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>4.6539249420166</v>
+        <v>4.65392541885376</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G686" t="n">
-        <v>4.56151866912842</v>
+        <v>4.56151914596558</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44391059875488</v>
+        <v>4.44391107559204</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271463394165</v>
+        <v>4.50271511077881</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G690" t="n">
-        <v>4.46911287307739</v>
+        <v>4.46911239624023</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350652694702</v>
+        <v>4.39350748062134</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.33470296859741</v>
+        <v>4.33470249176025</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>4.05328321456909</v>
+        <v>4.05328273773193</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748414993286</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788774490356</v>
+        <v>4.10788679122925</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95667600631714</v>
+        <v>3.95667695999146</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.80546617507935</v>
+        <v>3.80546641349792</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286503791809</v>
+        <v>3.79286479949951</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>3.51144528388977</v>
+        <v>3.51144552230835</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.625</v>
       </c>
       <c r="G706" t="n">
-        <v>3.04521298408508</v>
+        <v>3.04521250724792</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.9528067111969</v>
+        <v>2.95280647277832</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.98220872879028</v>
+        <v>2.9822084903717</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>2.86880040168762</v>
+        <v>2.86880016326904</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419682502747</v>
+        <v>2.81419658660889</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G718" t="n">
-        <v>2.67978763580322</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G719" t="n">
-        <v>2.66718626022339</v>
+        <v>2.66718649864197</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G721" t="n">
-        <v>2.67978763580322</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>2.7973952293396</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.1418194770813</v>
+        <v>3.14181971549988</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G728" t="n">
-        <v>3.09141612052917</v>
+        <v>3.09141635894775</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>3.31823182106018</v>
+        <v>3.31823205947876</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>3.28883004188538</v>
+        <v>3.2888298034668</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G735" t="n">
-        <v>3.10401701927185</v>
+        <v>3.10401678085327</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="n">
-        <v>3.09141612052917</v>
+        <v>3.09141635894775</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380781173706</v>
+        <v>2.97380805015564</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.84779906272888</v>
+        <v>2.84779930114746</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.27622890472412</v>
+        <v>3.27622938156128</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781364440918</v>
+        <v>3.05781388282776</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.625</v>
       </c>
       <c r="G751" t="n">
-        <v>3.04521298408508</v>
+        <v>3.04521250724792</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.98220872879028</v>
+        <v>2.9822084903717</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380781173706</v>
+        <v>2.97380805015564</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G754" t="n">
-        <v>3.02001118659973</v>
+        <v>3.02001094818115</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060893058777</v>
+        <v>2.99060916900635</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.25</v>
       </c>
       <c r="G757" t="n">
-        <v>2.73019075393677</v>
+        <v>2.73019099235535</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.7973952293396</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.67978763580322</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G761" t="n">
-        <v>2.64618515968323</v>
+        <v>2.64618492126465</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G762" t="n">
-        <v>2.54957842826843</v>
+        <v>2.54957795143127</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.7973952293396</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G764" t="n">
-        <v>2.84779906272888</v>
+        <v>2.84779930114746</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400243759155</v>
+        <v>2.89400219917297</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>3.20482397079468</v>
+        <v>3.20482420921326</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.0788152217865</v>
+        <v>3.07881498336792</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00741028785706</v>
+        <v>3.00741004943848</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.22582530975342</v>
+        <v>3.225825548172</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026437759399</v>
+        <v>3.78026390075684</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>3.73406100273132</v>
+        <v>3.7340612411499</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226777076721</v>
+        <v>3.82226729393005</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98607850074768</v>
+        <v>3.9860782623291</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G790" t="n">
-        <v>4.00288009643555</v>
+        <v>4.00287961959839</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486795425415</v>
+        <v>3.83486771583557</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.70465850830078</v>
+        <v>3.70465898513794</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.87267065048218</v>
+        <v>3.87267112731934</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.88107132911682</v>
+        <v>3.88107109069824</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>3.9356746673584</v>
+        <v>3.93567490577698</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827651977539</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147492408752</v>
+        <v>3.93147444725037</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507716178894</v>
+        <v>3.96507668495178</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627336502075</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126571655273</v>
+        <v>3.80126547813416</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885896682739</v>
+        <v>3.70885920524597</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G809" t="n">
-        <v>3.62905406951904</v>
+        <v>3.62905383110046</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845584869385</v>
+        <v>3.65845561027527</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208724975586</v>
+        <v>4.11208772659302</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627336502075</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987536430359</v>
+        <v>3.93987560272217</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G822" t="n">
-        <v>3.9356746673584</v>
+        <v>3.93567490577698</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688592910767</v>
+        <v>4.08688545227051</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948635101318</v>
+        <v>4.09948682785034</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008457183838</v>
+        <v>4.07008409500122</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631734848022</v>
+        <v>4.53631687164307</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.49431419372559</v>
+        <v>4.49431371688843</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030883789062</v>
+        <v>4.41030836105347</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950117111206</v>
+        <v>4.30950164794922</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G840" t="n">
-        <v>4.1498908996582</v>
+        <v>4.14988994598389</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627336502075</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746861457825</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>3.92307448387146</v>
+        <v>3.92307496070862</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.87267065048218</v>
+        <v>3.87267112731934</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.8856372833252</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71274995803833</v>
+        <v>3.71275043487549</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.73436093330383</v>
+        <v>3.73436117172241</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868274688721</v>
+        <v>3.73868298530579</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G858" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707224845886</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.5</v>
       </c>
       <c r="G859" t="n">
-        <v>3.88995933532715</v>
+        <v>3.88995909690857</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91156983375549</v>
+        <v>3.91157007217407</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8337709903717</v>
+        <v>3.83377122879028</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G863" t="n">
-        <v>3.62630653381348</v>
+        <v>3.62630677223206</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707224845886</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359521865845</v>
+        <v>3.64359545707703</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.125</v>
       </c>
       <c r="G867" t="n">
-        <v>3.56579613685608</v>
+        <v>3.5657958984375</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G868" t="n">
-        <v>3.41019749641418</v>
+        <v>3.41019773483276</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>3.37562036514282</v>
+        <v>3.37562012672424</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>3.55715131759644</v>
+        <v>3.55715155601501</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>3.38858675956726</v>
+        <v>3.38858699798584</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G882" t="n">
-        <v>3.3626537322998</v>
+        <v>3.36265397071838</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G885" t="n">
-        <v>3.3194317817688</v>
+        <v>3.31943202018738</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163269996643</v>
+        <v>3.24163293838501</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137738227844</v>
+        <v>3.21137762069702</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G892" t="n">
-        <v>3.28917670249939</v>
+        <v>3.28917694091797</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.17680025100708</v>
+        <v>3.1768000125885</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>3.27621006965637</v>
+        <v>3.27621030807495</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G901" t="n">
-        <v>3.3626537322998</v>
+        <v>3.36265397071838</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349875450134</v>
+        <v>3.29349899291992</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G905" t="n">
-        <v>3.22866606712341</v>
+        <v>3.22866630554199</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G908" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G909" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.41884207725525</v>
+        <v>3.41884183883667</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.59605121612549</v>
+        <v>3.59605145454407</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68681669235229</v>
+        <v>3.68681693077087</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G917" t="n">
-        <v>3.6479172706604</v>
+        <v>3.64791750907898</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.51392984390259</v>
+        <v>3.51393008232117</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G927" t="n">
-        <v>3.59172892570496</v>
+        <v>3.59172940254211</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56147384643555</v>
+        <v>3.56147408485413</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>3.55282974243164</v>
+        <v>3.55282950401306</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>3.60901761054993</v>
+        <v>3.60901808738708</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.56147384643555</v>
+        <v>3.56147408485413</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.55715131759644</v>
+        <v>3.55715155601501</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960779190063</v>
+        <v>3.50960803031921</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>3.51392984390259</v>
+        <v>3.51393008232117</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.61766195297241</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G947" t="n">
-        <v>3.62630653381348</v>
+        <v>3.62630677223206</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>3.59605121612549</v>
+        <v>3.59605145454407</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G949" t="n">
-        <v>3.57876253128052</v>
+        <v>3.5787627696991</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>3.60901761054993</v>
+        <v>3.60901808738708</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>3.61766195297241</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638607978821</v>
+        <v>3.46638631820679</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45341944694519</v>
+        <v>3.45341920852661</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G965" t="n">
-        <v>3.57876253128052</v>
+        <v>3.5787627696991</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054927825928</v>
+        <v>3.79054975509644</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402606964111</v>
+        <v>3.86402630805969</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85538172721863</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="n">
-        <v>3.99801325798035</v>
+        <v>3.9980137348175</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343612670898</v>
+        <v>3.96343636512756</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724778175354</v>
+        <v>3.90724802017212</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.80351591110229</v>
+        <v>3.80351543426514</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.78622722625732</v>
+        <v>3.78622698783875</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="n">
-        <v>3.78190493583679</v>
+        <v>3.78190469741821</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.85538172721863</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.95046997070312</v>
+        <v>3.9504702091217</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>4.06284666061401</v>
+        <v>4.0628457069397</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699270248413</v>
+        <v>3.87699317932129</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911455154419</v>
+        <v>3.95911383628845</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.8856372833252</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445739746094</v>
+        <v>4.08445692062378</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319820404053</v>
+        <v>4.44319772720337</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.5037088394165</v>
+        <v>4.50370836257935</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.68524026870728</v>
+        <v>4.68523979187012</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.84948253631592</v>
+        <v>4.84948301315308</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.70252895355225</v>
+        <v>4.70252847671509</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.96185922622681</v>
+        <v>4.96185874938965</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659521102905</v>
+        <v>4.67659568786621</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.65930652618408</v>
+        <v>4.65930700302124</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.0742359161377</v>
+        <v>5.07423543930054</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340709686279</v>
+        <v>5.65340757369995</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.49780893325806</v>
+        <v>5.49780941009521</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846174240112</v>
+        <v>4.72846126556396</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.55557489395142</v>
+        <v>4.55557537078857</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.56421947479248</v>
+        <v>4.56421899795532</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48641967773438</v>
+        <v>4.48642015457153</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.65930652618408</v>
+        <v>4.65930700302124</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.0153021812439</v>
+        <v>4.01530265808105</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.8942813873291</v>
+        <v>3.89428162574768</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970401763916</v>
+        <v>3.85970377922058</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.78622722625732</v>
+        <v>3.78622698783875</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.68249487876892</v>
+        <v>3.68249464035034</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59172892570496</v>
+        <v>3.59172940254211</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.02984642982483</v>
+        <v>3.02984619140625</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.06010127067566</v>
+        <v>3.06010150909424</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287497520447</v>
+        <v>2.37287521362305</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.04006767272949</v>
+        <v>2.04006743431091</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.18702173233032</v>
+        <v>2.18702149391174</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.27346539497375</v>
+        <v>2.27346515655518</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.40313053131104</v>
+        <v>2.40313029289246</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584184646606</v>
+        <v>2.38584160804749</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.40313053131104</v>
+        <v>2.40313029289246</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.4809296131134</v>
+        <v>2.48092937469482</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.65381646156311</v>
+        <v>2.65381669998169</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790035247803</v>
+        <v>3.13790082931519</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.01255702972412</v>
+        <v>3.0125572681427</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.8267035484314</v>
+        <v>2.82670378684998</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.90450310707092</v>
+        <v>2.90450286865234</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399223327637</v>
+        <v>2.84399247169495</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.85263657569885</v>
+        <v>2.85263681411743</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.80077052116394</v>
+        <v>2.80077075958252</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.88289213180542</v>
+        <v>2.88289189338684</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91746926307678</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.11076879501343</v>
+        <v>3.11076903343201</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.89948797225952</v>
+        <v>2.8994882106781</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.67472171783447</v>
+        <v>2.67472147941589</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.81857204437256</v>
+        <v>2.81857228279114</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169353485107</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.17574024200439</v>
+        <v>2.17574000358582</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.34206748008728</v>
+        <v>2.3420672416687</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.38702082633972</v>
+        <v>2.38702058792114</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.17574024200439</v>
+        <v>2.17574000358582</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.17574024200439</v>
+        <v>2.17574000358582</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.05886149406433</v>
+        <v>2.05886125564575</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.09032893180847</v>
+        <v>2.09032869338989</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.81161844730377</v>
+        <v>1.81161832809448</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.67046499252319</v>
+        <v>1.6704648733139</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.74418842792511</v>
+        <v>1.74418830871582</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.82510423660278</v>
+        <v>1.82510435581207</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.05886149406433</v>
+        <v>2.05886125564575</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.4274787902832</v>
+        <v>2.42747855186462</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.58031988143921</v>
+        <v>2.58031964302063</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.63426399230957</v>
+        <v>2.63426375389099</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.67921733856201</v>
+        <v>2.67921710014343</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.40500211715698</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.44546008110046</v>
+        <v>2.44545984268188</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.25665593147278</v>
+        <v>2.25665616989136</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.56233859062195</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.58031988143921</v>
+        <v>2.58031964302063</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746926307678</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.89948797225952</v>
+        <v>2.8994882106781</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.51534867286682</v>
+        <v>3.5153489112854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.22315192222595</v>
+        <v>3.22315216064453</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.34003043174744</v>
+        <v>3.34003067016602</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.375</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.07930135726929</v>
+        <v>3.07930159568787</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.39397478103638</v>
+        <v>3.3939745426178</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.20517063140869</v>
+        <v>3.20517086982727</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.375</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.89948797225952</v>
+        <v>2.8994882106781</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.375</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.11076879501343</v>
+        <v>3.11076903343201</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.20517063140869</v>
+        <v>3.20517086982727</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.29957294464111</v>
+        <v>3.29957270622253</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.625</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.625</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.22315192222595</v>
+        <v>3.22315216064453</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.20517063140869</v>
+        <v>3.20517086982727</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29957294464111</v>
+        <v>3.29957270622253</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.11076879501343</v>
+        <v>3.11076903343201</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.26361012458801</v>
+        <v>3.26361036300659</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.07930135726929</v>
+        <v>3.07930159568787</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.97141337394714</v>
+        <v>2.97141361236572</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.375</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.11076879501343</v>
+        <v>3.11076903343201</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.375</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.81857204437256</v>
+        <v>2.81857228279114</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.58031988143921</v>
+        <v>2.58031964302063</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.375</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.375</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.03434801101685</v>
+        <v>3.03434824943542</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746926307678</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.83655333518982</v>
+        <v>2.8365535736084</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.89499282836914</v>
+        <v>2.89499306678772</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.88150668144226</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.56233859062195</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169353485107</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.81857204437256</v>
+        <v>2.81857228279114</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.81857204437256</v>
+        <v>2.81857228279114</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.82756280899048</v>
+        <v>2.82756304740906</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967482566833</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967482566833</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.67921733856201</v>
+        <v>2.67921710014343</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967482566833</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.63426399230957</v>
+        <v>2.63426375389099</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.67472171783447</v>
+        <v>2.67472147941589</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.72417020797729</v>
+        <v>2.72417044639587</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169353485107</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.4274787902832</v>
+        <v>2.42747855186462</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.4274787902832</v>
+        <v>2.42747855186462</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.40500211715698</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.40500211715698</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.40500211715698</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.34206748008728</v>
+        <v>2.3420672416687</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.25216102600098</v>
+        <v>2.2521607875824</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.27014231681824</v>
+        <v>2.27014207839966</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.27014231681824</v>
+        <v>2.27014207839966</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473076820374</v>
+        <v>2.18473052978516</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.17574024200439</v>
+        <v>2.17574000358582</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15326356887817</v>
+        <v>2.15326333045959</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794556617737</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501092910767</v>
+        <v>1.91501080989838</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.01840353012085</v>
+        <v>2.01840329170227</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84308564662933</v>
+        <v>1.84308552742004</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.79453599452972</v>
+        <v>1.79453611373901</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923496246338</v>
+        <v>1.69923508167267</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.74778461456299</v>
+        <v>1.7477844953537</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.72081255912781</v>
+        <v>1.7208126783371</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879396915436</v>
+        <v>1.73879384994507</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.72081255912781</v>
+        <v>1.7208126783371</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.6830518245697</v>
+        <v>1.68305170536041</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.65068531036377</v>
+        <v>1.65068542957306</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406117916107</v>
+        <v>1.67406105995178</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.65068531036377</v>
+        <v>1.65068542957306</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794556617737</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546877384186</v>
+        <v>1.95546865463257</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>2.375</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.13528227806091</v>
+        <v>2.13528203964233</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.31060004234314</v>
+        <v>2.31059980392456</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2048" t="n">
-        <v>2.4274787902832</v>
+        <v>2.42747855186462</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.56233859062195</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2065" t="n">
-        <v>2.58031988143921</v>
+        <v>2.58031964302063</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.58031988143921</v>
+        <v>2.58031964302063</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.56233859062195</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.56233859062195</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2088" t="n">
-        <v>2.97141337394714</v>
+        <v>2.97141361236572</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="n">
-        <v>3.52883458137512</v>
+        <v>3.52883434295654</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.78506851196289</v>
+        <v>3.78506827354431</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.69516205787659</v>
+        <v>3.69516181945801</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.625</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.47489047050476</v>
+        <v>3.47489070892334</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.53137922286987</v>
+        <v>3.53137946128845</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.64800333976746</v>
+        <v>3.64800357818604</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.62001371383667</v>
+        <v>3.62001347541809</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2135" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2142" t="n">
-        <v>3.60601854324341</v>
+        <v>3.60601878166199</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2147" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2148" t="n">
-        <v>3.53137922286987</v>
+        <v>3.53137946128845</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56321,7 +56321,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2152" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2152" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.38676524162292</v>
+        <v>3.3867654800415</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2157" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2162" t="n">
-        <v>3.41008996963501</v>
+        <v>3.41009020805359</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2180" t="n">
-        <v>3.92323613166809</v>
+        <v>3.92323637008667</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.66199827194214</v>
+        <v>3.66199803352356</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57283,7 +57283,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2189" t="n">
-        <v>3.36810517311096</v>
+        <v>3.36810541152954</v>
       </c>
       <c r="H2189" t="s">
         <v>8</v>
@@ -57361,7 +57361,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2192" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2192" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2194" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2198" t="n">
-        <v>3.42408514022827</v>
+        <v>3.42408490180969</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2199" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2201" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2207" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.27014112472534</v>
+        <v>3.27014136314392</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2213" t="n">
-        <v>3.28880095481873</v>
+        <v>3.2888011932373</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58063,7 +58063,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2219" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2219" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2223" t="n">
-        <v>3.28880095481873</v>
+        <v>3.2888011932373</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2224" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58297,7 +58297,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2228" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2228" t="s">
         <v>8</v>
@@ -58349,7 +58349,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.17217683792114</v>
+        <v>3.17217707633972</v>
       </c>
       <c r="H2230" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2232" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58427,7 +58427,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2233" t="n">
-        <v>3.19550156593323</v>
+        <v>3.19550180435181</v>
       </c>
       <c r="H2233" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2236" t="n">
-        <v>3.19550156593323</v>
+        <v>3.19550180435181</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58531,7 +58531,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2237" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2237" t="s">
         <v>8</v>
@@ -58583,7 +58583,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2239" t="n">
-        <v>3.27014112472534</v>
+        <v>3.27014136314392</v>
       </c>
       <c r="H2239" t="s">
         <v>8</v>
@@ -58609,7 +58609,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2240" t="n">
-        <v>3.42408514022827</v>
+        <v>3.42408490180969</v>
       </c>
       <c r="H2240" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>3.92790126800537</v>
+        <v>3.92790102958679</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G2246" t="n">
-        <v>3.94189596176147</v>
+        <v>3.94189620018005</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2248" t="n">
-        <v>3.92323613166809</v>
+        <v>3.92323637008667</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2249" t="n">
-        <v>3.99321103096008</v>
+        <v>3.9932107925415</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G2251" t="n">
-        <v>3.8952465057373</v>
+        <v>3.89524674415588</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2258" t="n">
-        <v>3.76929235458374</v>
+        <v>3.76929259300232</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2259" t="n">
-        <v>3.64800333976746</v>
+        <v>3.64800357818604</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G2260" t="n">
-        <v>3.86725640296936</v>
+        <v>3.86725664138794</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G2261" t="n">
-        <v>3.90457630157471</v>
+        <v>3.90457653999329</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59467,7 +59467,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2273" t="n">
-        <v>3.66199827194214</v>
+        <v>3.66199803352356</v>
       </c>
       <c r="H2273" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2278" t="n">
-        <v>3.92790126800537</v>
+        <v>3.92790102958679</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59623,7 +59623,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2279" t="n">
-        <v>4.00720548629761</v>
+        <v>4.00720596313477</v>
       </c>
       <c r="H2279" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2281" t="n">
-        <v>4.10517024993896</v>
+        <v>4.10516977310181</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2299" t="n">
-        <v>4.00720548629761</v>
+        <v>4.00720596313477</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2300" t="n">
-        <v>3.97921562194824</v>
+        <v>3.97921586036682</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2302" t="n">
-        <v>4.10517024993896</v>
+        <v>4.10516977310181</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2307" t="n">
-        <v>4.3850679397583</v>
+        <v>4.38506746292114</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60403,7 +60403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2309" t="n">
-        <v>4.51568746566772</v>
+        <v>4.51568698883057</v>
       </c>
       <c r="H2309" t="s">
         <v>8</v>
@@ -60481,7 +60481,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2312" t="n">
-        <v>4.71161603927612</v>
+        <v>4.71161556243896</v>
       </c>
       <c r="H2312" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2314" t="n">
-        <v>4.5809965133667</v>
+        <v>4.58099603652954</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60715,7 +60715,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2321" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2321" t="s">
         <v>8</v>
@@ -60767,7 +60767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2323" t="n">
-        <v>5.10347270965576</v>
+        <v>5.1034722328186</v>
       </c>
       <c r="H2323" t="s">
         <v>8</v>
@@ -60793,7 +60793,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2324" t="n">
-        <v>4.90754461288452</v>
+        <v>4.90754413604736</v>
       </c>
       <c r="H2324" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2326" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60897,7 +60897,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G2328" t="n">
-        <v>4.86089468002319</v>
+        <v>4.86089420318604</v>
       </c>
       <c r="H2328" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2332" t="n">
-        <v>4.67429637908936</v>
+        <v>4.6742959022522</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2335" t="n">
-        <v>4.6836256980896</v>
+        <v>4.68362617492676</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2337" t="n">
-        <v>4.5809965133667</v>
+        <v>4.58099603652954</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2339" t="n">
-        <v>4.67429637908936</v>
+        <v>4.6742959022522</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2342" t="n">
-        <v>4.87955474853516</v>
+        <v>4.879554271698</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2344" t="n">
-        <v>5.07548332214355</v>
+        <v>5.0754828453064</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2346" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61443,7 +61443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2349" t="n">
-        <v>4.90754461288452</v>
+        <v>4.90754413604736</v>
       </c>
       <c r="H2349" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G2355" t="n">
-        <v>4.56700134277344</v>
+        <v>4.5670018196106</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61625,7 +61625,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2356" t="n">
-        <v>4.33841848373413</v>
+        <v>4.33841800689697</v>
       </c>
       <c r="H2356" t="s">
         <v>8</v>
@@ -61651,7 +61651,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G2357" t="n">
-        <v>4.1844744682312</v>
+        <v>4.18447494506836</v>
       </c>
       <c r="H2357" t="s">
         <v>8</v>
@@ -61677,7 +61677,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2358" t="n">
-        <v>4.3850679397583</v>
+        <v>4.38506746292114</v>
       </c>
       <c r="H2358" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.15181970596313</v>
+        <v>4.15181922912598</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G2360" t="n">
-        <v>4.33375310897827</v>
+        <v>4.33375358581543</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G2362" t="n">
-        <v>4.46437215805054</v>
+        <v>4.4643726348877</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2366" t="n">
-        <v>4.6836256980896</v>
+        <v>4.68362617492676</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2367" t="n">
-        <v>4.75826549530029</v>
+        <v>4.75826501846313</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2368" t="n">
-        <v>4.87955474853516</v>
+        <v>4.879554271698</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>7.73999977111816</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>40901</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>7.82999992370605</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>7.63000011444092</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853250980377</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980905056</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139390945435</v>
+        <v>1.63139402866364</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71371984481812</v>
+        <v>1.71371972560883</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69019818305969</v>
+        <v>1.69019830226898</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754958629608</v>
+        <v>1.56754970550537</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47514307498932</v>
+        <v>1.47514319419861</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314015865326</v>
+        <v>1.43314027786255</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.40877854824066</v>
+        <v>1.40877842903137</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G30" t="n">
-        <v>1.16936159133911</v>
+        <v>1.1693617105484</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204342365265</v>
+        <v>1.19204330444336</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35333442687988</v>
+        <v>1.35333466529846</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346293926239</v>
+        <v>1.47346305847168</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254241466522</v>
+        <v>1.46254229545593</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G47" t="n">
-        <v>1.50874543190002</v>
+        <v>1.50874555110931</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.48018336296082</v>
+        <v>1.4801834821701</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586933135986</v>
+        <v>1.56586945056915</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G54" t="n">
-        <v>1.62131333351135</v>
+        <v>1.62131321430206</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491569042206</v>
+        <v>1.65491580963135</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551355361938</v>
+        <v>1.62551367282867</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G58" t="n">
-        <v>1.5818305015564</v>
+        <v>1.58183062076569</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994115829468</v>
+        <v>1.44994127750397</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G65" t="n">
-        <v>1.43482029438019</v>
+        <v>1.4348201751709</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G67" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30965149402618</v>
+        <v>1.30965161323547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G70" t="n">
-        <v>1.41465878486633</v>
+        <v>1.41465890407562</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847034931183</v>
+        <v>1.57847023010254</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G77" t="n">
-        <v>1.57426989078522</v>
+        <v>1.57427000999451</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646731376648</v>
+        <v>1.53646743297577</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G81" t="n">
-        <v>1.50538527965546</v>
+        <v>1.50538516044617</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.53898751735687</v>
+        <v>1.53898763656616</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574117660522</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G93" t="n">
-        <v>1.42305934429169</v>
+        <v>1.42305946350098</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G96" t="n">
-        <v>1.51882612705231</v>
+        <v>1.51882600784302</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47514307498932</v>
+        <v>1.47514319419861</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278438091278</v>
+        <v>1.49278426170349</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G103" t="n">
-        <v>1.49866461753845</v>
+        <v>1.49866485595703</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G106" t="n">
-        <v>1.52470672130585</v>
+        <v>1.52470660209656</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338224411011</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>1.51210570335388</v>
+        <v>1.51210558414459</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577417373657</v>
+        <v>1.34577405452728</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205788612366</v>
+        <v>1.40205800533295</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490110874176</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G125" t="n">
-        <v>1.28780996799469</v>
+        <v>1.28781008720398</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G134" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G135" t="n">
-        <v>1.31889224052429</v>
+        <v>1.318892121315</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.31889224052429</v>
+        <v>1.318892121315</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.3499743938446</v>
+        <v>1.34997427463531</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769627571106</v>
+        <v>1.37769615650177</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357663154602</v>
+        <v>1.38357651233673</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G150" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G153" t="n">
-        <v>1.33737361431122</v>
+        <v>1.33737349510193</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G154" t="n">
-        <v>1.32309246063232</v>
+        <v>1.32309257984161</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.32309246063232</v>
+        <v>1.32309257984161</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28949022293091</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G163" t="n">
-        <v>1.26092803478241</v>
+        <v>1.26092827320099</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545115470886</v>
+        <v>1.30545127391815</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29201018810272</v>
+        <v>1.29201030731201</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301164627075</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713129043579</v>
+        <v>1.30713140964508</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265586853027</v>
+        <v>1.37265598773956</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921490192413</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G180" t="n">
-        <v>1.35165441036224</v>
+        <v>1.35165452957153</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33989369869232</v>
+        <v>1.33989357948303</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477271556854</v>
+        <v>1.32477247714996</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G191" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G194" t="n">
-        <v>1.36845564842224</v>
+        <v>1.36845552921295</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G195" t="n">
-        <v>1.35165441036224</v>
+        <v>1.35165452957153</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.625</v>
       </c>
       <c r="G198" t="n">
-        <v>1.36509549617767</v>
+        <v>1.36509537696838</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105642795563</v>
+        <v>1.38105666637421</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881154537201</v>
+        <v>1.30881142616272</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31637215614319</v>
+        <v>1.3163720369339</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G210" t="n">
-        <v>1.28865015506744</v>
+        <v>1.28865027427673</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.27772927284241</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28949022293091</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G218" t="n">
-        <v>1.14247977733612</v>
+        <v>1.1424800157547</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>1.25168752670288</v>
+        <v>1.25168764591217</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036316871643</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036316871643</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G233" t="n">
-        <v>1.07947540283203</v>
+        <v>1.07947552204132</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115553855896</v>
+        <v>1.08115541934967</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.08031535148621</v>
+        <v>1.0803154706955</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.03915274143219</v>
+        <v>1.0391526222229</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939470767975</v>
+        <v>1.06939482688904</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G242" t="n">
-        <v>1.12651860713959</v>
+        <v>1.12651872634888</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584004878998</v>
+        <v>1.14583992958069</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364286422729</v>
+        <v>1.18364262580872</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G258" t="n">
-        <v>1.19792366027832</v>
+        <v>1.19792377948761</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.3550146818161</v>
+        <v>1.35501480102539</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.3037713766098</v>
+        <v>1.30377113819122</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G269" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036316871643</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.1886830329895</v>
+        <v>1.18868315219879</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448281288147</v>
+        <v>1.18448269367218</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G282" t="n">
-        <v>1.19792366027832</v>
+        <v>1.19792377948761</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388506889343</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G284" t="n">
-        <v>1.18784308433533</v>
+        <v>1.18784320354462</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G289" t="n">
-        <v>1.17776238918304</v>
+        <v>1.17776226997375</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G290" t="n">
-        <v>1.16936159133911</v>
+        <v>1.1693617105484</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G292" t="n">
-        <v>1.15340054035187</v>
+        <v>1.15340065956116</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G294" t="n">
-        <v>1.16432130336761</v>
+        <v>1.1643214225769</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G295" t="n">
-        <v>1.15088045597076</v>
+        <v>1.15088057518005</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424072742462</v>
+        <v>1.15424060821533</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G298" t="n">
-        <v>1.16516149044037</v>
+        <v>1.16516137123108</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G300" t="n">
-        <v>1.19540345668793</v>
+        <v>1.19540369510651</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740637302399</v>
+        <v>1.23740661144257</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236620426178</v>
+        <v>1.23236608505249</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380413532257</v>
+        <v>1.20380401611328</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G310" t="n">
-        <v>1.19708359241486</v>
+        <v>1.19708371162415</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G311" t="n">
-        <v>1.18784308433533</v>
+        <v>1.18784320354462</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036316871643</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19540345668793</v>
+        <v>1.19540369510651</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036316871643</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18196260929108</v>
+        <v>1.18196249008179</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688932418823</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688932418823</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908674716949</v>
+        <v>1.23908662796021</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G337" t="n">
-        <v>1.22564578056335</v>
+        <v>1.22564566135406</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488628864288</v>
+        <v>1.23488640785217</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.2248055934906</v>
+        <v>1.22480547428131</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388506889343</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664723873138</v>
+        <v>1.24664711952209</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.27772927284241</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G350" t="n">
-        <v>1.29705059528351</v>
+        <v>1.2970507144928</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30209100246429</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301164627075</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194431304932</v>
+        <v>1.49194443225861</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G359" t="n">
-        <v>1.45162153244019</v>
+        <v>1.45162165164948</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G360" t="n">
-        <v>1.46002221107483</v>
+        <v>1.46002209186554</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>1.45498180389404</v>
+        <v>1.45498168468475</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490110874176</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.38861691951752</v>
+        <v>1.3886171579361</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.625</v>
       </c>
       <c r="G367" t="n">
-        <v>1.36509549617767</v>
+        <v>1.36509537696838</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G370" t="n">
-        <v>1.36845564842224</v>
+        <v>1.36845552921295</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921490192413</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>1.44070076942444</v>
+        <v>1.44070065021515</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297888755798</v>
+        <v>1.41297876834869</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G393" t="n">
-        <v>1.4104585647583</v>
+        <v>1.41045868396759</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G395" t="n">
-        <v>1.4272598028183</v>
+        <v>1.42725968360901</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G404" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338224411011</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918202400208</v>
+        <v>1.45918190479279</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G409" t="n">
-        <v>1.52554666996002</v>
+        <v>1.52554678916931</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.5331072807312</v>
+        <v>1.53310716152191</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574117660522</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G418" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G422" t="n">
-        <v>1.44070076942444</v>
+        <v>1.44070065021515</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490110874176</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422231197357</v>
+        <v>1.46422243118286</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G428" t="n">
-        <v>1.43398034572601</v>
+        <v>1.43398022651672</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842277050018</v>
+        <v>1.4684225320816</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254241466522</v>
+        <v>1.46254229545593</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45162153244019</v>
+        <v>1.45162165164948</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422231197357</v>
+        <v>1.46422243118286</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.5213463306427</v>
+        <v>1.52134621143341</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G441" t="n">
-        <v>1.59527146816254</v>
+        <v>1.59527158737183</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531928539276</v>
+        <v>1.70531916618347</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.8010858297348</v>
+        <v>1.80108618736267</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G445" t="n">
-        <v>1.80780637264252</v>
+        <v>1.80780625343323</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G446" t="n">
-        <v>1.78428471088409</v>
+        <v>1.78428483009338</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429953098297</v>
+        <v>1.99429941177368</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.94053554534912</v>
+        <v>1.9405357837677</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757874965668</v>
+        <v>1.98757898807526</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229625701904</v>
+        <v>1.95229637622833</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869390010834</v>
+        <v>1.91869401931763</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812903404236</v>
+        <v>1.84812915325165</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980905056</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>1.856529712677</v>
+        <v>1.85652995109558</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G459" t="n">
-        <v>1.84644901752472</v>
+        <v>1.84644877910614</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100501537323</v>
+        <v>1.79100513458252</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420401573181</v>
+        <v>1.77420389652252</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165093421936</v>
+        <v>1.87165069580078</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.86493039131165</v>
+        <v>1.86493027210236</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>1.95733666419983</v>
+        <v>1.95733690261841</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581803798676</v>
+        <v>1.97581791877747</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061647891998</v>
+        <v>1.9506162405014</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>1.95733666419983</v>
+        <v>1.95733690261841</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213510513306</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341200351715</v>
+        <v>1.88341188430786</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879312992096</v>
+        <v>1.61879324913025</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G484" t="n">
-        <v>1.62635362148285</v>
+        <v>1.62635374069214</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763040065765</v>
+        <v>1.57763016223907</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G488" t="n">
-        <v>1.57595026493073</v>
+        <v>1.57595014572144</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G490" t="n">
-        <v>1.50874543190002</v>
+        <v>1.50874555110931</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G494" t="n">
-        <v>1.58771097660065</v>
+        <v>1.58771085739136</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.612912774086</v>
+        <v>1.61291265487671</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811457157135</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531928539276</v>
+        <v>1.70531916618347</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G499" t="n">
-        <v>1.69019818305969</v>
+        <v>1.69019830226898</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299335002899</v>
+        <v>1.62299346923828</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G502" t="n">
-        <v>1.62131333351135</v>
+        <v>1.62131321430206</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.57931041717529</v>
+        <v>1.579310297966</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811457157135</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>1.63643431663513</v>
+        <v>1.63643443584442</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267056941986</v>
+        <v>1.58267068862915</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090985774994</v>
+        <v>1.57090973854065</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535228252411</v>
+        <v>1.60535204410553</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G514" t="n">
-        <v>1.66163623332977</v>
+        <v>1.66163611412048</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G515" t="n">
-        <v>1.62635362148285</v>
+        <v>1.62635374069214</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G516" t="n">
-        <v>1.61627292633057</v>
+        <v>1.61627304553986</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G520" t="n">
-        <v>1.67339694499969</v>
+        <v>1.67339706420898</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827572345734</v>
+        <v>1.65827596187592</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>1.87333106994629</v>
+        <v>1.87333118915558</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G530" t="n">
-        <v>1.86493039131165</v>
+        <v>1.86493027210236</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G531" t="n">
-        <v>1.93213510513306</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433264732361</v>
+        <v>1.8943327665329</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>1.93213510513306</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82712757587433</v>
+        <v>1.82712769508362</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.75992298126221</v>
+        <v>1.7599231004715</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>1.83552825450897</v>
+        <v>1.83552837371826</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>1.75152254104614</v>
+        <v>1.75152266025543</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>1.75152254104614</v>
+        <v>1.75152266025543</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632086277008</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G551" t="n">
-        <v>1.75572276115417</v>
+        <v>1.75572264194489</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472142219543</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632086277008</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011748790741</v>
+        <v>1.68011736869812</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472142219543</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>1.84812903404236</v>
+        <v>1.84812915325165</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>1.83972859382629</v>
+        <v>1.83972871303558</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G569" t="n">
-        <v>1.83132815361023</v>
+        <v>1.83132791519165</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872725486755</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>1.7767242193222</v>
+        <v>1.77672433853149</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872725486755</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192589759827</v>
+        <v>1.80192601680756</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.84812903404236</v>
+        <v>1.84812915325165</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>1.83972859382629</v>
+        <v>1.83972871303558</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853250980377</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253834247589</v>
+        <v>1.98253858089447</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993780136108</v>
+        <v>1.96993768215179</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>2.00774049758911</v>
+        <v>2.00774073600769</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.01614093780518</v>
+        <v>2.01614117622375</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>2.04554319381714</v>
+        <v>2.04554295539856</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093914031982</v>
+        <v>1.99093902111053</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>2.23035597801208</v>
+        <v>2.23035573959351</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935487747192</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935487747192</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>2.21355509757996</v>
+        <v>2.2135546207428</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41096830368042</v>
+        <v>2.410968542099</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.74699211120605</v>
+        <v>2.74699234962463</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099770545959</v>
+        <v>2.83099794387817</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519816398621</v>
+        <v>2.83519840240479</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00320982933044</v>
+        <v>3.00321006774902</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G626" t="n">
-        <v>3.13761925697327</v>
+        <v>3.13761901855469</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.26362824440002</v>
+        <v>3.26362800598145</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.1628212928772</v>
+        <v>3.16282105445862</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422622680664</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>3.17542195320129</v>
+        <v>3.17542171478271</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422622680664</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>3.24262666702271</v>
+        <v>3.24262642860413</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803767204285</v>
+        <v>3.39803743362427</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645245552063</v>
+        <v>3.61645269393921</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.68785762786865</v>
+        <v>3.68785738945007</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887378692627</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927666664124</v>
+        <v>3.96927714347839</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887378692627</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.74666213989258</v>
+        <v>3.74666237831116</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G654" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545111656189</v>
+        <v>3.59545159339905</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.79706525802612</v>
+        <v>3.79706501960754</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407606124878</v>
+        <v>3.94407534599304</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407606124878</v>
+        <v>3.94407534599304</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>4.11628770828247</v>
+        <v>4.11628818511963</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.47751331329346</v>
+        <v>4.4775128364563</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G666" t="n">
-        <v>4.59512090682983</v>
+        <v>4.59512138366699</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>4.60352182388306</v>
+        <v>4.60352230072021</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.75</v>
       </c>
       <c r="G669" t="n">
-        <v>4.83033752441406</v>
+        <v>4.83033800125122</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.82193660736084</v>
+        <v>4.821937084198</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553979873657</v>
+        <v>4.85554027557373</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074064254761</v>
+        <v>4.88074111938477</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>4.76313257217407</v>
+        <v>4.76313304901123</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.75</v>
       </c>
       <c r="G679" t="n">
-        <v>4.83033752441406</v>
+        <v>4.83033800125122</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.70432901382446</v>
+        <v>4.7043285369873</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G681" t="n">
-        <v>4.73793125152588</v>
+        <v>4.73793077468872</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>4.67912721633911</v>
+        <v>4.67912769317627</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192226409912</v>
+        <v>4.61192178726196</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G687" t="n">
-        <v>4.46071195602417</v>
+        <v>4.46071147918701</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44391107559204</v>
+        <v>4.44391059875488</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271511077881</v>
+        <v>4.50271463394165</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749849319458</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>4.05328273773193</v>
+        <v>4.05328321456909</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.05748414993286</v>
+        <v>4.0574836730957</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286479949951</v>
+        <v>3.79286503791809</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.66265630722046</v>
+        <v>3.6626558303833</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>3.51144552230835</v>
+        <v>3.51144528388977</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G710" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>2.86880016326904</v>
+        <v>2.8688006401062</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G715" t="n">
-        <v>2.80579614639282</v>
+        <v>2.80579590797424</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419658660889</v>
+        <v>2.81419682502747</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G717" t="n">
-        <v>2.931804895401</v>
+        <v>2.93180513381958</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G718" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G721" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>2.79739546775818</v>
+        <v>2.79739570617676</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860601425171</v>
+        <v>2.94860625267029</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>3.15862083435059</v>
+        <v>3.15862059593201</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.14181971549988</v>
+        <v>3.1418194770813</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G727" t="n">
-        <v>3.13761925697327</v>
+        <v>3.13761901855469</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G732" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422622680664</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G735" t="n">
-        <v>3.10401678085327</v>
+        <v>3.10401701927185</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380757331848</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G742" t="n">
-        <v>2.88140153884888</v>
+        <v>2.8814013004303</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92760443687439</v>
+        <v>2.92760467529297</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G745" t="n">
-        <v>3.17542195320129</v>
+        <v>3.17542171478271</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.27622938156128</v>
+        <v>3.2762291431427</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15862083435059</v>
+        <v>3.15862059593201</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380757331848</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G754" t="n">
-        <v>3.02001094818115</v>
+        <v>3.02001118659973</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060916900635</v>
+        <v>2.99060893058777</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>2.96960759162903</v>
+        <v>2.96960783004761</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.25</v>
       </c>
       <c r="G757" t="n">
-        <v>2.73019099235535</v>
+        <v>2.73019075393677</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418200492859</v>
+        <v>2.60418176651001</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.79739546775818</v>
+        <v>2.79739570617676</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G761" t="n">
-        <v>2.64618492126465</v>
+        <v>2.64618515968323</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G762" t="n">
-        <v>2.54957795143127</v>
+        <v>2.54957818984985</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.79739546775818</v>
+        <v>2.79739570617676</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G764" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>3.20482420921326</v>
+        <v>3.20482397079468</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15862083435059</v>
+        <v>3.15862059593201</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.07881498336792</v>
+        <v>3.0788152217865</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.225825548172</v>
+        <v>3.22582530975342</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026390075684</v>
+        <v>3.78026413917542</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.9860782623291</v>
+        <v>3.98607873916626</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>4.11628770828247</v>
+        <v>4.11628818511963</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G789" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G790" t="n">
-        <v>4.00287961959839</v>
+        <v>4.00287914276123</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486771583557</v>
+        <v>3.83486819267273</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>3.81806683540344</v>
+        <v>3.81806659698486</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.87267112731934</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.88107109069824</v>
+        <v>3.8810715675354</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147444725037</v>
+        <v>3.93147492408752</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88947224617004</v>
+        <v>3.88947200775146</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507668495178</v>
+        <v>3.96507716178894</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627264976501</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.86427021026611</v>
+        <v>3.86426997184753</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126547813416</v>
+        <v>3.80126571655273</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885920524597</v>
+        <v>3.70885944366455</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>3.74666213989258</v>
+        <v>3.74666237831116</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845561027527</v>
+        <v>3.65845584869385</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>3.74666213989258</v>
+        <v>3.74666237831116</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G815" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208772659302</v>
+        <v>4.11208724975586</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G818" t="n">
-        <v>3.96087718009949</v>
+        <v>3.96087694168091</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627264976501</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987560272217</v>
+        <v>3.93987536430359</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.86427021026611</v>
+        <v>3.86426997184753</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G823" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228187561035</v>
+        <v>4.03228235244751</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688545227051</v>
+        <v>4.08688592910767</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948682785034</v>
+        <v>4.09948635101318</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008409500122</v>
+        <v>4.07008457183838</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192226409912</v>
+        <v>4.61192178726196</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.57832002639771</v>
+        <v>4.57831954956055</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.49431371688843</v>
+        <v>4.49431467056274</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030836105347</v>
+        <v>4.41030788421631</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950164794922</v>
+        <v>4.30950117111206</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>4.25909805297852</v>
+        <v>4.25909757614136</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749849319458</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G840" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228187561035</v>
+        <v>4.03228235244751</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627264976501</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866529464722</v>
+        <v>3.7886655330658</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>3.92307496070862</v>
+        <v>3.92307424545288</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.87267112731934</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>4.13632345199585</v>
+        <v>4.13632297515869</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563704490662</v>
+        <v>3.88563752174377</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487109184265</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G852" t="n">
-        <v>4.093101978302</v>
+        <v>4.09310150146484</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G853" t="n">
-        <v>3.88131475448608</v>
+        <v>3.8813145160675</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71275043487549</v>
+        <v>3.71275019645691</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.5</v>
       </c>
       <c r="G859" t="n">
-        <v>3.88995909690857</v>
+        <v>3.88995933532715</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157007217407</v>
+        <v>3.91157031059265</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.83377122879028</v>
+        <v>3.8337709903717</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.125</v>
       </c>
       <c r="G867" t="n">
-        <v>3.5657958984375</v>
+        <v>3.56579613685608</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53554105758667</v>
+        <v>3.53554081916809</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.40155339241028</v>
+        <v>3.4015531539917</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>3.41451978683472</v>
+        <v>3.4145200252533</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>3.31078767776489</v>
+        <v>3.31078743934631</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>3.31510972976685</v>
+        <v>3.31510996818542</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G882" t="n">
-        <v>3.36265397071838</v>
+        <v>3.36265349388123</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G885" t="n">
-        <v>3.31943202018738</v>
+        <v>3.3194317817688</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>3.26324367523193</v>
+        <v>3.26324391365051</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137762069702</v>
+        <v>3.21137738227844</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>3.25892162322998</v>
+        <v>3.2589213848114</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.2502772808075</v>
+        <v>3.25027704238892</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756596565247</v>
+        <v>3.26756572723389</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>3.27621030807495</v>
+        <v>3.27621006965637</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>3.25892162322998</v>
+        <v>3.2589213848114</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.2502772808075</v>
+        <v>3.25027704238892</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G901" t="n">
-        <v>3.36265397071838</v>
+        <v>3.36265349388123</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349899291992</v>
+        <v>3.29349875450134</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>3.20273303985596</v>
+        <v>3.20273327827454</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G905" t="n">
-        <v>3.22866630554199</v>
+        <v>3.22866606712341</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68681693077087</v>
+        <v>3.68681716918945</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G917" t="n">
-        <v>3.64791750907898</v>
+        <v>3.6479172706604</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.53554105758667</v>
+        <v>3.53554081916809</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G927" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56147408485413</v>
+        <v>3.56147360801697</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>3.55282950401306</v>
+        <v>3.55282974243164</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>3.58308458328247</v>
+        <v>3.58308482170105</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>3.60469579696655</v>
+        <v>3.60469603538513</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.56147408485413</v>
+        <v>3.56147360801697</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960803031921</v>
+        <v>3.50960779190063</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>3.4966413974762</v>
+        <v>3.49664115905762</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G939" t="n">
-        <v>3.47070813179016</v>
+        <v>3.47070837020874</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>3.87267065048218</v>
+        <v>3.8726704120636</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487109184265</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G949" t="n">
-        <v>3.5787627696991</v>
+        <v>3.57876253128052</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G954" t="n">
-        <v>3.5182523727417</v>
+        <v>3.51825213432312</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638631820679</v>
+        <v>3.46638607978821</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45341920852661</v>
+        <v>3.45341944694519</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>3.53554105758667</v>
+        <v>3.53554081916809</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G965" t="n">
-        <v>3.5787627696991</v>
+        <v>3.57876253128052</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054975509644</v>
+        <v>3.79054951667786</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85538220405579</v>
+        <v>3.85538244247437</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="n">
-        <v>3.9980137348175</v>
+        <v>3.99801421165466</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92453646659851</v>
+        <v>3.92453670501709</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343636512756</v>
+        <v>3.96343588829041</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724802017212</v>
+        <v>3.90724778175354</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.80351543426514</v>
+        <v>3.80351567268372</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.78622698783875</v>
+        <v>3.7862274646759</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="n">
-        <v>3.78190469741821</v>
+        <v>3.78190493583679</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.85538220405579</v>
+        <v>3.85538244247437</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.91589283943176</v>
+        <v>3.91589260101318</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893854141235</v>
+        <v>3.76893830299377</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.9504702091217</v>
+        <v>3.95046997070312</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>4.0628457069397</v>
+        <v>4.06284618377686</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699317932129</v>
+        <v>3.87699294090271</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="n">
-        <v>4.04555749893188</v>
+        <v>4.04555797576904</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563704490662</v>
+        <v>3.88563752174377</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G992" t="n">
-        <v>4.093101978302</v>
+        <v>4.09310150146484</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="n">
-        <v>4.32217693328857</v>
+        <v>4.32217741012573</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G996" t="n">
-        <v>4.49506378173828</v>
+        <v>4.49506425857544</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319772720337</v>
+        <v>4.44319820404053</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G998" t="n">
-        <v>4.49506378173828</v>
+        <v>4.49506425857544</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.50370836257935</v>
+        <v>4.5037088394165</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.49506378173828</v>
+        <v>4.49506425857544</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.84948301315308</v>
+        <v>4.84948253631592</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.70252847671509</v>
+        <v>4.7025294303894</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.82354974746704</v>
+        <v>4.82354927062988</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.88406038284302</v>
+        <v>4.88405990600586</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659568786621</v>
+        <v>4.67659521102905</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.90999317169189</v>
+        <v>4.90999269485474</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.88406038284302</v>
+        <v>4.88405990600586</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.07423543930054</v>
+        <v>5.0742359161377</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.28170013427734</v>
+        <v>5.2817006111145</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340757369995</v>
+        <v>5.65340805053711</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.49780941009521</v>
+        <v>5.49780988693237</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.28170013427734</v>
+        <v>5.2817006111145</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846126556396</v>
+        <v>4.72846221923828</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.55557537078857</v>
+        <v>4.55557441711426</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.59015226364136</v>
+        <v>4.5901517868042</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48642015457153</v>
+        <v>4.48641967773438</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.52964115142822</v>
+        <v>4.52964162826538</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49506378173828</v>
+        <v>4.49506425857544</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895545959473</v>
+        <v>4.27895498275757</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.01530265808105</v>
+        <v>4.0153021812439</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428162574768</v>
+        <v>3.8942813873291</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970377922058</v>
+        <v>3.85970425605774</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.78622698783875</v>
+        <v>3.7862274646759</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.82512664794922</v>
+        <v>3.8251268863678</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.68249464035034</v>
+        <v>3.6824951171875</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.06010150909424</v>
+        <v>3.06010127067566</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085006713867</v>
+        <v>2.64085030555725</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287521362305</v>
+        <v>2.37287497520447</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.07464504241943</v>
+        <v>2.07464528083801</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.93633532524109</v>
+        <v>1.9363352060318</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.27346515655518</v>
+        <v>2.27346539497375</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.46364068984985</v>
+        <v>2.46364092826843</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584160804749</v>
+        <v>2.38584184646606</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790082931519</v>
+        <v>3.13790059089661</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.10332298278809</v>
+        <v>3.10332322120667</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.0125572681427</v>
+        <v>3.01255750656128</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.82670378684998</v>
+        <v>2.82670402526855</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187109947205</v>
+        <v>2.76187133789062</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.90450286865234</v>
+        <v>2.90450310707092</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399247169495</v>
+        <v>2.84399271011353</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.88289189338684</v>
+        <v>2.88289213180542</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232930183411</v>
+        <v>3.05232954025269</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.06785202026367</v>
+        <v>2.06785178184509</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.75</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.36903953552246</v>
+        <v>2.3690390586853</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.41848802566528</v>
+        <v>2.41848826408386</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.22518873214722</v>
+        <v>2.22518849372864</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.10381460189819</v>
+        <v>2.10381484031677</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.05886125564575</v>
+        <v>2.05886149406433</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620701789856</v>
+        <v>1.72620689868927</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.7603714466095</v>
+        <v>1.76037156581879</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.74059200286865</v>
+        <v>1.74059212207794</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.96895480155945</v>
+        <v>1.96895503997803</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.05886125564575</v>
+        <v>2.05886149406433</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.63426375389099</v>
+        <v>2.63426399230957</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.67921710014343</v>
+        <v>2.67921733856201</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.75</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408618927002</v>
+        <v>2.32408595085144</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.25665616989136</v>
+        <v>2.25665593147278</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.27913284301758</v>
+        <v>2.279132604599</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.5153489112854</v>
+        <v>3.51534867286682</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406785011292</v>
+        <v>3.30406808853149</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.34003067016602</v>
+        <v>3.34003043174744</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406785011292</v>
+        <v>3.30406808853149</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39847016334534</v>
+        <v>3.39846992492676</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.4434232711792</v>
+        <v>3.44342303276062</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.4299373626709</v>
+        <v>3.42993712425232</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.3535168170929</v>
+        <v>3.35351657867432</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.3939745426178</v>
+        <v>3.39397478103638</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875032424927</v>
+        <v>3.12875008583069</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673161506653</v>
+        <v>3.14673137664795</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875032424927</v>
+        <v>3.12875008583069</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673161506653</v>
+        <v>3.14673137664795</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.40746068954468</v>
+        <v>3.4074604511261</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.31755423545837</v>
+        <v>3.31755399703979</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.21865677833557</v>
+        <v>3.21865701675415</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.40746068954468</v>
+        <v>3.4074604511261</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39847016334534</v>
+        <v>3.39846992492676</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.26361036300659</v>
+        <v>3.26361012458801</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031059265137</v>
+        <v>3.07031083106995</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.92646026611328</v>
+        <v>2.92646050453186</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682516098022</v>
+        <v>3.05682492256165</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.93095564842224</v>
+        <v>2.93095541000366</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682516098022</v>
+        <v>3.05682492256165</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.8365535736084</v>
+        <v>2.83655381202698</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.93545079231262</v>
+        <v>2.9354510307312</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178684234619</v>
+        <v>2.61178731918335</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.80958151817322</v>
+        <v>2.8095817565918</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.80958151817322</v>
+        <v>2.8095817565918</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.863525390625</v>
+        <v>2.86352562904358</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325451850891</v>
+        <v>2.64325428009033</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.67921710014343</v>
+        <v>2.67921733856201</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674018859863</v>
+        <v>2.65674042701721</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.63426375389099</v>
+        <v>2.63426399230957</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178684234619</v>
+        <v>2.61178731918335</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674018859863</v>
+        <v>2.65674042701721</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.41848802566528</v>
+        <v>2.41848826408386</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.75</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36004877090454</v>
+        <v>2.36004853248596</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.1892261505127</v>
+        <v>2.18922591209412</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417949676514</v>
+        <v>2.23417925834656</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417949676514</v>
+        <v>2.23417925834656</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.1892261505127</v>
+        <v>2.18922591209412</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473052978516</v>
+        <v>2.18473076820374</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977742195129</v>
+        <v>2.13977766036987</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977742195129</v>
+        <v>2.13977766036987</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10831022262573</v>
+        <v>2.10830998420715</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280512809753</v>
+        <v>2.11280536651611</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280512809753</v>
+        <v>2.11280536651611</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.10831022262573</v>
+        <v>2.10830998420715</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143135547638</v>
+        <v>1.99143147468567</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794532775879</v>
+        <v>1.97794544696808</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996427536011</v>
+        <v>1.9599643945694</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1944" t="n">
-        <v>1.91950619220734</v>
+        <v>1.91950607299805</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501080989838</v>
+        <v>1.91501104831696</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299221992493</v>
+        <v>1.93299210071564</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.91950619220734</v>
+        <v>1.91950607299805</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198298454285</v>
+        <v>1.94198286533356</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.98693609237671</v>
+        <v>1.98693597316742</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299221992493</v>
+        <v>1.93299210071564</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647812843323</v>
+        <v>1.94647836685181</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996427536011</v>
+        <v>1.9599643945694</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.96445953845978</v>
+        <v>1.9644593000412</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702951908112</v>
+        <v>1.89702939987183</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262780189514</v>
+        <v>1.80262768268585</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923508167267</v>
+        <v>1.69923496246338</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.7208126783371</v>
+        <v>1.72081255912781</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.73699569702148</v>
+        <v>1.73699581623077</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879384994507</v>
+        <v>1.73879396915436</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.7208126783371</v>
+        <v>1.72081255912781</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.6956387758255</v>
+        <v>1.69563889503479</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.73519766330719</v>
+        <v>1.7351975440979</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406105995178</v>
+        <v>1.67406117916107</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.62910795211792</v>
+        <v>1.62910783290863</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.62910795211792</v>
+        <v>1.62910783290863</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.76576590538025</v>
+        <v>1.76576578617096</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794532775879</v>
+        <v>1.97794544696808</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198298454285</v>
+        <v>1.94198286533356</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546865463257</v>
+        <v>1.95546877384186</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.30160927772522</v>
+        <v>2.30160903930664</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.31059980392456</v>
+        <v>2.31060004234314</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.30160927772522</v>
+        <v>2.30160903930664</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>2.75</v>
       </c>
       <c r="G2050" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>2.75</v>
       </c>
       <c r="G2060" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031059265137</v>
+        <v>3.07031083106995</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241403579712</v>
+        <v>3.45241379737854</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="n">
-        <v>3.52883434295654</v>
+        <v>3.52883458137512</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.78506827354431</v>
+        <v>3.78506851196289</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.69516181945801</v>
+        <v>3.69516205787659</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.32204914093018</v>
+        <v>3.32204937934875</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="n">
-        <v>3.34902119636536</v>
+        <v>3.34902143478394</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.47489070892334</v>
+        <v>3.47489047050476</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2117" t="n">
-        <v>3.4434232711792</v>
+        <v>3.44342303276062</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>7.71999979019165</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>42017</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>7.59000015258789</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>7.59000015258789</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349222183228</v>
+        <v>1.89349234104156</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853250980377</v>
+        <v>1.89853274822235</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139402866364</v>
+        <v>1.63139414787292</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69019830226898</v>
+        <v>1.69019818305969</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754970550537</v>
+        <v>1.56754946708679</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314027786255</v>
+        <v>1.43314015865326</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>1.50370502471924</v>
+        <v>1.50370526313782</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995957374573</v>
+        <v>1.13995981216431</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>1.43650043010712</v>
+        <v>1.43650054931641</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G45" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G46" t="n">
-        <v>1.53730750083923</v>
+        <v>1.53730738162994</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586945056915</v>
+        <v>1.56586933135986</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491580963135</v>
+        <v>1.65491569042206</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551367282867</v>
+        <v>1.62551355361938</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>1.60283195972443</v>
+        <v>1.60283207893372</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G59" t="n">
-        <v>1.55578863620758</v>
+        <v>1.55578875541687</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G63" t="n">
-        <v>1.45078134536743</v>
+        <v>1.45078146457672</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G65" t="n">
-        <v>1.4348201751709</v>
+        <v>1.43482029438019</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349593639374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30965161323547</v>
+        <v>1.30965173244476</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829437732697</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G73" t="n">
-        <v>1.53730750083923</v>
+        <v>1.53730738162994</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830895900726</v>
+        <v>1.55830883979797</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G77" t="n">
-        <v>1.57427000999451</v>
+        <v>1.57426989078522</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.6078724861145</v>
+        <v>1.60787236690521</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646743297577</v>
+        <v>1.53646731376648</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G81" t="n">
-        <v>1.50538516044617</v>
+        <v>1.50538527965546</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.53898763656616</v>
+        <v>1.53898739814758</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>1.50370502471924</v>
+        <v>1.50370526313782</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574117660522</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G89" t="n">
-        <v>1.41213858127594</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>1.43650043010712</v>
+        <v>1.43650054931641</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G94" t="n">
-        <v>1.53730750083923</v>
+        <v>1.53730738162994</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G96" t="n">
-        <v>1.51882600784302</v>
+        <v>1.5188262462616</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278426170349</v>
+        <v>1.49278438091278</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G103" t="n">
-        <v>1.49866485595703</v>
+        <v>1.49866473674774</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.5020250082016</v>
+        <v>1.50202512741089</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G110" t="n">
-        <v>1.46338224411011</v>
+        <v>1.4633823633194</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>1.51210558414459</v>
+        <v>1.51210570335388</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614453315735</v>
+        <v>1.49614465236664</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457820892334</v>
+        <v>1.40457808971405</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577405452728</v>
+        <v>1.34577417373657</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G117" t="n">
-        <v>1.35669481754303</v>
+        <v>1.35669493675232</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490110874176</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G123" t="n">
-        <v>1.43734037876129</v>
+        <v>1.43734049797058</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G125" t="n">
-        <v>1.28781008720398</v>
+        <v>1.28780996799469</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537069797516</v>
+        <v>1.29537057876587</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G135" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829437732697</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401322364807</v>
+        <v>1.33401346206665</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G143" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.36005508899689</v>
+        <v>1.3600549697876</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34997427463531</v>
+        <v>1.34997451305389</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769615650177</v>
+        <v>1.37769627571106</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357651233673</v>
+        <v>1.38357663154602</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.31385183334351</v>
+        <v>1.3138519525528</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125093460083</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28949022293091</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545127391815</v>
+        <v>1.30545139312744</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G168" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813274860382</v>
+        <v>1.32813286781311</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301176548004</v>
+        <v>1.31301188468933</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29621052742004</v>
+        <v>1.29621064662933</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265598773956</v>
+        <v>1.37265586853027</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G181" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677551269531</v>
+        <v>1.36677539348602</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G183" t="n">
-        <v>1.32225239276886</v>
+        <v>1.32225227355957</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33989357948303</v>
+        <v>1.33989369869232</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477247714996</v>
+        <v>1.32477259635925</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33821368217468</v>
+        <v>1.33821356296539</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417461395264</v>
+        <v>1.35417473316193</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149313926697</v>
+        <v>1.33149302005768</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G192" t="n">
-        <v>1.36929571628571</v>
+        <v>1.36929559707642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349593639374</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G204" t="n">
-        <v>1.3046110868454</v>
+        <v>1.30461120605469</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125093460083</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G210" t="n">
-        <v>1.28865027427673</v>
+        <v>1.28865015506744</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G211" t="n">
-        <v>1.27940952777863</v>
+        <v>1.27940940856934</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28949022293091</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27940952777863</v>
+        <v>1.27940940856934</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G215" t="n">
-        <v>1.27856934070587</v>
+        <v>1.27856922149658</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G218" t="n">
-        <v>1.1424800157547</v>
+        <v>1.14247989654541</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>1.25168764591217</v>
+        <v>1.25168752670288</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G222" t="n">
-        <v>1.17944264411926</v>
+        <v>1.17944252490997</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036316871643</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036316871643</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G227" t="n">
-        <v>1.12147843837738</v>
+        <v>1.12147831916809</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G229" t="n">
-        <v>1.09543669223785</v>
+        <v>1.09543657302856</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G232" t="n">
-        <v>1.09795677661896</v>
+        <v>1.09795689582825</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G233" t="n">
-        <v>1.07947552204132</v>
+        <v>1.07947540283203</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.06351435184479</v>
+        <v>1.0635142326355</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>1.05847406387329</v>
+        <v>1.058473944664</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939482688904</v>
+        <v>1.06939458847046</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14583992958069</v>
+        <v>1.14584004878998</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G247" t="n">
-        <v>1.16768157482147</v>
+        <v>1.16768169403076</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G248" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624376296997</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20632433891296</v>
+        <v>1.20632421970367</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G250" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624376296997</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.16180121898651</v>
+        <v>1.16180109977722</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348135471344</v>
+        <v>1.16348123550415</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364262580872</v>
+        <v>1.18364286422729</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G258" t="n">
-        <v>1.19792377948761</v>
+        <v>1.1979238986969</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G261" t="n">
-        <v>1.3407336473465</v>
+        <v>1.34073376655579</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501480102539</v>
+        <v>1.35501492023468</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.34325385093689</v>
+        <v>1.34325397014618</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33821368217468</v>
+        <v>1.33821356296539</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377113819122</v>
+        <v>1.30377125740051</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832725524902</v>
+        <v>1.24832713603973</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036316871643</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G279" t="n">
-        <v>1.18532288074493</v>
+        <v>1.18532299995422</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448269367218</v>
+        <v>1.18448281288147</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G282" t="n">
-        <v>1.19792377948761</v>
+        <v>1.1979238986969</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388506889343</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G284" t="n">
-        <v>1.18784320354462</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.38900005817413</v>
       </c>
       <c r="G287" t="n">
-        <v>1.16684150695801</v>
+        <v>1.1668416261673</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G289" t="n">
-        <v>1.17776226997375</v>
+        <v>1.17776238918304</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G294" t="n">
-        <v>1.1643214225769</v>
+        <v>1.16432154178619</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G295" t="n">
-        <v>1.15088057518005</v>
+        <v>1.15088045597076</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.375</v>
       </c>
       <c r="G299" t="n">
-        <v>1.15508079528809</v>
+        <v>1.1550806760788</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G300" t="n">
-        <v>1.19540369510651</v>
+        <v>1.19540357589722</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740661144257</v>
+        <v>1.23740637302399</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G304" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G310" t="n">
-        <v>1.19708371162415</v>
+        <v>1.19708359241486</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G311" t="n">
-        <v>1.18784320354462</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036316871643</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19540369510651</v>
+        <v>1.19540357589722</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036316871643</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18196249008179</v>
+        <v>1.18196260929108</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884454250336</v>
+        <v>1.20884442329407</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G321" t="n">
-        <v>1.20632433891296</v>
+        <v>1.20632421970367</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.210524559021</v>
+        <v>1.21052443981171</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252759456635</v>
+        <v>1.25252747535706</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688908576965</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688908576965</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G327" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.2659684419632</v>
+        <v>1.26596856117249</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320627212524</v>
+        <v>1.23320603370667</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908662796021</v>
+        <v>1.23908650875092</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.2441269159317</v>
+        <v>1.24412679672241</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488640785217</v>
+        <v>1.23488616943359</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.22480547428131</v>
+        <v>1.2248055934906</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388506889343</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G347" t="n">
-        <v>1.29789078235626</v>
+        <v>1.29789066314697</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301176548004</v>
+        <v>1.31301188468933</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890694141388</v>
+        <v>1.52890682220459</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194443225861</v>
+        <v>1.49194419384003</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G359" t="n">
-        <v>1.45162165164948</v>
+        <v>1.4516214132309</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490110874176</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.3886171579361</v>
+        <v>1.38861703872681</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173522472382</v>
+        <v>1.36173510551453</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349593639374</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829437732697</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.34325385093689</v>
+        <v>1.34325397014618</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.36005508899689</v>
+        <v>1.3600549697876</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G382" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>1.44070065021515</v>
+        <v>1.44070076942444</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221939563751</v>
+        <v>1.42221927642822</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G392" t="n">
-        <v>1.41381883621216</v>
+        <v>1.41381871700287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G393" t="n">
-        <v>1.41045868396759</v>
+        <v>1.4104585647583</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>1.41213858127594</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102355003357</v>
+        <v>1.48102366924286</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G404" t="n">
-        <v>1.46338224411011</v>
+        <v>1.4633823633194</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G405" t="n">
-        <v>1.43734037876129</v>
+        <v>1.43734049797058</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918190479279</v>
+        <v>1.45918202400208</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G409" t="n">
-        <v>1.52554678916931</v>
+        <v>1.52554643154144</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G415" t="n">
-        <v>1.43986058235168</v>
+        <v>1.43986070156097</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574117660522</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G418" t="n">
-        <v>1.44826126098633</v>
+        <v>1.44826114177704</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>1.44826126098633</v>
+        <v>1.44826114177704</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G422" t="n">
-        <v>1.44070065021515</v>
+        <v>1.44070076942444</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490110874176</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238090515137</v>
+        <v>1.44238078594208</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>1.44826126098633</v>
+        <v>1.44826114177704</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.4684225320816</v>
+        <v>1.46842277050018</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45162165164948</v>
+        <v>1.4516214132309</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51966619491577</v>
+        <v>1.51966631412506</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.52134621143341</v>
+        <v>1.52134644985199</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.80108618736267</v>
+        <v>1.8010858297348</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G445" t="n">
-        <v>1.80780625343323</v>
+        <v>1.80780637264252</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429941177368</v>
+        <v>1.99429953098297</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757898807526</v>
+        <v>1.98757874965668</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476912021637</v>
+        <v>1.84476900100708</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G459" t="n">
-        <v>1.84644877910614</v>
+        <v>1.84644901752472</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100513458252</v>
+        <v>1.79100501537323</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452703475952</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420389652252</v>
+        <v>1.7742041349411</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165069580078</v>
+        <v>1.87165081501007</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669110298157</v>
+        <v>1.87669122219086</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>1.95733690261841</v>
+        <v>1.95733666419983</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.0043797492981</v>
+        <v>2.00438022613525</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.94893610477448</v>
+        <v>1.94893634319305</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581791877747</v>
+        <v>1.97581803798676</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.9506162405014</v>
+        <v>1.95061659812927</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>1.95733690261841</v>
+        <v>1.95733666419983</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341188430786</v>
+        <v>1.88341164588928</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308886528015</v>
+        <v>1.84308874607086</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316956043243</v>
+        <v>1.85316967964172</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G480" t="n">
-        <v>1.66751670837402</v>
+        <v>1.66751658916473</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.6465151309967</v>
+        <v>1.64651525020599</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763016223907</v>
+        <v>1.57763028144836</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G491" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G492" t="n">
-        <v>1.54654812812805</v>
+        <v>1.54654800891876</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G494" t="n">
-        <v>1.58771085739136</v>
+        <v>1.58771097660065</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G499" t="n">
-        <v>1.69019830226898</v>
+        <v>1.69019818305969</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459290981293</v>
+        <v>1.61459279060364</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887382507324</v>
+        <v>1.62887394428253</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267068862915</v>
+        <v>1.58267045021057</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535204410553</v>
+        <v>1.60535216331482</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G516" t="n">
-        <v>1.61627304553986</v>
+        <v>1.61627292633057</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171680927277</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827596187592</v>
+        <v>1.65827584266663</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851804733276</v>
+        <v>1.68851792812347</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>1.87333118915558</v>
+        <v>1.873330950737</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>1.8229273557663</v>
+        <v>1.82292747497559</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G531" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.8943327665329</v>
+        <v>1.89433252811432</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82712769508362</v>
+        <v>1.82712757587433</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>1.83552837371826</v>
+        <v>1.83552825450897</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>1.75152266025543</v>
+        <v>1.75152242183685</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>1.75152266025543</v>
+        <v>1.75152242183685</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G543" t="n">
-        <v>1.77252388000488</v>
+        <v>1.77252376079559</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.72632086277008</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472130298615</v>
+        <v>1.73472118377686</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72632086277008</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171680927277</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011736869812</v>
+        <v>1.6801176071167</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472130298615</v>
+        <v>1.73472118377686</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772579669952</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G564" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452703475952</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>1.83972871303558</v>
+        <v>1.839728474617</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>1.8229273557663</v>
+        <v>1.82292747497559</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872725486755</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>1.77672433853149</v>
+        <v>1.77672410011292</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>1.76832354068756</v>
+        <v>1.76832365989685</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G579" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872725486755</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192601680756</v>
+        <v>1.80192589759827</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G582" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452703475952</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113364696503</v>
+        <v>1.91113376617432</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.91953432559967</v>
+        <v>1.91953444480896</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86913049221039</v>
+        <v>1.86913061141968</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>1.83972871303558</v>
+        <v>1.839728474617</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.94893610477448</v>
+        <v>1.94893634319305</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853250980377</v>
+        <v>1.89853274822235</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.92373430728912</v>
+        <v>1.9237345457077</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.92373430728912</v>
+        <v>1.9237345457077</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253858089447</v>
+        <v>1.98253846168518</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993768215179</v>
+        <v>1.96993780136108</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>1.97833847999573</v>
+        <v>1.97833836078644</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>2.11694812774658</v>
+        <v>2.116947889328</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.26395845413208</v>
+        <v>2.2639582157135</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935487747192</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935487747192</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214968681335</v>
+        <v>2.14214944839478</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G608" t="n">
-        <v>2.23455619812012</v>
+        <v>2.2345564365387</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316584587097</v>
+        <v>2.37316608428955</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.410968542099</v>
+        <v>2.41096830368042</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.74699234962463</v>
+        <v>2.74699187278748</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099794387817</v>
+        <v>2.83099770545959</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519840240479</v>
+        <v>2.83519816398621</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G626" t="n">
-        <v>3.13761901855469</v>
+        <v>3.13761925697327</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.75</v>
       </c>
       <c r="G627" t="n">
-        <v>3.15022039413452</v>
+        <v>3.15022015571594</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661791801453</v>
+        <v>3.11661767959595</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.875</v>
       </c>
       <c r="G630" t="n">
-        <v>3.25522756576538</v>
+        <v>3.25522780418396</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10821747779846</v>
+        <v>3.10821723937988</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.26362800598145</v>
+        <v>3.26362824440002</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16282105445862</v>
+        <v>3.1628212928772</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081789970398</v>
+        <v>3.12081813812256</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.23422622680664</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.23422622680664</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803743362427</v>
+        <v>3.39803767204285</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703609466553</v>
+        <v>3.37703585624695</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G642" t="n">
-        <v>3.40223813056946</v>
+        <v>3.40223789215088</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>3.51564574241638</v>
+        <v>3.5156455039978</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645269393921</v>
+        <v>3.61645293235779</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.68785738945007</v>
+        <v>3.68785762786865</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446435928345</v>
+        <v>3.78446483612061</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827604293823</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887426376343</v>
+        <v>3.91887378692627</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927714347839</v>
+        <v>3.96927690505981</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887426376343</v>
+        <v>3.91887378692627</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.74666237831116</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G654" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226729393005</v>
+        <v>3.82226753234863</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746909141541</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545159339905</v>
+        <v>3.59545135498047</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.79706501960754</v>
+        <v>3.7970654964447</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407534599304</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407534599304</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.12048816680908</v>
+        <v>4.12048768997192</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G666" t="n">
-        <v>4.59512138366699</v>
+        <v>4.59512090682983</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>4.60352230072021</v>
+        <v>4.60352182388306</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.89754247665405</v>
+        <v>4.89754199981689</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.75</v>
       </c>
       <c r="G669" t="n">
-        <v>4.83033800125122</v>
+        <v>4.83033752441406</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>4.79673480987549</v>
+        <v>4.79673528671265</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>4.72112989425659</v>
+        <v>4.72113037109375</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G672" t="n">
-        <v>4.1834921836853</v>
+        <v>4.18349266052246</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.821937084198</v>
+        <v>4.82193660736084</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85554027557373</v>
+        <v>4.85553932189941</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074111938477</v>
+        <v>4.88074064254761</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>4.67072629928589</v>
+        <v>4.67072677612305</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.75</v>
       </c>
       <c r="G679" t="n">
-        <v>4.83033800125122</v>
+        <v>4.83033752441406</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.7043285369873</v>
+        <v>4.70432901382446</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G681" t="n">
-        <v>4.73793077468872</v>
+        <v>4.73793125152588</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>4.67912769317627</v>
+        <v>4.67912721633911</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G686" t="n">
-        <v>4.56151914596558</v>
+        <v>4.56151866912842</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G690" t="n">
-        <v>4.46911239624023</v>
+        <v>4.46911287307739</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350748062134</v>
+        <v>4.39350700378418</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788679122925</v>
+        <v>4.10788774490356</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95667695999146</v>
+        <v>3.95667672157288</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.80546641349792</v>
+        <v>3.80546593666077</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286503791809</v>
+        <v>3.79286551475525</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.73826098442078</v>
+        <v>3.73826122283936</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>4.01128053665161</v>
+        <v>4.01128005981445</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>3.18382263183594</v>
+        <v>3.18382239341736</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.625</v>
       </c>
       <c r="G706" t="n">
-        <v>3.04521250724792</v>
+        <v>3.0452127456665</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.99480938911438</v>
+        <v>2.99480962753296</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.5</v>
       </c>
       <c r="G711" t="n">
-        <v>2.94020557403564</v>
+        <v>2.94020581245422</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.95280647277832</v>
+        <v>2.9528067111969</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>2.8688006401062</v>
+        <v>2.86880040168762</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419682502747</v>
+        <v>2.81419634819031</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G718" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G720" t="n">
-        <v>2.71758961677551</v>
+        <v>2.71758985519409</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G721" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860625267029</v>
+        <v>2.94860601425171</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G727" t="n">
-        <v>3.13761901855469</v>
+        <v>3.13761925697327</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G728" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G730" t="n">
-        <v>3.33083271980286</v>
+        <v>3.33083319664001</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>3.2888298034668</v>
+        <v>3.28883004188538</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G732" t="n">
-        <v>3.23422622680664</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>3.18382263183594</v>
+        <v>3.18382239341736</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081789970398</v>
+        <v>3.12081813812256</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G735" t="n">
-        <v>3.10401701927185</v>
+        <v>3.10401678085327</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380757331848</v>
+        <v>2.97380781173706</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.77639412879944</v>
+        <v>2.77639389038086</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>2.79319524765015</v>
+        <v>2.79319500923157</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G742" t="n">
-        <v>2.8814013004303</v>
+        <v>2.88140153884888</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92760467529297</v>
+        <v>2.92760443687439</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G745" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.2762291431427</v>
+        <v>3.27622938156128</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.875</v>
       </c>
       <c r="G748" t="n">
-        <v>3.25522756576538</v>
+        <v>3.25522780418396</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781388282776</v>
+        <v>3.05781364440918</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.625</v>
       </c>
       <c r="G751" t="n">
-        <v>3.04521250724792</v>
+        <v>3.0452127456665</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380757331848</v>
+        <v>2.97380781173706</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418176651001</v>
+        <v>2.60418200492859</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G762" t="n">
-        <v>2.54957818984985</v>
+        <v>2.54957842826843</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>2.94020557403564</v>
+        <v>2.94020581245422</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400219917297</v>
+        <v>2.89400243759155</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.07461500167847</v>
+        <v>3.07461476325989</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00741004943848</v>
+        <v>3.00741052627563</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.06201386451721</v>
+        <v>3.06201410293579</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G775" t="n">
-        <v>3.07461500167847</v>
+        <v>3.07461476325989</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346302032471</v>
+        <v>3.76346254348755</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026413917542</v>
+        <v>3.78026437759399</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>3.7340612411499</v>
+        <v>3.73406100273132</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226729393005</v>
+        <v>3.82226753234863</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98607873916626</v>
+        <v>3.98607850074768</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>4.01128053665161</v>
+        <v>4.01128005981445</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347784042358</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G790" t="n">
-        <v>4.00287914276123</v>
+        <v>4.00287961959839</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486819267273</v>
+        <v>3.83486795425415</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.70465898513794</v>
+        <v>3.70465874671936</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G793" t="n">
-        <v>3.84326863288879</v>
+        <v>3.84326839447021</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>3.81806659698486</v>
+        <v>3.81806707382202</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.87267065048218</v>
+        <v>3.8726704120636</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347784042358</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>3.93567490577698</v>
+        <v>3.93567514419556</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827604293823</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147492408752</v>
+        <v>3.93147444725037</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507716178894</v>
+        <v>3.96507692337036</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627264976501</v>
+        <v>3.90627312660217</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427021026611</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126571655273</v>
+        <v>3.80126595497131</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885944366455</v>
+        <v>3.70885896682739</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165472984314</v>
+        <v>3.64165496826172</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G809" t="n">
-        <v>3.62905383110046</v>
+        <v>3.62905406951904</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.51564574241638</v>
+        <v>3.5156455039978</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>3.74666237831116</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845584869385</v>
+        <v>3.65845608711243</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>3.74666237831116</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208724975586</v>
+        <v>4.11208772659302</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G818" t="n">
-        <v>3.96087694168091</v>
+        <v>3.96087718009949</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627264976501</v>
+        <v>3.90627312660217</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987536430359</v>
+        <v>3.93987560272217</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427021026611</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G822" t="n">
-        <v>3.93567490577698</v>
+        <v>3.93567514419556</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688592910767</v>
+        <v>4.08688497543335</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948635101318</v>
+        <v>4.09948682785034</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631687164307</v>
+        <v>4.53631734848022</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.5</v>
       </c>
       <c r="G833" t="n">
-        <v>4.62032318115234</v>
+        <v>4.62032270431519</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.57831954956055</v>
+        <v>4.57832002639771</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030788421631</v>
+        <v>4.41030836105347</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627264976501</v>
+        <v>3.90627312660217</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746909141541</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.7886655330658</v>
+        <v>3.78866505622864</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347784042358</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>3.92307424545288</v>
+        <v>3.92307448387146</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.87267065048218</v>
+        <v>3.8726704120636</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>3.99369168281555</v>
+        <v>3.99369144439697</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563752174377</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487109184265</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G852" t="n">
-        <v>4.09310150146484</v>
+        <v>4.093101978302</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G853" t="n">
-        <v>3.8813145160675</v>
+        <v>3.88131499290466</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71275019645691</v>
+        <v>3.71274995803833</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.73436117172241</v>
+        <v>3.73436141014099</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G858" t="n">
-        <v>3.71707224845886</v>
+        <v>3.71707248687744</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157031059265</v>
+        <v>3.91157054901123</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385029792786</v>
+        <v>3.67385053634644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.71707224845886</v>
+        <v>3.71707248687744</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359545707703</v>
+        <v>3.64359521865845</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>3.37562012672424</v>
+        <v>3.37562036514282</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>3.55715155601501</v>
+        <v>3.55715131759644</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>3.48367476463318</v>
+        <v>3.48367500305176</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48367476463318</v>
+        <v>3.48367500305176</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>3.52689647674561</v>
+        <v>3.52689623832703</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.4015531539917</v>
+        <v>3.40155291557312</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>3.31078743934631</v>
+        <v>3.31078767776489</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>3.31510996818542</v>
+        <v>3.31510972976685</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G882" t="n">
-        <v>3.36265349388123</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G892" t="n">
-        <v>3.28917694091797</v>
+        <v>3.28917670249939</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.1768000125885</v>
+        <v>3.17680025100708</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>3.27621006965637</v>
+        <v>3.27621030807495</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G901" t="n">
-        <v>3.36265349388123</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349875450134</v>
+        <v>3.29349899291992</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>3.18112254142761</v>
+        <v>3.18112230300903</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385029792786</v>
+        <v>3.67385053634644</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.48799681663513</v>
+        <v>3.48799657821655</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.44477510452271</v>
+        <v>3.44477486610413</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56147360801697</v>
+        <v>3.56147384643555</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.56147360801697</v>
+        <v>3.56147384643555</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.55715155601501</v>
+        <v>3.55715131759644</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960779190063</v>
+        <v>3.50960755348206</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>3.49664115905762</v>
+        <v>3.4966413974762</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G939" t="n">
-        <v>3.47070837020874</v>
+        <v>3.47070813179016</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487109184265</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241580963135</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G954" t="n">
-        <v>3.51825213432312</v>
+        <v>3.5182523727417</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G957" t="n">
-        <v>3.48799681663513</v>
+        <v>3.48799657821655</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638607978821</v>
+        <v>3.46638631820679</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318104743958</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402630805969</v>
+        <v>3.86402654647827</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343588829041</v>
+        <v>3.96343636512756</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.91589260101318</v>
+        <v>3.91589283943176</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241580963135</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>3.81216025352478</v>
+        <v>3.81216049194336</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.95046997070312</v>
+        <v>3.9504702091217</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318104743958</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699294090271</v>
+        <v>3.87699317932129</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911383628845</v>
+        <v>3.95911407470703</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318104743958</v>
+        <v>3.93318128585815</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563752174377</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G992" t="n">
-        <v>4.09310150146484</v>
+        <v>4.093101978302</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G996" t="n">
-        <v>4.49506425857544</v>
+        <v>4.49506378173828</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319820404053</v>
+        <v>4.44319772720337</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G998" t="n">
-        <v>4.49506425857544</v>
+        <v>4.49506378173828</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.5037088394165</v>
+        <v>4.50370836257935</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337326049805</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.49506425857544</v>
+        <v>4.49506378173828</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337326049805</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.75439500808716</v>
+        <v>4.75439453125</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.7025294303894</v>
+        <v>4.70252895355225</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.96185874938965</v>
+        <v>4.96185922622681</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.7889723777771</v>
+        <v>4.78897190093994</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84083843231201</v>
+        <v>4.84083795547485</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.49780988693237</v>
+        <v>5.49780941009521</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.25576734542847</v>
+        <v>5.25576686859131</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846221923828</v>
+        <v>4.72846174240112</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48641967773438</v>
+        <v>4.48642015457153</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.52964162826538</v>
+        <v>4.52964115142822</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49506425857544</v>
+        <v>4.49506378173828</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895498275757</v>
+        <v>4.27895545959473</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.8942813873291</v>
+        <v>3.89428114891052</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.6824951171875</v>
+        <v>3.68249487876892</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15086698532104</v>
+        <v>3.15086722373962</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.38151955604553</v>
+        <v>2.38151979446411</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.07464528083801</v>
+        <v>2.07464504241943</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.04006743431091</v>
+        <v>2.04006767272949</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.37719750404358</v>
+        <v>2.377197265625</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.48092937469482</v>
+        <v>2.4809296131134</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790059089661</v>
+        <v>3.13790082931519</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.10332322120667</v>
+        <v>3.10332298278809</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.90450310707092</v>
+        <v>2.90450286865234</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.80077075958252</v>
+        <v>2.80077052116394</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.0341682434082</v>
+        <v>3.03416848182678</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.62976813316345</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.17370367050171</v>
+        <v>3.17370343208313</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.17819905281067</v>
+        <v>3.17819881439209</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17819905281067</v>
+        <v>3.17819881439209</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.17370367050171</v>
+        <v>3.17370343208313</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.67472147941589</v>
+        <v>2.67472171783447</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.51288986206055</v>
+        <v>2.51289010047913</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.06785178184509</v>
+        <v>2.06785202026367</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.47692728042603</v>
+        <v>2.4769275188446</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.75</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.47243165969849</v>
+        <v>2.47243189811707</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.3420672416687</v>
+        <v>2.34206748008728</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.3780300617218</v>
+        <v>2.37802982330322</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.355553150177</v>
+        <v>2.35555338859558</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.41848826408386</v>
+        <v>2.41848802566528</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.40050673484802</v>
+        <v>2.40050649642944</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.4409646987915</v>
+        <v>2.44096446037292</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.19821667671204</v>
+        <v>2.19821643829346</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.95097351074219</v>
+        <v>1.95097362995148</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.00941276550293</v>
+        <v>2.00941252708435</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.6704648733139</v>
+        <v>1.67046499252319</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.76037156581879</v>
+        <v>1.7603714466095</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.74059212207794</v>
+        <v>1.74059200286865</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.82510435581207</v>
+        <v>1.82510423660278</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.96895503997803</v>
+        <v>1.96895492076874</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.43646907806396</v>
+        <v>2.43646931648254</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.49940371513367</v>
+        <v>2.49940395355225</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.75</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.47243165969849</v>
+        <v>2.47243189811707</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.49940371513367</v>
+        <v>2.49940395355225</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.51288986206055</v>
+        <v>2.51289010047913</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.49940371513367</v>
+        <v>2.49940395355225</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.47692728042603</v>
+        <v>2.4769275188446</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737643241882</v>
+        <v>3.00737619400024</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.13774085044861</v>
+        <v>3.13774061203003</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.11526393890381</v>
+        <v>3.11526417732239</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.17370367050171</v>
+        <v>3.17370343208313</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.50635814666748</v>
+        <v>3.5063579082489</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.23663783073425</v>
+        <v>3.23663806915283</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.28159141540527</v>
+        <v>3.28159165382385</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856323242188</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.07930135726929</v>
+        <v>3.07930159568787</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.17819905281067</v>
+        <v>3.17819881439209</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.32654476165771</v>
+        <v>3.32654452323914</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.36700248718262</v>
+        <v>3.3670027256012</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.44342303276062</v>
+        <v>3.4434232711792</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33553552627563</v>
+        <v>3.33553528785706</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.42993712425232</v>
+        <v>3.4299373626709</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27260065078735</v>
+        <v>3.27260088920593</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.11526393890381</v>
+        <v>3.11526417732239</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737643241882</v>
+        <v>3.00737619400024</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.13774085044861</v>
+        <v>3.13774061203003</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.28159141540527</v>
+        <v>3.28159165382385</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.17819905281067</v>
+        <v>3.17819881439209</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.29957270622253</v>
+        <v>3.29957294464111</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.625</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.25911450386047</v>
+        <v>3.25911474227905</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.23663783073425</v>
+        <v>3.23663806915283</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856323242188</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.625</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.25911450386047</v>
+        <v>3.25911474227905</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.28159141540527</v>
+        <v>3.28159165382385</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.21865701675415</v>
+        <v>3.21865677833557</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.33553552627563</v>
+        <v>3.33553528785706</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29957270622253</v>
+        <v>3.29957294464111</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27260065078735</v>
+        <v>3.27260088920593</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856347084045</v>
+        <v>3.30856323242188</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.23663783073425</v>
+        <v>3.23663806915283</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.23214268684387</v>
+        <v>3.23214292526245</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.33553552627563</v>
+        <v>3.33553528785706</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.27709603309631</v>
+        <v>3.27709627151489</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.23663783073425</v>
+        <v>3.23663806915283</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.27260065078735</v>
+        <v>3.27260088920593</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.28159141540527</v>
+        <v>3.28159165382385</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737643241882</v>
+        <v>3.00737619400024</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.11526393890381</v>
+        <v>3.11526417732239</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.07930135726929</v>
+        <v>3.07930159568787</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.92646050453186</v>
+        <v>2.92646026611328</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.13774085044861</v>
+        <v>3.13774061203003</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.17370367050171</v>
+        <v>3.17370343208313</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.04333877563477</v>
+        <v>3.04333901405334</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737643241882</v>
+        <v>3.00737619400024</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.0478343963623</v>
+        <v>3.04783415794373</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.0478343963623</v>
+        <v>3.04783415794373</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737643241882</v>
+        <v>3.00737619400024</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.8005907535553</v>
+        <v>2.80059099197388</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.9354510307312</v>
+        <v>2.93545079231262</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.96691823005676</v>
+        <v>2.96691799163818</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178731918335</v>
+        <v>2.61178708076477</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.40050673484802</v>
+        <v>2.40050649642944</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.62976813316345</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.71068429946899</v>
+        <v>2.71068453788757</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.71068429946899</v>
+        <v>2.71068453788757</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.8005907535553</v>
+        <v>2.80059099197388</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.86802077293396</v>
+        <v>2.86802101135254</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.76462841033936</v>
+        <v>2.76462817192078</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.74215173721313</v>
+        <v>2.74215149879456</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.85003995895386</v>
+        <v>2.85003972053528</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.76912379264832</v>
+        <v>2.76912355422974</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.71068429946899</v>
+        <v>2.71068453788757</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664735794067</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178731918335</v>
+        <v>2.61178708076477</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.67472147941589</v>
+        <v>2.67472171783447</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.71068429946899</v>
+        <v>2.71068453788757</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.54885268211365</v>
+        <v>2.54885244369507</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.41848826408386</v>
+        <v>2.41848802566528</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.47692728042603</v>
+        <v>2.4769275188446</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.43646907806396</v>
+        <v>2.43646931648254</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.4409646987915</v>
+        <v>2.44096446037292</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.75</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.47243165969849</v>
+        <v>2.47243189811707</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.43646907806396</v>
+        <v>2.43646931648254</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.4409646987915</v>
+        <v>2.44096446037292</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.37353491783142</v>
+        <v>2.37353467941284</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.3420672416687</v>
+        <v>2.34206748008728</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.31509518623352</v>
+        <v>2.3150954246521</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.18023538589478</v>
+        <v>2.1802351474762</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15326333045959</v>
+        <v>2.15326356887817</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.11730098724365</v>
+        <v>2.11730074882507</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.04987096786499</v>
+        <v>2.04987072944641</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.04987096786499</v>
+        <v>2.04987072944641</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.00491762161255</v>
+        <v>2.00491738319397</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.00491762161255</v>
+        <v>2.00491738319397</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143147468567</v>
+        <v>1.99143159389496</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.9599643945694</v>
+        <v>1.95996415615082</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1944" t="n">
-        <v>1.91950607299805</v>
+        <v>1.91950619220734</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299210071564</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.91950607299805</v>
+        <v>1.91950619220734</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.95097351074219</v>
+        <v>1.95097362995148</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.99592685699463</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.98693597316742</v>
+        <v>1.986936211586</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299210071564</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647836685181</v>
+        <v>1.94647824764252</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.99592685699463</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.00491762161255</v>
+        <v>2.00491738319397</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.9599643945694</v>
+        <v>1.95996415615082</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.95097351074219</v>
+        <v>1.95097362995148</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.85207629203796</v>
+        <v>1.85207617282867</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262768268585</v>
+        <v>1.80262780189514</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.7477844953537</v>
+        <v>1.74778461456299</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.7351975440979</v>
+        <v>1.73519766330719</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.66686856746674</v>
+        <v>1.66686868667603</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.771160364151</v>
+        <v>1.77116024494171</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.76576578617096</v>
+        <v>1.76576590538025</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.99592685699463</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.04987096786499</v>
+        <v>2.04987072944641</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.00491762161255</v>
+        <v>2.00491738319397</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.11730098724365</v>
+        <v>2.11730074882507</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.20720744132996</v>
+        <v>2.20720720291138</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.19821667671204</v>
+        <v>2.19821643829346</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.31509518623352</v>
+        <v>2.3150954246521</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.31509518623352</v>
+        <v>2.3150954246521</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.3645441532135</v>
+        <v>2.36454391479492</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.54885268211365</v>
+        <v>2.54885244369507</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.54885268211365</v>
+        <v>2.54885244369507</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.51738500595093</v>
+        <v>2.51738524436951</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>2.75</v>
       </c>
       <c r="G2050" t="n">
-        <v>2.47243165969849</v>
+        <v>2.47243189811707</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.54435706138611</v>
+        <v>2.54435729980469</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>2.75</v>
       </c>
       <c r="G2060" t="n">
-        <v>2.47243165969849</v>
+        <v>2.47243189811707</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.62976813316345</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.80508637428284</v>
+        <v>2.80508613586426</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>3.13774085044861</v>
+        <v>3.13774061203003</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="n">
-        <v>3.52883458137512</v>
+        <v>3.52883434295654</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.69516205787659</v>
+        <v>3.69516181945801</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.32654476165771</v>
+        <v>3.32654452323914</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.37599349021912</v>
+        <v>3.37599325180054</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="n">
-        <v>3.34902143478394</v>
+        <v>3.34902119636536</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="n">
-        <v>3.28608655929565</v>
+        <v>3.28608679771423</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.625</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.25911450386047</v>
+        <v>3.25911474227905</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.47489047050476</v>
+        <v>3.47489070892334</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2117" t="n">
-        <v>3.44342303276062</v>
+        <v>3.4434232711792</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.53137946128845</v>
+        <v>3.53137922286987</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.55003929138184</v>
+        <v>3.55003905296326</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.64800357818604</v>
+        <v>3.64800333976746</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.62001347541809</v>
+        <v>3.62001371383667</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2135" t="n">
-        <v>3.52204918861389</v>
+        <v>3.52204942703247</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2142" t="n">
-        <v>3.60601878166199</v>
+        <v>3.60601854324341</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2147" t="n">
-        <v>3.55003929138184</v>
+        <v>3.55003905296326</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2148" t="n">
-        <v>3.53137946128845</v>
+        <v>3.53137922286987</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56321,7 +56321,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2152" t="n">
-        <v>3.24681639671326</v>
+        <v>3.24681615829468</v>
       </c>
       <c r="H2152" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.3867654800415</v>
+        <v>3.38676524162292</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2157" t="n">
-        <v>3.34478068351746</v>
+        <v>3.34478044509888</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2162" t="n">
-        <v>3.41009020805359</v>
+        <v>3.41008996963501</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2180" t="n">
-        <v>3.92323637008667</v>
+        <v>3.92323613166809</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.66199803352356</v>
+        <v>3.66199827194214</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57283,7 +57283,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2189" t="n">
-        <v>3.36810541152954</v>
+        <v>3.36810517311096</v>
       </c>
       <c r="H2189" t="s">
         <v>8</v>
@@ -57361,7 +57361,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2192" t="n">
-        <v>3.34478068351746</v>
+        <v>3.34478044509888</v>
       </c>
       <c r="H2192" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2194" t="n">
-        <v>3.34478068351746</v>
+        <v>3.34478044509888</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2198" t="n">
-        <v>3.42408490180969</v>
+        <v>3.42408514022827</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2199" t="n">
-        <v>3.52204918861389</v>
+        <v>3.52204942703247</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2201" t="n">
-        <v>3.55003929138184</v>
+        <v>3.55003905296326</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2207" t="n">
-        <v>3.52204918861389</v>
+        <v>3.52204942703247</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.27014136314392</v>
+        <v>3.27014112472534</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2213" t="n">
-        <v>3.2888011932373</v>
+        <v>3.28880095481873</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.22815656661987</v>
+        <v>3.22815632820129</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58063,7 +58063,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2219" t="n">
-        <v>3.34478068351746</v>
+        <v>3.34478044509888</v>
       </c>
       <c r="H2219" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2223" t="n">
-        <v>3.2888011932373</v>
+        <v>3.28880095481873</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2224" t="n">
-        <v>3.24681639671326</v>
+        <v>3.24681615829468</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58297,7 +58297,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2228" t="n">
-        <v>3.22815656661987</v>
+        <v>3.22815632820129</v>
       </c>
       <c r="H2228" t="s">
         <v>8</v>
@@ -58349,7 +58349,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.17217707633972</v>
+        <v>3.17217683792114</v>
       </c>
       <c r="H2230" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2232" t="n">
-        <v>3.22815656661987</v>
+        <v>3.22815632820129</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58427,7 +58427,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2233" t="n">
-        <v>3.19550180435181</v>
+        <v>3.19550156593323</v>
       </c>
       <c r="H2233" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2236" t="n">
-        <v>3.19550180435181</v>
+        <v>3.19550156593323</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58531,7 +58531,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2237" t="n">
-        <v>3.24681639671326</v>
+        <v>3.24681615829468</v>
       </c>
       <c r="H2237" t="s">
         <v>8</v>
@@ -58583,7 +58583,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2239" t="n">
-        <v>3.27014136314392</v>
+        <v>3.27014112472534</v>
       </c>
       <c r="H2239" t="s">
         <v>8</v>
@@ -58609,7 +58609,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2240" t="n">
-        <v>3.42408490180969</v>
+        <v>3.42408514022827</v>
       </c>
       <c r="H2240" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>3.92790102958679</v>
+        <v>3.92790126800537</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G2246" t="n">
-        <v>3.94189620018005</v>
+        <v>3.94189596176147</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2248" t="n">
-        <v>3.92323637008667</v>
+        <v>3.92323613166809</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2249" t="n">
-        <v>3.9932107925415</v>
+        <v>3.99321103096008</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G2251" t="n">
-        <v>3.89524674415588</v>
+        <v>3.8952465057373</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2258" t="n">
-        <v>3.76929259300232</v>
+        <v>3.76929235458374</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2259" t="n">
-        <v>3.64800357818604</v>
+        <v>3.64800333976746</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G2260" t="n">
-        <v>3.86725664138794</v>
+        <v>3.86725640296936</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G2261" t="n">
-        <v>3.90457653999329</v>
+        <v>3.90457630157471</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59467,7 +59467,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2273" t="n">
-        <v>3.66199803352356</v>
+        <v>3.66199827194214</v>
       </c>
       <c r="H2273" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2278" t="n">
-        <v>3.92790102958679</v>
+        <v>3.92790126800537</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59623,7 +59623,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2279" t="n">
-        <v>4.00720596313477</v>
+        <v>4.00720548629761</v>
       </c>
       <c r="H2279" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2281" t="n">
-        <v>4.10516977310181</v>
+        <v>4.10517024993896</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2299" t="n">
-        <v>4.00720596313477</v>
+        <v>4.00720548629761</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2300" t="n">
-        <v>3.97921586036682</v>
+        <v>3.97921562194824</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2302" t="n">
-        <v>4.10516977310181</v>
+        <v>4.10517024993896</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2307" t="n">
-        <v>4.38506746292114</v>
+        <v>4.3850679397583</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60403,7 +60403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2309" t="n">
-        <v>4.51568698883057</v>
+        <v>4.51568746566772</v>
       </c>
       <c r="H2309" t="s">
         <v>8</v>
@@ -60481,7 +60481,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2312" t="n">
-        <v>4.71161556243896</v>
+        <v>4.71161603927612</v>
       </c>
       <c r="H2312" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2314" t="n">
-        <v>4.58099603652954</v>
+        <v>4.5809965133667</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60715,7 +60715,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2321" t="n">
-        <v>4.94486379623413</v>
+        <v>4.94486427307129</v>
       </c>
       <c r="H2321" t="s">
         <v>8</v>
@@ -60767,7 +60767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2323" t="n">
-        <v>5.1034722328186</v>
+        <v>5.10347270965576</v>
       </c>
       <c r="H2323" t="s">
         <v>8</v>
@@ -60793,7 +60793,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2324" t="n">
-        <v>4.90754413604736</v>
+        <v>4.90754461288452</v>
       </c>
       <c r="H2324" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2326" t="n">
-        <v>4.94486379623413</v>
+        <v>4.94486427307129</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60897,7 +60897,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G2328" t="n">
-        <v>4.86089420318604</v>
+        <v>4.86089468002319</v>
       </c>
       <c r="H2328" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2332" t="n">
-        <v>4.6742959022522</v>
+        <v>4.67429637908936</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2335" t="n">
-        <v>4.68362617492676</v>
+        <v>4.6836256980896</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2337" t="n">
-        <v>4.58099603652954</v>
+        <v>4.5809965133667</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2339" t="n">
-        <v>4.6742959022522</v>
+        <v>4.67429637908936</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2342" t="n">
-        <v>4.879554271698</v>
+        <v>4.87955474853516</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2344" t="n">
-        <v>5.0754828453064</v>
+        <v>5.07548332214355</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2346" t="n">
-        <v>4.94486379623413</v>
+        <v>4.94486427307129</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61443,7 +61443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2349" t="n">
-        <v>4.90754413604736</v>
+        <v>4.90754461288452</v>
       </c>
       <c r="H2349" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G2355" t="n">
-        <v>4.5670018196106</v>
+        <v>4.56700134277344</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61625,7 +61625,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2356" t="n">
-        <v>4.33841800689697</v>
+        <v>4.33841848373413</v>
       </c>
       <c r="H2356" t="s">
         <v>8</v>
@@ -61651,7 +61651,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G2357" t="n">
-        <v>4.18447494506836</v>
+        <v>4.1844744682312</v>
       </c>
       <c r="H2357" t="s">
         <v>8</v>
@@ -61677,7 +61677,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2358" t="n">
-        <v>4.38506746292114</v>
+        <v>4.3850679397583</v>
       </c>
       <c r="H2358" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.15181922912598</v>
+        <v>4.15181970596313</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G2360" t="n">
-        <v>4.33375358581543</v>
+        <v>4.33375310897827</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G2362" t="n">
-        <v>4.4643726348877</v>
+        <v>4.46437215805054</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2366" t="n">
-        <v>4.68362617492676</v>
+        <v>4.6836256980896</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2367" t="n">
-        <v>4.75826501846313</v>
+        <v>4.75826549530029</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2368" t="n">
-        <v>4.879554271698</v>
+        <v>4.87955474853516</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>7.59000015258789</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>13697</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349234104156</v>
+        <v>1.89349222183228</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853286743164</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980905056</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612623691559</v>
+        <v>1.80612635612488</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69019818305969</v>
+        <v>1.69019830226898</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64231491088867</v>
+        <v>1.64231479167938</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754946708679</v>
+        <v>1.56754958629608</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.40877842903137</v>
+        <v>1.40877854824066</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>1.50370526313782</v>
+        <v>1.50370514392853</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995981216431</v>
+        <v>1.13995969295502</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204330444336</v>
+        <v>1.19204342365265</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G32" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35333466529846</v>
+        <v>1.35333454608917</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G46" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G47" t="n">
-        <v>1.50874555110931</v>
+        <v>1.50874543190002</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G52" t="n">
-        <v>1.50286507606506</v>
+        <v>1.50286519527435</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586933135986</v>
+        <v>1.56586956977844</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491569042206</v>
+        <v>1.65491580963135</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551355361938</v>
+        <v>1.62551367282867</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349593639374</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G67" t="n">
-        <v>1.35585474967957</v>
+        <v>1.35585463047028</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829437732697</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G73" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847023010254</v>
+        <v>1.57847034931183</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830883979797</v>
+        <v>1.55830895900726</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G77" t="n">
-        <v>1.57426989078522</v>
+        <v>1.57427000999451</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.60787236690521</v>
+        <v>1.6078724861145</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646731376648</v>
+        <v>1.53646743297577</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.53898739814758</v>
+        <v>1.53898751735687</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>1.50370526313782</v>
+        <v>1.50370514392853</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574105739594</v>
+        <v>1.44574117660522</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G94" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G96" t="n">
-        <v>1.5188262462616</v>
+        <v>1.51882612705231</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278438091278</v>
+        <v>1.49278426170349</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.50202512741089</v>
+        <v>1.5020250082016</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51798617839813</v>
+        <v>1.51798605918884</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G106" t="n">
-        <v>1.52470660209656</v>
+        <v>1.52470672130585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338212490082</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.54150784015656</v>
+        <v>1.54150772094727</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614465236664</v>
+        <v>1.49614453315735</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457808971405</v>
+        <v>1.40457832813263</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577417373657</v>
+        <v>1.34577405452728</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G117" t="n">
-        <v>1.35669493675232</v>
+        <v>1.35669481754303</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28192961215973</v>
+        <v>1.28192949295044</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G125" t="n">
-        <v>1.28780996799469</v>
+        <v>1.28781008720398</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537057876587</v>
+        <v>1.29537069797516</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G132" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>1.33485329151154</v>
+        <v>1.33485317230225</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829437732697</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401346206665</v>
+        <v>1.33401334285736</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34997451305389</v>
+        <v>1.3499743938446</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357663154602</v>
+        <v>1.38357675075531</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G150" t="n">
-        <v>1.35585474967957</v>
+        <v>1.35585463047028</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3138519525528</v>
+        <v>1.31385183334351</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125093460083</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28948998451233</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G162" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G163" t="n">
-        <v>1.26092827320099</v>
+        <v>1.26092803478241</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680850982666</v>
+        <v>1.26680862903595</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545139312744</v>
+        <v>1.30545127391815</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G168" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29621064662933</v>
+        <v>1.29621052742004</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30629134178162</v>
+        <v>1.30629122257233</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G176" t="n">
-        <v>1.30629134178162</v>
+        <v>1.30629122257233</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265586853027</v>
+        <v>1.37265598773956</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921514034271</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677539348602</v>
+        <v>1.36677551269531</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G183" t="n">
-        <v>1.32225227355957</v>
+        <v>1.32225239276886</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477259635925</v>
+        <v>1.32477247714996</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33821356296539</v>
+        <v>1.33821368217468</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417473316193</v>
+        <v>1.35417461395264</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149302005768</v>
+        <v>1.33149313926697</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G191" t="n">
-        <v>1.35585474967957</v>
+        <v>1.35585463047028</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G197" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.625</v>
       </c>
       <c r="G198" t="n">
-        <v>1.36509537696838</v>
+        <v>1.36509549617767</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349593639374</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881142616272</v>
+        <v>1.30881154537201</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125093460083</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G211" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28948998451233</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G215" t="n">
-        <v>1.27856922149658</v>
+        <v>1.27856934070587</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G217" t="n">
-        <v>1.27184903621674</v>
+        <v>1.27184891700745</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G219" t="n">
-        <v>1.2222855091095</v>
+        <v>1.22228562831879</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367562294006</v>
+        <v>1.08367574214935</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G232" t="n">
-        <v>1.09795689582825</v>
+        <v>1.09795677661896</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115541934967</v>
+        <v>1.08115553855896</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.0803154706955</v>
+        <v>1.08031558990479</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.0635142326355</v>
+        <v>1.06351435184479</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939458847046</v>
+        <v>1.06939482688904</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G245" t="n">
-        <v>1.14163982868195</v>
+        <v>1.14163970947266</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G247" t="n">
-        <v>1.16768169403076</v>
+        <v>1.16768157482147</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G248" t="n">
-        <v>1.19624376296997</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G250" t="n">
-        <v>1.19624376296997</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.16180109977722</v>
+        <v>1.16180121898651</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348123550415</v>
+        <v>1.16348135471344</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364286422729</v>
+        <v>1.18364274501801</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G258" t="n">
-        <v>1.1979238986969</v>
+        <v>1.19792377948761</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G261" t="n">
-        <v>1.34073376655579</v>
+        <v>1.3407336473465</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501492023468</v>
+        <v>1.35501480102539</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.34325397014618</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G264" t="n">
-        <v>1.31469202041626</v>
+        <v>1.31469178199768</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33821356296539</v>
+        <v>1.33821368217468</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377125740051</v>
+        <v>1.30377101898193</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.18868315219879</v>
+        <v>1.1886830329895</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.21724510192871</v>
+        <v>1.21724498271942</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G279" t="n">
-        <v>1.18532299995422</v>
+        <v>1.18532288074493</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G282" t="n">
-        <v>1.1979238986969</v>
+        <v>1.19792377948761</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G284" t="n">
-        <v>1.18784308433533</v>
+        <v>1.18784320354462</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104196548462</v>
+        <v>1.17104184627533</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G289" t="n">
-        <v>1.17776238918304</v>
+        <v>1.17776226997375</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G291" t="n">
-        <v>1.17860245704651</v>
+        <v>1.17860233783722</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G292" t="n">
-        <v>1.15340065956116</v>
+        <v>1.15340054035187</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G294" t="n">
-        <v>1.16432154178619</v>
+        <v>1.1643214225769</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G295" t="n">
-        <v>1.15088045597076</v>
+        <v>1.15088057518005</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424060821533</v>
+        <v>1.15424048900604</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740637302399</v>
+        <v>1.23740661144257</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G304" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G306" t="n">
-        <v>1.22396552562714</v>
+        <v>1.22396564483643</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G311" t="n">
-        <v>1.18784308433533</v>
+        <v>1.18784320354462</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G316" t="n">
-        <v>1.17860245704651</v>
+        <v>1.17860233783722</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18196260929108</v>
+        <v>1.18196249008179</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.21724510192871</v>
+        <v>1.21724498271942</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884442329407</v>
+        <v>1.20884454250336</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G320" t="n">
-        <v>1.22396552562714</v>
+        <v>1.22396564483643</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.21052443981171</v>
+        <v>1.210524559021</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252747535706</v>
+        <v>1.25252771377563</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688908576965</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688908576965</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G327" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320603370667</v>
+        <v>1.23320627212524</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>1.20128393173218</v>
+        <v>1.20128405094147</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908650875092</v>
+        <v>1.23908662796021</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.21724510192871</v>
+        <v>1.21724498271942</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.24412679672241</v>
+        <v>1.2441269159317</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488616943359</v>
+        <v>1.23488640785217</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.2248055934906</v>
+        <v>1.22480547428131</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664711952209</v>
+        <v>1.24664700031281</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G354" t="n">
-        <v>1.36761558055878</v>
+        <v>1.36761569976807</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890682220459</v>
+        <v>1.52890694141388</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G359" t="n">
-        <v>1.4516214132309</v>
+        <v>1.45162153244019</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>1.45498168468475</v>
+        <v>1.45498156547546</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G364" t="n">
-        <v>1.43230020999908</v>
+        <v>1.43230009078979</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.625</v>
       </c>
       <c r="G367" t="n">
-        <v>1.36509537696838</v>
+        <v>1.36509549617767</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173510551453</v>
+        <v>1.36173522472382</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349593639374</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829437732697</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.34325397014618</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921514034271</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G385" t="n">
-        <v>1.42557966709137</v>
+        <v>1.42557978630066</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221927642822</v>
+        <v>1.42221939563751</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G395" t="n">
-        <v>1.42725968360901</v>
+        <v>1.4272598028183</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102366924286</v>
+        <v>1.48102355003357</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G404" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338212490082</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G409" t="n">
-        <v>1.52554643154144</v>
+        <v>1.52554666996002</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.53310716152191</v>
+        <v>1.5331072807312</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G415" t="n">
-        <v>1.43986070156097</v>
+        <v>1.43986058235168</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574105739594</v>
+        <v>1.44574117660522</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G418" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490087032318</v>
+        <v>1.44490098953247</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238078594208</v>
+        <v>1.44238066673279</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G426" t="n">
-        <v>1.43230020999908</v>
+        <v>1.43230009078979</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G427" t="n">
-        <v>1.43230020999908</v>
+        <v>1.43230009078979</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G428" t="n">
-        <v>1.43398022651672</v>
+        <v>1.43398010730743</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>1.44826114177704</v>
+        <v>1.44826126098633</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842277050018</v>
+        <v>1.46842265129089</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G436" t="n">
-        <v>1.4516214132309</v>
+        <v>1.45162153244019</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51966631412506</v>
+        <v>1.51966619491577</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.52134644985199</v>
+        <v>1.5213463306427</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G441" t="n">
-        <v>1.59527158737183</v>
+        <v>1.59527146816254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531904697418</v>
+        <v>1.70531916618347</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.8010858297348</v>
+        <v>1.80108618736267</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G445" t="n">
-        <v>1.80780637264252</v>
+        <v>1.80780625343323</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717551231384</v>
+        <v>1.93717527389526</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429953098297</v>
+        <v>1.99429941177368</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.9405357837677</v>
+        <v>1.94053590297699</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757874965668</v>
+        <v>1.98757898807526</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229637622833</v>
+        <v>1.95229649543762</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869401931763</v>
+        <v>1.91869390010834</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476900100708</v>
+        <v>1.84476912021637</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980905056</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>1.85652995109558</v>
+        <v>1.856529712677</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100501537323</v>
+        <v>1.79100513458252</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.7742041349411</v>
+        <v>1.77420377731323</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>1.78932523727417</v>
+        <v>1.78932511806488</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669122219086</v>
+        <v>1.87669110298157</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.86493027210236</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173127174377</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533374786377</v>
+        <v>1.91533386707306</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>1.95733666419983</v>
+        <v>1.95733690261841</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.00438022613525</v>
+        <v>2.00437998771667</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581803798676</v>
+        <v>1.97581791877747</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061659812927</v>
+        <v>1.95061635971069</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>1.95733666419983</v>
+        <v>1.95733690261841</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341164588928</v>
+        <v>1.88341188430786</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308874607086</v>
+        <v>1.84308886528015</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316967964172</v>
+        <v>1.85316956043243</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879324913025</v>
+        <v>1.61879336833954</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.64651525020599</v>
+        <v>1.6465151309967</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63475430011749</v>
+        <v>1.6347541809082</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G484" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G488" t="n">
-        <v>1.57595014572144</v>
+        <v>1.57595026493073</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326855182648</v>
+        <v>1.55326867103577</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G490" t="n">
-        <v>1.50874555110931</v>
+        <v>1.50874543190002</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54150784015656</v>
+        <v>1.54150772094727</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>1.59695160388947</v>
+        <v>1.59695172309875</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531904697418</v>
+        <v>1.70531916618347</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G499" t="n">
-        <v>1.69019818305969</v>
+        <v>1.69019830226898</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507708072662</v>
+        <v>1.67507696151733</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299346923828</v>
+        <v>1.62299358844757</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451221466064</v>
+        <v>1.60451209545135</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.579310297966</v>
+        <v>1.57931041717529</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887394428253</v>
+        <v>1.62887382507324</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62467360496521</v>
+        <v>1.62467348575592</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267045021057</v>
+        <v>1.58267068862915</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G514" t="n">
-        <v>1.66163611412048</v>
+        <v>1.66163623332977</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G515" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323567390442</v>
+        <v>1.65323555469513</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851792812347</v>
+        <v>1.68851804733276</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>1.72212028503418</v>
+        <v>1.72212040424347</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G530" t="n">
-        <v>1.86493027210236</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433252811432</v>
+        <v>1.89433240890503</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533374786377</v>
+        <v>1.91533386707306</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152266025543</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152266025543</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G543" t="n">
-        <v>1.77252376079559</v>
+        <v>1.77252399921417</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>1.78932523727417</v>
+        <v>1.78932511806488</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.7935254573822</v>
+        <v>1.79352557659149</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.78932523727417</v>
+        <v>1.78932511806488</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>1.72212028503418</v>
+        <v>1.72212040424347</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632086277008</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G552" t="n">
-        <v>1.72212028503418</v>
+        <v>1.72212040424347</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632086277008</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.6801176071167</v>
+        <v>1.68011736869812</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G564" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>1.839728474617</v>
+        <v>1.83972859382629</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173127174377</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173127174377</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872701644897</v>
+        <v>1.81872713565826</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>1.77672410011292</v>
+        <v>1.7767242193222</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.7935254573822</v>
+        <v>1.79352557659149</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G579" t="n">
-        <v>1.78932523727417</v>
+        <v>1.78932511806488</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872701644897</v>
+        <v>1.81872713565826</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192589759827</v>
+        <v>1.80192601680756</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G582" t="n">
-        <v>1.81452703475952</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113376617432</v>
+        <v>1.91113352775574</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.91953444480896</v>
+        <v>1.91953432559967</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173127174377</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86913061141968</v>
+        <v>1.8691303730011</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G588" t="n">
-        <v>1.839728474617</v>
+        <v>1.83972859382629</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853286743164</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253846168518</v>
+        <v>1.98253858089447</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993780136108</v>
+        <v>1.96993768215179</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>1.97833836078644</v>
+        <v>1.97833824157715</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>2.00774073600769</v>
+        <v>2.00774002075195</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.01614117622375</v>
+        <v>2.01614093780518</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093902111053</v>
+        <v>1.99093878269196</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.2639582157135</v>
+        <v>2.26395797729492</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>2.23035573959351</v>
+        <v>2.23035621643066</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214944839478</v>
+        <v>2.14214968681335</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G608" t="n">
-        <v>2.2345564365387</v>
+        <v>2.23455619812012</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316608428955</v>
+        <v>2.37316584587097</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41096830368042</v>
+        <v>2.410968542099</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177549362183</v>
+        <v>2.51177573204041</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41936922073364</v>
+        <v>2.41936945915222</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>2.49497437477112</v>
+        <v>2.4949746131897</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>2.54537796974182</v>
+        <v>2.54537773132324</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>2.62938404083252</v>
+        <v>2.62938356399536</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.74699187278748</v>
+        <v>2.74699211120605</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099770545959</v>
+        <v>2.83099794387817</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059434890747</v>
+        <v>2.78059411048889</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519816398621</v>
+        <v>2.83519792556763</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661767959595</v>
+        <v>3.11661791801453</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.875</v>
       </c>
       <c r="G630" t="n">
-        <v>3.25522780418396</v>
+        <v>3.25522756576538</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10821723937988</v>
+        <v>3.10821747779846</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.26362824440002</v>
+        <v>3.26362800598145</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.1628212928772</v>
+        <v>3.16282105445862</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803767204285</v>
+        <v>3.39803743362427</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703585624695</v>
+        <v>3.37703609466553</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>3.44424057006836</v>
+        <v>3.44424080848694</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>3.44424057006836</v>
+        <v>3.44424080848694</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>3.5156455039978</v>
+        <v>3.51564598083496</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645293235779</v>
+        <v>3.61645245552063</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.68785762786865</v>
+        <v>3.68785786628723</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446483612061</v>
+        <v>3.78446435928345</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887378692627</v>
+        <v>3.91887402534485</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927690505981</v>
+        <v>3.96927738189697</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887378692627</v>
+        <v>3.91887402534485</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G654" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226753234863</v>
+        <v>3.82226705551147</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545135498047</v>
+        <v>3.59545159339905</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.7970654964447</v>
+        <v>3.79706573486328</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407606124878</v>
+        <v>3.9440758228302</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407606124878</v>
+        <v>3.9440758228302</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.12048768997192</v>
+        <v>4.12048816680908</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G665" t="n">
-        <v>4.43551015853882</v>
+        <v>4.43551063537598</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>4.60352182388306</v>
+        <v>4.60352230072021</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.75</v>
       </c>
       <c r="G669" t="n">
-        <v>4.83033752441406</v>
+        <v>4.8303370475769</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G672" t="n">
-        <v>4.18349266052246</v>
+        <v>4.1834921836853</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>4.6539249420166</v>
+        <v>4.65392541885376</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.82193660736084</v>
+        <v>4.821937084198</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553932189941</v>
+        <v>4.85553979873657</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074064254761</v>
+        <v>4.88074159622192</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>4.76313304901123</v>
+        <v>4.76313352584839</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>4.67072677612305</v>
+        <v>4.67072629928589</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.75</v>
       </c>
       <c r="G679" t="n">
-        <v>4.83033752441406</v>
+        <v>4.8303370475769</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.70432901382446</v>
+        <v>4.7043285369873</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>4.6539249420166</v>
+        <v>4.65392541885376</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192226409912</v>
+        <v>4.61192178726196</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G685" t="n">
-        <v>4.40190744400024</v>
+        <v>4.40190696716309</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G687" t="n">
-        <v>4.46071147918701</v>
+        <v>4.46071243286133</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G690" t="n">
-        <v>4.46911287307739</v>
+        <v>4.46911239624023</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350700378418</v>
+        <v>4.39350748062134</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.33470249176025</v>
+        <v>4.33470296859741</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.0574836730957</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788774490356</v>
+        <v>4.10788726806641</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95667672157288</v>
+        <v>3.9566764831543</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.80546593666077</v>
+        <v>3.80546641349792</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286551475525</v>
+        <v>3.79286503791809</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.73826122283936</v>
+        <v>3.7382607460022</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.625</v>
       </c>
       <c r="G706" t="n">
-        <v>3.0452127456665</v>
+        <v>3.04521298408508</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.99480962753296</v>
+        <v>2.99480938911438</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.5</v>
       </c>
       <c r="G711" t="n">
-        <v>2.94020581245422</v>
+        <v>2.94020557403564</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.9528067111969</v>
+        <v>2.95280647277832</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G715" t="n">
-        <v>2.80579590797424</v>
+        <v>2.80579614639282</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419634819031</v>
+        <v>2.81419658660889</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G717" t="n">
-        <v>2.93180513381958</v>
+        <v>2.931804895401</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860601425171</v>
+        <v>2.94860625267029</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>3.31823205947876</v>
+        <v>3.31823182106018</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G730" t="n">
-        <v>3.33083319664001</v>
+        <v>3.33083295822144</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>3.28883004188538</v>
+        <v>3.2888298034668</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.77639389038086</v>
+        <v>2.77639412879944</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>2.79319500923157</v>
+        <v>2.79319524765015</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.27622938156128</v>
+        <v>3.27622890472412</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.875</v>
       </c>
       <c r="G748" t="n">
-        <v>3.25522780418396</v>
+        <v>3.25522756576538</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781364440918</v>
+        <v>3.05781388282776</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.625</v>
       </c>
       <c r="G751" t="n">
-        <v>3.0452127456665</v>
+        <v>3.04521298408508</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060893058777</v>
+        <v>2.99060916900635</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>2.96960783004761</v>
+        <v>2.96960759162903</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.25</v>
       </c>
       <c r="G757" t="n">
-        <v>2.73019075393677</v>
+        <v>2.73019099235535</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>2.94020581245422</v>
+        <v>2.94020557403564</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.07461476325989</v>
+        <v>3.07461500167847</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G769" t="n">
-        <v>3.20062375068665</v>
+        <v>3.20062351226807</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.0788152217865</v>
+        <v>3.07881498336792</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00741052627563</v>
+        <v>3.00741028785706</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.06201410293579</v>
+        <v>3.06201386451721</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G775" t="n">
-        <v>3.07461476325989</v>
+        <v>3.07461500167847</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346254348755</v>
+        <v>3.76346302032471</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026437759399</v>
+        <v>3.78026413917542</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226753234863</v>
+        <v>3.82226705551147</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98607850074768</v>
+        <v>3.98607802391052</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.97347784042358</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G789" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548004150391</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486795425415</v>
+        <v>3.83486843109131</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.8726704120636</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.8810715675354</v>
+        <v>3.88107180595398</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.97347784042358</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88947200775146</v>
+        <v>3.88947176933289</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>3.91467332839966</v>
+        <v>3.91467380523682</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507692337036</v>
+        <v>3.96507716178894</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885896682739</v>
+        <v>3.70885944366455</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165496826172</v>
+        <v>3.64165449142456</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G809" t="n">
-        <v>3.62905406951904</v>
+        <v>3.62905383110046</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.5156455039978</v>
+        <v>3.51564598083496</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G811" t="n">
-        <v>3.45684146881104</v>
+        <v>3.45684123039246</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845608711243</v>
+        <v>3.65845584869385</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G815" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548004150391</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G818" t="n">
-        <v>3.96087718009949</v>
+        <v>3.96087670326233</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987560272217</v>
+        <v>3.93987536430359</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G823" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548004150391</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548004150391</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688497543335</v>
+        <v>4.08688545227051</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948682785034</v>
+        <v>4.09948587417603</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008457183838</v>
+        <v>4.07008409500122</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>4.72953081130981</v>
+        <v>4.72953033447266</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192226409912</v>
+        <v>4.61192178726196</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.49431467056274</v>
+        <v>4.49431419372559</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030836105347</v>
+        <v>4.41030883789062</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866505622864</v>
+        <v>3.78866481781006</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.97347784042358</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.8726704120636</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>4.13632297515869</v>
+        <v>4.13632345199585</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>3.99369144439697</v>
+        <v>3.99369168281555</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487156867981</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G853" t="n">
-        <v>3.88131499290466</v>
+        <v>3.88131475448608</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71274995803833</v>
+        <v>3.71275043487549</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.73436141014099</v>
+        <v>3.73436093330383</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868298530579</v>
+        <v>3.73868322372437</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157054901123</v>
+        <v>3.91157031059265</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>3.50096368789673</v>
+        <v>3.50096344947815</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G868" t="n">
-        <v>3.41019773483276</v>
+        <v>3.41019749641418</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G871" t="n">
-        <v>3.48367500305176</v>
+        <v>3.48367476463318</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G873" t="n">
-        <v>3.48367500305176</v>
+        <v>3.48367476463318</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.40155291557312</v>
+        <v>3.4015531539917</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>3.4145200252533</v>
+        <v>3.41451978683472</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163293838501</v>
+        <v>3.24163269996643</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G892" t="n">
-        <v>3.28917670249939</v>
+        <v>3.28917694091797</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.17680025100708</v>
+        <v>3.17680048942566</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756572723389</v>
+        <v>3.26756596565247</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>3.27621030807495</v>
+        <v>3.27621006965637</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349899291992</v>
+        <v>3.29349875450134</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>3.20273327827454</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>3.18112230300903</v>
+        <v>3.18112254142761</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G908" t="n">
-        <v>3.24595522880554</v>
+        <v>3.24595499038696</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G909" t="n">
-        <v>3.24595522880554</v>
+        <v>3.24595499038696</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.24595522880554</v>
+        <v>3.24595499038696</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.41884183883667</v>
+        <v>3.41884207725525</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G917" t="n">
-        <v>3.6479172706604</v>
+        <v>3.64791750907898</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.44477486610413</v>
+        <v>3.44477510452271</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G921" t="n">
-        <v>3.35833168029785</v>
+        <v>3.35833144187927</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G922" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444047927856</v>
+        <v>3.57444095611572</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.57011842727661</v>
+        <v>3.57011818885803</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>3.8726704120636</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487156867981</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241533279419</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.61766219139099</v>
+        <v>3.61766242980957</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>3.61766219139099</v>
+        <v>3.61766242980957</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G957" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638631820679</v>
+        <v>3.46638607978821</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G963" t="n">
-        <v>3.57011842727661</v>
+        <v>3.57011818885803</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054951667786</v>
+        <v>3.79054927825928</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402654647827</v>
+        <v>3.86402606964111</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85538244247437</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="n">
-        <v>3.99801421165466</v>
+        <v>3.9980137348175</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92453670501709</v>
+        <v>3.92453646659851</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343636512756</v>
+        <v>3.96343660354614</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724778175354</v>
+        <v>3.9072482585907</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.80351567268372</v>
+        <v>3.80351591110229</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.7862274646759</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.85538244247437</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241533279419</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>3.81216049194336</v>
+        <v>3.81216025352478</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893830299377</v>
+        <v>3.76893854141235</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.9504702091217</v>
+        <v>3.95046997070312</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>4.06284618377686</v>
+        <v>4.06284666061401</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699317932129</v>
+        <v>3.87699270248413</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="n">
-        <v>4.04555797576904</v>
+        <v>4.04555702209473</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445692062378</v>
+        <v>4.08445739746094</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="n">
-        <v>4.32217741012573</v>
+        <v>4.32217693328857</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319772720337</v>
+        <v>4.44319820404053</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.50370836257935</v>
+        <v>4.5037088394165</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337326049805</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337326049805</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.82354927062988</v>
+        <v>4.82354974746704</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.88405990600586</v>
+        <v>4.88406038284302</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.61608552932739</v>
+        <v>4.61608505249023</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.78897190093994</v>
+        <v>4.7889723777771</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.90999269485474</v>
+        <v>4.90999317169189</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.88405990600586</v>
+        <v>4.88406038284302</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340805053711</v>
+        <v>5.65340757369995</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.25576686859131</v>
+        <v>5.25576734542847</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.56421899795532</v>
+        <v>4.56421947479248</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.5901517868042</v>
+        <v>4.59015226364136</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48642015457153</v>
+        <v>4.48641967773438</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.41726541519165</v>
+        <v>4.41726493835449</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.61608552932739</v>
+        <v>4.61608505249023</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428114891052</v>
+        <v>3.8942813873291</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970425605774</v>
+        <v>3.85970449447632</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7862274646759</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.8251268863678</v>
+        <v>3.82512712478638</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.68249487876892</v>
+        <v>3.68249464035034</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15086722373962</v>
+        <v>3.15086698532104</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.38151979446411</v>
+        <v>2.38151955604553</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.9363352060318</v>
+        <v>1.93633532524109</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.18702149391174</v>
+        <v>2.18702173233032</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.46364092826843</v>
+        <v>2.46364068984985</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.65381669998169</v>
+        <v>2.65381646156311</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790082931519</v>
+        <v>3.13790059089661</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.01255750656128</v>
+        <v>3.0125572681427</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.82670402526855</v>
+        <v>2.82670378684998</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187133789062</v>
+        <v>2.76187109947205</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.90450286865234</v>
+        <v>2.90450310707092</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399271011353</v>
+        <v>2.84399247169495</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.76619338989258</v>
+        <v>2.76619362831116</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.90882515907288</v>
+        <v>2.90882539749146</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746926307678</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232954025269</v>
+        <v>3.05232930183411</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.11076903343201</v>
+        <v>3.11076879501343</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.06132030487061</v>
+        <v>3.06132006645203</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.8994882106781</v>
+        <v>2.89948797225952</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.81857228279114</v>
+        <v>2.81857204437256</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169353485107</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.51289010047913</v>
+        <v>2.51288986206055</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.17574000358582</v>
+        <v>2.17574024200439</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.38252520561218</v>
+        <v>2.38252544403076</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.3690390586853</v>
+        <v>2.36903953552246</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.38702058792114</v>
+        <v>2.38702082633972</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.37802982330322</v>
+        <v>2.3780300617218</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.35555338859558</v>
+        <v>2.355553150177</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.40050649642944</v>
+        <v>2.40050673484802</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.44995498657227</v>
+        <v>2.44995522499084</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.44995498657227</v>
+        <v>2.44995522499084</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.38252520561218</v>
+        <v>2.38252544403076</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.22518849372864</v>
+        <v>2.22518873214722</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.17574000358582</v>
+        <v>2.17574024200439</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.10381484031677</v>
+        <v>2.10381460189819</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.19821643829346</v>
+        <v>2.19821667671204</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.17574000358582</v>
+        <v>2.17574024200439</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.09032869338989</v>
+        <v>2.09032893180847</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.00941252708435</v>
+        <v>2.00941276550293</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.91051542758942</v>
+        <v>1.91051554679871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.81161832809448</v>
+        <v>1.81161844730377</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620689868927</v>
+        <v>1.72620701789856</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.74418830871582</v>
+        <v>1.74418842792511</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.96895492076874</v>
+        <v>1.96895480155945</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.38252520561218</v>
+        <v>2.38252544403076</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.42747855186462</v>
+        <v>2.4274787902832</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.58031964302063</v>
+        <v>2.58031988143921</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.40500164031982</v>
+        <v>2.40500211715698</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.44545984268188</v>
+        <v>2.44546008110046</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408595085144</v>
+        <v>2.32408618927002</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.279132604599</v>
+        <v>2.27913284301758</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.51289010047913</v>
+        <v>2.51288986206055</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233859062195</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.58031964302063</v>
+        <v>2.58031988143921</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99389028549194</v>
+        <v>2.99389004707336</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.95343232154846</v>
+        <v>2.95343208312988</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746926307678</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.8994882106781</v>
+        <v>2.89948797225952</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.01636695861816</v>
+        <v>3.01636672019958</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.15122699737549</v>
+        <v>3.15122675895691</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.18718957901001</v>
+        <v>3.18718934059143</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.15122699737549</v>
+        <v>3.15122675895691</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.5063579082489</v>
+        <v>3.50635814666748</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.22315216064453</v>
+        <v>3.22315192222595</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.01636695861816</v>
+        <v>3.01636672019958</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.375</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.18718957901001</v>
+        <v>3.18718934059143</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.15122699737549</v>
+        <v>3.15122675895691</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.32654452323914</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.3670027256012</v>
+        <v>3.36700248718262</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.35351657867432</v>
+        <v>3.3535168170929</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.20517086982727</v>
+        <v>3.20517063140869</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.375</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.06132030487061</v>
+        <v>3.06132006645203</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.8994882106781</v>
+        <v>2.89948797225952</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.8725163936615</v>
+        <v>2.87251615524292</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.375</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.11076903343201</v>
+        <v>3.11076879501343</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.20517086982727</v>
+        <v>3.20517063140869</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.31755399703979</v>
+        <v>3.31755423545837</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.22315216064453</v>
+        <v>3.22315192222595</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.20517086982727</v>
+        <v>3.20517063140869</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.23214292526245</v>
+        <v>3.23214268684387</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.11076903343201</v>
+        <v>3.11076879501343</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.27709627151489</v>
+        <v>3.27709603309631</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95343232154846</v>
+        <v>2.95343208312988</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.97141361236572</v>
+        <v>2.97141337394714</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.04333901405334</v>
+        <v>3.04333877563477</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.01636695861816</v>
+        <v>3.01636672019958</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.95343232154846</v>
+        <v>2.95343208312988</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.375</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.11076903343201</v>
+        <v>3.11076879501343</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.04783415794373</v>
+        <v>3.0478343963623</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.04783415794373</v>
+        <v>3.0478343963623</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.375</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.81857228279114</v>
+        <v>2.81857204437256</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.58031964302063</v>
+        <v>2.58031988143921</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.375</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.93095541000366</v>
+        <v>2.93095564842224</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.375</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.03434824943542</v>
+        <v>3.03434801101685</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746926307678</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.83655381202698</v>
+        <v>2.83655333518982</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.78260970115662</v>
+        <v>2.78260946273804</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.89499306678772</v>
+        <v>2.89499282836914</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.99389028549194</v>
+        <v>2.99389004707336</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150668144226</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233859062195</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.40050649642944</v>
+        <v>2.40050673484802</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169353485107</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.81857228279114</v>
+        <v>2.81857204437256</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.81857228279114</v>
+        <v>2.81857204437256</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.82756304740906</v>
+        <v>2.82756280899048</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.8590304851532</v>
+        <v>2.85903024673462</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.8725163936615</v>
+        <v>2.87251615524292</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.78260970115662</v>
+        <v>2.78260946273804</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.78260970115662</v>
+        <v>2.78260946273804</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.86352562904358</v>
+        <v>2.863525390625</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967482566833</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325428009033</v>
+        <v>2.64325451850891</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967482566833</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.7601330280304</v>
+        <v>2.76013278961182</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967482566833</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.68820762634277</v>
+        <v>2.68820786476135</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.72417044639587</v>
+        <v>2.72417020797729</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169353485107</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.42747855186462</v>
+        <v>2.4274787902832</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.42747855186462</v>
+        <v>2.4274787902832</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.45894575119019</v>
+        <v>2.45894598960876</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.45894575119019</v>
+        <v>2.45894598960876</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.45894575119019</v>
+        <v>2.45894598960876</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.40500164031982</v>
+        <v>2.40500211715698</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.38252520561218</v>
+        <v>2.38252544403076</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.40500164031982</v>
+        <v>2.40500211715698</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.38252520561218</v>
+        <v>2.38252544403076</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.40500164031982</v>
+        <v>2.40500211715698</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36004853248596</v>
+        <v>2.36004877090454</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.2521607875824</v>
+        <v>2.25216102600098</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.27014207839966</v>
+        <v>2.27014231681824</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.21170258522034</v>
+        <v>2.21170282363892</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.21170258522034</v>
+        <v>2.21170282363892</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.27014207839966</v>
+        <v>2.27014231681824</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.1802351474762</v>
+        <v>2.18023538589478</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.17574000358582</v>
+        <v>2.17574024200439</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143159389496</v>
+        <v>1.99143135547638</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794556617737</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501104831696</v>
+        <v>1.91501092910767</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.01840329170227</v>
+        <v>2.01840353012085</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.986936211586</v>
+        <v>1.98693609237671</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647824764252</v>
+        <v>1.94647812843323</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.9644593000412</v>
+        <v>1.96445953845978</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.91051542758942</v>
+        <v>1.91051554679871</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702939987183</v>
+        <v>1.89702951908112</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.85207617282867</v>
+        <v>1.85207629203796</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84308552742004</v>
+        <v>1.84308564662933</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.79453611373901</v>
+        <v>1.79453599452972</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.73699581623077</v>
+        <v>1.73699569702148</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.69563889503479</v>
+        <v>1.6956387758255</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.68305170536041</v>
+        <v>1.6830518245697</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.65068542957306</v>
+        <v>1.65068531036377</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.65068542957306</v>
+        <v>1.65068531036377</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.66686868667603</v>
+        <v>1.66686856746674</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.77116024494171</v>
+        <v>1.771160364151</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794556617737</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>2.375</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.13528203964233</v>
+        <v>2.13528227806091</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.19821643829346</v>
+        <v>2.19821667671204</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.61628246307373</v>
+        <v>2.61628270149231</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2048" t="n">
-        <v>2.42747855186462</v>
+        <v>2.4274787902832</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233859062195</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2065" t="n">
-        <v>2.58031964302063</v>
+        <v>2.58031988143921</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.58031964302063</v>
+        <v>2.58031988143921</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233859062195</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233859062195</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.87701177597046</v>
+        <v>2.87701153755188</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2088" t="n">
-        <v>2.97141361236572</v>
+        <v>2.97141337394714</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241379737854</v>
+        <v>3.45241403579712</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="n">
-        <v>3.52883434295654</v>
+        <v>3.52883458137512</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.69516181945801</v>
+        <v>3.69516205787659</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.32654452323914</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.37599325180054</v>
+        <v>3.37599349021912</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.32204937934875</v>
+        <v>3.32204914093018</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.47489070892334</v>
+        <v>3.47489047050476</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>7.44000005722046</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>29411</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>7.48999977111816</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>7.48999977111816</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853298664093</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612635612488</v>
+        <v>1.80612623691559</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139414787292</v>
+        <v>1.63139402866364</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71371960639954</v>
+        <v>1.71371972560883</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754958629608</v>
+        <v>1.56754970550537</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47514319419861</v>
+        <v>1.47514307498932</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314015865326</v>
+        <v>1.43314003944397</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204354286194</v>
+        <v>1.19204330444336</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G32" t="n">
-        <v>1.39365756511688</v>
+        <v>1.3936573266983</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.4196994304657</v>
+        <v>1.41969931125641</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346293926239</v>
+        <v>1.47346305847168</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G39" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742131233215</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G40" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742131233215</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G41" t="n">
-        <v>1.43061983585358</v>
+        <v>1.43061995506287</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42893970012665</v>
+        <v>1.42893981933594</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254217624664</v>
+        <v>1.46254229545593</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G51" t="n">
-        <v>1.46506237983704</v>
+        <v>1.46506226062775</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586956977844</v>
+        <v>1.56586945056915</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491580963135</v>
+        <v>1.65491569042206</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>1.60283207893372</v>
+        <v>1.60283195972443</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G58" t="n">
-        <v>1.58183073997498</v>
+        <v>1.5818305015564</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742131233215</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830895900726</v>
+        <v>1.55830883979797</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.60787236690521</v>
+        <v>1.6078724861145</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646743297577</v>
+        <v>1.53646731376648</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G83" t="n">
-        <v>1.55074834823608</v>
+        <v>1.55074822902679</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G89" t="n">
-        <v>1.41213881969452</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.42809998989105</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410861968994</v>
+        <v>1.55410873889923</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G96" t="n">
-        <v>1.51882612705231</v>
+        <v>1.5188262462616</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47514319419861</v>
+        <v>1.47514307498932</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.48270380496979</v>
+        <v>1.48270356655121</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51798605918884</v>
+        <v>1.51798617839813</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G106" t="n">
-        <v>1.52470660209656</v>
+        <v>1.52470672130585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G114" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457820892334</v>
+        <v>1.40457832813263</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577405452728</v>
+        <v>1.34577393531799</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205800533295</v>
+        <v>1.40205812454224</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G120" t="n">
-        <v>1.42809998989105</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G127" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493374824524</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G132" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.5</v>
       </c>
       <c r="G133" t="n">
-        <v>1.26008808612823</v>
+        <v>1.26008820533752</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G134" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G135" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>1.33485329151154</v>
+        <v>1.33485317230225</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G139" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493374824524</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401346206665</v>
+        <v>1.33401334285736</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G143" t="n">
-        <v>1.36089503765106</v>
+        <v>1.36089515686035</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769639492035</v>
+        <v>1.37769627571106</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.36089503765106</v>
+        <v>1.36089515686035</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357651233673</v>
+        <v>1.38357663154602</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G153" t="n">
-        <v>1.33737361431122</v>
+        <v>1.33737337589264</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3138519525528</v>
+        <v>1.31385183334351</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125093460083</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G162" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.50100004673004</v>
       </c>
       <c r="G163" t="n">
-        <v>1.26092827320099</v>
+        <v>1.2609281539917</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680850982666</v>
+        <v>1.26680862903595</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545127391815</v>
+        <v>1.30545139312744</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29201030731201</v>
+        <v>1.29201018810272</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813274860382</v>
+        <v>1.3281329870224</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713129043579</v>
+        <v>1.30713140964508</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29621064662933</v>
+        <v>1.29621052742004</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G181" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677539348602</v>
+        <v>1.36677551269531</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33989357948303</v>
+        <v>1.33989369869232</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477259635925</v>
+        <v>1.32477271556854</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149302005768</v>
+        <v>1.33149313926697</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G192" t="n">
-        <v>1.369295835495</v>
+        <v>1.36929559707642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.37685632705688</v>
+        <v>1.3768562078476</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G194" t="n">
-        <v>1.36845564842224</v>
+        <v>1.36845552921295</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G197" t="n">
-        <v>1.39365756511688</v>
+        <v>1.3936573266983</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105654716492</v>
+        <v>1.38105666637421</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881142616272</v>
+        <v>1.30881154537201</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31637215614319</v>
+        <v>1.3163720369339</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125093460083</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.26008808612823</v>
+        <v>1.26008820533752</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G218" t="n">
-        <v>1.14247989654541</v>
+        <v>1.14247977733612</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G219" t="n">
-        <v>1.2222855091095</v>
+        <v>1.22228538990021</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G227" t="n">
-        <v>1.12147843837738</v>
+        <v>1.12147831916809</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367586135864</v>
+        <v>1.08367562294006</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G229" t="n">
-        <v>1.09543645381927</v>
+        <v>1.09543657302856</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G232" t="n">
-        <v>1.09795677661896</v>
+        <v>1.09795689582825</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.0635142326355</v>
+        <v>1.06351435184479</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.03915250301361</v>
+        <v>1.0391526222229</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939470767975</v>
+        <v>1.06939482688904</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G241" t="n">
-        <v>1.11811816692352</v>
+        <v>1.11811804771423</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G245" t="n">
-        <v>1.14163982868195</v>
+        <v>1.14163970947266</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584004878998</v>
+        <v>1.14584016799927</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G248" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G250" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364286422729</v>
+        <v>1.18364274501801</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3432537317276</v>
+        <v>1.34325385093689</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G264" t="n">
-        <v>1.31469202041626</v>
+        <v>1.31469190120697</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377113819122</v>
+        <v>1.30377125740051</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G269" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832737445831</v>
+        <v>1.24832713603973</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G284" t="n">
-        <v>1.18784296512604</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104196548462</v>
+        <v>1.17104184627533</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424072742462</v>
+        <v>1.15424048900604</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236632347107</v>
+        <v>1.23236620426178</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G304" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900605201721</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G306" t="n">
-        <v>1.22396564483643</v>
+        <v>1.22396552562714</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380401611328</v>
+        <v>1.20380413532257</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G311" t="n">
-        <v>1.18784296512604</v>
+        <v>1.18784308433533</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.45700001716614</v>
       </c>
       <c r="G320" t="n">
-        <v>1.22396564483643</v>
+        <v>1.22396552562714</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.210524559021</v>
+        <v>1.21052467823029</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252759456635</v>
+        <v>1.25252771377563</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688908576965</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688908576965</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G327" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.2659684419632</v>
+        <v>1.26596856117249</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.25756776332855</v>
+        <v>1.25756788253784</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320615291595</v>
+        <v>1.23320627212524</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908662796021</v>
+        <v>1.23908650875092</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G334" t="n">
-        <v>1.23068618774414</v>
+        <v>1.23068606853485</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G337" t="n">
-        <v>1.22564566135406</v>
+        <v>1.22564554214478</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488616943359</v>
+        <v>1.23488628864288</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.2248055934906</v>
+        <v>1.22480547428131</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496686458588</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496686458588</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664723873138</v>
+        <v>1.24664700031281</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G350" t="n">
-        <v>1.2970507144928</v>
+        <v>1.29705059528351</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G354" t="n">
-        <v>1.36761558055878</v>
+        <v>1.36761546134949</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890694141388</v>
+        <v>1.52890682220459</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.75100004673004</v>
       </c>
       <c r="G356" t="n">
-        <v>1.470942735672</v>
+        <v>1.47094285488129</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194419384003</v>
+        <v>1.49194431304932</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G360" t="n">
-        <v>1.46002221107483</v>
+        <v>1.46002209186554</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G361" t="n">
-        <v>1.46506237983704</v>
+        <v>1.46506226062775</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G370" t="n">
-        <v>1.36845564842224</v>
+        <v>1.36845552921295</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349605560303</v>
+        <v>1.37349617481232</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.3432537317276</v>
+        <v>1.34325385093689</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005508899689</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G382" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G383" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493374824524</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>1.44070088863373</v>
+        <v>1.44070065021515</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221927642822</v>
+        <v>1.42221939563751</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G392" t="n">
-        <v>1.41381871700287</v>
+        <v>1.41381883621216</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G393" t="n">
-        <v>1.41045868396759</v>
+        <v>1.4104585647583</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G394" t="n">
-        <v>1.4440610408783</v>
+        <v>1.44406092166901</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.42809998989105</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>1.41213881969452</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.42809998989105</v>
+        <v>1.42809987068176</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102366924286</v>
+        <v>1.48102355003357</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918214321136</v>
+        <v>1.45918202400208</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G409" t="n">
-        <v>1.52554655075073</v>
+        <v>1.52554666996002</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.5331072807312</v>
+        <v>1.53310716152191</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G412" t="n">
-        <v>1.48774397373199</v>
+        <v>1.48774385452271</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742131233215</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G415" t="n">
-        <v>1.43986070156097</v>
+        <v>1.43986058235168</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G420" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G422" t="n">
-        <v>1.44070088863373</v>
+        <v>1.44070065021515</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238090515137</v>
+        <v>1.44238078594208</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.4415408372879</v>
+        <v>1.44154071807861</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842265129089</v>
+        <v>1.46842277050018</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254217624664</v>
+        <v>1.46254229545593</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330142974854</v>
+        <v>1.45330166816711</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531904697418</v>
+        <v>1.70531928539276</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.80108594894409</v>
+        <v>1.80108606815338</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G446" t="n">
-        <v>1.78428483009338</v>
+        <v>1.78428494930267</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717527389526</v>
+        <v>1.93717551231384</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429953098297</v>
+        <v>1.99429965019226</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.94053554534912</v>
+        <v>1.94053566455841</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229637622833</v>
+        <v>1.95229625701904</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452715396881</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420389652252</v>
+        <v>1.77420401573181</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165069580078</v>
+        <v>1.87165081501007</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669134140015</v>
+        <v>1.87669110298157</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.86493027210236</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173162937164</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>1.95733690261841</v>
+        <v>1.95733666419983</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.00438022613525</v>
+        <v>2.00437998771667</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581803798676</v>
+        <v>1.97581791877747</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061635971069</v>
+        <v>1.95061647891998</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>1.95733690261841</v>
+        <v>1.95733666419983</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341176509857</v>
+        <v>1.88341164588928</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308898448944</v>
+        <v>1.84308874607086</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316956043243</v>
+        <v>1.85316967964172</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879324913025</v>
+        <v>1.61879336833954</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.64651525020599</v>
+        <v>1.64651501178741</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G483" t="n">
-        <v>1.6347541809082</v>
+        <v>1.63475430011749</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763016223907</v>
+        <v>1.57763028144836</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G488" t="n">
-        <v>1.57595014572144</v>
+        <v>1.57595026493073</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326855182648</v>
+        <v>1.55326867103577</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.61291265487671</v>
+        <v>1.612912774086</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811457157135</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531904697418</v>
+        <v>1.70531928539276</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507708072662</v>
+        <v>1.67507696151733</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299358844757</v>
+        <v>1.62299346923828</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451221466064</v>
+        <v>1.60451209545135</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.579310297966</v>
+        <v>1.57931041717529</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811457157135</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887382507324</v>
+        <v>1.62887394428253</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>1.63643443584442</v>
+        <v>1.63643431663513</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62467348575592</v>
+        <v>1.62467360496521</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267068862915</v>
+        <v>1.58267045021057</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090973854065</v>
+        <v>1.57090985774994</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535228252411</v>
+        <v>1.60535216331482</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G516" t="n">
-        <v>1.61627292633057</v>
+        <v>1.61627304553986</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>1.66331624984741</v>
+        <v>1.6633163690567</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323567390442</v>
+        <v>1.65323555469513</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171680927277</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827584266663</v>
+        <v>1.65827596187592</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851804733276</v>
+        <v>1.68851792812347</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G530" t="n">
-        <v>1.86493027210236</v>
+        <v>1.86493039131165</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G531" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433264732361</v>
+        <v>1.89433240890503</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213510513306</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.75992298126221</v>
+        <v>1.75992321968079</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G543" t="n">
-        <v>1.77252376079559</v>
+        <v>1.7725236415863</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.72632074356079</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72632074356079</v>
+        <v>1.7263206243515</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171680927277</v>
+        <v>1.67171692848206</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011748790741</v>
+        <v>1.68011736869812</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052084445953</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G564" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452715396881</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173162937164</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173162937164</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872725486755</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.125</v>
       </c>
       <c r="G572" t="n">
-        <v>1.78512477874756</v>
+        <v>1.78512465953827</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>1.78092443943024</v>
+        <v>1.78092455863953</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>1.78092443943024</v>
+        <v>1.78092455863953</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872725486755</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192589759827</v>
+        <v>1.80192613601685</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G582" t="n">
-        <v>1.81452691555023</v>
+        <v>1.81452715396881</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812903404236</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113352775574</v>
+        <v>1.91113388538361</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173162937164</v>
+        <v>1.88173127174377</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.8691303730011</v>
+        <v>1.86913049221039</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853298664093</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373466491699</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.9237345457077</v>
+        <v>1.92373466491699</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.9825382232666</v>
+        <v>1.98253858089447</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993780136108</v>
+        <v>1.96993768215179</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>1.97833812236786</v>
+        <v>1.97833800315857</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>2.00774073600769</v>
+        <v>2.00774049758911</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.0161406993866</v>
+        <v>2.01614093780518</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093925952911</v>
+        <v>1.99093902111053</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.2639582157135</v>
+        <v>2.26395797729492</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214944839478</v>
+        <v>2.14214968681335</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>2.2135546207428</v>
+        <v>2.21355485916138</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316584587097</v>
+        <v>2.37316560745239</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41096830368042</v>
+        <v>2.410968542099</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177549362183</v>
+        <v>2.51177573204041</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>2.31436204910278</v>
+        <v>2.3143618106842</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41936922073364</v>
+        <v>2.41936945915222</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>2.4949746131897</v>
+        <v>2.49497437477112</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>2.54537796974182</v>
+        <v>2.54537773132324</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>2.62938404083252</v>
+        <v>2.62938380241394</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.74699211120605</v>
+        <v>2.74699234962463</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099770545959</v>
+        <v>2.83099794387817</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>2.8393988609314</v>
+        <v>2.83939862251282</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059434890747</v>
+        <v>2.78059387207031</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519792556763</v>
+        <v>2.83519816398621</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661791801453</v>
+        <v>3.11661767959595</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.15442037582397</v>
+        <v>3.15442085266113</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10821723937988</v>
+        <v>3.10821747779846</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081789970398</v>
+        <v>3.12081813812256</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.23422574996948</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.23422574996948</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803743362427</v>
+        <v>3.39803767204285</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703609466553</v>
+        <v>3.37703585624695</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G642" t="n">
-        <v>3.40223813056946</v>
+        <v>3.4022376537323</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>3.5156455039978</v>
+        <v>3.51564574241638</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>3.5492479801178</v>
+        <v>3.54924821853638</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446459770203</v>
+        <v>3.78446483612061</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887426376343</v>
+        <v>3.91887402534485</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927785873413</v>
+        <v>3.96927690505981</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887426376343</v>
+        <v>3.91887402534485</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G654" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226705551147</v>
+        <v>3.82226777076721</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746932983398</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545135498047</v>
+        <v>3.59545111656189</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.79706525802612</v>
+        <v>3.79706597328186</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.4775128364563</v>
+        <v>4.47751235961914</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G666" t="n">
-        <v>4.59512090682983</v>
+        <v>4.59512138366699</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.75</v>
       </c>
       <c r="G669" t="n">
-        <v>4.83033800125122</v>
+        <v>4.83033752441406</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>4.79673528671265</v>
+        <v>4.7967357635498</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.82193660736084</v>
+        <v>4.821937084198</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553932189941</v>
+        <v>4.85553979873657</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074111938477</v>
+        <v>4.88074159622192</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>4.76313304901123</v>
+        <v>4.76313257217407</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.75</v>
       </c>
       <c r="G679" t="n">
-        <v>4.83033800125122</v>
+        <v>4.83033752441406</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.70432901382446</v>
+        <v>4.7043285369873</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>4.67912673950195</v>
+        <v>4.67912721633911</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G686" t="n">
-        <v>4.56151914596558</v>
+        <v>4.56151866912842</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44391107559204</v>
+        <v>4.44391059875488</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271511077881</v>
+        <v>4.50271463394165</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350700378418</v>
+        <v>4.39350748062134</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.33470344543457</v>
+        <v>4.33470249176025</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749897003174</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788679122925</v>
+        <v>4.10788774490356</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95667624473572</v>
+        <v>3.95667600631714</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.7382607460022</v>
+        <v>3.73826098442078</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.99480938911438</v>
+        <v>2.9948091506958</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.5</v>
       </c>
       <c r="G711" t="n">
-        <v>2.94020533561707</v>
+        <v>2.94020581245422</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.9528067111969</v>
+        <v>2.95280647277832</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G718" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G721" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.1418194770813</v>
+        <v>3.14181971549988</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G732" t="n">
-        <v>3.23422574996948</v>
+        <v>3.23422598838806</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081789970398</v>
+        <v>3.12081813812256</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>2.8393988609314</v>
+        <v>2.83939862251282</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G742" t="n">
-        <v>2.88140177726746</v>
+        <v>2.8814013004303</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.27622938156128</v>
+        <v>3.2762291431427</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781388282776</v>
+        <v>3.05781364440918</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>2.96960783004761</v>
+        <v>2.96960759162903</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418200492859</v>
+        <v>2.60418224334717</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.67978715896606</v>
+        <v>2.67978739738464</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G762" t="n">
-        <v>2.54957818984985</v>
+        <v>2.54957842826843</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>2.94020533561707</v>
+        <v>2.94020581245422</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400243759155</v>
+        <v>2.89400219917297</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G769" t="n">
-        <v>3.20062375068665</v>
+        <v>3.20062351226807</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>3.20482420921326</v>
+        <v>3.20482397079468</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.0788152217865</v>
+        <v>3.07881498336792</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.22582530975342</v>
+        <v>3.225825548172</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G778" t="n">
-        <v>3.47784280776978</v>
+        <v>3.47784328460693</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346325874329</v>
+        <v>3.76346254348755</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026437759399</v>
+        <v>3.78026461601257</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>3.7340612411499</v>
+        <v>3.73406147956848</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226705551147</v>
+        <v>3.82226777076721</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98607850074768</v>
+        <v>3.98607873916626</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.97347831726074</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G789" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486843109131</v>
+        <v>3.83486819267273</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G793" t="n">
-        <v>3.84326839447021</v>
+        <v>3.84326815605164</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.87267088890076</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.88107109069824</v>
+        <v>3.88107132911682</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.97347831726074</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88947200775146</v>
+        <v>3.88947176933289</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>3.91467380523682</v>
+        <v>3.91467332839966</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.9650764465332</v>
+        <v>3.96507716178894</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427021026611</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126595497131</v>
+        <v>3.80126547813416</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885968208313</v>
+        <v>3.70885896682739</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165449142456</v>
+        <v>3.64165496826172</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G809" t="n">
-        <v>3.62905383110046</v>
+        <v>3.62905430793762</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.5156455039978</v>
+        <v>3.51564574241638</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G811" t="n">
-        <v>3.45684170722961</v>
+        <v>3.45684146881104</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G815" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208772659302</v>
+        <v>4.11208724975586</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>4.04068231582642</v>
+        <v>4.04068279266357</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G818" t="n">
-        <v>3.96087670326233</v>
+        <v>3.96087718009949</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987560272217</v>
+        <v>3.93987536430359</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427021026611</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G823" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228139877319</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688545227051</v>
+        <v>4.08688592910767</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948682785034</v>
+        <v>4.09948635101318</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008457183838</v>
+        <v>4.07008409500122</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148950576782</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631687164307</v>
+        <v>4.53631734848022</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>4.72953033447266</v>
+        <v>4.72953081130981</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.57831954956055</v>
+        <v>4.57832002639771</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.49431419372559</v>
+        <v>4.49431467056274</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950164794922</v>
+        <v>4.30950117111206</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>4.25909757614136</v>
+        <v>4.25909805297852</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749897003174</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G840" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228139877319</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746909141541</v>
+        <v>3.84746932983398</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866529464722</v>
+        <v>3.78866481781006</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.97347831726074</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.87267088890076</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>4.13632297515869</v>
+        <v>4.13632345199585</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>3.99369144439697</v>
+        <v>3.99369168281555</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G852" t="n">
-        <v>4.093101978302</v>
+        <v>4.09310245513916</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G853" t="n">
-        <v>3.88131499290466</v>
+        <v>3.88131475448608</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80783796310425</v>
+        <v>3.80783820152283</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G858" t="n">
-        <v>3.71707224845886</v>
+        <v>3.71707248687744</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157054901123</v>
+        <v>3.91157031059265</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.83377075195312</v>
+        <v>3.83377122879028</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385029792786</v>
+        <v>3.67385077476501</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G863" t="n">
-        <v>3.62630653381348</v>
+        <v>3.62630677223206</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.71707224845886</v>
+        <v>3.71707248687744</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359545707703</v>
+        <v>3.64359521865845</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>3.50096368789673</v>
+        <v>3.50096344947815</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.125</v>
       </c>
       <c r="G867" t="n">
-        <v>3.56579613685608</v>
+        <v>3.5657958984375</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G868" t="n">
-        <v>3.41019773483276</v>
+        <v>3.41019749641418</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G870" t="n">
-        <v>3.55715131759644</v>
+        <v>3.55715155601501</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503042221069</v>
+        <v>3.47503018379211</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.4015531539917</v>
+        <v>3.40155363082886</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>3.4145200252533</v>
+        <v>3.41451978683472</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>3.31510972976685</v>
+        <v>3.31510996818542</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646562576294</v>
+        <v>3.30646538734436</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137738227844</v>
+        <v>3.21137762069702</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.22434401512146</v>
+        <v>3.22434425354004</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646562576294</v>
+        <v>3.30646538734436</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G892" t="n">
-        <v>3.28917670249939</v>
+        <v>3.28917694091797</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.17680025100708</v>
+        <v>3.1768000125885</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756572723389</v>
+        <v>3.26756596565247</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>3.27621030807495</v>
+        <v>3.27621006965637</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349899291992</v>
+        <v>3.29349875450134</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>3.18112230300903</v>
+        <v>3.18112254142761</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G905" t="n">
-        <v>3.22866630554199</v>
+        <v>3.22866606712341</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G908" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G909" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68681716918945</v>
+        <v>3.68681693077087</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G917" t="n">
-        <v>3.64791703224182</v>
+        <v>3.6479172706604</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385029792786</v>
+        <v>3.67385077476501</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G921" t="n">
-        <v>3.35833144187927</v>
+        <v>3.35833168029785</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G925" t="n">
-        <v>3.66520571708679</v>
+        <v>3.66520595550537</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444071769714</v>
+        <v>3.57444047927856</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>3.55282974243164</v>
+        <v>3.55282926559448</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>3.58308506011963</v>
+        <v>3.58308482170105</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>3.60469579696655</v>
+        <v>3.60469555854797</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.55715131759644</v>
+        <v>3.55715155601501</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960755348206</v>
+        <v>3.50960779190063</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>3.87267088890076</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241580963135</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G947" t="n">
-        <v>3.62630653381348</v>
+        <v>3.62630677223206</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49231886863708</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G957" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49231886863708</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49231886863708</v>
+        <v>3.49231934547424</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638655662537</v>
+        <v>3.46638631820679</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054951667786</v>
+        <v>3.79054975509644</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85538196563721</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92453670501709</v>
+        <v>3.92453646659851</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343636512756</v>
+        <v>3.96343660354614</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.9072482585907</v>
+        <v>3.90724778175354</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="n">
-        <v>3.78190493583679</v>
+        <v>3.78190445899963</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.85538196563721</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241580963135</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>3.81216025352478</v>
+        <v>3.81216049194336</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893830299377</v>
+        <v>3.76893854141235</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G983" t="n">
-        <v>3.80783796310425</v>
+        <v>3.80783820152283</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.9504702091217</v>
+        <v>3.95046997070312</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="n">
-        <v>4.04555797576904</v>
+        <v>4.04555749893188</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G992" t="n">
-        <v>4.093101978302</v>
+        <v>4.09310245513916</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445739746094</v>
+        <v>4.08445692062378</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319820404053</v>
+        <v>4.44319772720337</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337421417236</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828525543213</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.68524026870728</v>
+        <v>4.68523979187012</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337421417236</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.75439500808716</v>
+        <v>4.75439453125</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.96185922622681</v>
+        <v>4.96185874938965</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.61608505249023</v>
+        <v>4.61608552932739</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659568786621</v>
+        <v>4.67659521102905</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.78897190093994</v>
+        <v>4.7889723777771</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84083795547485</v>
+        <v>4.84083843231201</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.28170108795166</v>
+        <v>5.28170013427734</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340757369995</v>
+        <v>5.65340709686279</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.28170108795166</v>
+        <v>5.28170013427734</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.25576686859131</v>
+        <v>5.25576734542847</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.99643707275391</v>
+        <v>4.99643754959106</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74575042724609</v>
+        <v>4.74574995040894</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846174240112</v>
+        <v>4.72846126556396</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.55557441711426</v>
+        <v>4.55557489395142</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828525543213</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.59015226364136</v>
+        <v>4.5901517868042</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48642015457153</v>
+        <v>4.48641967773438</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.52964115142822</v>
+        <v>4.52964162826538</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.41726541519165</v>
+        <v>4.41726493835449</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895498275757</v>
+        <v>4.27895545959473</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.61608505249023</v>
+        <v>4.61608552932739</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828525543213</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428162574768</v>
+        <v>3.89428186416626</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.8597047328949</v>
+        <v>3.85970401763916</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.8251268863678</v>
+        <v>3.82512664794922</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.66520571708679</v>
+        <v>3.66520595550537</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.6824951171875</v>
+        <v>3.68249487876892</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503042221069</v>
+        <v>3.47503018379211</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15086722373962</v>
+        <v>3.15086698532104</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085054397583</v>
+        <v>2.64085006713867</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.67110514640808</v>
+        <v>2.67110538482666</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287521362305</v>
+        <v>2.37287497520447</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.38152003288269</v>
+        <v>2.38151955604553</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.93633544445038</v>
+        <v>1.93633532524109</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.32533144950867</v>
+        <v>2.32533121109009</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.32533144950867</v>
+        <v>2.32533121109009</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.37719750404358</v>
+        <v>2.377197265625</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.4809296131134</v>
+        <v>2.48092937469482</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.65381693840027</v>
+        <v>2.65381669998169</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.82670378684998</v>
+        <v>2.8267035484314</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187133789062</v>
+        <v>2.76187109947205</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.85263657569885</v>
+        <v>2.85263681411743</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.80077052116394</v>
+        <v>2.80077075958252</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.882892370224</v>
+        <v>2.88289213180542</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.90882515907288</v>
+        <v>2.90882539749146</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.03416848182678</v>
+        <v>3.0341682434082</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232954025269</v>
+        <v>3.05232930183411</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.06132030487061</v>
+        <v>3.06132006645203</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.67472171783447</v>
+        <v>2.67472147941589</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.51289010047913</v>
+        <v>2.51288986206055</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.34206748008728</v>
+        <v>2.3420672416687</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.3690390586853</v>
+        <v>2.36903953552246</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.37802982330322</v>
+        <v>2.3780300617218</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.35555338859558</v>
+        <v>2.355553150177</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.40050649642944</v>
+        <v>2.40050673484802</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.44995498657227</v>
+        <v>2.44995522499084</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.44995498657227</v>
+        <v>2.44995522499084</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.22518849372864</v>
+        <v>2.22518873214722</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.10381484031677</v>
+        <v>2.10381460189819</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.19821643829346</v>
+        <v>2.19821667671204</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.05886149406433</v>
+        <v>2.05886125564575</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.00941252708435</v>
+        <v>2.00941276550293</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.91051542758942</v>
+        <v>1.91051554679871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620689868927</v>
+        <v>1.72620701789856</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.67046499252319</v>
+        <v>1.6704648733139</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.82510423660278</v>
+        <v>1.82510435581207</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.96895492076874</v>
+        <v>1.96895480155945</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.05886149406433</v>
+        <v>2.05886125564575</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.63426399230957</v>
+        <v>2.63426375389099</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.67921733856201</v>
+        <v>2.67921710014343</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.40500164031982</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408595085144</v>
+        <v>2.32408618927002</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.25665593147278</v>
+        <v>2.25665616989136</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.279132604599</v>
+        <v>2.27913284301758</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.51289010047913</v>
+        <v>2.51288986206055</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.49940395355225</v>
+        <v>2.49940371513367</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.62077760696411</v>
+        <v>2.62077784538269</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.18718957901001</v>
+        <v>3.18718934059143</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.5063579082489</v>
+        <v>3.50635814666748</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.51534867286682</v>
+        <v>3.5153489112854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.34003043174744</v>
+        <v>3.34003067016602</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.18718957901001</v>
+        <v>3.18718934059143</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.32654452323914</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.3670027256012</v>
+        <v>3.36700248718262</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.35351657867432</v>
+        <v>3.3535168170929</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.39397478103638</v>
+        <v>3.3939745426178</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.06132030487061</v>
+        <v>3.06132006645203</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.8725163936615</v>
+        <v>2.87251615524292</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.19618034362793</v>
+        <v>3.19618010520935</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.29957294464111</v>
+        <v>3.29957270622253</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.625</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.625</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.31755399703979</v>
+        <v>3.31755423545837</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29957294464111</v>
+        <v>3.29957270622253</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856323242188</v>
+        <v>3.30856370925903</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.23214292526245</v>
+        <v>3.23214268684387</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.27709627151489</v>
+        <v>3.27709603309631</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.26361012458801</v>
+        <v>3.26361036300659</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.28159165382385</v>
+        <v>3.28159141540527</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.26810550689697</v>
+        <v>3.26810526847839</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.16471290588379</v>
+        <v>3.16471266746521</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.18269395828247</v>
+        <v>3.18269419670105</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.17370343208313</v>
+        <v>3.17370367050171</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.04333901405334</v>
+        <v>3.04333877563477</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.02985286712646</v>
+        <v>3.02985262870789</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.04783415794373</v>
+        <v>3.0478343963623</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.04783415794373</v>
+        <v>3.0478343963623</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.9983856678009</v>
+        <v>2.99838542938232</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.93095541000366</v>
+        <v>2.93095564842224</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746973991394</v>
+        <v>2.91746950149536</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.83655381202698</v>
+        <v>2.8365535736084</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.9759087562561</v>
+        <v>2.97590899467468</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.96691799163818</v>
+        <v>2.96691823005676</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.88150715827942</v>
+        <v>2.88150691986084</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.40050649642944</v>
+        <v>2.40050673484802</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.84104919433594</v>
+        <v>2.84104895591736</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.8725163936615</v>
+        <v>2.87251615524292</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.86352562904358</v>
+        <v>2.863525390625</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.787104845047</v>
+        <v>2.78710508346558</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.76462817192078</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.77811408042908</v>
+        <v>2.77811431884766</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.74215149879456</v>
+        <v>2.74215173721313</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325428009033</v>
+        <v>2.64325451850891</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.60729169845581</v>
+        <v>2.60729193687439</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.85003972053528</v>
+        <v>2.85003995895386</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.67921733856201</v>
+        <v>2.67921710014343</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.63426399230957</v>
+        <v>2.63426375389099</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.67472171783447</v>
+        <v>2.67472147941589</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.70618915557861</v>
+        <v>2.70618891716003</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.42298316955566</v>
+        <v>2.42298340797424</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.4769275188446</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.40500164031982</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.43646931648254</v>
+        <v>2.43646907806396</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.40500164031982</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.44096446037292</v>
+        <v>2.4409646987915</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.40500164031982</v>
+        <v>2.4050018787384</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36004853248596</v>
+        <v>2.36004877090454</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.34206748008728</v>
+        <v>2.3420672416687</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.21170258522034</v>
+        <v>2.21170282363892</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.21170258522034</v>
+        <v>2.21170282363892</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.1802351474762</v>
+        <v>2.18023538589478</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473076820374</v>
+        <v>2.18473052978516</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15326356887817</v>
+        <v>2.15326333045959</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.14876842498779</v>
+        <v>2.14876818656921</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143159389496</v>
+        <v>1.99143135547638</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501104831696</v>
+        <v>1.91501080989838</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.986936211586</v>
+        <v>1.98693609237671</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647824764252</v>
+        <v>1.94647812843323</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.95097362995148</v>
+        <v>1.95097351074219</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.9644593000412</v>
+        <v>1.96445953845978</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.91051542758942</v>
+        <v>1.91051554679871</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702939987183</v>
+        <v>1.89702951908112</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.85207617282867</v>
+        <v>1.85207629203796</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923496246338</v>
+        <v>1.69923508167267</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.74778461456299</v>
+        <v>1.7477844953537</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.72081255912781</v>
+        <v>1.7208126783371</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.73699581623077</v>
+        <v>1.73699569702148</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879396915436</v>
+        <v>1.73879384994507</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.72081255912781</v>
+        <v>1.7208126783371</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.69563889503479</v>
+        <v>1.6956387758255</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406117916107</v>
+        <v>1.67406105995178</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.66686868667603</v>
+        <v>1.66686856746674</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.77116024494171</v>
+        <v>1.771160364151</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.99592673778534</v>
+        <v>1.99592685699463</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546877384186</v>
+        <v>1.95546865463257</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.00491738319397</v>
+        <v>2.00491762161255</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.19821643829346</v>
+        <v>2.19821667671204</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.20271182060242</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.31060004234314</v>
+        <v>2.31059980392456</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.31959056854248</v>
+        <v>2.3195903301239</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.48591780662537</v>
+        <v>2.48591804504395</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.57582426071167</v>
+        <v>2.57582449913025</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.59830117225647</v>
+        <v>2.59830141067505</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.54435729980469</v>
+        <v>2.54435706138611</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.50839471817017</v>
+        <v>2.50839447975159</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.56233811378479</v>
+        <v>2.56233835220337</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.90398383140564</v>
+        <v>2.90398359298706</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.94444155693054</v>
+        <v>2.94444179534912</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.80508613586426</v>
+        <v>2.80508637428284</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884387016296</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="n">
-        <v>3.07480645179749</v>
+        <v>3.07480621337891</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>3.13774061203003</v>
+        <v>3.13774085044861</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241379737854</v>
+        <v>3.45241403579712</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.78506851196289</v>
+        <v>3.78506827354431</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.32654452323914</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.37599325180054</v>
+        <v>3.37599349021912</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.32204937934875</v>
+        <v>3.32204914093018</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>3.625</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.25911474227905</v>
+        <v>3.25911450386047</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.53137922286987</v>
+        <v>3.53137946128845</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.64800333976746</v>
+        <v>3.64800357818604</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.62001371383667</v>
+        <v>3.62001347541809</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2135" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2142" t="n">
-        <v>3.60601854324341</v>
+        <v>3.60601878166199</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2147" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2148" t="n">
-        <v>3.53137922286987</v>
+        <v>3.53137946128845</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56321,7 +56321,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2152" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2152" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.38676524162292</v>
+        <v>3.3867654800415</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2157" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2162" t="n">
-        <v>3.41008996963501</v>
+        <v>3.41009020805359</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2180" t="n">
-        <v>3.92323613166809</v>
+        <v>3.92323637008667</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.66199827194214</v>
+        <v>3.66199803352356</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57283,7 +57283,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2189" t="n">
-        <v>3.36810517311096</v>
+        <v>3.36810541152954</v>
       </c>
       <c r="H2189" t="s">
         <v>8</v>
@@ -57361,7 +57361,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2192" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2192" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2194" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2198" t="n">
-        <v>3.42408514022827</v>
+        <v>3.42408490180969</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2199" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2201" t="n">
-        <v>3.55003905296326</v>
+        <v>3.55003929138184</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2207" t="n">
-        <v>3.52204942703247</v>
+        <v>3.52204918861389</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.27014112472534</v>
+        <v>3.27014136314392</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2213" t="n">
-        <v>3.28880095481873</v>
+        <v>3.2888011932373</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58063,7 +58063,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2219" t="n">
-        <v>3.34478044509888</v>
+        <v>3.34478068351746</v>
       </c>
       <c r="H2219" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2223" t="n">
-        <v>3.28880095481873</v>
+        <v>3.2888011932373</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2224" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58297,7 +58297,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2228" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2228" t="s">
         <v>8</v>
@@ -58349,7 +58349,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.17217683792114</v>
+        <v>3.17217707633972</v>
       </c>
       <c r="H2230" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2232" t="n">
-        <v>3.22815632820129</v>
+        <v>3.22815656661987</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58427,7 +58427,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2233" t="n">
-        <v>3.19550156593323</v>
+        <v>3.19550180435181</v>
       </c>
       <c r="H2233" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2236" t="n">
-        <v>3.19550156593323</v>
+        <v>3.19550180435181</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58531,7 +58531,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2237" t="n">
-        <v>3.24681615829468</v>
+        <v>3.24681639671326</v>
       </c>
       <c r="H2237" t="s">
         <v>8</v>
@@ -58583,7 +58583,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2239" t="n">
-        <v>3.27014112472534</v>
+        <v>3.27014136314392</v>
       </c>
       <c r="H2239" t="s">
         <v>8</v>
@@ -58609,7 +58609,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2240" t="n">
-        <v>3.42408514022827</v>
+        <v>3.42408490180969</v>
       </c>
       <c r="H2240" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>3.92790126800537</v>
+        <v>3.92790102958679</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G2246" t="n">
-        <v>3.94189596176147</v>
+        <v>3.94189620018005</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2248" t="n">
-        <v>3.92323613166809</v>
+        <v>3.92323637008667</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2249" t="n">
-        <v>3.99321103096008</v>
+        <v>3.9932107925415</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G2251" t="n">
-        <v>3.8952465057373</v>
+        <v>3.89524674415588</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2258" t="n">
-        <v>3.76929235458374</v>
+        <v>3.76929259300232</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2259" t="n">
-        <v>3.64800333976746</v>
+        <v>3.64800357818604</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G2260" t="n">
-        <v>3.86725640296936</v>
+        <v>3.86725664138794</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G2261" t="n">
-        <v>3.90457630157471</v>
+        <v>3.90457653999329</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59467,7 +59467,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2273" t="n">
-        <v>3.66199827194214</v>
+        <v>3.66199803352356</v>
       </c>
       <c r="H2273" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2278" t="n">
-        <v>3.92790126800537</v>
+        <v>3.92790102958679</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59623,7 +59623,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2279" t="n">
-        <v>4.00720548629761</v>
+        <v>4.00720596313477</v>
       </c>
       <c r="H2279" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2281" t="n">
-        <v>4.10517024993896</v>
+        <v>4.10516977310181</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2299" t="n">
-        <v>4.00720548629761</v>
+        <v>4.00720596313477</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2300" t="n">
-        <v>3.97921562194824</v>
+        <v>3.97921586036682</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2302" t="n">
-        <v>4.10517024993896</v>
+        <v>4.10516977310181</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2307" t="n">
-        <v>4.3850679397583</v>
+        <v>4.38506746292114</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60403,7 +60403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2309" t="n">
-        <v>4.51568746566772</v>
+        <v>4.51568698883057</v>
       </c>
       <c r="H2309" t="s">
         <v>8</v>
@@ -60481,7 +60481,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2312" t="n">
-        <v>4.71161603927612</v>
+        <v>4.71161556243896</v>
       </c>
       <c r="H2312" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2314" t="n">
-        <v>4.5809965133667</v>
+        <v>4.58099603652954</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60715,7 +60715,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2321" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2321" t="s">
         <v>8</v>
@@ -60767,7 +60767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2323" t="n">
-        <v>5.10347270965576</v>
+        <v>5.1034722328186</v>
       </c>
       <c r="H2323" t="s">
         <v>8</v>
@@ -60793,7 +60793,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2324" t="n">
-        <v>4.90754461288452</v>
+        <v>4.90754413604736</v>
       </c>
       <c r="H2324" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2326" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60897,7 +60897,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G2328" t="n">
-        <v>4.86089468002319</v>
+        <v>4.86089420318604</v>
       </c>
       <c r="H2328" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2332" t="n">
-        <v>4.67429637908936</v>
+        <v>4.6742959022522</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2335" t="n">
-        <v>4.6836256980896</v>
+        <v>4.68362617492676</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2337" t="n">
-        <v>4.5809965133667</v>
+        <v>4.58099603652954</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2339" t="n">
-        <v>4.67429637908936</v>
+        <v>4.6742959022522</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2342" t="n">
-        <v>4.87955474853516</v>
+        <v>4.879554271698</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2344" t="n">
-        <v>5.07548332214355</v>
+        <v>5.0754828453064</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2346" t="n">
-        <v>4.94486427307129</v>
+        <v>4.94486379623413</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61443,7 +61443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2349" t="n">
-        <v>4.90754461288452</v>
+        <v>4.90754413604736</v>
       </c>
       <c r="H2349" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G2355" t="n">
-        <v>4.56700134277344</v>
+        <v>4.5670018196106</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61625,7 +61625,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2356" t="n">
-        <v>4.33841848373413</v>
+        <v>4.33841800689697</v>
       </c>
       <c r="H2356" t="s">
         <v>8</v>
@@ -61651,7 +61651,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G2357" t="n">
-        <v>4.1844744682312</v>
+        <v>4.18447494506836</v>
       </c>
       <c r="H2357" t="s">
         <v>8</v>
@@ -61677,7 +61677,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2358" t="n">
-        <v>4.3850679397583</v>
+        <v>4.38506746292114</v>
       </c>
       <c r="H2358" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.15181970596313</v>
+        <v>4.15181922912598</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G2360" t="n">
-        <v>4.33375310897827</v>
+        <v>4.33375358581543</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G2362" t="n">
-        <v>4.46437215805054</v>
+        <v>4.4643726348877</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2366" t="n">
-        <v>4.6836256980896</v>
+        <v>4.68362617492676</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2367" t="n">
-        <v>4.75826549530029</v>
+        <v>4.75826501846313</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2368" t="n">
-        <v>4.87955474853516</v>
+        <v>4.879554271698</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>7.44999980926514</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>86324</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>7.11999988555908</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>7.28000020980835</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>33686</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>7.42999982833862</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>7.36999988555908</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>7.38000011444092</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>32390</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>7.34999990463257</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>7.32999992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>7.21999979019165</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>42768</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>7.17000007629395</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>7.15000009536743</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>7.15000009536743</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>7.05999994277954</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>18978</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>99597</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>7.13000011444092</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>6.98999977111816</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>7.05000019073486</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349234104156</v>
+        <v>1.89349222183228</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980905056</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139402866364</v>
+        <v>1.63139390945435</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754958629608</v>
+        <v>1.56754970550537</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47514319419861</v>
+        <v>1.4751433134079</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314015865326</v>
+        <v>1.43314003944397</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.40877842903137</v>
+        <v>1.40877854824066</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>1.48522388935089</v>
+        <v>1.4852237701416</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>1.24328696727753</v>
+        <v>1.24328684806824</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42893993854523</v>
+        <v>1.42893981933594</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126575469971</v>
+        <v>1.511265873909</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G47" t="n">
-        <v>1.50874531269073</v>
+        <v>1.50874555110931</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.4801834821701</v>
+        <v>1.48018336296082</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G49" t="n">
-        <v>1.49446451663971</v>
+        <v>1.49446439743042</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G52" t="n">
-        <v>1.50286519527435</v>
+        <v>1.50286507606506</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586945056915</v>
+        <v>1.56586933135986</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491569042206</v>
+        <v>1.65491580963135</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551355361938</v>
+        <v>1.62551367282867</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G58" t="n">
-        <v>1.58183073997498</v>
+        <v>1.58183062076569</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G63" t="n">
-        <v>1.45078134536743</v>
+        <v>1.45078146457672</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G70" t="n">
-        <v>1.41465902328491</v>
+        <v>1.41465890407562</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.60787260532379</v>
+        <v>1.60787236690521</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646731376648</v>
+        <v>1.53646743297577</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G83" t="n">
-        <v>1.55074846744537</v>
+        <v>1.55074834823608</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G93" t="n">
-        <v>1.42305946350098</v>
+        <v>1.42305958271027</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G96" t="n">
-        <v>1.51882612705231</v>
+        <v>1.51882600784302</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47514319419861</v>
+        <v>1.4751433134079</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.48270356655121</v>
+        <v>1.48270344734192</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>1.52050614356995</v>
+        <v>1.52050626277924</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.50202488899231</v>
+        <v>1.5020250082016</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51798617839813</v>
+        <v>1.51798629760742</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G106" t="n">
-        <v>1.52470660209656</v>
+        <v>1.52470672130585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126575469971</v>
+        <v>1.511265873909</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>1.51210570335388</v>
+        <v>1.51210558414459</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577405452728</v>
+        <v>1.34577417373657</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409415721893</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205800533295</v>
+        <v>1.40205812454224</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28192973136902</v>
+        <v>1.28192961215973</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409415721893</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G127" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537057876587</v>
+        <v>1.29537069797516</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G132" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>1.33485329151154</v>
+        <v>1.33485341072083</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G139" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401334285736</v>
+        <v>1.33401322364807</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G143" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.3499743938446</v>
+        <v>1.34997427463531</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769615650177</v>
+        <v>1.37769627571106</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G154" t="n">
-        <v>1.32309246063232</v>
+        <v>1.3230926990509</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.32309246063232</v>
+        <v>1.3230926990509</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.31385171413422</v>
+        <v>1.31385183334351</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125081539154</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G162" t="n">
-        <v>1.27016878128052</v>
+        <v>1.27016866207123</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813274860382</v>
+        <v>1.32813286781311</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713129043579</v>
+        <v>1.30713140964508</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30629122257233</v>
+        <v>1.30629110336304</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G176" t="n">
-        <v>1.30629122257233</v>
+        <v>1.30629110336304</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921514034271</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G180" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G181" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677551269531</v>
+        <v>1.36677539348602</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33989369869232</v>
+        <v>1.33989357948303</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G187" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409415721893</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G195" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105642795563</v>
+        <v>1.38105666637421</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881142616272</v>
+        <v>1.30881154537201</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G204" t="n">
-        <v>1.30461120605469</v>
+        <v>1.3046110868454</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G206" t="n">
-        <v>1.3214123249054</v>
+        <v>1.32141244411469</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125081539154</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G210" t="n">
-        <v>1.28865015506744</v>
+        <v>1.28865027427673</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G218" t="n">
-        <v>1.14247977733612</v>
+        <v>1.14247989654541</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G219" t="n">
-        <v>1.2222855091095</v>
+        <v>1.22228538990021</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G222" t="n">
-        <v>1.17944264411926</v>
+        <v>1.17944252490997</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G226" t="n">
-        <v>1.14836037158966</v>
+        <v>1.14836025238037</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367562294006</v>
+        <v>1.08367574214935</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.08031535148621</v>
+        <v>1.0803154706955</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.0391526222229</v>
+        <v>1.03915250301361</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939482688904</v>
+        <v>1.06939470767975</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G241" t="n">
-        <v>1.11811816692352</v>
+        <v>1.11811792850494</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584004878998</v>
+        <v>1.14583992958069</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G247" t="n">
-        <v>1.16768157482147</v>
+        <v>1.16768169403076</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G248" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G250" t="n">
-        <v>1.19624364376068</v>
+        <v>1.19624352455139</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.1618013381958</v>
+        <v>1.16180109977722</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348135471344</v>
+        <v>1.16348123550415</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G261" t="n">
-        <v>1.34073376655579</v>
+        <v>1.3407336473465</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501480102539</v>
+        <v>1.3550146818161</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377113819122</v>
+        <v>1.30377101898193</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808528900146</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G272" t="n">
-        <v>1.19456350803375</v>
+        <v>1.19456362724304</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G273" t="n">
-        <v>1.19456350803375</v>
+        <v>1.19456362724304</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G276" t="n">
-        <v>1.19456350803375</v>
+        <v>1.19456362724304</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.18868315219879</v>
+        <v>1.1886830329895</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448281288147</v>
+        <v>1.18448269367218</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104184627533</v>
+        <v>1.17104196548462</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G289" t="n">
-        <v>1.17776238918304</v>
+        <v>1.17776226997375</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G292" t="n">
-        <v>1.15340077877045</v>
+        <v>1.15340065956116</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G295" t="n">
-        <v>1.15088033676147</v>
+        <v>1.15088045597076</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424060821533</v>
+        <v>1.15424072742462</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G298" t="n">
-        <v>1.16516137123108</v>
+        <v>1.16516149044037</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.375</v>
       </c>
       <c r="G299" t="n">
-        <v>1.15508079528809</v>
+        <v>1.1550806760788</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740649223328</v>
+        <v>1.23740661144257</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380401611328</v>
+        <v>1.20380413532257</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G313" t="n">
-        <v>1.19456350803375</v>
+        <v>1.19456362724304</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884454250336</v>
+        <v>1.20884442329407</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.21052467823029</v>
+        <v>1.210524559021</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G323" t="n">
-        <v>1.25000751018524</v>
+        <v>1.25000739097595</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252759456635</v>
+        <v>1.25252771377563</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.2659684419632</v>
+        <v>1.26596856117249</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320615291595</v>
+        <v>1.23320627212524</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808528900146</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>1.20128381252289</v>
+        <v>1.20128393173218</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908674716949</v>
+        <v>1.23908662796021</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.24412679672241</v>
+        <v>1.2441269159317</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488628864288</v>
+        <v>1.23488640785217</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664723873138</v>
+        <v>1.24664711952209</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G347" t="n">
-        <v>1.29789078235626</v>
+        <v>1.29789066314697</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G350" t="n">
-        <v>1.2970507144928</v>
+        <v>1.29705059528351</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890706062317</v>
+        <v>1.52890694141388</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.75100004673004</v>
       </c>
       <c r="G356" t="n">
-        <v>1.47094285488129</v>
+        <v>1.470942735672</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194443225861</v>
+        <v>1.49194419384003</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.38861703872681</v>
+        <v>1.3886171579361</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G368" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409415721893</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173522472382</v>
+        <v>1.36173510551453</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.33569347858429</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G375" t="n">
-        <v>1.34157371520996</v>
+        <v>1.34157383441925</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G376" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409415721893</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921514034271</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G382" t="n">
-        <v>1.35081446170807</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G383" t="n">
-        <v>1.34493386745453</v>
+        <v>1.34493398666382</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G385" t="n">
-        <v>1.42557978630066</v>
+        <v>1.42557966709137</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G387" t="n">
-        <v>1.42978000640869</v>
+        <v>1.42978012561798</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221939563751</v>
+        <v>1.42221927642822</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297888755798</v>
+        <v>1.41297876834869</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G392" t="n">
-        <v>1.41381871700287</v>
+        <v>1.41381883621216</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G399" t="n">
-        <v>1.42978000640869</v>
+        <v>1.42978012561798</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102343082428</v>
+        <v>1.48102355003357</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>1.48522388935089</v>
+        <v>1.4852237701416</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530446529388</v>
+        <v>1.49530458450317</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>1.52050614356995</v>
+        <v>1.52050626277924</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G412" t="n">
-        <v>1.48774397373199</v>
+        <v>1.48774409294128</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238078594208</v>
+        <v>1.44238090515137</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842277050018</v>
+        <v>1.46842265129089</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51966631412506</v>
+        <v>1.51966619491577</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G441" t="n">
-        <v>1.59527146816254</v>
+        <v>1.59527158737183</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.8010858297348</v>
+        <v>1.80108594894409</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G445" t="n">
-        <v>1.80780637264252</v>
+        <v>1.80780625343323</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717539310455</v>
+        <v>1.93717551231384</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429953098297</v>
+        <v>1.99429929256439</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229637622833</v>
+        <v>1.95229613780975</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869425773621</v>
+        <v>1.91869413852692</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476900100708</v>
+        <v>1.84476923942566</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812939167023</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980905056</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669122219086</v>
+        <v>1.87669098377228</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533374786377</v>
+        <v>1.91533398628235</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.00438046455383</v>
+        <v>2.00438022613525</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581815719604</v>
+        <v>1.97581791877747</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061612129211</v>
+        <v>1.95061635971069</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213522434235</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341176509857</v>
+        <v>1.88341164588928</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308874607086</v>
+        <v>1.84308910369873</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G480" t="n">
-        <v>1.66751658916473</v>
+        <v>1.66751646995544</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879312992096</v>
+        <v>1.61879324913025</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63475430011749</v>
+        <v>1.6347541809082</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G485" t="n">
-        <v>1.5885511636734</v>
+        <v>1.58855104446411</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763028144836</v>
+        <v>1.57763016223907</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326843261719</v>
+        <v>1.55326855182648</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G490" t="n">
-        <v>1.50874531269073</v>
+        <v>1.50874555110931</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G494" t="n">
-        <v>1.58771085739136</v>
+        <v>1.58771097660065</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>1.59695160388947</v>
+        <v>1.59695172309875</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.612912774086</v>
+        <v>1.61291265487671</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507719993591</v>
+        <v>1.67507708072662</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451233386993</v>
+        <v>1.60451221466064</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.579310297966</v>
+        <v>1.57931041717529</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>1.63643443584442</v>
+        <v>1.63643431663513</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267045021057</v>
+        <v>1.58267056941986</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535228252411</v>
+        <v>1.60535216331482</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G514" t="n">
-        <v>1.66163611412048</v>
+        <v>1.66163623332977</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323555469513</v>
+        <v>1.65323567390442</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G520" t="n">
-        <v>1.67339706420898</v>
+        <v>1.67339694499969</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827584266663</v>
+        <v>1.65827596187592</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851792812347</v>
+        <v>1.68851804733276</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>1.873330950737</v>
+        <v>1.87333106994629</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G531" t="n">
-        <v>1.93213522434235</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433252811432</v>
+        <v>1.8943327665329</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>1.93213522434235</v>
+        <v>1.93213498592377</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533374786377</v>
+        <v>1.91533398628235</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82712757587433</v>
+        <v>1.82712769508362</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.75992298126221</v>
+        <v>1.75992321968079</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152254104614</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>1.75152242183685</v>
+        <v>1.75152254104614</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G551" t="n">
-        <v>1.75572276115417</v>
+        <v>1.75572264194489</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011748790741</v>
+        <v>1.68011736869812</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052084445953</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772579669952</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>1.90693330764771</v>
+        <v>1.90693318843842</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>1.90693330764771</v>
+        <v>1.90693318843842</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812939167023</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G569" t="n">
-        <v>1.83132815361023</v>
+        <v>1.83132791519165</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.125</v>
       </c>
       <c r="G572" t="n">
-        <v>1.78512477874756</v>
+        <v>1.78512465953827</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>1.78092432022095</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>1.78092432022095</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812939167023</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113376617432</v>
+        <v>1.91113352775574</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173151016235</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.94893634319305</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.92373430728912</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.92373430728912</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.9825382232666</v>
+        <v>1.98253870010376</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>2.00774073600769</v>
+        <v>2.00774049758911</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>2.04554319381714</v>
+        <v>2.04554295539856</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.2639582157135</v>
+        <v>2.26395797729492</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214992523193</v>
+        <v>2.14214968681335</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G608" t="n">
-        <v>2.2345564365387</v>
+        <v>2.23455619812012</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316584587097</v>
+        <v>2.37316608428955</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41096830368042</v>
+        <v>2.410968542099</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177549362183</v>
+        <v>2.51177573204041</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>2.83099746704102</v>
+        <v>2.83099770545959</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059458732605</v>
+        <v>2.78059434890747</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00321006774902</v>
+        <v>3.00320982933044</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.75</v>
       </c>
       <c r="G627" t="n">
-        <v>3.15022039413452</v>
+        <v>3.15022015571594</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.15442061424255</v>
+        <v>3.15442085266113</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.875</v>
       </c>
       <c r="G630" t="n">
-        <v>3.2552273273468</v>
+        <v>3.25522756576538</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703585624695</v>
+        <v>3.37703609466553</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645245552063</v>
+        <v>3.61645269393921</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.68785786628723</v>
+        <v>3.68785762786865</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446483612061</v>
+        <v>3.78446435928345</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.9482753276825</v>
+        <v>3.94827580451965</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927714347839</v>
+        <v>3.96927762031555</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226753234863</v>
+        <v>3.82226705551147</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545135498047</v>
+        <v>3.59545159339905</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.47751331329346</v>
+        <v>4.4775128364563</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G665" t="n">
-        <v>4.43551015853882</v>
+        <v>4.43551063537598</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G666" t="n">
-        <v>4.59512090682983</v>
+        <v>4.59512138366699</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>4.6035213470459</v>
+        <v>4.60352182388306</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G672" t="n">
-        <v>4.1834921836853</v>
+        <v>4.18349170684814</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.82193660736084</v>
+        <v>4.821937084198</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>4.88074064254761</v>
+        <v>4.88074111938477</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>4.67072629928589</v>
+        <v>4.67072677612305</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.70432949066162</v>
+        <v>4.7043285369873</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G681" t="n">
-        <v>4.73793125152588</v>
+        <v>4.73793077468872</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271511077881</v>
+        <v>4.50271463394165</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G690" t="n">
-        <v>4.46911287307739</v>
+        <v>4.46911239624023</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350700378418</v>
+        <v>4.39350748062134</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.33470249176025</v>
+        <v>4.33470296859741</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749753952026</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.05748414993286</v>
+        <v>4.0574836730957</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788679122925</v>
+        <v>4.10788631439209</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.80546617507935</v>
+        <v>3.80546641349792</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286456108093</v>
+        <v>3.79286527633667</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.66265630722046</v>
+        <v>3.6626558303833</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>4.01128053665161</v>
+        <v>4.01128005981445</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>3.51144552230835</v>
+        <v>3.51144528388977</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902466773987</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.99480962753296</v>
+        <v>2.99480938911438</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G710" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.95280647277832</v>
+        <v>2.9528067111969</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>2.86880016326904</v>
+        <v>2.8688006401062</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419658660889</v>
+        <v>2.81419682502747</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G717" t="n">
-        <v>2.931804895401</v>
+        <v>2.93180513381958</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G718" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G720" t="n">
-        <v>2.71758961677551</v>
+        <v>2.71758985519409</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G721" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>2.79739546775818</v>
+        <v>2.7973952293396</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860601425171</v>
+        <v>2.94860625267029</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902466773987</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>3.31823205947876</v>
+        <v>3.31823182106018</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380781173706</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.77639412879944</v>
+        <v>2.77639436721802</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92760419845581</v>
+        <v>2.92760443687439</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902466773987</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G745" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.2762291431427</v>
+        <v>3.27622890472412</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.875</v>
       </c>
       <c r="G748" t="n">
-        <v>3.2552273273468</v>
+        <v>3.25522756576538</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781412124634</v>
+        <v>3.05781388282776</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380781173706</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060893058777</v>
+        <v>2.99060916900635</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418176651001</v>
+        <v>2.60418200492859</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.79739546775818</v>
+        <v>2.7973952293396</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.67978739738464</v>
+        <v>2.67978715896606</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G761" t="n">
-        <v>2.64618492126465</v>
+        <v>2.64618539810181</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G762" t="n">
-        <v>2.54957818984985</v>
+        <v>2.54957842826843</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.79739546775818</v>
+        <v>2.7973952293396</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G764" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400219917297</v>
+        <v>2.89400243759155</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>3.20482420921326</v>
+        <v>3.20482397079468</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.07881498336792</v>
+        <v>3.0788152217865</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.225825548172</v>
+        <v>3.22582530975342</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>3.3518340587616</v>
+        <v>3.35183453559875</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G778" t="n">
-        <v>3.47784280776978</v>
+        <v>3.47784304618835</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346278190613</v>
+        <v>3.76346302032471</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226753234863</v>
+        <v>3.82226705551147</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.9860782623291</v>
+        <v>3.98607873916626</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>4.01128053665161</v>
+        <v>4.01128005981445</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G789" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486795425415</v>
+        <v>3.83486819267273</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>3.81806707382202</v>
+        <v>3.81806683540344</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>3.93567514419556</v>
+        <v>3.9356746673584</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.9482753276825</v>
+        <v>3.94827580451965</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.9314751625061</v>
+        <v>3.93147468566895</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.9650764465332</v>
+        <v>3.96507740020752</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.86427044868469</v>
+        <v>3.86426997184753</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>3.746661901474</v>
+        <v>3.74666213989258</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G815" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.86427044868469</v>
+        <v>3.86426997184753</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G822" t="n">
-        <v>3.93567514419556</v>
+        <v>3.9356746673584</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G823" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>4.01548147201538</v>
+        <v>4.01548099517822</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688545227051</v>
+        <v>4.08688497543335</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>4.09948682785034</v>
+        <v>4.09948635101318</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631734848022</v>
+        <v>4.53631687164307</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.5</v>
       </c>
       <c r="G833" t="n">
-        <v>4.62032318115234</v>
+        <v>4.62032270431519</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.49431371688843</v>
+        <v>4.49431419372559</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030788421631</v>
+        <v>4.41030836105347</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950164794922</v>
+        <v>4.30950117111206</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749753952026</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G840" t="n">
-        <v>4.14988994598389</v>
+        <v>4.14989042282104</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866505622864</v>
+        <v>3.7886655330658</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>4.13632345199585</v>
+        <v>4.13632297515869</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563704490662</v>
+        <v>3.88563680648804</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G853" t="n">
-        <v>3.8813145160675</v>
+        <v>3.88131427764893</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71275043487549</v>
+        <v>3.71275019645691</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868274688721</v>
+        <v>3.73868322372437</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80783843994141</v>
+        <v>3.80783796310425</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.83377075195312</v>
+        <v>3.8337709903717</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359545707703</v>
+        <v>3.64359498023987</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>3.4145200252533</v>
+        <v>3.41451978683472</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G882" t="n">
-        <v>3.36265349388123</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G885" t="n">
-        <v>3.31943202018738</v>
+        <v>3.3194317817688</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>3.26324367523193</v>
+        <v>3.26324391365051</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163293838501</v>
+        <v>3.24163269996643</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137762069702</v>
+        <v>3.21137738227844</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.22434401512146</v>
+        <v>3.22434425354004</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.1768000125885</v>
+        <v>3.17680025100708</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756572723389</v>
+        <v>3.26756596565247</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G901" t="n">
-        <v>3.36265349388123</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>3.20273327827454</v>
+        <v>3.20273303985596</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G908" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G909" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>3.24595499038696</v>
+        <v>3.24595522880554</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>3.41884207725525</v>
+        <v>3.41884183883667</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G922" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G925" t="n">
-        <v>3.66520571708679</v>
+        <v>3.66520595550537</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444047927856</v>
+        <v>3.57444071769714</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G927" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56147360801697</v>
+        <v>3.56147384643555</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G929" t="n">
-        <v>3.62198424339294</v>
+        <v>3.6219847202301</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>3.58308458328247</v>
+        <v>3.58308482170105</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>3.60469555854797</v>
+        <v>3.60469579696655</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>3.60901808738708</v>
+        <v>3.60901832580566</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.56147360801697</v>
+        <v>3.56147384643555</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960779190063</v>
+        <v>3.50960755348206</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113945960999</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>3.8726704120636</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G949" t="n">
-        <v>3.57876229286194</v>
+        <v>3.57876253128052</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>3.60901808738708</v>
+        <v>3.60901832580566</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G952" t="n">
-        <v>3.62198424339294</v>
+        <v>3.6219847202301</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45341920852661</v>
+        <v>3.45341944694519</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G965" t="n">
-        <v>3.57876229286194</v>
+        <v>3.57876253128052</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402583122253</v>
+        <v>3.86402606964111</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85538196563721</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="n">
-        <v>3.99801421165466</v>
+        <v>3.9980137348175</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92453670501709</v>
+        <v>3.92453646659851</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343636512756</v>
+        <v>3.96343612670898</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.80351591110229</v>
+        <v>3.80351614952087</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.7862274646759</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.85538196563721</v>
+        <v>3.85538220405579</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>3.91589260101318</v>
+        <v>3.91589283943176</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893877983093</v>
+        <v>3.76893830299377</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G983" t="n">
-        <v>3.80783843994141</v>
+        <v>3.80783796310425</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>4.0628457069397</v>
+        <v>4.06284618377686</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699294090271</v>
+        <v>3.87699317932129</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="n">
-        <v>4.04555797576904</v>
+        <v>4.04555749893188</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911383628845</v>
+        <v>3.95911407470703</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318152427673</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563704490662</v>
+        <v>3.88563680648804</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445692062378</v>
+        <v>4.08445739746094</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="n">
-        <v>4.32217693328857</v>
+        <v>4.32217741012573</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>4.39133167266846</v>
+        <v>4.3913311958313</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.50370836257935</v>
+        <v>4.5037088394165</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.60744094848633</v>
+        <v>4.60744047164917</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.60744094848633</v>
+        <v>4.60744047164917</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.68524026870728</v>
+        <v>4.68523979187012</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.75439500808716</v>
+        <v>4.75439453125</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.84948253631592</v>
+        <v>4.84948205947876</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.70252847671509</v>
+        <v>4.70252895355225</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.82354927062988</v>
+        <v>4.82354974746704</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.96185874938965</v>
+        <v>4.96185922622681</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.88405990600586</v>
+        <v>4.88406038284302</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.73710584640503</v>
+        <v>4.73710632324219</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659568786621</v>
+        <v>4.67659521102905</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.73710584640503</v>
+        <v>4.73710632324219</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.7889723777771</v>
+        <v>4.78897190093994</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84083890914917</v>
+        <v>4.84083795547485</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.88405990600586</v>
+        <v>4.88406038284302</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.28170013427734</v>
+        <v>5.2817006111145</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.49780988693237</v>
+        <v>5.49780941009521</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.28170013427734</v>
+        <v>5.2817006111145</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846126556396</v>
+        <v>4.72846174240112</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.60744094848633</v>
+        <v>4.60744047164917</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.56421899795532</v>
+        <v>4.56421947479248</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.41726541519165</v>
+        <v>4.41726493835449</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895498275757</v>
+        <v>4.27895545959473</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828620910645</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.01530313491821</v>
+        <v>4.01530265808105</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428186416626</v>
+        <v>3.8942813873291</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970377922058</v>
+        <v>3.85970449447632</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.7862274646759</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.82512664794922</v>
+        <v>3.8251268863678</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.66520571708679</v>
+        <v>3.66520595550537</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.02984619140625</v>
+        <v>3.02984595298767</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.06010150909424</v>
+        <v>3.06010127067566</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085006713867</v>
+        <v>2.64085030555725</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.67110562324524</v>
+        <v>2.67110538482666</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287497520447</v>
+        <v>2.37287521362305</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.9363352060318</v>
+        <v>1.93633532524109</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.04006719589233</v>
+        <v>2.04006767272949</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.18702149391174</v>
+        <v>2.18702173233032</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.40313029289246</v>
+        <v>2.40313053131104</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.37719750404358</v>
+        <v>2.377197265625</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584160804749</v>
+        <v>2.38584184646606</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.40313029289246</v>
+        <v>2.40313053131104</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.48092937469482</v>
+        <v>2.4809296131134</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790059089661</v>
+        <v>3.13790082931519</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.10332322120667</v>
+        <v>3.10332298278809</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.01255702972412</v>
+        <v>3.0125572681427</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187109947205</v>
+        <v>2.76187133789062</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399247169495</v>
+        <v>2.84399271011353</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.80077075958252</v>
+        <v>2.80077052116394</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.76619338989258</v>
+        <v>2.76619362831116</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.0341682434082</v>
+        <v>3.03416848182678</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232954025269</v>
+        <v>3.05232930183411</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.28362774848938</v>
+        <v>2.28362798690796</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.36903929710388</v>
+        <v>2.36903953552246</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.12629127502441</v>
+        <v>2.12629151344299</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.88354349136353</v>
+        <v>1.88354361057281</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620689868927</v>
+        <v>1.72620701789856</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.76037156581879</v>
+        <v>1.7603714466095</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408595085144</v>
+        <v>2.32408618927002</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.279132604599</v>
+        <v>2.27913284301758</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.14223623275757</v>
+        <v>3.14223599433899</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.38947916030884</v>
+        <v>3.38947939872742</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.51534867286682</v>
+        <v>3.5153489112854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.32654500007629</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.58277821540833</v>
+        <v>3.5827784538269</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.42544174194336</v>
+        <v>3.42544198036194</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.42544174194336</v>
+        <v>3.42544198036194</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.35351657867432</v>
+        <v>3.3535168170929</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.39397478103638</v>
+        <v>3.3939745426178</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.14223623275757</v>
+        <v>3.14223599433899</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.02535772323608</v>
+        <v>3.0253574848175</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.02535772323608</v>
+        <v>3.0253574848175</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.9354510307312</v>
+        <v>2.93545079231262</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325428009033</v>
+        <v>2.64325451850891</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.46793627738953</v>
+        <v>2.46793651580811</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.28362774848938</v>
+        <v>2.28362798690796</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.26115131378174</v>
+        <v>2.26115155220032</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.26564693450928</v>
+        <v>2.2656466960907</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.26564693450928</v>
+        <v>2.2656466960907</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473076820374</v>
+        <v>2.18473052978516</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15326309204102</v>
+        <v>2.15326333045959</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.12629127502441</v>
+        <v>2.12629151344299</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143147468567</v>
+        <v>1.99143135547638</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501092910767</v>
+        <v>1.91501080989838</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.98693597316742</v>
+        <v>1.98693609237671</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702939987183</v>
+        <v>1.89702951908112</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.85207617282867</v>
+        <v>1.85207629203796</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262768268585</v>
+        <v>1.80262780189514</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923496246338</v>
+        <v>1.69923508167267</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.68125355243683</v>
+        <v>1.68125367164612</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879396915436</v>
+        <v>1.73879384994507</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.71361994743347</v>
+        <v>1.71362006664276</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.69563889503479</v>
+        <v>1.6956387758255</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.7351975440979</v>
+        <v>1.73519766330719</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406117916107</v>
+        <v>1.67406105995178</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546877384186</v>
+        <v>1.95546865463257</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2017" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.52188038825989</v>
+        <v>2.52188062667847</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241379737854</v>
+        <v>3.45241403579712</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2098" t="n">
-        <v>3.465900182724</v>
+        <v>3.46589994430542</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2100" t="n">
-        <v>3.465900182724</v>
+        <v>3.46589994430542</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.32654500007629</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="n">
-        <v>3.34902143478394</v>
+        <v>3.34902119636536</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2109" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>65410</v>
+        <v>66349</v>
       </c>
       <c r="C2743" t="n">
         <v>7.21000003814697</v>
@@ -71690,6 +71690,32 @@
         <v>7.1399998664856</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>56577</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>7.03999996185303</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>7.03999996185303</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>7.17999982833862</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>7.17999982833862</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349222183228</v>
+        <v>1.89349234104156</v>
       </c>
       <c r="H2" t="n">
         <v>142675</v>
@@ -456,7 +456,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853262901306</v>
       </c>
       <c r="H3" t="n">
         <v>134991</v>
@@ -485,7 +485,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H4" t="n">
         <v>96004</v>
@@ -543,7 +543,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612647533417</v>
+        <v>1.80612635612488</v>
       </c>
       <c r="H6" t="n">
         <v>149442</v>
@@ -572,7 +572,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139402866364</v>
+        <v>1.63139414787292</v>
       </c>
       <c r="H7" t="n">
         <v>346523</v>
@@ -601,7 +601,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71371984481812</v>
+        <v>1.71371960639954</v>
       </c>
       <c r="H8" t="n">
         <v>694813</v>
@@ -717,7 +717,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47514307498932</v>
+        <v>1.47514319419861</v>
       </c>
       <c r="H12" t="n">
         <v>173495</v>
@@ -746,7 +746,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314027786255</v>
+        <v>1.43314015865326</v>
       </c>
       <c r="H13" t="n">
         <v>146017</v>
@@ -775,7 +775,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H14" t="n">
         <v>179103</v>
@@ -804,7 +804,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>1.40877866744995</v>
+        <v>1.40877854824066</v>
       </c>
       <c r="H15" t="n">
         <v>185103</v>
@@ -833,7 +833,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>1.50370502471924</v>
+        <v>1.50370514392853</v>
       </c>
       <c r="H16" t="n">
         <v>387378</v>
@@ -891,7 +891,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530434608459</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H18" t="n">
         <v>156541</v>
@@ -920,7 +920,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H19" t="n">
         <v>171415</v>
@@ -949,7 +949,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46590232849121</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H20" t="n">
         <v>164363</v>
@@ -978,7 +978,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530434608459</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H21" t="n">
         <v>65291</v>
@@ -1065,7 +1065,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H24" t="n">
         <v>64863</v>
@@ -1094,7 +1094,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H25" t="n">
         <v>50052</v>
@@ -1123,7 +1123,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G26" t="n">
-        <v>1.34241390228271</v>
+        <v>1.34241378307343</v>
       </c>
       <c r="H26" t="n">
         <v>105494</v>
@@ -1181,7 +1181,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995981216431</v>
+        <v>1.13995969295502</v>
       </c>
       <c r="H28" t="n">
         <v>177163</v>
@@ -1210,7 +1210,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G29" t="n">
-        <v>1.2029641866684</v>
+        <v>1.20296406745911</v>
       </c>
       <c r="H29" t="n">
         <v>181158</v>
@@ -1268,7 +1268,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204330444336</v>
+        <v>1.19204354286194</v>
       </c>
       <c r="H31" t="n">
         <v>55919</v>
@@ -1297,7 +1297,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G32" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H32" t="n">
         <v>226070</v>
@@ -1355,7 +1355,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H34" t="n">
         <v>136172</v>
@@ -1384,7 +1384,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>1.43650054931641</v>
+        <v>1.43650043010712</v>
       </c>
       <c r="H35" t="n">
         <v>108719</v>
@@ -1413,7 +1413,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.41969931125641</v>
+        <v>1.4196994304657</v>
       </c>
       <c r="H36" t="n">
         <v>50293</v>
@@ -1442,7 +1442,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H37" t="n">
         <v>122783</v>
@@ -1558,7 +1558,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G41" t="n">
-        <v>1.43061995506287</v>
+        <v>1.43061983585358</v>
       </c>
       <c r="H41" t="n">
         <v>35142</v>
@@ -1587,7 +1587,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42893981933594</v>
+        <v>1.42893970012665</v>
       </c>
       <c r="H42" t="n">
         <v>25450</v>
@@ -1616,7 +1616,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254217624664</v>
       </c>
       <c r="H43" t="n">
         <v>49994</v>
@@ -1645,7 +1645,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126551628113</v>
+        <v>1.51126563549042</v>
       </c>
       <c r="H44" t="n">
         <v>126947</v>
@@ -1674,7 +1674,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G45" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H45" t="n">
         <v>61294</v>
@@ -1703,7 +1703,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G46" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H46" t="n">
         <v>61115</v>
@@ -1819,7 +1819,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H50" t="n">
         <v>34548</v>
@@ -1877,7 +1877,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G52" t="n">
-        <v>1.50286495685577</v>
+        <v>1.50286507606506</v>
       </c>
       <c r="H52" t="n">
         <v>58786</v>
@@ -1964,7 +1964,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491569042206</v>
+        <v>1.65491580963135</v>
       </c>
       <c r="H55" t="n">
         <v>234559</v>
@@ -2022,7 +2022,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>1.60283219814301</v>
+        <v>1.60283207893372</v>
       </c>
       <c r="H57" t="n">
         <v>64816</v>
@@ -2080,7 +2080,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G59" t="n">
-        <v>1.55578887462616</v>
+        <v>1.55578875541687</v>
       </c>
       <c r="H59" t="n">
         <v>177054</v>
@@ -2138,7 +2138,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.46590232849121</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H61" t="n">
         <v>52361</v>
@@ -2225,7 +2225,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994115829468</v>
+        <v>1.44994127750397</v>
       </c>
       <c r="H64" t="n">
         <v>18558</v>
@@ -2283,7 +2283,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349581718445</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H66" t="n">
         <v>47890</v>
@@ -2312,7 +2312,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G67" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H67" t="n">
         <v>35838</v>
@@ -2399,7 +2399,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G70" t="n">
-        <v>1.41465902328491</v>
+        <v>1.41465890407562</v>
       </c>
       <c r="H70" t="n">
         <v>71018</v>
@@ -2486,7 +2486,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G73" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H73" t="n">
         <v>42880</v>
@@ -2515,7 +2515,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847034931183</v>
+        <v>1.57847023010254</v>
       </c>
       <c r="H74" t="n">
         <v>128291</v>
@@ -2544,7 +2544,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H75" t="n">
         <v>74007</v>
@@ -2573,7 +2573,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830883979797</v>
+        <v>1.55830895900726</v>
       </c>
       <c r="H76" t="n">
         <v>60173</v>
@@ -2631,7 +2631,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.6078724861145</v>
+        <v>1.60787236690521</v>
       </c>
       <c r="H78" t="n">
         <v>161214</v>
@@ -2660,7 +2660,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H79" t="n">
         <v>123106</v>
@@ -2747,7 +2747,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530434608459</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H82" t="n">
         <v>54671</v>
@@ -2834,7 +2834,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>1.50370502471924</v>
+        <v>1.50370514392853</v>
       </c>
       <c r="H85" t="n">
         <v>62878</v>
@@ -2863,7 +2863,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H86" t="n">
         <v>72814</v>
@@ -2892,7 +2892,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H87" t="n">
         <v>10859</v>
@@ -2921,7 +2921,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574105739594</v>
+        <v>1.44574093818665</v>
       </c>
       <c r="H88" t="n">
         <v>34314</v>
@@ -2979,7 +2979,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>1.43650054931641</v>
+        <v>1.43650043010712</v>
       </c>
       <c r="H90" t="n">
         <v>36190</v>
@@ -3037,7 +3037,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809998989105</v>
       </c>
       <c r="H92" t="n">
         <v>40091</v>
@@ -3066,7 +3066,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G93" t="n">
-        <v>1.42305958271027</v>
+        <v>1.42305946350098</v>
       </c>
       <c r="H93" t="n">
         <v>34973</v>
@@ -3095,7 +3095,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G94" t="n">
-        <v>1.53730738162994</v>
+        <v>1.53730750083923</v>
       </c>
       <c r="H94" t="n">
         <v>288215</v>
@@ -3124,7 +3124,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H95" t="n">
         <v>124547</v>
@@ -3211,7 +3211,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H98" t="n">
         <v>24454</v>
@@ -3240,7 +3240,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47514307498932</v>
+        <v>1.47514319419861</v>
       </c>
       <c r="H99" t="n">
         <v>20179</v>
@@ -3269,7 +3269,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.4827036857605</v>
+        <v>1.48270380496979</v>
       </c>
       <c r="H100" t="n">
         <v>26242</v>
@@ -3298,7 +3298,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278426170349</v>
+        <v>1.49278438091278</v>
       </c>
       <c r="H101" t="n">
         <v>25555</v>
@@ -3327,7 +3327,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>1.52050614356995</v>
+        <v>1.52050626277924</v>
       </c>
       <c r="H102" t="n">
         <v>40357</v>
@@ -3414,7 +3414,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51798617839813</v>
+        <v>1.51798605918884</v>
       </c>
       <c r="H105" t="n">
         <v>85860</v>
@@ -3472,7 +3472,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126551628113</v>
+        <v>1.51126563549042</v>
       </c>
       <c r="H107" t="n">
         <v>33834</v>
@@ -3559,7 +3559,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338224411011</v>
       </c>
       <c r="H110" t="n">
         <v>33234</v>
@@ -3588,7 +3588,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H111" t="n">
         <v>68477</v>
@@ -3617,7 +3617,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>1.51210558414459</v>
+        <v>1.51210570335388</v>
       </c>
       <c r="H112" t="n">
         <v>28155</v>
@@ -3646,7 +3646,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614453315735</v>
+        <v>1.49614465236664</v>
       </c>
       <c r="H113" t="n">
         <v>17040</v>
@@ -3704,7 +3704,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457832813263</v>
+        <v>1.40457820892334</v>
       </c>
       <c r="H115" t="n">
         <v>72247</v>
@@ -3762,7 +3762,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G117" t="n">
-        <v>1.35669481754303</v>
+        <v>1.35669493675232</v>
       </c>
       <c r="H117" t="n">
         <v>31255</v>
@@ -3820,7 +3820,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205812454224</v>
+        <v>1.40205800533295</v>
       </c>
       <c r="H119" t="n">
         <v>39107</v>
@@ -3849,7 +3849,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G120" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809998989105</v>
       </c>
       <c r="H120" t="n">
         <v>68309</v>
@@ -3907,7 +3907,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H122" t="n">
         <v>57149</v>
@@ -3994,7 +3994,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G125" t="n">
-        <v>1.28781008720398</v>
+        <v>1.28780996799469</v>
       </c>
       <c r="H125" t="n">
         <v>106010</v>
@@ -4110,7 +4110,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H129" t="n">
         <v>34201</v>
@@ -4139,7 +4139,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H130" t="n">
         <v>59203</v>
@@ -4168,7 +4168,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537069797516</v>
+        <v>1.29537057876587</v>
       </c>
       <c r="H131" t="n">
         <v>29496</v>
@@ -4371,7 +4371,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H138" t="n">
         <v>37733</v>
@@ -4429,7 +4429,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G140" t="n">
-        <v>1.35249447822571</v>
+        <v>1.352494597435</v>
       </c>
       <c r="H140" t="n">
         <v>20369</v>
@@ -4487,7 +4487,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401334285736</v>
+        <v>1.33401346206665</v>
       </c>
       <c r="H142" t="n">
         <v>22761</v>
@@ -4603,7 +4603,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.3499743938446</v>
+        <v>1.34997451305389</v>
       </c>
       <c r="H146" t="n">
         <v>25885</v>
@@ -4632,7 +4632,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769627571106</v>
+        <v>1.37769639492035</v>
       </c>
       <c r="H147" t="n">
         <v>103585</v>
@@ -4690,7 +4690,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357663154602</v>
+        <v>1.38357651233673</v>
       </c>
       <c r="H149" t="n">
         <v>37470</v>
@@ -4719,7 +4719,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G150" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H150" t="n">
         <v>52663</v>
@@ -4748,7 +4748,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569347858429</v>
       </c>
       <c r="H151" t="n">
         <v>35803</v>
@@ -4777,7 +4777,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H152" t="n">
         <v>12097</v>
@@ -4806,7 +4806,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G153" t="n">
-        <v>1.33737349510193</v>
+        <v>1.33737361431122</v>
       </c>
       <c r="H153" t="n">
         <v>11912</v>
@@ -4893,7 +4893,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.31385183334351</v>
+        <v>1.3138519525528</v>
       </c>
       <c r="H156" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H157" t="n">
         <v>6004</v>
@@ -4951,7 +4951,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H158" t="n">
         <v>35138</v>
@@ -5009,7 +5009,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28948998451233</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H160" t="n">
         <v>3220</v>
@@ -5125,7 +5125,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680862903595</v>
+        <v>1.26680850982666</v>
       </c>
       <c r="H164" t="n">
         <v>13879</v>
@@ -5299,7 +5299,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H170" t="n">
         <v>9592</v>
@@ -5328,7 +5328,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813286781311</v>
+        <v>1.32813274860382</v>
       </c>
       <c r="H171" t="n">
         <v>34956</v>
@@ -5386,7 +5386,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713140964508</v>
+        <v>1.30713129043579</v>
       </c>
       <c r="H173" t="n">
         <v>6108</v>
@@ -5502,7 +5502,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265586853027</v>
+        <v>1.37265598773956</v>
       </c>
       <c r="H177" t="n">
         <v>159638</v>
@@ -5531,7 +5531,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921490192413</v>
       </c>
       <c r="H178" t="n">
         <v>176056</v>
@@ -5560,7 +5560,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569347858429</v>
       </c>
       <c r="H179" t="n">
         <v>49524</v>
@@ -5647,7 +5647,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677551269531</v>
+        <v>1.36677539348602</v>
       </c>
       <c r="H182" t="n">
         <v>13176</v>
@@ -5734,7 +5734,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G185" t="n">
-        <v>1.32477271556854</v>
+        <v>1.32477259635925</v>
       </c>
       <c r="H185" t="n">
         <v>43881</v>
@@ -5821,7 +5821,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417461395264</v>
+        <v>1.35417473316193</v>
       </c>
       <c r="H188" t="n">
         <v>58082</v>
@@ -5850,7 +5850,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H189" t="n">
         <v>17138</v>
@@ -5908,7 +5908,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G191" t="n">
-        <v>1.35585463047028</v>
+        <v>1.35585474967957</v>
       </c>
       <c r="H191" t="n">
         <v>23395</v>
@@ -5937,7 +5937,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G192" t="n">
-        <v>1.36929571628571</v>
+        <v>1.369295835495</v>
       </c>
       <c r="H192" t="n">
         <v>60792</v>
@@ -5966,7 +5966,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3768562078476</v>
+        <v>1.37685632705688</v>
       </c>
       <c r="H193" t="n">
         <v>34278</v>
@@ -5995,7 +5995,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G194" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H194" t="n">
         <v>9694</v>
@@ -6053,7 +6053,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H196" t="n">
         <v>26702</v>
@@ -6082,7 +6082,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G197" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H197" t="n">
         <v>31070</v>
@@ -6140,7 +6140,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349581718445</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H199" t="n">
         <v>91074</v>
@@ -6198,7 +6198,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569347858429</v>
       </c>
       <c r="H201" t="n">
         <v>114562</v>
@@ -6314,7 +6314,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H205" t="n">
         <v>18321</v>
@@ -6372,7 +6372,7 @@
         <v>1.57099997997284</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31973230838776</v>
+        <v>1.31973218917847</v>
       </c>
       <c r="H207" t="n">
         <v>19744</v>
@@ -6401,7 +6401,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H208" t="n">
         <v>31170</v>
@@ -6517,7 +6517,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.27772951126099</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H212" t="n">
         <v>16453</v>
@@ -6546,7 +6546,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28948998451233</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H213" t="n">
         <v>13131</v>
@@ -6720,7 +6720,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G219" t="n">
-        <v>1.22228562831879</v>
+        <v>1.2222855091095</v>
       </c>
       <c r="H219" t="n">
         <v>254583</v>
@@ -6865,7 +6865,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H224" t="n">
         <v>38946</v>
@@ -6894,7 +6894,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H225" t="n">
         <v>27800</v>
@@ -6923,7 +6923,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G226" t="n">
-        <v>1.14836037158966</v>
+        <v>1.14836025238037</v>
       </c>
       <c r="H226" t="n">
         <v>42201</v>
@@ -6952,7 +6952,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G227" t="n">
-        <v>1.12147855758667</v>
+        <v>1.12147843837738</v>
       </c>
       <c r="H227" t="n">
         <v>91568</v>
@@ -6981,7 +6981,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367574214935</v>
+        <v>1.08367586135864</v>
       </c>
       <c r="H228" t="n">
         <v>60344</v>
@@ -7039,7 +7039,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H230" t="n">
         <v>21769</v>
@@ -7068,7 +7068,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H231" t="n">
         <v>21196</v>
@@ -7126,7 +7126,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G233" t="n">
-        <v>1.07947540283203</v>
+        <v>1.07947528362274</v>
       </c>
       <c r="H233" t="n">
         <v>22285</v>
@@ -7155,7 +7155,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115541934967</v>
+        <v>1.08115553855896</v>
       </c>
       <c r="H234" t="n">
         <v>38205</v>
@@ -7213,7 +7213,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.06351435184479</v>
+        <v>1.0635142326355</v>
       </c>
       <c r="H236" t="n">
         <v>37238</v>
@@ -7300,7 +7300,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.0391526222229</v>
+        <v>1.03915250301361</v>
       </c>
       <c r="H239" t="n">
         <v>11183</v>
@@ -7329,7 +7329,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939458847046</v>
+        <v>1.06939470767975</v>
       </c>
       <c r="H240" t="n">
         <v>41501</v>
@@ -7474,7 +7474,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G245" t="n">
-        <v>1.14163970947266</v>
+        <v>1.14163982868195</v>
       </c>
       <c r="H245" t="n">
         <v>77628</v>
@@ -7503,7 +7503,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14583992958069</v>
+        <v>1.14584004878998</v>
       </c>
       <c r="H246" t="n">
         <v>30733</v>
@@ -7677,7 +7677,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.16180109977722</v>
+        <v>1.16180121898651</v>
       </c>
       <c r="H252" t="n">
         <v>24822</v>
@@ -7706,7 +7706,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348135471344</v>
+        <v>1.16348123550415</v>
       </c>
       <c r="H253" t="n">
         <v>60273</v>
@@ -7793,7 +7793,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H256" t="n">
         <v>13371</v>
@@ -7822,7 +7822,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G257" t="n">
-        <v>1.18364274501801</v>
+        <v>1.18364286422729</v>
       </c>
       <c r="H257" t="n">
         <v>22300</v>
@@ -7880,7 +7880,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H259" t="n">
         <v>167866</v>
@@ -7909,7 +7909,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H260" t="n">
         <v>166425</v>
@@ -7938,7 +7938,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G261" t="n">
-        <v>1.34073376655579</v>
+        <v>1.3407336473465</v>
       </c>
       <c r="H261" t="n">
         <v>560773</v>
@@ -7967,7 +7967,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.3550146818161</v>
+        <v>1.35501480102539</v>
       </c>
       <c r="H262" t="n">
         <v>277449</v>
@@ -7996,7 +7996,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.34325385093689</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H263" t="n">
         <v>158414</v>
@@ -8083,7 +8083,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377125740051</v>
+        <v>1.30377113819122</v>
       </c>
       <c r="H266" t="n">
         <v>53629</v>
@@ -8141,7 +8141,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H268" t="n">
         <v>271352</v>
@@ -8199,7 +8199,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832725524902</v>
+        <v>1.24832737445831</v>
       </c>
       <c r="H270" t="n">
         <v>55365</v>
@@ -8228,7 +8228,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H271" t="n">
         <v>103512</v>
@@ -8315,7 +8315,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H274" t="n">
         <v>53621</v>
@@ -8344,7 +8344,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H275" t="n">
         <v>109224</v>
@@ -8402,7 +8402,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.1886830329895</v>
+        <v>1.18868315219879</v>
       </c>
       <c r="H277" t="n">
         <v>23809</v>
@@ -8431,7 +8431,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H278" t="n">
         <v>152723</v>
@@ -8460,7 +8460,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G279" t="n">
-        <v>1.18532299995422</v>
+        <v>1.18532288074493</v>
       </c>
       <c r="H279" t="n">
         <v>48771</v>
@@ -8489,7 +8489,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448281288147</v>
+        <v>1.18448269367218</v>
       </c>
       <c r="H280" t="n">
         <v>20220</v>
@@ -8576,7 +8576,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H283" t="n">
         <v>60336</v>
@@ -8634,7 +8634,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H285" t="n">
         <v>42766</v>
@@ -8663,7 +8663,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104184627533</v>
+        <v>1.17104196548462</v>
       </c>
       <c r="H286" t="n">
         <v>21577</v>
@@ -8866,7 +8866,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H293" t="n">
         <v>25900</v>
@@ -8953,7 +8953,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H296" t="n">
         <v>39885</v>
@@ -8982,7 +8982,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424060821533</v>
+        <v>1.15424072742462</v>
       </c>
       <c r="H297" t="n">
         <v>24335</v>
@@ -9040,7 +9040,7 @@
         <v>1.375</v>
       </c>
       <c r="G299" t="n">
-        <v>1.15508079528809</v>
+        <v>1.1550806760788</v>
       </c>
       <c r="H299" t="n">
         <v>27476</v>
@@ -9069,7 +9069,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G300" t="n">
-        <v>1.19540357589722</v>
+        <v>1.19540345668793</v>
       </c>
       <c r="H300" t="n">
         <v>61794</v>
@@ -9098,7 +9098,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H301" t="n">
         <v>112526</v>
@@ -9156,7 +9156,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236620426178</v>
+        <v>1.23236632347107</v>
       </c>
       <c r="H303" t="n">
         <v>66001</v>
@@ -9185,7 +9185,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G304" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H304" t="n">
         <v>108629</v>
@@ -9214,7 +9214,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900605201721</v>
       </c>
       <c r="H305" t="n">
         <v>29402</v>
@@ -9272,7 +9272,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548415184021</v>
       </c>
       <c r="H307" t="n">
         <v>124489</v>
@@ -9330,7 +9330,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380413532257</v>
+        <v>1.20380401611328</v>
       </c>
       <c r="H309" t="n">
         <v>25149</v>
@@ -9417,7 +9417,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H312" t="n">
         <v>169466</v>
@@ -9475,7 +9475,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19540357589722</v>
+        <v>1.19540345668793</v>
       </c>
       <c r="H314" t="n">
         <v>51473</v>
@@ -9504,7 +9504,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H315" t="n">
         <v>26439</v>
@@ -9591,7 +9591,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H318" t="n">
         <v>363589</v>
@@ -9620,7 +9620,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884442329407</v>
+        <v>1.20884454250336</v>
       </c>
       <c r="H319" t="n">
         <v>228508</v>
@@ -9765,7 +9765,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252747535706</v>
+        <v>1.25252759456635</v>
       </c>
       <c r="H324" t="n">
         <v>69914</v>
@@ -9794,7 +9794,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688908576965</v>
       </c>
       <c r="H325" t="n">
         <v>165501</v>
@@ -9823,7 +9823,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688908576965</v>
       </c>
       <c r="H326" t="n">
         <v>59125</v>
@@ -9852,7 +9852,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G327" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H327" t="n">
         <v>51574</v>
@@ -9881,7 +9881,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.26596856117249</v>
+        <v>1.2659684419632</v>
       </c>
       <c r="H328" t="n">
         <v>28100</v>
@@ -9910,7 +9910,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.25756788253784</v>
+        <v>1.25756776332855</v>
       </c>
       <c r="H329" t="n">
         <v>42003</v>
@@ -9968,7 +9968,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H331" t="n">
         <v>30919</v>
@@ -9997,7 +9997,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>1.20128405094147</v>
+        <v>1.20128393173218</v>
       </c>
       <c r="H332" t="n">
         <v>77707</v>
@@ -10055,7 +10055,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G334" t="n">
-        <v>1.23068606853485</v>
+        <v>1.23068618774414</v>
       </c>
       <c r="H334" t="n">
         <v>125457</v>
@@ -10113,7 +10113,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H336" t="n">
         <v>36491</v>
@@ -10142,7 +10142,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G337" t="n">
-        <v>1.22564554214478</v>
+        <v>1.22564566135406</v>
       </c>
       <c r="H337" t="n">
         <v>21126</v>
@@ -10171,7 +10171,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.24412679672241</v>
+        <v>1.2441269159317</v>
       </c>
       <c r="H338" t="n">
         <v>121442</v>
@@ -10200,7 +10200,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488628864288</v>
+        <v>1.23488616943359</v>
       </c>
       <c r="H339" t="n">
         <v>28767</v>
@@ -10229,7 +10229,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.22480547428131</v>
+        <v>1.2248055934906</v>
       </c>
       <c r="H340" t="n">
         <v>28390</v>
@@ -10258,7 +10258,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H341" t="n">
         <v>33517</v>
@@ -10287,7 +10287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H342" t="n">
         <v>37872</v>
@@ -10316,7 +10316,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H343" t="n">
         <v>29781</v>
@@ -10345,7 +10345,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664711952209</v>
+        <v>1.24664723873138</v>
       </c>
       <c r="H344" t="n">
         <v>72151</v>
@@ -10403,7 +10403,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H346" t="n">
         <v>142637</v>
@@ -10461,7 +10461,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.27772951126099</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H348" t="n">
         <v>58888</v>
@@ -10548,7 +10548,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H351" t="n">
         <v>99220</v>
@@ -10577,7 +10577,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.302090883255</v>
+        <v>1.30209100246429</v>
       </c>
       <c r="H352" t="n">
         <v>134003</v>
@@ -10722,7 +10722,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194431304932</v>
+        <v>1.49194419384003</v>
       </c>
       <c r="H357" t="n">
         <v>183588</v>
@@ -10867,7 +10867,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>1.45498180389404</v>
+        <v>1.45498168468475</v>
       </c>
       <c r="H362" t="n">
         <v>33038</v>
@@ -10954,7 +10954,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H365" t="n">
         <v>28050</v>
@@ -11070,7 +11070,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173534393311</v>
+        <v>1.36173522472382</v>
       </c>
       <c r="H369" t="n">
         <v>94755</v>
@@ -11099,7 +11099,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G370" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H370" t="n">
         <v>29886</v>
@@ -11128,7 +11128,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349581718445</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H371" t="n">
         <v>27079</v>
@@ -11157,7 +11157,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341524124146</v>
+        <v>1.36341536045074</v>
       </c>
       <c r="H372" t="n">
         <v>45469</v>
@@ -11215,7 +11215,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569347858429</v>
       </c>
       <c r="H374" t="n">
         <v>54288</v>
@@ -11302,7 +11302,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.34325385093689</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H377" t="n">
         <v>25858</v>
@@ -11331,7 +11331,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G378" t="n">
-        <v>1.35249447822571</v>
+        <v>1.352494597435</v>
       </c>
       <c r="H378" t="n">
         <v>49855</v>
@@ -11418,7 +11418,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921502113342</v>
+        <v>1.35921490192413</v>
       </c>
       <c r="H381" t="n">
         <v>12422</v>
@@ -11505,7 +11505,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G384" t="n">
-        <v>1.35249447822571</v>
+        <v>1.352494597435</v>
       </c>
       <c r="H384" t="n">
         <v>29150</v>
@@ -11534,7 +11534,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G385" t="n">
-        <v>1.42557978630066</v>
+        <v>1.42557966709137</v>
       </c>
       <c r="H385" t="n">
         <v>153814</v>
@@ -11563,7 +11563,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>1.44070076942444</v>
+        <v>1.44070088863373</v>
       </c>
       <c r="H386" t="n">
         <v>56358</v>
@@ -11592,7 +11592,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G387" t="n">
-        <v>1.42978000640869</v>
+        <v>1.4297798871994</v>
       </c>
       <c r="H387" t="n">
         <v>25887</v>
@@ -11650,7 +11650,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221939563751</v>
+        <v>1.42221927642822</v>
       </c>
       <c r="H389" t="n">
         <v>26833</v>
@@ -11679,7 +11679,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297888755798</v>
+        <v>1.41297876834869</v>
       </c>
       <c r="H390" t="n">
         <v>62429</v>
@@ -11737,7 +11737,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G392" t="n">
-        <v>1.41381883621216</v>
+        <v>1.41381871700287</v>
       </c>
       <c r="H392" t="n">
         <v>37725</v>
@@ -11766,7 +11766,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G393" t="n">
-        <v>1.4104585647583</v>
+        <v>1.41045868396759</v>
       </c>
       <c r="H393" t="n">
         <v>28476</v>
@@ -11853,7 +11853,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809998989105</v>
       </c>
       <c r="H396" t="n">
         <v>24332</v>
@@ -11911,7 +11911,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809998989105</v>
       </c>
       <c r="H398" t="n">
         <v>43866</v>
@@ -11940,7 +11940,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G399" t="n">
-        <v>1.42978000640869</v>
+        <v>1.4297798871994</v>
       </c>
       <c r="H399" t="n">
         <v>73782</v>
@@ -11969,7 +11969,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.46590232849121</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H400" t="n">
         <v>136155</v>
@@ -12056,7 +12056,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.46590232849121</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H403" t="n">
         <v>39945</v>
@@ -12085,7 +12085,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G404" t="n">
-        <v>1.4633823633194</v>
+        <v>1.46338224411011</v>
       </c>
       <c r="H404" t="n">
         <v>73283</v>
@@ -12143,7 +12143,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918202400208</v>
+        <v>1.45918214321136</v>
       </c>
       <c r="H406" t="n">
         <v>60682</v>
@@ -12172,7 +12172,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530434608459</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H407" t="n">
         <v>275109</v>
@@ -12201,7 +12201,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>1.52050614356995</v>
+        <v>1.52050626277924</v>
       </c>
       <c r="H408" t="n">
         <v>200957</v>
@@ -12259,7 +12259,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.53310716152191</v>
+        <v>1.5331072807312</v>
       </c>
       <c r="H410" t="n">
         <v>122279</v>
@@ -12288,7 +12288,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H411" t="n">
         <v>96313</v>
@@ -12404,7 +12404,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G415" t="n">
-        <v>1.43986058235168</v>
+        <v>1.43986070156097</v>
       </c>
       <c r="H415" t="n">
         <v>5593</v>
@@ -12433,7 +12433,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H416" t="n">
         <v>30670</v>
@@ -12462,7 +12462,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574105739594</v>
+        <v>1.44574093818665</v>
       </c>
       <c r="H417" t="n">
         <v>20631</v>
@@ -12520,7 +12520,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H419" t="n">
         <v>24016</v>
@@ -12607,7 +12607,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G422" t="n">
-        <v>1.44070076942444</v>
+        <v>1.44070088863373</v>
       </c>
       <c r="H422" t="n">
         <v>8832</v>
@@ -12636,7 +12636,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H423" t="n">
         <v>14289</v>
@@ -12665,7 +12665,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H424" t="n">
         <v>83230</v>
@@ -12810,7 +12810,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.44154071807861</v>
+        <v>1.4415408372879</v>
       </c>
       <c r="H429" t="n">
         <v>13399</v>
@@ -12926,7 +12926,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.46590232849121</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H433" t="n">
         <v>23096</v>
@@ -12955,7 +12955,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254217624664</v>
       </c>
       <c r="H434" t="n">
         <v>24018</v>
@@ -12984,7 +12984,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330154895782</v>
+        <v>1.45330142974854</v>
       </c>
       <c r="H435" t="n">
         <v>34256</v>
@@ -13042,7 +13042,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H437" t="n">
         <v>60693</v>
@@ -13100,7 +13100,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H439" t="n">
         <v>106284</v>
@@ -13129,7 +13129,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.52134621143341</v>
+        <v>1.52134644985199</v>
       </c>
       <c r="H440" t="n">
         <v>37061</v>
@@ -13216,7 +13216,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H443" t="n">
         <v>662645</v>
@@ -13245,7 +13245,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.8010858297348</v>
+        <v>1.80108594894409</v>
       </c>
       <c r="H444" t="n">
         <v>1350440</v>
@@ -13274,7 +13274,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G445" t="n">
-        <v>1.80780625343323</v>
+        <v>1.80780637264252</v>
       </c>
       <c r="H445" t="n">
         <v>397899</v>
@@ -13303,7 +13303,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G446" t="n">
-        <v>1.78428471088409</v>
+        <v>1.78428483009338</v>
       </c>
       <c r="H446" t="n">
         <v>238019</v>
@@ -13361,7 +13361,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717551231384</v>
+        <v>1.93717527389526</v>
       </c>
       <c r="H448" t="n">
         <v>1651667</v>
@@ -13419,7 +13419,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.9405357837677</v>
+        <v>1.94053554534912</v>
       </c>
       <c r="H450" t="n">
         <v>303798</v>
@@ -13448,7 +13448,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H451" t="n">
         <v>274964</v>
@@ -13477,7 +13477,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757874965668</v>
+        <v>1.98757898807526</v>
       </c>
       <c r="H452" t="n">
         <v>517407</v>
@@ -13535,7 +13535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869401931763</v>
+        <v>1.91869413852692</v>
       </c>
       <c r="H454" t="n">
         <v>179721</v>
@@ -13564,7 +13564,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476888179779</v>
+        <v>1.84476912021637</v>
       </c>
       <c r="H455" t="n">
         <v>293919</v>
@@ -13622,7 +13622,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H457" t="n">
         <v>133644</v>
@@ -13709,7 +13709,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100501537323</v>
+        <v>1.79100513458252</v>
       </c>
       <c r="H460" t="n">
         <v>175490</v>
@@ -13767,7 +13767,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420401573181</v>
+        <v>1.77420389652252</v>
       </c>
       <c r="H462" t="n">
         <v>87616</v>
@@ -13854,7 +13854,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669098377228</v>
+        <v>1.87669134140015</v>
       </c>
       <c r="H465" t="n">
         <v>93915</v>
@@ -13912,7 +13912,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173162937164</v>
       </c>
       <c r="H467" t="n">
         <v>129153</v>
@@ -13941,7 +13941,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533410549164</v>
+        <v>1.91533386707306</v>
       </c>
       <c r="H468" t="n">
         <v>291840</v>
@@ -14173,7 +14173,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341164588928</v>
+        <v>1.88341176509857</v>
       </c>
       <c r="H476" t="n">
         <v>139588</v>
@@ -14202,7 +14202,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308874607086</v>
+        <v>1.84308898448944</v>
       </c>
       <c r="H477" t="n">
         <v>210138</v>
@@ -14231,7 +14231,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H478" t="n">
         <v>93091</v>
@@ -14260,7 +14260,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316944122314</v>
+        <v>1.85316956043243</v>
       </c>
       <c r="H479" t="n">
         <v>100214</v>
@@ -14347,7 +14347,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.6465151309967</v>
+        <v>1.64651525020599</v>
       </c>
       <c r="H482" t="n">
         <v>88167</v>
@@ -14376,7 +14376,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63475430011749</v>
+        <v>1.6347541809082</v>
       </c>
       <c r="H483" t="n">
         <v>59107</v>
@@ -14492,7 +14492,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763028144836</v>
+        <v>1.57763016223907</v>
       </c>
       <c r="H487" t="n">
         <v>65136</v>
@@ -14608,7 +14608,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G491" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H491" t="n">
         <v>85084</v>
@@ -14637,7 +14637,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G492" t="n">
-        <v>1.54654812812805</v>
+        <v>1.54654800891876</v>
       </c>
       <c r="H492" t="n">
         <v>70153</v>
@@ -14666,7 +14666,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H493" t="n">
         <v>23515</v>
@@ -14782,7 +14782,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H497" t="n">
         <v>118911</v>
@@ -14811,7 +14811,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531916618347</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H498" t="n">
         <v>229181</v>
@@ -14898,7 +14898,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299335002899</v>
+        <v>1.62299358844757</v>
       </c>
       <c r="H501" t="n">
         <v>82089</v>
@@ -14956,7 +14956,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451209545135</v>
+        <v>1.60451221466064</v>
       </c>
       <c r="H503" t="n">
         <v>18702</v>
@@ -15014,7 +15014,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459279060364</v>
+        <v>1.61459290981293</v>
       </c>
       <c r="H505" t="n">
         <v>51477</v>
@@ -15043,7 +15043,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H506" t="n">
         <v>34414</v>
@@ -15072,7 +15072,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887394428253</v>
+        <v>1.62887382507324</v>
       </c>
       <c r="H507" t="n">
         <v>38889</v>
@@ -15159,7 +15159,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267056941986</v>
+        <v>1.58267068862915</v>
       </c>
       <c r="H510" t="n">
         <v>44384</v>
@@ -15188,7 +15188,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090985774994</v>
+        <v>1.57090973854065</v>
       </c>
       <c r="H511" t="n">
         <v>27246</v>
@@ -15217,7 +15217,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535216331482</v>
+        <v>1.60535228252411</v>
       </c>
       <c r="H512" t="n">
         <v>44066</v>
@@ -15275,7 +15275,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G514" t="n">
-        <v>1.66163611412048</v>
+        <v>1.66163623332977</v>
       </c>
       <c r="H514" t="n">
         <v>105164</v>
@@ -15391,7 +15391,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323555469513</v>
+        <v>1.65323567390442</v>
       </c>
       <c r="H518" t="n">
         <v>361901</v>
@@ -15478,7 +15478,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827596187592</v>
+        <v>1.65827584266663</v>
       </c>
       <c r="H521" t="n">
         <v>58377</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851792812347</v>
+        <v>1.68851804733276</v>
       </c>
       <c r="H522" t="n">
         <v>255362</v>
@@ -15536,7 +15536,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H523" t="n">
         <v>146655</v>
@@ -15710,7 +15710,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H529" t="n">
         <v>236640</v>
@@ -15855,7 +15855,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533410549164</v>
+        <v>1.91533386707306</v>
       </c>
       <c r="H534" t="n">
         <v>163101</v>
@@ -15884,7 +15884,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82712781429291</v>
+        <v>1.82712769508362</v>
       </c>
       <c r="H535" t="n">
         <v>146091</v>
@@ -15913,7 +15913,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.7599231004715</v>
+        <v>1.75992298126221</v>
       </c>
       <c r="H536" t="n">
         <v>155319</v>
@@ -15971,7 +15971,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>1.83552837371826</v>
+        <v>1.83552825450897</v>
       </c>
       <c r="H538" t="n">
         <v>97475</v>
@@ -16261,7 +16261,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H548" t="n">
         <v>27650</v>
@@ -16290,7 +16290,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H549" t="n">
         <v>41493</v>
@@ -16377,7 +16377,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G552" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H552" t="n">
         <v>46221</v>
@@ -16406,7 +16406,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472130298615</v>
+        <v>1.73472118377686</v>
       </c>
       <c r="H553" t="n">
         <v>11561</v>
@@ -16493,7 +16493,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011736869812</v>
+        <v>1.68011748790741</v>
       </c>
       <c r="H556" t="n">
         <v>110142</v>
@@ -16551,7 +16551,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.70951962471008</v>
+        <v>1.70951974391937</v>
       </c>
       <c r="H558" t="n">
         <v>51378</v>
@@ -16580,7 +16580,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472130298615</v>
+        <v>1.73472118377686</v>
       </c>
       <c r="H559" t="n">
         <v>125349</v>
@@ -16812,7 +16812,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173162937164</v>
       </c>
       <c r="H567" t="n">
         <v>123060</v>
@@ -16841,7 +16841,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173162937164</v>
       </c>
       <c r="H568" t="n">
         <v>60488</v>
@@ -16899,7 +16899,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872725486755</v>
       </c>
       <c r="H570" t="n">
         <v>90250</v>
@@ -16957,7 +16957,7 @@
         <v>2.125</v>
       </c>
       <c r="G572" t="n">
-        <v>1.78512489795685</v>
+        <v>1.78512477874756</v>
       </c>
       <c r="H572" t="n">
         <v>93097</v>
@@ -17015,7 +17015,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>1.78092432022095</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H574" t="n">
         <v>39527</v>
@@ -17044,7 +17044,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H575" t="n">
         <v>126706</v>
@@ -17073,7 +17073,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H576" t="n">
         <v>42580</v>
@@ -17131,7 +17131,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>1.78092432022095</v>
+        <v>1.78092443943024</v>
       </c>
       <c r="H578" t="n">
         <v>72943</v>
@@ -17189,7 +17189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872725486755</v>
       </c>
       <c r="H580" t="n">
         <v>129414</v>
@@ -17363,7 +17363,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173162937164</v>
       </c>
       <c r="H586" t="n">
         <v>107760</v>
@@ -17392,7 +17392,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86913061141968</v>
+        <v>1.8691303730011</v>
       </c>
       <c r="H587" t="n">
         <v>102743</v>
@@ -17450,7 +17450,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.89013206958771</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H589" t="n">
         <v>435390</v>
@@ -17508,7 +17508,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853274822235</v>
+        <v>1.89853262901306</v>
       </c>
       <c r="H591" t="n">
         <v>268816</v>
@@ -17595,7 +17595,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253870010376</v>
+        <v>1.9825382232666</v>
       </c>
       <c r="H594" t="n">
         <v>224369</v>
@@ -17624,7 +17624,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.9699375629425</v>
+        <v>1.96993780136108</v>
       </c>
       <c r="H595" t="n">
         <v>316600</v>
@@ -17653,7 +17653,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>1.97833836078644</v>
+        <v>1.97833812236786</v>
       </c>
       <c r="H596" t="n">
         <v>162459</v>
@@ -17682,7 +17682,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G597" t="n">
-        <v>2.00774049758911</v>
+        <v>2.00774073600769</v>
       </c>
       <c r="H597" t="n">
         <v>339872</v>
@@ -17711,7 +17711,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.01614117622375</v>
+        <v>2.0161406993866</v>
       </c>
       <c r="H598" t="n">
         <v>203153</v>
@@ -17798,7 +17798,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093902111053</v>
+        <v>1.99093925952911</v>
       </c>
       <c r="H601" t="n">
         <v>580375</v>
@@ -17914,7 +17914,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H605" t="n">
         <v>545260</v>
@@ -17943,7 +17943,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H606" t="n">
         <v>207664</v>
@@ -17972,7 +17972,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G607" t="n">
-        <v>2.14214968681335</v>
+        <v>2.14214944839478</v>
       </c>
       <c r="H607" t="n">
         <v>147311</v>
@@ -18059,7 +18059,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316632270813</v>
+        <v>2.37316584587097</v>
       </c>
       <c r="H610" t="n">
         <v>1841688</v>
@@ -18088,7 +18088,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.410968542099</v>
+        <v>2.41096830368042</v>
       </c>
       <c r="H611" t="n">
         <v>984452</v>
@@ -18117,7 +18117,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177573204041</v>
+        <v>2.51177549362183</v>
       </c>
       <c r="H612" t="n">
         <v>948656</v>
@@ -18146,7 +18146,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>2.3143618106842</v>
+        <v>2.31436204910278</v>
       </c>
       <c r="H613" t="n">
         <v>1745359</v>
@@ -18204,7 +18204,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>2.49497437477112</v>
+        <v>2.4949746131897</v>
       </c>
       <c r="H615" t="n">
         <v>1432335</v>
@@ -18233,7 +18233,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>2.54537773132324</v>
+        <v>2.54537796974182</v>
       </c>
       <c r="H616" t="n">
         <v>745527</v>
@@ -18320,7 +18320,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.7469916343689</v>
+        <v>2.74699211120605</v>
       </c>
       <c r="H619" t="n">
         <v>726908</v>
@@ -18407,7 +18407,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>2.83939862251282</v>
+        <v>2.8393988609314</v>
       </c>
       <c r="H622" t="n">
         <v>500692</v>
@@ -18465,7 +18465,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519816398621</v>
+        <v>2.83519792556763</v>
       </c>
       <c r="H624" t="n">
         <v>415404</v>
@@ -18494,7 +18494,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00320982933044</v>
+        <v>3.00321006774902</v>
       </c>
       <c r="H625" t="n">
         <v>870894</v>
@@ -18523,7 +18523,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G626" t="n">
-        <v>3.13761901855469</v>
+        <v>3.13761925697327</v>
       </c>
       <c r="H626" t="n">
         <v>800677</v>
@@ -18552,7 +18552,7 @@
         <v>3.75</v>
       </c>
       <c r="G627" t="n">
-        <v>3.15022039413452</v>
+        <v>3.15022015571594</v>
       </c>
       <c r="H627" t="n">
         <v>455671</v>
@@ -18581,7 +18581,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661767959595</v>
+        <v>3.11661791801453</v>
       </c>
       <c r="H628" t="n">
         <v>314606</v>
@@ -18668,7 +18668,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10821747779846</v>
+        <v>3.10821723937988</v>
       </c>
       <c r="H631" t="n">
         <v>698546</v>
@@ -18726,7 +18726,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.1628212928772</v>
+        <v>3.16282105445862</v>
       </c>
       <c r="H633" t="n">
         <v>315758</v>
@@ -18755,7 +18755,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H634" t="n">
         <v>300032</v>
@@ -18784,7 +18784,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422574996948</v>
       </c>
       <c r="H635" t="n">
         <v>397354</v>
@@ -18842,7 +18842,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422574996948</v>
       </c>
       <c r="H637" t="n">
         <v>198942</v>
@@ -18929,7 +18929,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703585624695</v>
+        <v>3.37703609466553</v>
       </c>
       <c r="H640" t="n">
         <v>341923</v>
@@ -18958,7 +18958,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>3.44424080848694</v>
+        <v>3.44424057006836</v>
       </c>
       <c r="H641" t="n">
         <v>310949</v>
@@ -19016,7 +19016,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>3.44424080848694</v>
+        <v>3.44424057006836</v>
       </c>
       <c r="H643" t="n">
         <v>257284</v>
@@ -19103,7 +19103,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645245552063</v>
+        <v>3.61645269393921</v>
       </c>
       <c r="H646" t="n">
         <v>320057</v>
@@ -19161,7 +19161,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446435928345</v>
+        <v>3.78446459770203</v>
       </c>
       <c r="H648" t="n">
         <v>331005</v>
@@ -19190,7 +19190,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827604293823</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H649" t="n">
         <v>536313</v>
@@ -19219,7 +19219,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887331008911</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H650" t="n">
         <v>324176</v>
@@ -19277,7 +19277,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887331008911</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H652" t="n">
         <v>229460</v>
@@ -19451,7 +19451,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.7970654964447</v>
+        <v>3.79706525802612</v>
       </c>
       <c r="H658" t="n">
         <v>467873</v>
@@ -19538,7 +19538,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H661" t="n">
         <v>680135</v>
@@ -19886,7 +19886,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H673" t="n">
         <v>834494</v>
@@ -19915,7 +19915,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.821937084198</v>
+        <v>4.82193660736084</v>
       </c>
       <c r="H674" t="n">
         <v>840694</v>
@@ -19944,7 +19944,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553979873657</v>
+        <v>4.85553932189941</v>
       </c>
       <c r="H675" t="n">
         <v>602751</v>
@@ -20118,7 +20118,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G681" t="n">
-        <v>4.73793125152588</v>
+        <v>4.73793077468872</v>
       </c>
       <c r="H681" t="n">
         <v>259923</v>
@@ -20176,7 +20176,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>4.65392541885376</v>
+        <v>4.6539249420166</v>
       </c>
       <c r="H683" t="n">
         <v>163478</v>
@@ -20437,7 +20437,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.33470296859741</v>
+        <v>4.33470344543457</v>
       </c>
       <c r="H692" t="n">
         <v>263689</v>
@@ -20466,7 +20466,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749897003174</v>
       </c>
       <c r="H693" t="n">
         <v>130168</v>
@@ -20524,7 +20524,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.05748319625854</v>
+        <v>4.0574836730957</v>
       </c>
       <c r="H695" t="n">
         <v>282929</v>
@@ -20582,7 +20582,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95667672157288</v>
+        <v>3.95667624473572</v>
       </c>
       <c r="H697" t="n">
         <v>144157</v>
@@ -20640,7 +20640,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286479949951</v>
+        <v>3.79286503791809</v>
       </c>
       <c r="H699" t="n">
         <v>286966</v>
@@ -20669,7 +20669,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.73826122283936</v>
+        <v>3.7382607460022</v>
       </c>
       <c r="H700" t="n">
         <v>569444</v>
@@ -20785,7 +20785,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H704" t="n">
         <v>848630</v>
@@ -20814,7 +20814,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>3.18382263183594</v>
+        <v>3.18382239341736</v>
       </c>
       <c r="H705" t="n">
         <v>692837</v>
@@ -20872,7 +20872,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H707" t="n">
         <v>426984</v>
@@ -20930,7 +20930,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H709" t="n">
         <v>375579</v>
@@ -20959,7 +20959,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G710" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H710" t="n">
         <v>559647</v>
@@ -20988,7 +20988,7 @@
         <v>3.5</v>
       </c>
       <c r="G711" t="n">
-        <v>2.94020557403564</v>
+        <v>2.94020533561707</v>
       </c>
       <c r="H711" t="n">
         <v>252013</v>
@@ -21017,7 +21017,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.95280647277832</v>
+        <v>2.9528067111969</v>
       </c>
       <c r="H712" t="n">
         <v>247551</v>
@@ -21104,7 +21104,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G715" t="n">
-        <v>2.80579590797424</v>
+        <v>2.80579614639282</v>
       </c>
       <c r="H715" t="n">
         <v>252342</v>
@@ -21133,7 +21133,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>2.81419682502747</v>
+        <v>2.81419658660889</v>
       </c>
       <c r="H716" t="n">
         <v>263881</v>
@@ -21162,7 +21162,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G717" t="n">
-        <v>2.93180465698242</v>
+        <v>2.931804895401</v>
       </c>
       <c r="H717" t="n">
         <v>318723</v>
@@ -21307,7 +21307,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H722" t="n">
         <v>404216</v>
@@ -21336,7 +21336,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860577583313</v>
+        <v>2.94860601425171</v>
       </c>
       <c r="H723" t="n">
         <v>797687</v>
@@ -21365,7 +21365,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H724" t="n">
         <v>1093352</v>
@@ -21423,7 +21423,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.14181971549988</v>
+        <v>3.1418194770813</v>
       </c>
       <c r="H726" t="n">
         <v>367513</v>
@@ -21452,7 +21452,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G727" t="n">
-        <v>3.13761901855469</v>
+        <v>3.13761925697327</v>
       </c>
       <c r="H727" t="n">
         <v>261268</v>
@@ -21481,7 +21481,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G728" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H728" t="n">
         <v>411240</v>
@@ -21510,7 +21510,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>3.31823182106018</v>
+        <v>3.31823205947876</v>
       </c>
       <c r="H729" t="n">
         <v>295648</v>
@@ -21539,7 +21539,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G730" t="n">
-        <v>3.33083295822144</v>
+        <v>3.33083271980286</v>
       </c>
       <c r="H730" t="n">
         <v>378411</v>
@@ -21568,7 +21568,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>3.28883004188538</v>
+        <v>3.2888298034668</v>
       </c>
       <c r="H731" t="n">
         <v>228748</v>
@@ -21597,7 +21597,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G732" t="n">
-        <v>3.23422598838806</v>
+        <v>3.23422574996948</v>
       </c>
       <c r="H732" t="n">
         <v>294785</v>
@@ -21626,7 +21626,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>3.18382263183594</v>
+        <v>3.18382239341736</v>
       </c>
       <c r="H733" t="n">
         <v>160282</v>
@@ -21655,7 +21655,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G734" t="n">
-        <v>3.12081813812256</v>
+        <v>3.12081789970398</v>
       </c>
       <c r="H734" t="n">
         <v>240290</v>
@@ -21713,7 +21713,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H736" t="n">
         <v>239182</v>
@@ -21829,7 +21829,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>2.79319524765015</v>
+        <v>2.79319500923157</v>
       </c>
       <c r="H740" t="n">
         <v>100946</v>
@@ -21858,7 +21858,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>2.83939862251282</v>
+        <v>2.8393988609314</v>
       </c>
       <c r="H741" t="n">
         <v>67826</v>
@@ -21887,7 +21887,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G742" t="n">
-        <v>2.88140153884888</v>
+        <v>2.88140177726746</v>
       </c>
       <c r="H742" t="n">
         <v>137508</v>
@@ -21916,7 +21916,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92760443687439</v>
+        <v>2.92760467529297</v>
       </c>
       <c r="H743" t="n">
         <v>213240</v>
@@ -21945,7 +21945,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902419090271</v>
+        <v>3.20902442932129</v>
       </c>
       <c r="H744" t="n">
         <v>370069</v>
@@ -22003,7 +22003,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.2762291431427</v>
+        <v>3.27622938156128</v>
       </c>
       <c r="H746" t="n">
         <v>277360</v>
@@ -22264,7 +22264,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060869216919</v>
+        <v>2.99060893058777</v>
       </c>
       <c r="H755" t="n">
         <v>113781</v>
@@ -22293,7 +22293,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>2.96960759162903</v>
+        <v>2.96960783004761</v>
       </c>
       <c r="H756" t="n">
         <v>215161</v>
@@ -22351,7 +22351,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418176651001</v>
+        <v>2.60418200492859</v>
       </c>
       <c r="H758" t="n">
         <v>295455</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H759" t="n">
         <v>179239</v>
@@ -22496,7 +22496,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.79739570617676</v>
+        <v>2.79739546775818</v>
       </c>
       <c r="H763" t="n">
         <v>410459</v>
@@ -22554,7 +22554,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H765" t="n">
         <v>153244</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>2.94020557403564</v>
+        <v>2.94020533561707</v>
       </c>
       <c r="H766" t="n">
         <v>120970</v>
@@ -22612,7 +22612,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400219917297</v>
+        <v>2.89400243759155</v>
       </c>
       <c r="H767" t="n">
         <v>120075</v>
@@ -22641,7 +22641,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G768" t="n">
-        <v>3.07461476325989</v>
+        <v>3.07461500167847</v>
       </c>
       <c r="H768" t="n">
         <v>279490</v>
@@ -22786,7 +22786,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00741004943848</v>
+        <v>3.00741028785706</v>
       </c>
       <c r="H773" t="n">
         <v>71849</v>
@@ -22844,7 +22844,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G775" t="n">
-        <v>3.07461476325989</v>
+        <v>3.07461500167847</v>
       </c>
       <c r="H775" t="n">
         <v>48253</v>
@@ -22931,7 +22931,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G778" t="n">
-        <v>3.47784304618835</v>
+        <v>3.47784280776978</v>
       </c>
       <c r="H778" t="n">
         <v>449236</v>
@@ -22960,7 +22960,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346278190613</v>
+        <v>3.76346325874329</v>
       </c>
       <c r="H779" t="n">
         <v>689270</v>
@@ -22989,7 +22989,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026413917542</v>
+        <v>3.78026437759399</v>
       </c>
       <c r="H780" t="n">
         <v>599313</v>
@@ -23018,7 +23018,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>3.73406100273132</v>
+        <v>3.7340612411499</v>
       </c>
       <c r="H781" t="n">
         <v>247790</v>
@@ -23134,7 +23134,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H785" t="n">
         <v>283610</v>
@@ -23221,7 +23221,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.97347784042358</v>
+        <v>3.97347831726074</v>
       </c>
       <c r="H788" t="n">
         <v>224507</v>
@@ -23250,7 +23250,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G789" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H789" t="n">
         <v>258856</v>
@@ -23279,7 +23279,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G790" t="n">
-        <v>4.00287961959839</v>
+        <v>4.00288009643555</v>
       </c>
       <c r="H790" t="n">
         <v>220886</v>
@@ -23308,7 +23308,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486771583557</v>
+        <v>3.83486843109131</v>
       </c>
       <c r="H791" t="n">
         <v>191763</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.70465898513794</v>
+        <v>3.70465874671936</v>
       </c>
       <c r="H792" t="n">
         <v>292131</v>
@@ -23366,7 +23366,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G793" t="n">
-        <v>3.84326815605164</v>
+        <v>3.84326839447021</v>
       </c>
       <c r="H793" t="n">
         <v>223832</v>
@@ -23395,7 +23395,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>3.81806659698486</v>
+        <v>3.81806683540344</v>
       </c>
       <c r="H794" t="n">
         <v>91725</v>
@@ -23453,7 +23453,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.8810715675354</v>
+        <v>3.88107109069824</v>
       </c>
       <c r="H796" t="n">
         <v>95197</v>
@@ -23482,7 +23482,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.97347784042358</v>
+        <v>3.97347831726074</v>
       </c>
       <c r="H797" t="n">
         <v>63961</v>
@@ -23540,7 +23540,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827604293823</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H799" t="n">
         <v>128867</v>
@@ -23569,7 +23569,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147492408752</v>
+        <v>3.93147444725037</v>
       </c>
       <c r="H800" t="n">
         <v>132720</v>
@@ -23656,7 +23656,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507740020752</v>
+        <v>3.9650764465332</v>
       </c>
       <c r="H803" t="n">
         <v>122911</v>
@@ -23743,7 +23743,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126523971558</v>
+        <v>3.80126595497131</v>
       </c>
       <c r="H806" t="n">
         <v>74797</v>
@@ -23772,7 +23772,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885896682739</v>
+        <v>3.70885968208313</v>
       </c>
       <c r="H807" t="n">
         <v>145265</v>
@@ -23801,7 +23801,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165425300598</v>
+        <v>3.64165449142456</v>
       </c>
       <c r="H808" t="n">
         <v>150135</v>
@@ -23888,7 +23888,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G811" t="n">
-        <v>3.45684146881104</v>
+        <v>3.45684170722961</v>
       </c>
       <c r="H811" t="n">
         <v>230634</v>
@@ -23946,7 +23946,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845537185669</v>
+        <v>3.65845561027527</v>
       </c>
       <c r="H813" t="n">
         <v>431429</v>
@@ -24004,7 +24004,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G815" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H815" t="n">
         <v>624543</v>
@@ -24033,7 +24033,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208724975586</v>
+        <v>4.11208772659302</v>
       </c>
       <c r="H816" t="n">
         <v>491127</v>
@@ -24149,7 +24149,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987512588501</v>
+        <v>3.93987560272217</v>
       </c>
       <c r="H820" t="n">
         <v>315880</v>
@@ -24236,7 +24236,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G823" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H823" t="n">
         <v>143208</v>
@@ -24265,7 +24265,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228139877319</v>
       </c>
       <c r="H824" t="n">
         <v>280086</v>
@@ -24294,7 +24294,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>4.01548099517822</v>
+        <v>4.01548147201538</v>
       </c>
       <c r="H825" t="n">
         <v>247911</v>
@@ -24323,7 +24323,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688497543335</v>
+        <v>4.08688545227051</v>
       </c>
       <c r="H826" t="n">
         <v>196766</v>
@@ -24439,7 +24439,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631734848022</v>
+        <v>4.53631687164307</v>
       </c>
       <c r="H830" t="n">
         <v>1165706</v>
@@ -24468,7 +24468,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>4.72953128814697</v>
+        <v>4.72953033447266</v>
       </c>
       <c r="H831" t="n">
         <v>734870</v>
@@ -24526,7 +24526,7 @@
         <v>5.5</v>
       </c>
       <c r="G833" t="n">
-        <v>4.62032318115234</v>
+        <v>4.62032270431519</v>
       </c>
       <c r="H833" t="n">
         <v>457602</v>
@@ -24555,7 +24555,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.57832002639771</v>
+        <v>4.57831954956055</v>
       </c>
       <c r="H834" t="n">
         <v>153136</v>
@@ -24642,7 +24642,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950117111206</v>
+        <v>4.30950164794922</v>
       </c>
       <c r="H837" t="n">
         <v>277391</v>
@@ -24671,7 +24671,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>4.25909805297852</v>
+        <v>4.25909757614136</v>
       </c>
       <c r="H838" t="n">
         <v>581777</v>
@@ -24700,7 +24700,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749897003174</v>
       </c>
       <c r="H839" t="n">
         <v>229262</v>
@@ -24758,7 +24758,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228139877319</v>
       </c>
       <c r="H841" t="n">
         <v>258680</v>
@@ -24874,7 +24874,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.97347784042358</v>
+        <v>3.97347831726074</v>
       </c>
       <c r="H845" t="n">
         <v>787756</v>
@@ -24990,7 +24990,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>3.99369192123413</v>
+        <v>3.99369144439697</v>
       </c>
       <c r="H849" t="n">
         <v>205858</v>
@@ -25048,7 +25048,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H851" t="n">
         <v>279899</v>
@@ -25135,7 +25135,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71274971961975</v>
+        <v>3.71275043487549</v>
       </c>
       <c r="H854" t="n">
         <v>237445</v>
@@ -25193,7 +25193,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868274688721</v>
+        <v>3.73868298530579</v>
       </c>
       <c r="H856" t="n">
         <v>149487</v>
@@ -25251,7 +25251,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G858" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707224845886</v>
       </c>
       <c r="H858" t="n">
         <v>143919</v>
@@ -25309,7 +25309,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157007217407</v>
+        <v>3.91157054901123</v>
       </c>
       <c r="H860" t="n">
         <v>222935</v>
@@ -25338,7 +25338,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8337709903717</v>
+        <v>3.83377075195312</v>
       </c>
       <c r="H861" t="n">
         <v>131749</v>
@@ -25367,7 +25367,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H862" t="n">
         <v>185171</v>
@@ -25396,7 +25396,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G863" t="n">
-        <v>3.6263062953949</v>
+        <v>3.62630653381348</v>
       </c>
       <c r="H863" t="n">
         <v>155367</v>
@@ -25425,7 +25425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707224845886</v>
       </c>
       <c r="H864" t="n">
         <v>92135</v>
@@ -25454,7 +25454,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359521865845</v>
+        <v>3.64359545707703</v>
       </c>
       <c r="H865" t="n">
         <v>139539</v>
@@ -25570,7 +25570,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>3.37562036514282</v>
+        <v>3.37562012672424</v>
       </c>
       <c r="H869" t="n">
         <v>157461</v>
@@ -25657,7 +25657,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H872" t="n">
         <v>217721</v>
@@ -25715,7 +25715,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>3.52689647674561</v>
+        <v>3.52689623832703</v>
       </c>
       <c r="H874" t="n">
         <v>98751</v>
@@ -25802,7 +25802,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>3.38858675956726</v>
+        <v>3.38858699798584</v>
       </c>
       <c r="H877" t="n">
         <v>342054</v>
@@ -25947,7 +25947,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G882" t="n">
-        <v>3.36265397071838</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H882" t="n">
         <v>184685</v>
@@ -25976,7 +25976,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G883" t="n">
-        <v>3.39723134040833</v>
+        <v>3.39723110198975</v>
       </c>
       <c r="H883" t="n">
         <v>257002</v>
@@ -26005,7 +26005,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H884" t="n">
         <v>244267</v>
@@ -26092,7 +26092,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163293838501</v>
+        <v>3.24163269996643</v>
       </c>
       <c r="H887" t="n">
         <v>163491</v>
@@ -26121,7 +26121,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137762069702</v>
+        <v>3.21137738227844</v>
       </c>
       <c r="H888" t="n">
         <v>151557</v>
@@ -26150,7 +26150,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.22434425354004</v>
+        <v>3.22434401512146</v>
       </c>
       <c r="H889" t="n">
         <v>96520</v>
@@ -26208,7 +26208,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H891" t="n">
         <v>200140</v>
@@ -26295,7 +26295,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H894" t="n">
         <v>85735</v>
@@ -26353,7 +26353,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H896" t="n">
         <v>119831</v>
@@ -26498,7 +26498,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G901" t="n">
-        <v>3.36265397071838</v>
+        <v>3.3626537322998</v>
       </c>
       <c r="H901" t="n">
         <v>458958</v>
@@ -26643,7 +26643,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H906" t="n">
         <v>93066</v>
@@ -26672,7 +26672,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705556869507</v>
+        <v>3.20705533027649</v>
       </c>
       <c r="H907" t="n">
         <v>135848</v>
@@ -26933,7 +26933,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68681693077087</v>
+        <v>3.68681716918945</v>
       </c>
       <c r="H916" t="n">
         <v>212057</v>
@@ -26962,7 +26962,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G917" t="n">
-        <v>3.6479172706604</v>
+        <v>3.64791703224182</v>
       </c>
       <c r="H917" t="n">
         <v>154954</v>
@@ -26991,7 +26991,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H918" t="n">
         <v>412035</v>
@@ -27078,7 +27078,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G921" t="n">
-        <v>3.35833168029785</v>
+        <v>3.35833144187927</v>
       </c>
       <c r="H921" t="n">
         <v>142300</v>
@@ -27136,7 +27136,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H923" t="n">
         <v>275779</v>
@@ -27194,7 +27194,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G925" t="n">
-        <v>3.66520595550537</v>
+        <v>3.66520571708679</v>
       </c>
       <c r="H925" t="n">
         <v>357166</v>
@@ -27223,7 +27223,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444024085999</v>
+        <v>3.57444071769714</v>
       </c>
       <c r="H926" t="n">
         <v>367003</v>
@@ -27252,7 +27252,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G927" t="n">
-        <v>3.59172892570496</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H927" t="n">
         <v>182647</v>
@@ -27397,7 +27397,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>3.58308458328247</v>
+        <v>3.58308506011963</v>
       </c>
       <c r="H932" t="n">
         <v>271781</v>
@@ -27455,7 +27455,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>3.60901761054993</v>
+        <v>3.60901808738708</v>
       </c>
       <c r="H934" t="n">
         <v>189340</v>
@@ -27542,7 +27542,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960779190063</v>
+        <v>3.50960755348206</v>
       </c>
       <c r="H937" t="n">
         <v>213268</v>
@@ -27600,7 +27600,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G939" t="n">
-        <v>3.47070789337158</v>
+        <v>3.47070813179016</v>
       </c>
       <c r="H939" t="n">
         <v>121939</v>
@@ -27629,7 +27629,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H940" t="n">
         <v>107731</v>
@@ -27658,7 +27658,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H941" t="n">
         <v>236550</v>
@@ -27716,7 +27716,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>3.8726704120636</v>
+        <v>3.87267088890076</v>
       </c>
       <c r="H943" t="n">
         <v>739272</v>
@@ -27745,7 +27745,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H944" t="n">
         <v>271076</v>
@@ -27774,7 +27774,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H945" t="n">
         <v>315309</v>
@@ -27803,7 +27803,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.61766195297241</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H946" t="n">
         <v>539098</v>
@@ -27832,7 +27832,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G947" t="n">
-        <v>3.6263062953949</v>
+        <v>3.62630653381348</v>
       </c>
       <c r="H947" t="n">
         <v>251889</v>
@@ -27948,7 +27948,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>3.60901761054993</v>
+        <v>3.60901808738708</v>
       </c>
       <c r="H951" t="n">
         <v>169897</v>
@@ -28006,7 +28006,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>3.61766195297241</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H953" t="n">
         <v>46261</v>
@@ -28064,7 +28064,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H955" t="n">
         <v>118165</v>
@@ -28093,7 +28093,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231886863708</v>
       </c>
       <c r="H956" t="n">
         <v>153789</v>
@@ -28151,7 +28151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231886863708</v>
       </c>
       <c r="H958" t="n">
         <v>64692</v>
@@ -28180,7 +28180,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49231910705566</v>
+        <v>3.49231886863708</v>
       </c>
       <c r="H959" t="n">
         <v>94617</v>
@@ -28209,7 +28209,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638631820679</v>
+        <v>3.46638655662537</v>
       </c>
       <c r="H960" t="n">
         <v>67763</v>
@@ -28238,7 +28238,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45341920852661</v>
+        <v>3.45341944694519</v>
       </c>
       <c r="H961" t="n">
         <v>86978</v>
@@ -28441,7 +28441,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054927825928</v>
+        <v>3.79054951667786</v>
       </c>
       <c r="H968" t="n">
         <v>389865</v>
@@ -28615,7 +28615,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724778175354</v>
+        <v>3.9072482585907</v>
       </c>
       <c r="H974" t="n">
         <v>225485</v>
@@ -28644,7 +28644,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="n">
-        <v>3.80351591110229</v>
+        <v>3.80351567268372</v>
       </c>
       <c r="H975" t="n">
         <v>152225</v>
@@ -28789,7 +28789,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H980" t="n">
         <v>205384</v>
@@ -28847,7 +28847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893854141235</v>
+        <v>3.76893830299377</v>
       </c>
       <c r="H982" t="n">
         <v>188043</v>
@@ -28934,7 +28934,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="n">
-        <v>4.06284666061401</v>
+        <v>4.06284618377686</v>
       </c>
       <c r="H985" t="n">
         <v>849398</v>
@@ -28992,7 +28992,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699270248413</v>
+        <v>3.87699317932129</v>
       </c>
       <c r="H987" t="n">
         <v>315026</v>
@@ -29050,7 +29050,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911455154419</v>
+        <v>3.95911407470703</v>
       </c>
       <c r="H989" t="n">
         <v>256400</v>
@@ -29282,7 +29282,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319772720337</v>
+        <v>4.44319820404053</v>
       </c>
       <c r="H997" t="n">
         <v>239472</v>
@@ -29340,7 +29340,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>4.5037088394165</v>
+        <v>4.50370836257935</v>
       </c>
       <c r="H999" t="n">
         <v>355133</v>
@@ -29369,7 +29369,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.60744047164917</v>
+        <v>4.60744094848633</v>
       </c>
       <c r="H1000" t="n">
         <v>319449</v>
@@ -29398,7 +29398,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1001" t="n">
         <v>803711</v>
@@ -29427,7 +29427,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.60744047164917</v>
+        <v>4.60744094848633</v>
       </c>
       <c r="H1002" t="n">
         <v>332585</v>
@@ -29485,7 +29485,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828525543213</v>
       </c>
       <c r="H1004" t="n">
         <v>150662</v>
@@ -29543,7 +29543,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1006" t="n">
         <v>237220</v>
@@ -29572,7 +29572,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1007" t="n">
         <v>291085</v>
@@ -29659,7 +29659,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1010" t="n">
         <v>284503</v>
@@ -29688,7 +29688,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.70252895355225</v>
+        <v>4.70252847671509</v>
       </c>
       <c r="H1011" t="n">
         <v>723932</v>
@@ -29775,7 +29775,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.88406038284302</v>
+        <v>4.88405990600586</v>
       </c>
       <c r="H1014" t="n">
         <v>313672</v>
@@ -29833,7 +29833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1016" t="n">
         <v>142573</v>
@@ -29891,7 +29891,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.61608552932739</v>
+        <v>4.61608505249023</v>
       </c>
       <c r="H1018" t="n">
         <v>471367</v>
@@ -29920,7 +29920,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659521102905</v>
+        <v>4.67659568786621</v>
       </c>
       <c r="H1019" t="n">
         <v>318021</v>
@@ -30007,7 +30007,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.7889723777771</v>
+        <v>4.78897190093994</v>
       </c>
       <c r="H1022" t="n">
         <v>293100</v>
@@ -30036,7 +30036,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.90999269485474</v>
+        <v>4.90999317169189</v>
       </c>
       <c r="H1023" t="n">
         <v>409189</v>
@@ -30065,7 +30065,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84083843231201</v>
+        <v>4.84083795547485</v>
       </c>
       <c r="H1024" t="n">
         <v>111612</v>
@@ -30094,7 +30094,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1025" t="n">
         <v>190180</v>
@@ -30123,7 +30123,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1026" t="n">
         <v>196836</v>
@@ -30152,7 +30152,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1027" t="n">
         <v>362151</v>
@@ -30181,7 +30181,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1028" t="n">
         <v>190796</v>
@@ -30210,7 +30210,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.88406038284302</v>
+        <v>4.88405990600586</v>
       </c>
       <c r="H1029" t="n">
         <v>479469</v>
@@ -30239,7 +30239,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.07423639297485</v>
+        <v>5.0742359161377</v>
       </c>
       <c r="H1030" t="n">
         <v>666781</v>
@@ -30268,7 +30268,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.28170013427734</v>
+        <v>5.28170108795166</v>
       </c>
       <c r="H1031" t="n">
         <v>1366658</v>
@@ -30297,7 +30297,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340709686279</v>
+        <v>5.65340757369995</v>
       </c>
       <c r="H1032" t="n">
         <v>1195444</v>
@@ -30326,7 +30326,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.49780893325806</v>
+        <v>5.49780941009521</v>
       </c>
       <c r="H1033" t="n">
         <v>970432</v>
@@ -30355,7 +30355,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.28170013427734</v>
+        <v>5.28170108795166</v>
       </c>
       <c r="H1034" t="n">
         <v>955078</v>
@@ -30442,7 +30442,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1037" t="n">
         <v>327363</v>
@@ -30471,7 +30471,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.6679515838623</v>
+        <v>4.66795110702515</v>
       </c>
       <c r="H1038" t="n">
         <v>423612</v>
@@ -30529,7 +30529,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.60744047164917</v>
+        <v>4.60744094848633</v>
       </c>
       <c r="H1040" t="n">
         <v>242251</v>
@@ -30558,7 +30558,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.55557489395142</v>
+        <v>4.55557441711426</v>
       </c>
       <c r="H1041" t="n">
         <v>544975</v>
@@ -30587,7 +30587,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.56421947479248</v>
+        <v>4.56421899795532</v>
       </c>
       <c r="H1042" t="n">
         <v>640983</v>
@@ -30616,7 +30616,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828525543213</v>
       </c>
       <c r="H1043" t="n">
         <v>234871</v>
@@ -30790,7 +30790,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895545959473</v>
+        <v>4.27895498275757</v>
       </c>
       <c r="H1049" t="n">
         <v>418848</v>
@@ -30848,7 +30848,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.61608552932739</v>
+        <v>4.61608505249023</v>
       </c>
       <c r="H1051" t="n">
         <v>527025</v>
@@ -30877,7 +30877,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828573226929</v>
+        <v>4.53828525543213</v>
       </c>
       <c r="H1052" t="n">
         <v>475739</v>
@@ -30906,7 +30906,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.0153021812439</v>
+        <v>4.01530265808105</v>
       </c>
       <c r="H1053" t="n">
         <v>585815</v>
@@ -30964,7 +30964,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970425605774</v>
+        <v>3.8597047328949</v>
       </c>
       <c r="H1055" t="n">
         <v>847899</v>
@@ -31022,7 +31022,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.82512664794922</v>
+        <v>3.8251268863678</v>
       </c>
       <c r="H1057" t="n">
         <v>541802</v>
@@ -31051,7 +31051,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.66520595550537</v>
+        <v>3.66520571708679</v>
       </c>
       <c r="H1058" t="n">
         <v>315473</v>
@@ -31109,7 +31109,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59172892570496</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H1060" t="n">
         <v>379798</v>
@@ -31138,7 +31138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H1061" t="n">
         <v>283526</v>
@@ -31167,7 +31167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.39723134040833</v>
+        <v>3.39723110198975</v>
       </c>
       <c r="H1062" t="n">
         <v>449166</v>
@@ -31196,7 +31196,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.02984619140625</v>
+        <v>3.02984642982483</v>
       </c>
       <c r="H1063" t="n">
         <v>357198</v>
@@ -31254,7 +31254,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15086698532104</v>
+        <v>3.15086722373962</v>
       </c>
       <c r="H1065" t="n">
         <v>1041323</v>
@@ -31283,7 +31283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085006713867</v>
+        <v>2.64085054397583</v>
       </c>
       <c r="H1066" t="n">
         <v>650023</v>
@@ -31312,7 +31312,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.67110538482666</v>
+        <v>2.67110514640808</v>
       </c>
       <c r="H1067" t="n">
         <v>618359</v>
@@ -31341,7 +31341,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287497520447</v>
+        <v>2.37287521362305</v>
       </c>
       <c r="H1068" t="n">
         <v>448476</v>
@@ -31370,7 +31370,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.38151979446411</v>
+        <v>2.38152003288269</v>
       </c>
       <c r="H1069" t="n">
         <v>130604</v>
@@ -31428,7 +31428,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.9363352060318</v>
+        <v>1.93633544445038</v>
       </c>
       <c r="H1071" t="n">
         <v>276781</v>
@@ -31457,7 +31457,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.04006767272949</v>
+        <v>2.04006743431091</v>
       </c>
       <c r="H1072" t="n">
         <v>436477</v>
@@ -31486,7 +31486,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.18702149391174</v>
+        <v>2.18702173233032</v>
       </c>
       <c r="H1073" t="n">
         <v>423283</v>
@@ -31573,7 +31573,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.46364092826843</v>
+        <v>2.46364068984985</v>
       </c>
       <c r="H1076" t="n">
         <v>308632</v>
@@ -31660,7 +31660,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.40313053131104</v>
+        <v>2.40313029289246</v>
       </c>
       <c r="H1079" t="n">
         <v>314475</v>
@@ -31718,7 +31718,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584184646606</v>
+        <v>2.38584160804749</v>
       </c>
       <c r="H1081" t="n">
         <v>211093</v>
@@ -31747,7 +31747,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.40313053131104</v>
+        <v>2.40313029289246</v>
       </c>
       <c r="H1082" t="n">
         <v>200547</v>
@@ -31805,7 +31805,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.65381669998169</v>
+        <v>2.65381693840027</v>
       </c>
       <c r="H1084" t="n">
         <v>782496</v>
@@ -31892,7 +31892,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.01255702972412</v>
+        <v>3.0125572681427</v>
       </c>
       <c r="H1087" t="n">
         <v>431366</v>
@@ -31921,7 +31921,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.8267035484314</v>
+        <v>2.82670378684998</v>
       </c>
       <c r="H1088" t="n">
         <v>426909</v>
@@ -31950,7 +31950,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187109947205</v>
+        <v>2.76187133789062</v>
       </c>
       <c r="H1089" t="n">
         <v>247451</v>
@@ -32008,7 +32008,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399223327637</v>
+        <v>2.84399247169495</v>
       </c>
       <c r="H1091" t="n">
         <v>383489</v>
@@ -32095,7 +32095,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.88289213180542</v>
+        <v>2.882892370224</v>
       </c>
       <c r="H1094" t="n">
         <v>580788</v>
@@ -32124,7 +32124,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.766193151474</v>
+        <v>2.76619338989258</v>
       </c>
       <c r="H1095" t="n">
         <v>290880</v>
@@ -32211,7 +32211,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.0341682434082</v>
+        <v>3.03416848182678</v>
       </c>
       <c r="H1098" t="n">
         <v>422193</v>
@@ -32240,7 +32240,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1099" t="n">
         <v>692765</v>
@@ -32298,7 +32298,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1101" t="n">
         <v>413566</v>
@@ -32385,7 +32385,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1104" t="n">
         <v>284338</v>
@@ -32443,7 +32443,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.79609537124634</v>
+        <v>2.79609560966492</v>
       </c>
       <c r="H1106" t="n">
         <v>469810</v>
@@ -32501,7 +32501,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.66123604774475</v>
+        <v>2.66123580932617</v>
       </c>
       <c r="H1108" t="n">
         <v>276387</v>
@@ -32530,7 +32530,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.62976861000061</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H1109" t="n">
         <v>419779</v>
@@ -32675,7 +32675,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1114" t="n">
         <v>623601</v>
@@ -32791,7 +32791,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.11975932121277</v>
+        <v>3.11975955963135</v>
       </c>
       <c r="H1118" t="n">
         <v>1034638</v>
@@ -32907,7 +32907,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H1122" t="n">
         <v>416689</v>
@@ -33197,7 +33197,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1132" t="n">
         <v>457229</v>
@@ -33226,7 +33226,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1133" t="n">
         <v>821840</v>
@@ -33429,7 +33429,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1140" t="n">
         <v>299367</v>
@@ -33516,7 +33516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1143" t="n">
         <v>886339</v>
@@ -33574,7 +33574,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1145" t="n">
         <v>572690</v>
@@ -33603,7 +33603,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1146" t="n">
         <v>308166</v>
@@ -33661,7 +33661,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1148" t="n">
         <v>421416</v>
@@ -33748,7 +33748,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.66573119163513</v>
+        <v>2.66573095321655</v>
       </c>
       <c r="H1151" t="n">
         <v>362832</v>
@@ -33864,7 +33864,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1155" t="n">
         <v>470106</v>
@@ -33980,7 +33980,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1159" t="n">
         <v>285234</v>
@@ -34009,7 +34009,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1160" t="n">
         <v>357619</v>
@@ -34067,7 +34067,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.49041342735291</v>
+        <v>2.49041318893433</v>
       </c>
       <c r="H1162" t="n">
         <v>417054</v>
@@ -34096,7 +34096,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.33757209777832</v>
+        <v>2.33757185935974</v>
       </c>
       <c r="H1163" t="n">
         <v>488508</v>
@@ -34357,7 +34357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1172" t="n">
         <v>666452</v>
@@ -34415,7 +34415,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.49490880966187</v>
+        <v>2.49490857124329</v>
       </c>
       <c r="H1174" t="n">
         <v>400645</v>
@@ -34647,7 +34647,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1182" t="n">
         <v>166462</v>
@@ -34676,7 +34676,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.36903929710388</v>
+        <v>2.3690390586853</v>
       </c>
       <c r="H1183" t="n">
         <v>325503</v>
@@ -34705,7 +34705,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.33757209777832</v>
+        <v>2.33757185935974</v>
       </c>
       <c r="H1184" t="n">
         <v>97973</v>
@@ -34850,7 +34850,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.40050673484802</v>
+        <v>2.40050649642944</v>
       </c>
       <c r="H1189" t="n">
         <v>251715</v>
@@ -34966,7 +34966,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1193" t="n">
         <v>83712</v>
@@ -34995,7 +34995,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1194" t="n">
         <v>412501</v>
@@ -35053,7 +35053,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.49041342735291</v>
+        <v>2.49041318893433</v>
       </c>
       <c r="H1196" t="n">
         <v>127418</v>
@@ -35082,7 +35082,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1197" t="n">
         <v>313243</v>
@@ -35111,7 +35111,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1198" t="n">
         <v>176835</v>
@@ -35140,7 +35140,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1199" t="n">
         <v>158261</v>
@@ -35459,7 +35459,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.19821667671204</v>
+        <v>2.19821643829346</v>
       </c>
       <c r="H1210" t="n">
         <v>65951</v>
@@ -35488,7 +35488,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.19372129440308</v>
+        <v>2.19372153282166</v>
       </c>
       <c r="H1211" t="n">
         <v>69076</v>
@@ -35575,7 +35575,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1214" t="n">
         <v>83174</v>
@@ -35749,7 +35749,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.09032893180847</v>
+        <v>2.09032869338989</v>
       </c>
       <c r="H1220" t="n">
         <v>781265</v>
@@ -35778,7 +35778,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.00941276550293</v>
+        <v>2.00941252708435</v>
       </c>
       <c r="H1221" t="n">
         <v>399437</v>
@@ -35807,7 +35807,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1222" t="n">
         <v>485043</v>
@@ -35836,7 +35836,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1223" t="n">
         <v>120064</v>
@@ -35894,7 +35894,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.81161844730377</v>
+        <v>1.81161832809448</v>
       </c>
       <c r="H1225" t="n">
         <v>299262</v>
@@ -35923,7 +35923,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620701789856</v>
+        <v>1.72620689868927</v>
       </c>
       <c r="H1226" t="n">
         <v>214567</v>
@@ -36039,7 +36039,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.74418842792511</v>
+        <v>1.74418830871582</v>
       </c>
       <c r="H1230" t="n">
         <v>252983</v>
@@ -36184,7 +36184,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1235" t="n">
         <v>1943646</v>
@@ -36532,7 +36532,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1247" t="n">
         <v>342197</v>
@@ -36590,7 +36590,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.69270324707031</v>
+        <v>2.69270300865173</v>
       </c>
       <c r="H1249" t="n">
         <v>508936</v>
@@ -36648,7 +36648,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1251" t="n">
         <v>180457</v>
@@ -36735,7 +36735,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.69270324707031</v>
+        <v>2.69270300865173</v>
       </c>
       <c r="H1254" t="n">
         <v>258466</v>
@@ -36764,7 +36764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1255" t="n">
         <v>150001</v>
@@ -36793,7 +36793,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1256" t="n">
         <v>104313</v>
@@ -36822,7 +36822,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.66573119163513</v>
+        <v>2.66573095321655</v>
       </c>
       <c r="H1257" t="n">
         <v>232982</v>
@@ -36996,7 +36996,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1263" t="n">
         <v>207732</v>
@@ -37025,7 +37025,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1264" t="n">
         <v>175562</v>
@@ -37170,7 +37170,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1269" t="n">
         <v>42041</v>
@@ -37228,7 +37228,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.49041342735291</v>
+        <v>2.49041318893433</v>
       </c>
       <c r="H1271" t="n">
         <v>217950</v>
@@ -37257,7 +37257,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1272" t="n">
         <v>37811</v>
@@ -37373,7 +37373,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1276" t="n">
         <v>70248</v>
@@ -37402,7 +37402,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.53087139129639</v>
+        <v>2.53087115287781</v>
       </c>
       <c r="H1277" t="n">
         <v>76149</v>
@@ -37547,7 +37547,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1282" t="n">
         <v>147768</v>
@@ -37576,7 +37576,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.44546008110046</v>
+        <v>2.44545984268188</v>
       </c>
       <c r="H1283" t="n">
         <v>253154</v>
@@ -37634,7 +37634,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408618927002</v>
+        <v>2.32408595085144</v>
       </c>
       <c r="H1285" t="n">
         <v>150077</v>
@@ -37663,7 +37663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1286" t="n">
         <v>215584</v>
@@ -37779,7 +37779,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1290" t="n">
         <v>119725</v>
@@ -37837,7 +37837,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.27913284301758</v>
+        <v>2.279132604599</v>
       </c>
       <c r="H1292" t="n">
         <v>82580</v>
@@ -37866,7 +37866,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.31959080696106</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1293" t="n">
         <v>141021</v>
@@ -38069,7 +38069,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H1300" t="n">
         <v>125036</v>
@@ -38127,7 +38127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.58481526374817</v>
+        <v>2.58481502532959</v>
       </c>
       <c r="H1302" t="n">
         <v>190894</v>
@@ -38243,7 +38243,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H1306" t="n">
         <v>127690</v>
@@ -38301,7 +38301,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1308" t="n">
         <v>456363</v>
@@ -38388,7 +38388,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1311" t="n">
         <v>260834</v>
@@ -38562,7 +38562,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1317" t="n">
         <v>1495587</v>
@@ -38620,7 +38620,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1319" t="n">
         <v>494591</v>
@@ -38678,7 +38678,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1321" t="n">
         <v>815713</v>
@@ -38707,7 +38707,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1322" t="n">
         <v>502079</v>
@@ -38794,7 +38794,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1325" t="n">
         <v>199637</v>
@@ -38852,7 +38852,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1327" t="n">
         <v>290870</v>
@@ -38939,7 +38939,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1330" t="n">
         <v>252995</v>
@@ -39055,7 +39055,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1334" t="n">
         <v>268572</v>
@@ -39084,7 +39084,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1335" t="n">
         <v>570248</v>
@@ -39142,7 +39142,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1337" t="n">
         <v>421991</v>
@@ -39287,7 +39287,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1342" t="n">
         <v>144840</v>
@@ -39374,7 +39374,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.38947916030884</v>
+        <v>3.38947939872742</v>
       </c>
       <c r="H1345" t="n">
         <v>658939</v>
@@ -39461,7 +39461,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.25012421607971</v>
+        <v>3.25012397766113</v>
       </c>
       <c r="H1348" t="n">
         <v>2154853</v>
@@ -39722,7 +39722,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.15572190284729</v>
+        <v>3.15572214126587</v>
       </c>
       <c r="H1357" t="n">
         <v>196185</v>
@@ -39780,7 +39780,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1359" t="n">
         <v>259201</v>
@@ -39838,7 +39838,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1361" t="n">
         <v>350756</v>
@@ -39954,7 +39954,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1365" t="n">
         <v>312867</v>
@@ -39983,7 +39983,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1366" t="n">
         <v>382149</v>
@@ -40302,7 +40302,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.36700248718262</v>
+        <v>3.3670027256012</v>
       </c>
       <c r="H1377" t="n">
         <v>501144</v>
@@ -40418,7 +40418,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.52433919906616</v>
+        <v>3.52433943748474</v>
       </c>
       <c r="H1381" t="n">
         <v>523192</v>
@@ -40447,7 +40447,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.43443250656128</v>
+        <v>3.43443274497986</v>
       </c>
       <c r="H1382" t="n">
         <v>673959</v>
@@ -40476,7 +40476,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.52433919906616</v>
+        <v>3.52433943748474</v>
       </c>
       <c r="H1383" t="n">
         <v>463906</v>
@@ -40882,7 +40882,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1397" t="n">
         <v>144695</v>
@@ -41114,7 +41114,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.11975932121277</v>
+        <v>3.11975955963135</v>
       </c>
       <c r="H1405" t="n">
         <v>266597</v>
@@ -41230,7 +41230,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1409" t="n">
         <v>725407</v>
@@ -41259,7 +41259,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1410" t="n">
         <v>303119</v>
@@ -41288,7 +41288,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1411" t="n">
         <v>178077</v>
@@ -41375,7 +41375,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1414" t="n">
         <v>102936</v>
@@ -41433,7 +41433,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1416" t="n">
         <v>191622</v>
@@ -41491,7 +41491,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1418" t="n">
         <v>281418</v>
@@ -41520,7 +41520,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1419" t="n">
         <v>212885</v>
@@ -41607,7 +41607,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1422" t="n">
         <v>157214</v>
@@ -41636,7 +41636,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1423" t="n">
         <v>101981</v>
@@ -41723,7 +41723,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1426" t="n">
         <v>186710</v>
@@ -41752,7 +41752,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.20067524909973</v>
+        <v>3.20067548751831</v>
       </c>
       <c r="H1427" t="n">
         <v>272169</v>
@@ -41810,7 +41810,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1429" t="n">
         <v>195227</v>
@@ -41839,7 +41839,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1430" t="n">
         <v>78000</v>
@@ -42158,7 +42158,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.3580117225647</v>
+        <v>3.35801196098328</v>
       </c>
       <c r="H1441" t="n">
         <v>346732</v>
@@ -42274,7 +42274,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1445" t="n">
         <v>323942</v>
@@ -42912,7 +42912,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.20067524909973</v>
+        <v>3.20067548751831</v>
       </c>
       <c r="H1467" t="n">
         <v>283438</v>
@@ -42941,7 +42941,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.21865653991699</v>
+        <v>3.21865677833557</v>
       </c>
       <c r="H1468" t="n">
         <v>194799</v>
@@ -43144,7 +43144,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.25012421607971</v>
+        <v>3.25012397766113</v>
       </c>
       <c r="H1475" t="n">
         <v>150619</v>
@@ -43260,7 +43260,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.23214268684387</v>
+        <v>3.23214292526245</v>
       </c>
       <c r="H1479" t="n">
         <v>598829</v>
@@ -43318,7 +43318,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.15572190284729</v>
+        <v>3.15572214126587</v>
       </c>
       <c r="H1481" t="n">
         <v>287388</v>
@@ -43521,7 +43521,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.27709603309631</v>
+        <v>3.27709627151489</v>
       </c>
       <c r="H1488" t="n">
         <v>477846</v>
@@ -43782,7 +43782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1497" t="n">
         <v>299328</v>
@@ -43956,7 +43956,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1503" t="n">
         <v>705439</v>
@@ -43985,7 +43985,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1504" t="n">
         <v>268987</v>
@@ -44014,7 +44014,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1505" t="n">
         <v>462367</v>
@@ -44043,7 +44043,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1506" t="n">
         <v>276651</v>
@@ -44072,7 +44072,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1507" t="n">
         <v>146234</v>
@@ -44101,7 +44101,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1508" t="n">
         <v>345238</v>
@@ -44333,7 +44333,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1516" t="n">
         <v>46706</v>
@@ -44449,7 +44449,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1520" t="n">
         <v>272492</v>
@@ -44478,7 +44478,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1521" t="n">
         <v>87667</v>
@@ -44623,7 +44623,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1526" t="n">
         <v>73450</v>
@@ -44768,7 +44768,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1531" t="n">
         <v>108386</v>
@@ -44855,7 +44855,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.04333877563477</v>
+        <v>3.04333901405334</v>
       </c>
       <c r="H1534" t="n">
         <v>226091</v>
@@ -44913,7 +44913,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1536" t="n">
         <v>79901</v>
@@ -44971,7 +44971,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.01636672019958</v>
+        <v>3.01636695861816</v>
       </c>
       <c r="H1538" t="n">
         <v>112099</v>
@@ -45029,7 +45029,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1540" t="n">
         <v>325007</v>
@@ -45116,7 +45116,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1543" t="n">
         <v>406374</v>
@@ -45203,7 +45203,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1546" t="n">
         <v>68156</v>
@@ -45232,7 +45232,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.95343208312988</v>
+        <v>2.95343232154846</v>
       </c>
       <c r="H1547" t="n">
         <v>64711</v>
@@ -45290,7 +45290,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H1549" t="n">
         <v>129232</v>
@@ -45319,7 +45319,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1550" t="n">
         <v>95039</v>
@@ -45667,7 +45667,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92196488380432</v>
+        <v>2.9219651222229</v>
       </c>
       <c r="H1562" t="n">
         <v>221866</v>
@@ -45754,7 +45754,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1565" t="n">
         <v>409791</v>
@@ -45841,7 +45841,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.7511420249939</v>
+        <v>2.75114226341248</v>
       </c>
       <c r="H1568" t="n">
         <v>125839</v>
@@ -45870,7 +45870,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1569" t="n">
         <v>254117</v>
@@ -45899,7 +45899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1570" t="n">
         <v>191841</v>
@@ -45957,7 +45957,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.31959080696106</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1572" t="n">
         <v>482762</v>
@@ -46015,7 +46015,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1574" t="n">
         <v>252389</v>
@@ -46102,7 +46102,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1577" t="n">
         <v>267897</v>
@@ -46189,7 +46189,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1580" t="n">
         <v>165698</v>
@@ -46276,7 +46276,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1583" t="n">
         <v>55903</v>
@@ -46421,7 +46421,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.99838542938232</v>
+        <v>2.9983856678009</v>
       </c>
       <c r="H1588" t="n">
         <v>189380</v>
@@ -46508,7 +46508,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1591" t="n">
         <v>153829</v>
@@ -46653,7 +46653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1596" t="n">
         <v>56957</v>
@@ -46682,7 +46682,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1597" t="n">
         <v>60882</v>
@@ -46769,7 +46769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1600" t="n">
         <v>47876</v>
@@ -47059,7 +47059,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1610" t="n">
         <v>39637</v>
@@ -47262,7 +47262,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1617" t="n">
         <v>40710</v>
@@ -47378,7 +47378,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.8365535736084</v>
+        <v>2.83655381202698</v>
       </c>
       <c r="H1621" t="n">
         <v>41778</v>
@@ -47436,7 +47436,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1623" t="n">
         <v>34309</v>
@@ -47494,7 +47494,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1625" t="n">
         <v>19281</v>
@@ -47639,7 +47639,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1630" t="n">
         <v>32369</v>
@@ -47784,7 +47784,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.94893670082092</v>
+        <v>2.9489369392395</v>
       </c>
       <c r="H1635" t="n">
         <v>38673</v>
@@ -47813,7 +47813,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1636" t="n">
         <v>22683</v>
@@ -47842,7 +47842,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H1637" t="n">
         <v>149249</v>
@@ -47900,7 +47900,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.88150691986084</v>
+        <v>2.88150715827942</v>
       </c>
       <c r="H1639" t="n">
         <v>75463</v>
@@ -48074,7 +48074,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.7511420249939</v>
+        <v>2.75114226341248</v>
       </c>
       <c r="H1645" t="n">
         <v>18743</v>
@@ -48132,7 +48132,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1647" t="n">
         <v>12343</v>
@@ -48190,7 +48190,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1649" t="n">
         <v>11528</v>
@@ -48248,7 +48248,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.66123604774475</v>
+        <v>2.66123580932617</v>
       </c>
       <c r="H1651" t="n">
         <v>25038</v>
@@ -48277,7 +48277,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1652" t="n">
         <v>23575</v>
@@ -48306,7 +48306,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H1653" t="n">
         <v>62360</v>
@@ -48364,7 +48364,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H1655" t="n">
         <v>31703</v>
@@ -48393,7 +48393,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1656" t="n">
         <v>57134</v>
@@ -48422,7 +48422,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1657" t="n">
         <v>67892</v>
@@ -48451,7 +48451,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.49490880966187</v>
+        <v>2.49490857124329</v>
       </c>
       <c r="H1658" t="n">
         <v>69491</v>
@@ -48509,7 +48509,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.53087139129639</v>
+        <v>2.53087115287781</v>
       </c>
       <c r="H1660" t="n">
         <v>19436</v>
@@ -48567,7 +48567,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1662" t="n">
         <v>16043</v>
@@ -48596,7 +48596,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.40050673484802</v>
+        <v>2.40050649642944</v>
       </c>
       <c r="H1663" t="n">
         <v>25133</v>
@@ -48654,7 +48654,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.53087139129639</v>
+        <v>2.53087115287781</v>
       </c>
       <c r="H1665" t="n">
         <v>17203</v>
@@ -48683,7 +48683,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1666" t="n">
         <v>17974</v>
@@ -48741,7 +48741,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986215591431</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1668" t="n">
         <v>19913</v>
@@ -48770,7 +48770,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1669" t="n">
         <v>22730</v>
@@ -48799,7 +48799,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.62976861000061</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H1670" t="n">
         <v>30918</v>
@@ -48828,7 +48828,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.69270324707031</v>
+        <v>2.69270300865173</v>
       </c>
       <c r="H1671" t="n">
         <v>16345</v>
@@ -48973,7 +48973,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1676" t="n">
         <v>7623</v>
@@ -49002,7 +49002,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1677" t="n">
         <v>20070</v>
@@ -49031,7 +49031,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1678" t="n">
         <v>33818</v>
@@ -49176,7 +49176,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1683" t="n">
         <v>45153</v>
@@ -49205,7 +49205,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1684" t="n">
         <v>6212</v>
@@ -49321,7 +49321,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1688" t="n">
         <v>42783</v>
@@ -49350,7 +49350,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1689" t="n">
         <v>16051</v>
@@ -49437,7 +49437,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.82756280899048</v>
+        <v>2.82756304740906</v>
       </c>
       <c r="H1692" t="n">
         <v>16029</v>
@@ -49582,7 +49582,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.79609537124634</v>
+        <v>2.79609560966492</v>
       </c>
       <c r="H1697" t="n">
         <v>17572</v>
@@ -49611,7 +49611,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.84104895591736</v>
+        <v>2.84104919433594</v>
       </c>
       <c r="H1698" t="n">
         <v>20337</v>
@@ -49640,7 +49640,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1699" t="n">
         <v>16843</v>
@@ -49814,7 +49814,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1705" t="n">
         <v>42695</v>
@@ -49843,7 +49843,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.85903024673462</v>
+        <v>2.8590304851532</v>
       </c>
       <c r="H1706" t="n">
         <v>15850</v>
@@ -49872,7 +49872,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1707" t="n">
         <v>12004</v>
@@ -49901,7 +49901,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1708" t="n">
         <v>4144</v>
@@ -49930,7 +49930,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1709" t="n">
         <v>28454</v>
@@ -49988,7 +49988,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1711" t="n">
         <v>18315</v>
@@ -50075,7 +50075,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1714" t="n">
         <v>12820</v>
@@ -50133,7 +50133,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1716" t="n">
         <v>50428</v>
@@ -50220,7 +50220,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1719" t="n">
         <v>17415</v>
@@ -50278,7 +50278,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.81407690048218</v>
+        <v>2.81407713890076</v>
       </c>
       <c r="H1721" t="n">
         <v>12894</v>
@@ -50336,7 +50336,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1723" t="n">
         <v>7107</v>
@@ -50539,7 +50539,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.79609537124634</v>
+        <v>2.79609560966492</v>
       </c>
       <c r="H1730" t="n">
         <v>104273</v>
@@ -50655,7 +50655,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.78260946273804</v>
+        <v>2.78260970115662</v>
       </c>
       <c r="H1734" t="n">
         <v>30301</v>
@@ -50916,7 +50916,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1743" t="n">
         <v>33930</v>
@@ -51032,7 +51032,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H1747" t="n">
         <v>81743</v>
@@ -51061,7 +51061,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.81407690048218</v>
+        <v>2.81407713890076</v>
       </c>
       <c r="H1748" t="n">
         <v>79296</v>
@@ -51206,7 +51206,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.7511420249939</v>
+        <v>2.75114226341248</v>
       </c>
       <c r="H1753" t="n">
         <v>9572</v>
@@ -51235,7 +51235,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1754" t="n">
         <v>5581</v>
@@ -51264,7 +51264,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1755" t="n">
         <v>35299</v>
@@ -51351,7 +51351,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1758" t="n">
         <v>6307</v>
@@ -51380,7 +51380,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.7511420249939</v>
+        <v>2.75114226341248</v>
       </c>
       <c r="H1759" t="n">
         <v>28793</v>
@@ -51409,7 +51409,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1760" t="n">
         <v>40934</v>
@@ -51525,7 +51525,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1764" t="n">
         <v>12378</v>
@@ -51554,7 +51554,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1765" t="n">
         <v>5013</v>
@@ -51612,7 +51612,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1767" t="n">
         <v>6388</v>
@@ -51670,7 +51670,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1769" t="n">
         <v>6051</v>
@@ -51728,7 +51728,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1771" t="n">
         <v>5520</v>
@@ -51786,7 +51786,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1773" t="n">
         <v>53791</v>
@@ -51844,7 +51844,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1775" t="n">
         <v>16855</v>
@@ -51873,7 +51873,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.64774990081787</v>
+        <v>2.64774966239929</v>
       </c>
       <c r="H1776" t="n">
         <v>43083</v>
@@ -51902,7 +51902,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325451850891</v>
+        <v>2.64325428009033</v>
       </c>
       <c r="H1777" t="n">
         <v>6473</v>
@@ -51931,7 +51931,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1778" t="n">
         <v>3334</v>
@@ -51989,7 +51989,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1780" t="n">
         <v>5480</v>
@@ -52018,7 +52018,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1781" t="n">
         <v>5433</v>
@@ -52047,7 +52047,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1782" t="n">
         <v>24341</v>
@@ -52076,7 +52076,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1783" t="n">
         <v>21408</v>
@@ -52105,7 +52105,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1784" t="n">
         <v>29962</v>
@@ -52134,7 +52134,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1785" t="n">
         <v>32553</v>
@@ -52337,7 +52337,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.81407690048218</v>
+        <v>2.81407713890076</v>
       </c>
       <c r="H1792" t="n">
         <v>10618</v>
@@ -52366,7 +52366,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1793" t="n">
         <v>25504</v>
@@ -52482,7 +52482,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664711952209</v>
       </c>
       <c r="H1797" t="n">
         <v>11787</v>
@@ -52569,7 +52569,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1800" t="n">
         <v>60052</v>
@@ -52627,7 +52627,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1802" t="n">
         <v>28436</v>
@@ -52656,7 +52656,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1803" t="n">
         <v>33741</v>
@@ -52685,7 +52685,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1804" t="n">
         <v>38789</v>
@@ -52714,7 +52714,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1805" t="n">
         <v>55060</v>
@@ -52743,7 +52743,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1806" t="n">
         <v>41327</v>
@@ -52772,7 +52772,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.66573119163513</v>
+        <v>2.66573095321655</v>
       </c>
       <c r="H1807" t="n">
         <v>117782</v>
@@ -52801,7 +52801,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1808" t="n">
         <v>57535</v>
@@ -52859,7 +52859,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.66573119163513</v>
+        <v>2.66573095321655</v>
       </c>
       <c r="H1810" t="n">
         <v>44782</v>
@@ -52975,7 +52975,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1814" t="n">
         <v>42615</v>
@@ -53004,7 +53004,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1815" t="n">
         <v>45668</v>
@@ -53062,7 +53062,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1817" t="n">
         <v>33665</v>
@@ -53178,7 +53178,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1821" t="n">
         <v>92970</v>
@@ -53294,7 +53294,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1825" t="n">
         <v>57594</v>
@@ -53323,7 +53323,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1826" t="n">
         <v>39291</v>
@@ -53352,7 +53352,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.68820786476135</v>
+        <v>2.68820762634277</v>
       </c>
       <c r="H1827" t="n">
         <v>117705</v>
@@ -53439,7 +53439,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1830" t="n">
         <v>33338</v>
@@ -53468,7 +53468,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1831" t="n">
         <v>16249</v>
@@ -53526,7 +53526,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1833" t="n">
         <v>141369</v>
@@ -53613,7 +53613,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.60279655456543</v>
+        <v>2.60279631614685</v>
       </c>
       <c r="H1836" t="n">
         <v>20616</v>
@@ -53700,7 +53700,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1839" t="n">
         <v>33738</v>
@@ -53729,7 +53729,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986215591431</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1840" t="n">
         <v>52048</v>
@@ -53787,7 +53787,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1842" t="n">
         <v>78570</v>
@@ -53874,7 +53874,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1845" t="n">
         <v>50260</v>
@@ -53932,7 +53932,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.49041342735291</v>
+        <v>2.49041318893433</v>
       </c>
       <c r="H1847" t="n">
         <v>28295</v>
@@ -53961,7 +53961,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1848" t="n">
         <v>92588</v>
@@ -54048,7 +54048,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.49041342735291</v>
+        <v>2.49041318893433</v>
       </c>
       <c r="H1851" t="n">
         <v>32650</v>
@@ -54077,7 +54077,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1852" t="n">
         <v>30308</v>
@@ -54193,7 +54193,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1856" t="n">
         <v>62589</v>
@@ -54251,7 +54251,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1858" t="n">
         <v>34367</v>
@@ -54280,7 +54280,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1859" t="n">
         <v>16373</v>
@@ -54309,7 +54309,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1860" t="n">
         <v>34753</v>
@@ -54425,7 +54425,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1864" t="n">
         <v>66648</v>
@@ -54483,7 +54483,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1866" t="n">
         <v>34697</v>
@@ -54512,7 +54512,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1867" t="n">
         <v>101913</v>
@@ -54686,7 +54686,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.38252544403076</v>
+        <v>2.38252520561218</v>
       </c>
       <c r="H1873" t="n">
         <v>93498</v>
@@ -54831,7 +54831,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.4050018787384</v>
+        <v>2.40500164031982</v>
       </c>
       <c r="H1878" t="n">
         <v>6692</v>
@@ -54860,7 +54860,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.39601111412048</v>
+        <v>2.39601135253906</v>
       </c>
       <c r="H1879" t="n">
         <v>16625</v>
@@ -55237,7 +55237,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1892" t="n">
         <v>91013</v>
@@ -55266,7 +55266,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1893" t="n">
         <v>79197</v>
@@ -55585,7 +55585,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.19372129440308</v>
+        <v>2.19372153282166</v>
       </c>
       <c r="H1904" t="n">
         <v>19773</v>
@@ -55643,7 +55643,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.18023538589478</v>
+        <v>2.1802351474762</v>
       </c>
       <c r="H1906" t="n">
         <v>29954</v>
@@ -55730,7 +55730,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H1909" t="n">
         <v>32256</v>
@@ -55788,7 +55788,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1911" t="n">
         <v>104467</v>
@@ -55817,7 +55817,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1912" t="n">
         <v>60529</v>
@@ -55846,7 +55846,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1913" t="n">
         <v>27604</v>
@@ -55933,7 +55933,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.12179613113403</v>
+        <v>2.12179589271545</v>
       </c>
       <c r="H1916" t="n">
         <v>50050</v>
@@ -56310,7 +56310,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.14876818656921</v>
+        <v>2.14876842498779</v>
       </c>
       <c r="H1929" t="n">
         <v>136857</v>
@@ -56629,7 +56629,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143135547638</v>
+        <v>1.99143159389496</v>
       </c>
       <c r="H1940" t="n">
         <v>43318</v>
@@ -56832,7 +56832,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1947" t="n">
         <v>69631</v>
@@ -57006,7 +57006,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.99592697620392</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1953" t="n">
         <v>33158</v>
@@ -57122,7 +57122,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1957" t="n">
         <v>28970</v>
@@ -57151,7 +57151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647800922394</v>
+        <v>1.94647824764252</v>
       </c>
       <c r="H1958" t="n">
         <v>84119</v>
@@ -57180,7 +57180,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.99592697620392</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1959" t="n">
         <v>29810</v>
@@ -57296,7 +57296,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.96445953845978</v>
+        <v>1.9644593000412</v>
       </c>
       <c r="H1963" t="n">
         <v>12830</v>
@@ -57325,7 +57325,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1964" t="n">
         <v>69130</v>
@@ -57354,7 +57354,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1965" t="n">
         <v>34147</v>
@@ -57383,7 +57383,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1966" t="n">
         <v>38443</v>
@@ -57412,7 +57412,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702951908112</v>
+        <v>1.89702939987183</v>
       </c>
       <c r="H1967" t="n">
         <v>37018</v>
@@ -57441,7 +57441,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1968" t="n">
         <v>36266</v>
@@ -57470,7 +57470,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.87904810905457</v>
+        <v>1.87904822826385</v>
       </c>
       <c r="H1969" t="n">
         <v>58149</v>
@@ -57557,7 +57557,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262768268585</v>
+        <v>1.80262780189514</v>
       </c>
       <c r="H1972" t="n">
         <v>64312</v>
@@ -57876,7 +57876,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.71361994743347</v>
+        <v>1.71362006664276</v>
       </c>
       <c r="H1983" t="n">
         <v>21437</v>
@@ -57934,7 +57934,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.6956387758255</v>
+        <v>1.69563889503479</v>
       </c>
       <c r="H1985" t="n">
         <v>50617</v>
@@ -58021,7 +58021,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.6830518245697</v>
+        <v>1.68305170536041</v>
       </c>
       <c r="H1988" t="n">
         <v>46442</v>
@@ -58050,7 +58050,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.65068531036377</v>
+        <v>1.65068542957306</v>
       </c>
       <c r="H1989" t="n">
         <v>51429</v>
@@ -58166,7 +58166,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.65068531036377</v>
+        <v>1.65068542957306</v>
       </c>
       <c r="H1993" t="n">
         <v>50733</v>
@@ -58195,7 +58195,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.66686856746674</v>
+        <v>1.66686868667603</v>
       </c>
       <c r="H1994" t="n">
         <v>91615</v>
@@ -58253,7 +58253,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.76216959953308</v>
+        <v>1.76216971874237</v>
       </c>
       <c r="H1996" t="n">
         <v>37383</v>
@@ -58340,7 +58340,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.99592697620392</v>
+        <v>1.99592673778534</v>
       </c>
       <c r="H1999" t="n">
         <v>201149</v>
@@ -58630,7 +58630,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.19372129440308</v>
+        <v>2.19372153282166</v>
       </c>
       <c r="H2009" t="n">
         <v>140038</v>
@@ -58746,7 +58746,7 @@
         <v>2.375</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.13528227806091</v>
+        <v>2.13528203964233</v>
       </c>
       <c r="H2013" t="n">
         <v>53002</v>
@@ -58804,7 +58804,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.19821667671204</v>
+        <v>2.19821643829346</v>
       </c>
       <c r="H2015" t="n">
         <v>107622</v>
@@ -58833,7 +58833,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.202712059021</v>
+        <v>2.20271182060242</v>
       </c>
       <c r="H2016" t="n">
         <v>120482</v>
@@ -58978,7 +58978,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2021" t="n">
-        <v>2.33757209777832</v>
+        <v>2.33757185935974</v>
       </c>
       <c r="H2021" t="n">
         <v>377903</v>
@@ -59065,7 +59065,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.33757209777832</v>
+        <v>2.33757185935974</v>
       </c>
       <c r="H2024" t="n">
         <v>80688</v>
@@ -59152,7 +59152,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.31959080696106</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2027" t="n">
         <v>94806</v>
@@ -59326,7 +59326,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.31959080696106</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2033" t="n">
         <v>278546</v>
@@ -59413,7 +59413,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H2036" t="n">
         <v>796398</v>
@@ -59558,7 +59558,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2041" t="n">
         <v>283736</v>
@@ -59587,7 +59587,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2042" t="n">
         <v>217481</v>
@@ -59674,7 +59674,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.57582449913025</v>
+        <v>2.57582426071167</v>
       </c>
       <c r="H2045" t="n">
         <v>205643</v>
@@ -59703,7 +59703,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H2046" t="n">
         <v>237419</v>
@@ -59848,7 +59848,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.52188086509705</v>
+        <v>2.52188062667847</v>
       </c>
       <c r="H2051" t="n">
         <v>243372</v>
@@ -59906,7 +59906,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986215591431</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H2053" t="n">
         <v>97873</v>
@@ -59993,7 +59993,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2056" t="n">
         <v>80880</v>
@@ -60138,7 +60138,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G2061" t="n">
-        <v>2.49490880966187</v>
+        <v>2.49490857124329</v>
       </c>
       <c r="H2061" t="n">
         <v>117757</v>
@@ -60167,7 +60167,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2062" t="n">
         <v>87801</v>
@@ -60312,7 +60312,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.62976861000061</v>
+        <v>2.62976837158203</v>
       </c>
       <c r="H2067" t="n">
         <v>158873</v>
@@ -60457,7 +60457,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2072" t="n">
         <v>36049</v>
@@ -60486,7 +60486,7 @@
         <v>2.875</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.58481526374817</v>
+        <v>2.58481502532959</v>
       </c>
       <c r="H2073" t="n">
         <v>38607</v>
@@ -60544,7 +60544,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2075" t="n">
         <v>50492</v>
@@ -60573,7 +60573,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.56233835220337</v>
+        <v>2.56233811378479</v>
       </c>
       <c r="H2076" t="n">
         <v>45763</v>
@@ -60631,7 +60631,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.81407690048218</v>
+        <v>2.81407713890076</v>
       </c>
       <c r="H2078" t="n">
         <v>714949</v>
@@ -60747,7 +60747,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H2082" t="n">
         <v>119791</v>
@@ -60834,7 +60834,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.87701153755188</v>
+        <v>2.87701177597046</v>
       </c>
       <c r="H2085" t="n">
         <v>146237</v>
@@ -60950,7 +60950,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884363174438</v>
+        <v>3.03884387016296</v>
       </c>
       <c r="H2089" t="n">
         <v>358716</v>
@@ -61008,7 +61008,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="n">
-        <v>3.07480621337891</v>
+        <v>3.07480645179749</v>
       </c>
       <c r="H2091" t="n">
         <v>359259</v>
@@ -61066,7 +61066,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.20067524909973</v>
+        <v>3.20067548751831</v>
       </c>
       <c r="H2093" t="n">
         <v>302622</v>
@@ -61095,7 +61095,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562859535217</v>
+        <v>3.24562883377075</v>
       </c>
       <c r="H2094" t="n">
         <v>470642</v>
@@ -61124,7 +61124,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241403579712</v>
+        <v>3.45241379737854</v>
       </c>
       <c r="H2095" t="n">
         <v>913593</v>
@@ -61153,7 +61153,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.52433919906616</v>
+        <v>3.52433943748474</v>
       </c>
       <c r="H2096" t="n">
         <v>531004</v>
@@ -61443,7 +61443,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.37599349021912</v>
+        <v>3.37599325180054</v>
       </c>
       <c r="H2106" t="n">
         <v>841002</v>
@@ -61472,7 +61472,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.32204914093018</v>
+        <v>3.32204937934875</v>
       </c>
       <c r="H2107" t="n">
         <v>603946</v>
@@ -80006,9 +80006,38 @@
         <v>7.09999990463257</v>
       </c>
       <c r="H2746" t="n">
-        <v>34499</v>
+        <v>34500</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>7.1399998664856</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>175525</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349246025085</v>
+        <v>1.89349234104156</v>
       </c>
       <c r="H2" t="n">
         <v>142675</v>
@@ -456,7 +456,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853274822235</v>
       </c>
       <c r="H3" t="n">
         <v>134991</v>
@@ -485,7 +485,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H4" t="n">
         <v>96004</v>
@@ -514,7 +514,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H5" t="n">
         <v>122356</v>
@@ -543,7 +543,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612635612488</v>
+        <v>1.80612647533417</v>
       </c>
       <c r="H6" t="n">
         <v>149442</v>
@@ -572,7 +572,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63139390945435</v>
+        <v>1.63139402866364</v>
       </c>
       <c r="H7" t="n">
         <v>346523</v>
@@ -601,7 +601,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71371984481812</v>
+        <v>1.71371972560883</v>
       </c>
       <c r="H8" t="n">
         <v>694813</v>
@@ -688,7 +688,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754958629608</v>
+        <v>1.56754970550537</v>
       </c>
       <c r="H11" t="n">
         <v>152370</v>
@@ -717,7 +717,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47514319419861</v>
+        <v>1.47514307498932</v>
       </c>
       <c r="H12" t="n">
         <v>173495</v>
@@ -746,7 +746,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314015865326</v>
+        <v>1.43314003944397</v>
       </c>
       <c r="H13" t="n">
         <v>146017</v>
@@ -775,7 +775,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H14" t="n">
         <v>179103</v>
@@ -862,7 +862,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H17" t="n">
         <v>299127</v>
@@ -891,7 +891,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H18" t="n">
         <v>156541</v>
@@ -920,7 +920,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H19" t="n">
         <v>171415</v>
@@ -978,7 +978,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H21" t="n">
         <v>65291</v>
@@ -1007,7 +1007,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>1.48522400856018</v>
+        <v>1.4852237701416</v>
       </c>
       <c r="H22" t="n">
         <v>52912</v>
@@ -1065,7 +1065,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H24" t="n">
         <v>64863</v>
@@ -1123,7 +1123,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G26" t="n">
-        <v>1.34241390228271</v>
+        <v>1.34241378307343</v>
       </c>
       <c r="H26" t="n">
         <v>105494</v>
@@ -1181,7 +1181,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995969295502</v>
+        <v>1.13995957374573</v>
       </c>
       <c r="H28" t="n">
         <v>177163</v>
@@ -1268,7 +1268,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204342365265</v>
+        <v>1.19204330444336</v>
       </c>
       <c r="H31" t="n">
         <v>55919</v>
@@ -1297,7 +1297,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G32" t="n">
-        <v>1.39365756511688</v>
+        <v>1.39365744590759</v>
       </c>
       <c r="H32" t="n">
         <v>226070</v>
@@ -1413,7 +1413,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.41969919204712</v>
+        <v>1.41969931125641</v>
       </c>
       <c r="H36" t="n">
         <v>50293</v>
@@ -1442,7 +1442,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H37" t="n">
         <v>122783</v>
@@ -1471,7 +1471,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H38" t="n">
         <v>41622</v>
@@ -1558,7 +1558,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G41" t="n">
-        <v>1.43061983585358</v>
+        <v>1.43061995506287</v>
       </c>
       <c r="H41" t="n">
         <v>35142</v>
@@ -1587,7 +1587,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42893970012665</v>
+        <v>1.42893993854523</v>
       </c>
       <c r="H42" t="n">
         <v>25450</v>
@@ -1674,7 +1674,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G45" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H45" t="n">
         <v>61294</v>
@@ -1848,7 +1848,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G51" t="n">
-        <v>1.46506249904633</v>
+        <v>1.46506226062775</v>
       </c>
       <c r="H51" t="n">
         <v>36075</v>
@@ -1906,7 +1906,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586933135986</v>
+        <v>1.56586945056915</v>
       </c>
       <c r="H53" t="n">
         <v>235408</v>
@@ -1935,7 +1935,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G54" t="n">
-        <v>1.62131321430206</v>
+        <v>1.62131333351135</v>
       </c>
       <c r="H54" t="n">
         <v>192895</v>
@@ -1964,7 +1964,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65491580963135</v>
+        <v>1.65491569042206</v>
       </c>
       <c r="H55" t="n">
         <v>234559</v>
@@ -1993,7 +1993,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551367282867</v>
+        <v>1.62551355361938</v>
       </c>
       <c r="H56" t="n">
         <v>112057</v>
@@ -2051,7 +2051,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G58" t="n">
-        <v>1.58183062076569</v>
+        <v>1.5818305015564</v>
       </c>
       <c r="H58" t="n">
         <v>75109</v>
@@ -2109,7 +2109,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H60" t="n">
         <v>70797</v>
@@ -2167,7 +2167,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H62" t="n">
         <v>74998</v>
@@ -2196,7 +2196,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G63" t="n">
-        <v>1.45078134536743</v>
+        <v>1.45078146457672</v>
       </c>
       <c r="H63" t="n">
         <v>29938</v>
@@ -2225,7 +2225,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994115829468</v>
+        <v>1.44994127750397</v>
       </c>
       <c r="H64" t="n">
         <v>18558</v>
@@ -2283,7 +2283,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H66" t="n">
         <v>47890</v>
@@ -2370,7 +2370,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H69" t="n">
         <v>97298</v>
@@ -2747,7 +2747,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H82" t="n">
         <v>54671</v>
@@ -2776,7 +2776,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G83" t="n">
-        <v>1.55074834823608</v>
+        <v>1.55074822902679</v>
       </c>
       <c r="H83" t="n">
         <v>74710</v>
@@ -2805,7 +2805,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.53898763656616</v>
+        <v>1.53898751735687</v>
       </c>
       <c r="H84" t="n">
         <v>87212</v>
@@ -2921,7 +2921,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G88" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H88" t="n">
         <v>34314</v>
@@ -2950,7 +2950,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G89" t="n">
-        <v>1.41213881969452</v>
+        <v>1.41213858127594</v>
       </c>
       <c r="H89" t="n">
         <v>42036</v>
@@ -3066,7 +3066,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G93" t="n">
-        <v>1.42305958271027</v>
+        <v>1.42305946350098</v>
       </c>
       <c r="H93" t="n">
         <v>34973</v>
@@ -3182,7 +3182,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G97" t="n">
-        <v>1.49110412597656</v>
+        <v>1.49110424518585</v>
       </c>
       <c r="H97" t="n">
         <v>35694</v>
@@ -3240,7 +3240,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47514319419861</v>
+        <v>1.47514307498932</v>
       </c>
       <c r="H99" t="n">
         <v>20179</v>
@@ -3298,7 +3298,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278426170349</v>
+        <v>1.49278438091278</v>
       </c>
       <c r="H101" t="n">
         <v>25555</v>
@@ -3356,7 +3356,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G103" t="n">
-        <v>1.49866485595703</v>
+        <v>1.49866473674774</v>
       </c>
       <c r="H103" t="n">
         <v>83894</v>
@@ -3385,7 +3385,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.50202488899231</v>
+        <v>1.5020250082016</v>
       </c>
       <c r="H104" t="n">
         <v>14686</v>
@@ -3530,7 +3530,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H109" t="n">
         <v>38996</v>
@@ -3646,7 +3646,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614465236664</v>
+        <v>1.49614453315735</v>
       </c>
       <c r="H113" t="n">
         <v>17040</v>
@@ -3675,7 +3675,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G114" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H114" t="n">
         <v>56900</v>
@@ -3733,7 +3733,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577405452728</v>
+        <v>1.34577393531799</v>
       </c>
       <c r="H116" t="n">
         <v>70118</v>
@@ -3791,7 +3791,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409391880035</v>
       </c>
       <c r="H118" t="n">
         <v>57849</v>
@@ -3965,7 +3965,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28192973136902</v>
+        <v>1.28192961215973</v>
       </c>
       <c r="H124" t="n">
         <v>145528</v>
@@ -4023,7 +4023,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409391880035</v>
       </c>
       <c r="H126" t="n">
         <v>40738</v>
@@ -4052,7 +4052,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G127" t="n">
-        <v>1.34493398666382</v>
+        <v>1.34493386745453</v>
       </c>
       <c r="H127" t="n">
         <v>23711</v>
@@ -4110,7 +4110,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H129" t="n">
         <v>34201</v>
@@ -4139,7 +4139,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H130" t="n">
         <v>59203</v>
@@ -4168,7 +4168,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537057876587</v>
+        <v>1.29537045955658</v>
       </c>
       <c r="H131" t="n">
         <v>29496</v>
@@ -4255,7 +4255,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G134" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H134" t="n">
         <v>18189</v>
@@ -4284,7 +4284,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G135" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H135" t="n">
         <v>36849</v>
@@ -4313,7 +4313,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>1.33485341072083</v>
+        <v>1.33485329151154</v>
       </c>
       <c r="H136" t="n">
         <v>74599</v>
@@ -4342,7 +4342,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.318892121315</v>
+        <v>1.31889224052429</v>
       </c>
       <c r="H137" t="n">
         <v>23614</v>
@@ -4371,7 +4371,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H138" t="n">
         <v>37733</v>
@@ -4400,7 +4400,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G139" t="n">
-        <v>1.34493398666382</v>
+        <v>1.34493386745453</v>
       </c>
       <c r="H139" t="n">
         <v>9455</v>
@@ -4458,7 +4458,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H141" t="n">
         <v>14979</v>
@@ -4487,7 +4487,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G142" t="n">
-        <v>1.33401322364807</v>
+        <v>1.33401334285736</v>
       </c>
       <c r="H142" t="n">
         <v>22761</v>
@@ -4516,7 +4516,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G143" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089527606964</v>
       </c>
       <c r="H143" t="n">
         <v>14444</v>
@@ -4545,7 +4545,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35081434249878</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H144" t="n">
         <v>20463</v>
@@ -4574,7 +4574,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005520820618</v>
       </c>
       <c r="H145" t="n">
         <v>15215</v>
@@ -4603,7 +4603,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34997427463531</v>
+        <v>1.34997451305389</v>
       </c>
       <c r="H146" t="n">
         <v>25885</v>
@@ -4661,7 +4661,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.36089515686035</v>
+        <v>1.36089527606964</v>
       </c>
       <c r="H148" t="n">
         <v>48909</v>
@@ -4690,7 +4690,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G149" t="n">
-        <v>1.38357675075531</v>
+        <v>1.38357663154602</v>
       </c>
       <c r="H149" t="n">
         <v>37470</v>
@@ -4777,7 +4777,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H152" t="n">
         <v>12097</v>
@@ -4835,7 +4835,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G154" t="n">
-        <v>1.32309257984161</v>
+        <v>1.32309246063232</v>
       </c>
       <c r="H154" t="n">
         <v>23094</v>
@@ -4864,7 +4864,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.32309257984161</v>
+        <v>1.32309246063232</v>
       </c>
       <c r="H155" t="n">
         <v>19485</v>
@@ -4922,7 +4922,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H157" t="n">
         <v>6004</v>
@@ -4951,7 +4951,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H158" t="n">
         <v>35138</v>
@@ -4980,7 +4980,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125117301941</v>
       </c>
       <c r="H159" t="n">
         <v>15586</v>
@@ -5183,7 +5183,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30293107032776</v>
+        <v>1.30293118953705</v>
       </c>
       <c r="H166" t="n">
         <v>20085</v>
@@ -5212,7 +5212,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.2920104265213</v>
+        <v>1.29201018810272</v>
       </c>
       <c r="H167" t="n">
         <v>8138</v>
@@ -5299,7 +5299,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H170" t="n">
         <v>9592</v>
@@ -5328,7 +5328,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813274860382</v>
+        <v>1.32813286781311</v>
       </c>
       <c r="H171" t="n">
         <v>34956</v>
@@ -5357,7 +5357,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H172" t="n">
         <v>47662</v>
@@ -5386,7 +5386,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713129043579</v>
+        <v>1.30713152885437</v>
       </c>
       <c r="H173" t="n">
         <v>6108</v>
@@ -5444,7 +5444,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30629122257233</v>
+        <v>1.30629146099091</v>
       </c>
       <c r="H175" t="n">
         <v>84071</v>
@@ -5473,7 +5473,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G176" t="n">
-        <v>1.30629122257233</v>
+        <v>1.30629146099091</v>
       </c>
       <c r="H176" t="n">
         <v>23238</v>
@@ -5502,7 +5502,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265586853027</v>
+        <v>1.37265598773956</v>
       </c>
       <c r="H177" t="n">
         <v>159638</v>
@@ -5531,7 +5531,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H178" t="n">
         <v>176056</v>
@@ -5618,7 +5618,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G181" t="n">
-        <v>1.35081434249878</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H181" t="n">
         <v>7307</v>
@@ -5792,7 +5792,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G187" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409391880035</v>
       </c>
       <c r="H187" t="n">
         <v>16776</v>
@@ -5821,7 +5821,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417461395264</v>
+        <v>1.35417473316193</v>
       </c>
       <c r="H188" t="n">
         <v>58082</v>
@@ -5850,7 +5850,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905351161957</v>
+        <v>1.33905363082886</v>
       </c>
       <c r="H189" t="n">
         <v>17138</v>
@@ -5879,7 +5879,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149325847626</v>
+        <v>1.33149313926697</v>
       </c>
       <c r="H190" t="n">
         <v>47211</v>
@@ -5937,7 +5937,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G192" t="n">
-        <v>1.36929571628571</v>
+        <v>1.36929559707642</v>
       </c>
       <c r="H192" t="n">
         <v>60792</v>
@@ -6053,7 +6053,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525676727295</v>
       </c>
       <c r="H196" t="n">
         <v>26702</v>
@@ -6082,7 +6082,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G197" t="n">
-        <v>1.39365756511688</v>
+        <v>1.39365744590759</v>
       </c>
       <c r="H197" t="n">
         <v>31070</v>
@@ -6140,7 +6140,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G199" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H199" t="n">
         <v>91074</v>
@@ -6169,7 +6169,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105642795563</v>
+        <v>1.38105666637421</v>
       </c>
       <c r="H200" t="n">
         <v>116025</v>
@@ -6227,7 +6227,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881142616272</v>
+        <v>1.30881154537201</v>
       </c>
       <c r="H202" t="n">
         <v>85287</v>
@@ -6314,7 +6314,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721198558807</v>
+        <v>1.31721210479736</v>
       </c>
       <c r="H205" t="n">
         <v>18321</v>
@@ -6343,7 +6343,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G206" t="n">
-        <v>1.32141244411469</v>
+        <v>1.32141220569611</v>
       </c>
       <c r="H206" t="n">
         <v>16873</v>
@@ -6401,7 +6401,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H208" t="n">
         <v>31170</v>
@@ -6430,7 +6430,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125117301941</v>
       </c>
       <c r="H209" t="n">
         <v>107376</v>
@@ -6459,7 +6459,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G210" t="n">
-        <v>1.28865015506744</v>
+        <v>1.28865003585815</v>
       </c>
       <c r="H210" t="n">
         <v>21941</v>
@@ -6517,7 +6517,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.27772927284241</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H212" t="n">
         <v>16453</v>
@@ -6604,7 +6604,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G215" t="n">
-        <v>1.27856945991516</v>
+        <v>1.27856934070587</v>
       </c>
       <c r="H215" t="n">
         <v>5900</v>
@@ -6662,7 +6662,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G217" t="n">
-        <v>1.27184903621674</v>
+        <v>1.27184891700745</v>
       </c>
       <c r="H217" t="n">
         <v>23154</v>
@@ -6778,7 +6778,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H221" t="n">
         <v>120506</v>
@@ -6807,7 +6807,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G222" t="n">
-        <v>1.17944264411926</v>
+        <v>1.17944252490997</v>
       </c>
       <c r="H222" t="n">
         <v>72928</v>
@@ -6836,7 +6836,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H223" t="n">
         <v>40673</v>
@@ -6923,7 +6923,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G226" t="n">
-        <v>1.14836025238037</v>
+        <v>1.14836037158966</v>
       </c>
       <c r="H226" t="n">
         <v>42201</v>
@@ -6981,7 +6981,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>1.08367550373077</v>
+        <v>1.08367562294006</v>
       </c>
       <c r="H228" t="n">
         <v>60344</v>
@@ -7010,7 +7010,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G229" t="n">
-        <v>1.09543657302856</v>
+        <v>1.09543669223785</v>
       </c>
       <c r="H229" t="n">
         <v>28645</v>
@@ -7039,7 +7039,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H230" t="n">
         <v>21769</v>
@@ -7068,7 +7068,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787608146667</v>
+        <v>1.08787596225739</v>
       </c>
       <c r="H231" t="n">
         <v>21196</v>
@@ -7126,7 +7126,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G233" t="n">
-        <v>1.07947540283203</v>
+        <v>1.07947528362274</v>
       </c>
       <c r="H233" t="n">
         <v>22285</v>
@@ -7155,7 +7155,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115553855896</v>
+        <v>1.08115541934967</v>
       </c>
       <c r="H234" t="n">
         <v>38205</v>
@@ -7213,7 +7213,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.06351435184479</v>
+        <v>1.06351447105408</v>
       </c>
       <c r="H236" t="n">
         <v>37238</v>
@@ -7242,7 +7242,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>1.05847406387329</v>
+        <v>1.058473944664</v>
       </c>
       <c r="H237" t="n">
         <v>12572</v>
@@ -7271,7 +7271,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>1.04167294502258</v>
+        <v>1.04167282581329</v>
       </c>
       <c r="H238" t="n">
         <v>76098</v>
@@ -7358,7 +7358,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G241" t="n">
-        <v>1.11811804771423</v>
+        <v>1.11811816692352</v>
       </c>
       <c r="H241" t="n">
         <v>72092</v>
@@ -7416,7 +7416,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.12567865848541</v>
+        <v>1.1256787776947</v>
       </c>
       <c r="H243" t="n">
         <v>24746</v>
@@ -7445,7 +7445,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.12567865848541</v>
+        <v>1.1256787776947</v>
       </c>
       <c r="H244" t="n">
         <v>42995</v>
@@ -7474,7 +7474,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G245" t="n">
-        <v>1.14163982868195</v>
+        <v>1.14163970947266</v>
       </c>
       <c r="H245" t="n">
         <v>77628</v>
@@ -7503,7 +7503,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584004878998</v>
+        <v>1.14584016799927</v>
       </c>
       <c r="H246" t="n">
         <v>30733</v>
@@ -7590,7 +7590,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20632421970367</v>
+        <v>1.20632433891296</v>
       </c>
       <c r="H249" t="n">
         <v>65944</v>
@@ -7648,7 +7648,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H251" t="n">
         <v>48253</v>
@@ -7677,7 +7677,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.1618013381958</v>
+        <v>1.16180121898651</v>
       </c>
       <c r="H252" t="n">
         <v>24822</v>
@@ -7735,7 +7735,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H254" t="n">
         <v>38587</v>
@@ -7764,7 +7764,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H255" t="n">
         <v>58672</v>
@@ -7909,7 +7909,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H260" t="n">
         <v>166425</v>
@@ -7967,7 +7967,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.3550146818161</v>
+        <v>1.35501480102539</v>
       </c>
       <c r="H262" t="n">
         <v>277449</v>
@@ -7996,7 +7996,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.34325397014618</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H263" t="n">
         <v>158414</v>
@@ -8025,7 +8025,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G264" t="n">
-        <v>1.31469202041626</v>
+        <v>1.31469190120697</v>
       </c>
       <c r="H264" t="n">
         <v>94734</v>
@@ -8083,7 +8083,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377113819122</v>
+        <v>1.30377125740051</v>
       </c>
       <c r="H266" t="n">
         <v>53629</v>
@@ -8112,7 +8112,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>1.29117023944855</v>
+        <v>1.29117012023926</v>
       </c>
       <c r="H267" t="n">
         <v>22423</v>
@@ -8141,7 +8141,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H268" t="n">
         <v>271352</v>
@@ -8170,7 +8170,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G269" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H269" t="n">
         <v>175414</v>
@@ -8228,7 +8228,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808528900146</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="n">
         <v>103512</v>
@@ -8344,7 +8344,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="n">
         <v>109224</v>
@@ -8431,7 +8431,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H278" t="n">
         <v>152723</v>
@@ -8518,7 +8518,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H281" t="n">
         <v>29155</v>
@@ -8634,7 +8634,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H285" t="n">
         <v>42766</v>
@@ -8663,7 +8663,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104196548462</v>
+        <v>1.17104184627533</v>
       </c>
       <c r="H286" t="n">
         <v>21577</v>
@@ -8721,7 +8721,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028259277344</v>
       </c>
       <c r="H288" t="n">
         <v>17766</v>
@@ -8808,7 +8808,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G291" t="n">
-        <v>1.17860233783722</v>
+        <v>1.17860245704651</v>
       </c>
       <c r="H291" t="n">
         <v>29246</v>
@@ -8837,7 +8837,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G292" t="n">
-        <v>1.15340077877045</v>
+        <v>1.15340065956116</v>
       </c>
       <c r="H292" t="n">
         <v>81653</v>
@@ -8866,7 +8866,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H293" t="n">
         <v>25900</v>
@@ -8953,7 +8953,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524218559265</v>
+        <v>1.17524206638336</v>
       </c>
       <c r="H296" t="n">
         <v>39885</v>
@@ -8982,7 +8982,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G297" t="n">
-        <v>1.15424072742462</v>
+        <v>1.15424060821533</v>
       </c>
       <c r="H297" t="n">
         <v>24335</v>
@@ -9040,7 +9040,7 @@
         <v>1.375</v>
       </c>
       <c r="G299" t="n">
-        <v>1.15508079528809</v>
+        <v>1.1550806760788</v>
       </c>
       <c r="H299" t="n">
         <v>27476</v>
@@ -9098,7 +9098,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H301" t="n">
         <v>112526</v>
@@ -9127,7 +9127,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23740637302399</v>
+        <v>1.23740649223328</v>
       </c>
       <c r="H302" t="n">
         <v>72113</v>
@@ -9156,7 +9156,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236608505249</v>
+        <v>1.23236620426178</v>
       </c>
       <c r="H303" t="n">
         <v>66001</v>
@@ -9214,7 +9214,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H305" t="n">
         <v>29402</v>
@@ -9272,7 +9272,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548415184021</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="n">
         <v>124489</v>
@@ -9301,7 +9301,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288337230682</v>
+        <v>1.19288325309753</v>
       </c>
       <c r="H308" t="n">
         <v>29585</v>
@@ -9330,7 +9330,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380401611328</v>
+        <v>1.20380413532257</v>
       </c>
       <c r="H309" t="n">
         <v>25149</v>
@@ -9533,7 +9533,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G316" t="n">
-        <v>1.17860233783722</v>
+        <v>1.17860245704651</v>
       </c>
       <c r="H316" t="n">
         <v>36707</v>
@@ -9591,7 +9591,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H318" t="n">
         <v>363589</v>
@@ -9620,7 +9620,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884442329407</v>
+        <v>1.20884454250336</v>
       </c>
       <c r="H319" t="n">
         <v>228508</v>
@@ -9678,7 +9678,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G321" t="n">
-        <v>1.20632421970367</v>
+        <v>1.20632433891296</v>
       </c>
       <c r="H321" t="n">
         <v>54622</v>
@@ -9707,7 +9707,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.21052467823029</v>
+        <v>1.21052479743958</v>
       </c>
       <c r="H322" t="n">
         <v>15835</v>
@@ -9736,7 +9736,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G323" t="n">
-        <v>1.25000751018524</v>
+        <v>1.25000739097595</v>
       </c>
       <c r="H323" t="n">
         <v>179491</v>
@@ -9794,7 +9794,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688932418823</v>
       </c>
       <c r="H325" t="n">
         <v>165501</v>
@@ -9823,7 +9823,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688920497894</v>
+        <v>1.27688932418823</v>
       </c>
       <c r="H326" t="n">
         <v>59125</v>
@@ -9968,7 +9968,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808528900146</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="n">
         <v>30919</v>
@@ -10026,7 +10026,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908650875092</v>
+        <v>1.23908662796021</v>
       </c>
       <c r="H333" t="n">
         <v>107368</v>
@@ -10055,7 +10055,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G334" t="n">
-        <v>1.23068594932556</v>
+        <v>1.23068606853485</v>
       </c>
       <c r="H334" t="n">
         <v>125457</v>
@@ -10084,7 +10084,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.20968461036682</v>
+        <v>1.20968472957611</v>
       </c>
       <c r="H335" t="n">
         <v>28289</v>
@@ -10113,7 +10113,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.21724498271942</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H336" t="n">
         <v>36491</v>
@@ -10229,7 +10229,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.2248055934906</v>
+        <v>1.22480547428131</v>
       </c>
       <c r="H340" t="n">
         <v>28390</v>
@@ -10287,7 +10287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H342" t="n">
         <v>37872</v>
@@ -10316,7 +10316,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496710300446</v>
+        <v>1.24496698379517</v>
       </c>
       <c r="H343" t="n">
         <v>29781</v>
@@ -10345,7 +10345,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664711952209</v>
+        <v>1.24664700031281</v>
       </c>
       <c r="H344" t="n">
         <v>72151</v>
@@ -10374,7 +10374,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G345" t="n">
-        <v>1.30293107032776</v>
+        <v>1.30293118953705</v>
       </c>
       <c r="H345" t="n">
         <v>228591</v>
@@ -10403,7 +10403,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H346" t="n">
         <v>142637</v>
@@ -10461,7 +10461,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.27772927284241</v>
+        <v>1.2777293920517</v>
       </c>
       <c r="H348" t="n">
         <v>58888</v>
@@ -10519,7 +10519,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G350" t="n">
-        <v>1.2970507144928</v>
+        <v>1.29705059528351</v>
       </c>
       <c r="H350" t="n">
         <v>56525</v>
@@ -10548,7 +10548,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H351" t="n">
         <v>99220</v>
@@ -10577,7 +10577,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30209100246429</v>
+        <v>1.30209112167358</v>
       </c>
       <c r="H352" t="n">
         <v>134003</v>
@@ -10606,7 +10606,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H353" t="n">
         <v>99196</v>
@@ -10664,7 +10664,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890706062317</v>
+        <v>1.52890682220459</v>
       </c>
       <c r="H355" t="n">
         <v>875535</v>
@@ -10693,7 +10693,7 @@
         <v>1.75100004673004</v>
       </c>
       <c r="G356" t="n">
-        <v>1.470942735672</v>
+        <v>1.47094285488129</v>
       </c>
       <c r="H356" t="n">
         <v>805529</v>
@@ -10751,7 +10751,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690378665924</v>
       </c>
       <c r="H358" t="n">
         <v>214405</v>
@@ -10838,7 +10838,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G361" t="n">
-        <v>1.46506249904633</v>
+        <v>1.46506226062775</v>
       </c>
       <c r="H361" t="n">
         <v>61803</v>
@@ -10867,7 +10867,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>1.45498180389404</v>
+        <v>1.45498168468475</v>
       </c>
       <c r="H362" t="n">
         <v>33038</v>
@@ -10983,7 +10983,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.38861703872681</v>
+        <v>1.38861691951752</v>
       </c>
       <c r="H366" t="n">
         <v>69743</v>
@@ -11041,7 +11041,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G368" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409391880035</v>
       </c>
       <c r="H368" t="n">
         <v>187011</v>
@@ -11128,7 +11128,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>1.37349617481232</v>
+        <v>1.37349605560303</v>
       </c>
       <c r="H371" t="n">
         <v>27079</v>
@@ -11186,7 +11186,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829425811768</v>
+        <v>1.34829413890839</v>
       </c>
       <c r="H373" t="n">
         <v>39211</v>
@@ -11244,7 +11244,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G375" t="n">
-        <v>1.34157383441925</v>
+        <v>1.34157371520996</v>
       </c>
       <c r="H375" t="n">
         <v>67186</v>
@@ -11273,7 +11273,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G376" t="n">
-        <v>1.34409403800964</v>
+        <v>1.34409391880035</v>
       </c>
       <c r="H376" t="n">
         <v>41045</v>
@@ -11302,7 +11302,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.34325397014618</v>
+        <v>1.3432537317276</v>
       </c>
       <c r="H377" t="n">
         <v>25858</v>
@@ -11389,7 +11389,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.3600549697876</v>
+        <v>1.36005520820618</v>
       </c>
       <c r="H380" t="n">
         <v>53916</v>
@@ -11418,7 +11418,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>1.35921490192413</v>
+        <v>1.35921502113342</v>
       </c>
       <c r="H381" t="n">
         <v>12422</v>
@@ -11447,7 +11447,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G382" t="n">
-        <v>1.35081434249878</v>
+        <v>1.35081458091736</v>
       </c>
       <c r="H382" t="n">
         <v>15021</v>
@@ -11476,7 +11476,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G383" t="n">
-        <v>1.34493398666382</v>
+        <v>1.34493386745453</v>
       </c>
       <c r="H383" t="n">
         <v>12117</v>
@@ -11534,7 +11534,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G385" t="n">
-        <v>1.42557966709137</v>
+        <v>1.42557978630066</v>
       </c>
       <c r="H385" t="n">
         <v>153814</v>
@@ -11679,7 +11679,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297888755798</v>
+        <v>1.41297876834869</v>
       </c>
       <c r="H390" t="n">
         <v>62429</v>
@@ -11795,7 +11795,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G394" t="n">
-        <v>1.44406092166901</v>
+        <v>1.44406080245972</v>
       </c>
       <c r="H394" t="n">
         <v>54757</v>
@@ -11824,7 +11824,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G395" t="n">
-        <v>1.42725968360901</v>
+        <v>1.4272598028183</v>
       </c>
       <c r="H395" t="n">
         <v>31306</v>
@@ -11882,7 +11882,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>1.41213881969452</v>
+        <v>1.41213858127594</v>
       </c>
       <c r="H397" t="n">
         <v>64069</v>
@@ -12027,7 +12027,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>1.48522400856018</v>
+        <v>1.4852237701416</v>
       </c>
       <c r="H402" t="n">
         <v>69708</v>
@@ -12143,7 +12143,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>1.45918190479279</v>
+        <v>1.45918202400208</v>
       </c>
       <c r="H406" t="n">
         <v>60682</v>
@@ -12172,7 +12172,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G407" t="n">
-        <v>1.49530458450317</v>
+        <v>1.49530446529388</v>
       </c>
       <c r="H407" t="n">
         <v>275109</v>
@@ -12462,7 +12462,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G417" t="n">
-        <v>1.44574093818665</v>
+        <v>1.44574105739594</v>
       </c>
       <c r="H417" t="n">
         <v>20631</v>
@@ -12549,7 +12549,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G420" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H420" t="n">
         <v>20737</v>
@@ -12665,7 +12665,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H424" t="n">
         <v>83230</v>
@@ -12694,7 +12694,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44238090515137</v>
+        <v>1.44238078594208</v>
       </c>
       <c r="H425" t="n">
         <v>40832</v>
@@ -12810,7 +12810,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.44154059886932</v>
+        <v>1.44154071807861</v>
       </c>
       <c r="H429" t="n">
         <v>13399</v>
@@ -12897,7 +12897,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926259994507</v>
+        <v>1.46926271915436</v>
       </c>
       <c r="H432" t="n">
         <v>101212</v>
@@ -13042,7 +13042,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H437" t="n">
         <v>60693</v>
@@ -13129,7 +13129,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.5213463306427</v>
+        <v>1.52134644985199</v>
       </c>
       <c r="H440" t="n">
         <v>37061</v>
@@ -13158,7 +13158,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G441" t="n">
-        <v>1.59527158737183</v>
+        <v>1.59527146816254</v>
       </c>
       <c r="H441" t="n">
         <v>630947</v>
@@ -13361,7 +13361,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717563152313</v>
+        <v>1.93717551231384</v>
       </c>
       <c r="H448" t="n">
         <v>1651667</v>
@@ -13390,7 +13390,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429953098297</v>
+        <v>1.99429965019226</v>
       </c>
       <c r="H449" t="n">
         <v>1092117</v>
@@ -13448,7 +13448,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H451" t="n">
         <v>274964</v>
@@ -13477,7 +13477,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757898807526</v>
+        <v>1.98757922649384</v>
       </c>
       <c r="H452" t="n">
         <v>517407</v>
@@ -13506,7 +13506,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229613780975</v>
+        <v>1.95229625701904</v>
       </c>
       <c r="H453" t="n">
         <v>344440</v>
@@ -13535,7 +13535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869413852692</v>
+        <v>1.91869401931763</v>
       </c>
       <c r="H454" t="n">
         <v>179721</v>
@@ -13564,7 +13564,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476900100708</v>
+        <v>1.84476888179779</v>
       </c>
       <c r="H455" t="n">
         <v>293919</v>
@@ -13593,7 +13593,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812927246094</v>
       </c>
       <c r="H456" t="n">
         <v>118562</v>
@@ -13622,7 +13622,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980928897858</v>
+        <v>1.84980916976929</v>
       </c>
       <c r="H457" t="n">
         <v>133644</v>
@@ -13680,7 +13680,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G459" t="n">
-        <v>1.84644889831543</v>
+        <v>1.84644901752472</v>
       </c>
       <c r="H459" t="n">
         <v>64839</v>
@@ -13709,7 +13709,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100501537323</v>
+        <v>1.79100513458252</v>
       </c>
       <c r="H460" t="n">
         <v>175490</v>
@@ -13738,7 +13738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>1.81452679634094</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H461" t="n">
         <v>102896</v>
@@ -13825,7 +13825,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165069580078</v>
+        <v>1.87165081501007</v>
       </c>
       <c r="H464" t="n">
         <v>216656</v>
@@ -13854,7 +13854,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669134140015</v>
+        <v>1.87669110298157</v>
       </c>
       <c r="H465" t="n">
         <v>93915</v>
@@ -13941,7 +13941,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H468" t="n">
         <v>291840</v>
@@ -14057,7 +14057,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581815719604</v>
+        <v>1.97581791877747</v>
       </c>
       <c r="H472" t="n">
         <v>124221</v>
@@ -14086,7 +14086,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061612129211</v>
+        <v>1.95061635971069</v>
       </c>
       <c r="H473" t="n">
         <v>90920</v>
@@ -14144,7 +14144,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213534355164</v>
       </c>
       <c r="H475" t="n">
         <v>75301</v>
@@ -14202,7 +14202,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308886528015</v>
+        <v>1.84308874607086</v>
       </c>
       <c r="H477" t="n">
         <v>210138</v>
@@ -14231,7 +14231,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H478" t="n">
         <v>93091</v>
@@ -14260,7 +14260,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316956043243</v>
+        <v>1.85316944122314</v>
       </c>
       <c r="H479" t="n">
         <v>100214</v>
@@ -14347,7 +14347,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.6465151309967</v>
+        <v>1.64651501178741</v>
       </c>
       <c r="H482" t="n">
         <v>88167</v>
@@ -14434,7 +14434,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G485" t="n">
-        <v>1.58855104446411</v>
+        <v>1.5885511636734</v>
       </c>
       <c r="H485" t="n">
         <v>80862</v>
@@ -14550,7 +14550,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326843261719</v>
+        <v>1.55326867103577</v>
       </c>
       <c r="H489" t="n">
         <v>75040</v>
@@ -14608,7 +14608,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G491" t="n">
-        <v>1.54570817947388</v>
+        <v>1.54570806026459</v>
       </c>
       <c r="H491" t="n">
         <v>85084</v>
@@ -14695,7 +14695,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G494" t="n">
-        <v>1.58771085739136</v>
+        <v>1.58771097660065</v>
       </c>
       <c r="H494" t="n">
         <v>65464</v>
@@ -14753,7 +14753,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.61291265487671</v>
+        <v>1.612912774086</v>
       </c>
       <c r="H496" t="n">
         <v>81035</v>
@@ -14869,7 +14869,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507719993591</v>
+        <v>1.67507708072662</v>
       </c>
       <c r="H500" t="n">
         <v>49637</v>
@@ -14898,7 +14898,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.62299335002899</v>
+        <v>1.62299346923828</v>
       </c>
       <c r="H501" t="n">
         <v>82089</v>
@@ -14927,7 +14927,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G502" t="n">
-        <v>1.62131321430206</v>
+        <v>1.62131333351135</v>
       </c>
       <c r="H502" t="n">
         <v>85690</v>
@@ -14956,7 +14956,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451221466064</v>
+        <v>1.60451209545135</v>
       </c>
       <c r="H503" t="n">
         <v>18702</v>
@@ -14985,7 +14985,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.579310297966</v>
+        <v>1.57931041717529</v>
       </c>
       <c r="H504" t="n">
         <v>91562</v>
@@ -15014,7 +15014,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459302902222</v>
+        <v>1.61459290981293</v>
       </c>
       <c r="H505" t="n">
         <v>51477</v>
@@ -15072,7 +15072,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887394428253</v>
+        <v>1.62887382507324</v>
       </c>
       <c r="H507" t="n">
         <v>38889</v>
@@ -15130,7 +15130,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62467360496521</v>
+        <v>1.62467348575592</v>
       </c>
       <c r="H509" t="n">
         <v>66555</v>
@@ -15188,7 +15188,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090961933136</v>
+        <v>1.57090973854065</v>
       </c>
       <c r="H511" t="n">
         <v>27246</v>
@@ -15275,7 +15275,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G514" t="n">
-        <v>1.66163611412048</v>
+        <v>1.66163623332977</v>
       </c>
       <c r="H514" t="n">
         <v>105164</v>
@@ -15362,7 +15362,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>1.66331624984741</v>
+        <v>1.6633163690567</v>
       </c>
       <c r="H517" t="n">
         <v>95411</v>
@@ -15449,7 +15449,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G520" t="n">
-        <v>1.67339694499969</v>
+        <v>1.67339706420898</v>
       </c>
       <c r="H520" t="n">
         <v>32553</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.68851804733276</v>
+        <v>1.68851792812347</v>
       </c>
       <c r="H522" t="n">
         <v>255362</v>
@@ -15536,7 +15536,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H523" t="n">
         <v>146655</v>
@@ -15565,7 +15565,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G524" t="n">
-        <v>1.71792006492615</v>
+        <v>1.71792018413544</v>
       </c>
       <c r="H524" t="n">
         <v>107099</v>
@@ -15594,7 +15594,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H525" t="n">
         <v>105751</v>
@@ -15623,7 +15623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H526" t="n">
         <v>208108</v>
@@ -15652,7 +15652,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>1.87333106994629</v>
+        <v>1.873330950737</v>
       </c>
       <c r="H527" t="n">
         <v>439755</v>
@@ -15681,7 +15681,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>1.8229273557663</v>
+        <v>1.82292747497559</v>
       </c>
       <c r="H528" t="n">
         <v>211486</v>
@@ -15710,7 +15710,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H529" t="n">
         <v>236640</v>
@@ -15768,7 +15768,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G531" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213534355164</v>
       </c>
       <c r="H531" t="n">
         <v>1030642</v>
@@ -15797,7 +15797,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433252811432</v>
+        <v>1.89433240890503</v>
       </c>
       <c r="H532" t="n">
         <v>278860</v>
@@ -15826,7 +15826,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>1.93213498592377</v>
+        <v>1.93213534355164</v>
       </c>
       <c r="H533" t="n">
         <v>230019</v>
@@ -15855,7 +15855,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>1.91533386707306</v>
+        <v>1.91533374786377</v>
       </c>
       <c r="H534" t="n">
         <v>163101</v>
@@ -15913,7 +15913,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.75992298126221</v>
+        <v>1.7599231004715</v>
       </c>
       <c r="H536" t="n">
         <v>155319</v>
@@ -15971,7 +15971,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>1.83552837371826</v>
+        <v>1.83552825450897</v>
       </c>
       <c r="H538" t="n">
         <v>97475</v>
@@ -16000,7 +16000,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H539" t="n">
         <v>120622</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.74732220172882</v>
+        <v>1.74732208251953</v>
       </c>
       <c r="H540" t="n">
         <v>87173</v>
@@ -16203,7 +16203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H546" t="n">
         <v>61265</v>
@@ -16261,7 +16261,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H548" t="n">
         <v>27650</v>
@@ -16290,7 +16290,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G549" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H549" t="n">
         <v>41493</v>
@@ -16348,7 +16348,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G551" t="n">
-        <v>1.75572276115417</v>
+        <v>1.75572264194489</v>
       </c>
       <c r="H551" t="n">
         <v>113928</v>
@@ -16377,7 +16377,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G552" t="n">
-        <v>1.72212040424347</v>
+        <v>1.72212028503418</v>
       </c>
       <c r="H552" t="n">
         <v>46221</v>
@@ -16406,7 +16406,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H553" t="n">
         <v>11561</v>
@@ -16493,7 +16493,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011748790741</v>
+        <v>1.68011736869812</v>
       </c>
       <c r="H556" t="n">
         <v>110142</v>
@@ -16580,7 +16580,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>1.73472118377686</v>
+        <v>1.73472130298615</v>
       </c>
       <c r="H559" t="n">
         <v>125349</v>
@@ -16609,7 +16609,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772555828094</v>
       </c>
       <c r="H560" t="n">
         <v>124459</v>
@@ -16696,7 +16696,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812927246094</v>
       </c>
       <c r="H563" t="n">
         <v>138274</v>
@@ -16725,7 +16725,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G564" t="n">
-        <v>1.81452679634094</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H564" t="n">
         <v>89223</v>
@@ -16783,7 +16783,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>1.8229273557663</v>
+        <v>1.82292747497559</v>
       </c>
       <c r="H566" t="n">
         <v>49850</v>
@@ -16870,7 +16870,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G569" t="n">
-        <v>1.83132791519165</v>
+        <v>1.83132803440094</v>
       </c>
       <c r="H569" t="n">
         <v>150077</v>
@@ -16899,7 +16899,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H570" t="n">
         <v>90250</v>
@@ -17044,7 +17044,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H575" t="n">
         <v>126706</v>
@@ -17073,7 +17073,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412332057953</v>
       </c>
       <c r="H576" t="n">
         <v>42580</v>
@@ -17189,7 +17189,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.81872713565826</v>
+        <v>1.81872701644897</v>
       </c>
       <c r="H580" t="n">
         <v>129414</v>
@@ -17247,7 +17247,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G582" t="n">
-        <v>1.81452679634094</v>
+        <v>1.81452691555023</v>
       </c>
       <c r="H582" t="n">
         <v>28117</v>
@@ -17276,7 +17276,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.84812915325165</v>
+        <v>1.84812927246094</v>
       </c>
       <c r="H583" t="n">
         <v>151416</v>
@@ -17305,7 +17305,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113364696503</v>
+        <v>1.91113388538361</v>
       </c>
       <c r="H584" t="n">
         <v>252203</v>
@@ -17392,7 +17392,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86913061141968</v>
+        <v>1.86913049221039</v>
       </c>
       <c r="H587" t="n">
         <v>102743</v>
@@ -17450,7 +17450,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.89013195037842</v>
+        <v>1.89013230800629</v>
       </c>
       <c r="H589" t="n">
         <v>435390</v>
@@ -17508,7 +17508,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>1.89853262901306</v>
+        <v>1.89853274822235</v>
       </c>
       <c r="H591" t="n">
         <v>268816</v>
@@ -17537,7 +17537,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.92373430728912</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H592" t="n">
         <v>234946</v>
@@ -17566,7 +17566,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.92373430728912</v>
+        <v>1.92373442649841</v>
       </c>
       <c r="H593" t="n">
         <v>139281</v>
@@ -17595,7 +17595,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98253846168518</v>
+        <v>1.98253858089447</v>
       </c>
       <c r="H594" t="n">
         <v>224369</v>
@@ -17711,7 +17711,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.01614117622375</v>
+        <v>2.01614093780518</v>
       </c>
       <c r="H598" t="n">
         <v>203153</v>
@@ -17740,7 +17740,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>2.04554295539856</v>
+        <v>2.04554271697998</v>
       </c>
       <c r="H599" t="n">
         <v>468694</v>
@@ -17769,7 +17769,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>2.08334589004517</v>
+        <v>2.08334565162659</v>
       </c>
       <c r="H600" t="n">
         <v>380134</v>
@@ -17798,7 +17798,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093902111053</v>
+        <v>1.99093925952911</v>
       </c>
       <c r="H601" t="n">
         <v>580375</v>
@@ -17827,7 +17827,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G602" t="n">
-        <v>2.11694812774658</v>
+        <v>2.116947889328</v>
       </c>
       <c r="H602" t="n">
         <v>777960</v>
@@ -17914,7 +17914,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H605" t="n">
         <v>545260</v>
@@ -17943,7 +17943,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935440063477</v>
+        <v>2.20935463905334</v>
       </c>
       <c r="H606" t="n">
         <v>207664</v>
@@ -18001,7 +18001,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G608" t="n">
-        <v>2.23455619812012</v>
+        <v>2.2345564365387</v>
       </c>
       <c r="H608" t="n">
         <v>253203</v>
@@ -18059,7 +18059,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316584587097</v>
+        <v>2.37316560745239</v>
       </c>
       <c r="H610" t="n">
         <v>1841688</v>
@@ -18088,7 +18088,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41096830368042</v>
+        <v>2.410968542099</v>
       </c>
       <c r="H611" t="n">
         <v>984452</v>
@@ -18117,7 +18117,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177549362183</v>
+        <v>2.51177573204041</v>
       </c>
       <c r="H612" t="n">
         <v>948656</v>
@@ -18146,7 +18146,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>2.31436157226562</v>
+        <v>2.3143618106842</v>
       </c>
       <c r="H613" t="n">
         <v>1745359</v>
@@ -18175,7 +18175,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41936922073364</v>
+        <v>2.41936945915222</v>
       </c>
       <c r="H614" t="n">
         <v>1222010</v>
@@ -18233,7 +18233,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>2.54537796974182</v>
+        <v>2.54537773132324</v>
       </c>
       <c r="H616" t="n">
         <v>745527</v>
@@ -18262,7 +18262,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>2.62938404083252</v>
+        <v>2.62938380241394</v>
       </c>
       <c r="H617" t="n">
         <v>902836</v>
@@ -18320,7 +18320,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>2.74699234962463</v>
+        <v>2.74699211120605</v>
       </c>
       <c r="H619" t="n">
         <v>726908</v>
@@ -18407,7 +18407,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>2.83939838409424</v>
+        <v>2.83939862251282</v>
       </c>
       <c r="H622" t="n">
         <v>500692</v>
@@ -18436,7 +18436,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059458732605</v>
+        <v>2.78059411048889</v>
       </c>
       <c r="H623" t="n">
         <v>401592</v>
@@ -18494,7 +18494,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00320982933044</v>
+        <v>3.00321006774902</v>
       </c>
       <c r="H625" t="n">
         <v>870894</v>
@@ -18610,7 +18610,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.15442085266113</v>
+        <v>3.15442061424255</v>
       </c>
       <c r="H629" t="n">
         <v>309284</v>
@@ -18813,7 +18813,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H636" t="n">
         <v>267220</v>
@@ -18871,7 +18871,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>3.24262642860413</v>
+        <v>3.24262666702271</v>
       </c>
       <c r="H638" t="n">
         <v>131141</v>
@@ -18900,7 +18900,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803767204285</v>
+        <v>3.39803743362427</v>
       </c>
       <c r="H639" t="n">
         <v>640363</v>
@@ -18929,7 +18929,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>3.37703609466553</v>
+        <v>3.37703585624695</v>
       </c>
       <c r="H640" t="n">
         <v>341923</v>
@@ -18958,7 +18958,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>3.44424080848694</v>
+        <v>3.44424057006836</v>
       </c>
       <c r="H641" t="n">
         <v>310949</v>
@@ -18987,7 +18987,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G642" t="n">
-        <v>3.40223813056946</v>
+        <v>3.40223789215088</v>
       </c>
       <c r="H642" t="n">
         <v>292921</v>
@@ -19016,7 +19016,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>3.44424080848694</v>
+        <v>3.44424057006836</v>
       </c>
       <c r="H643" t="n">
         <v>257284</v>
@@ -19074,7 +19074,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>3.5492479801178</v>
+        <v>3.54924821853638</v>
       </c>
       <c r="H645" t="n">
         <v>327182</v>
@@ -19103,7 +19103,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645269393921</v>
+        <v>3.61645245552063</v>
       </c>
       <c r="H646" t="n">
         <v>320057</v>
@@ -19132,7 +19132,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.68785786628723</v>
+        <v>3.68785762786865</v>
       </c>
       <c r="H647" t="n">
         <v>693802</v>
@@ -19161,7 +19161,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446459770203</v>
+        <v>3.78446483612061</v>
       </c>
       <c r="H648" t="n">
         <v>331005</v>
@@ -19190,7 +19190,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827580451965</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H649" t="n">
         <v>536313</v>
@@ -19248,7 +19248,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927762031555</v>
+        <v>3.96927738189697</v>
       </c>
       <c r="H651" t="n">
         <v>414943</v>
@@ -19306,7 +19306,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.74666213989258</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H653" t="n">
         <v>890296</v>
@@ -19364,7 +19364,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226729393005</v>
+        <v>3.82226777076721</v>
       </c>
       <c r="H655" t="n">
         <v>304092</v>
@@ -19393,7 +19393,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H656" t="n">
         <v>309751</v>
@@ -19422,7 +19422,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545135498047</v>
+        <v>3.59545111656189</v>
       </c>
       <c r="H657" t="n">
         <v>526354</v>
@@ -19451,7 +19451,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>3.79706525802612</v>
+        <v>3.7970654964447</v>
       </c>
       <c r="H658" t="n">
         <v>467873</v>
@@ -19480,7 +19480,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G659" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H659" t="n">
         <v>604346</v>
@@ -19509,7 +19509,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G660" t="n">
-        <v>3.94407558441162</v>
+        <v>3.94407606124878</v>
       </c>
       <c r="H660" t="n">
         <v>225534</v>
@@ -19538,7 +19538,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H661" t="n">
         <v>680135</v>
@@ -19567,7 +19567,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.12048768997192</v>
+        <v>4.12048816680908</v>
       </c>
       <c r="H662" t="n">
         <v>313436</v>
@@ -19625,7 +19625,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.47751331329346</v>
+        <v>4.47751235961914</v>
       </c>
       <c r="H664" t="n">
         <v>885590</v>
@@ -19799,7 +19799,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>4.79673528671265</v>
+        <v>4.7967357635498</v>
       </c>
       <c r="H670" t="n">
         <v>250557</v>
@@ -19828,7 +19828,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>4.72112989425659</v>
+        <v>4.72113037109375</v>
       </c>
       <c r="H671" t="n">
         <v>193001</v>
@@ -19857,7 +19857,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G672" t="n">
-        <v>4.1834921836853</v>
+        <v>4.18349266052246</v>
       </c>
       <c r="H672" t="n">
         <v>1024929</v>
@@ -19915,7 +19915,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.82193660736084</v>
+        <v>4.821937084198</v>
       </c>
       <c r="H674" t="n">
         <v>840694</v>
@@ -20089,7 +20089,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.70432901382446</v>
+        <v>4.7043285369873</v>
       </c>
       <c r="H680" t="n">
         <v>305866</v>
@@ -20147,7 +20147,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>4.67912721633911</v>
+        <v>4.67912769317627</v>
       </c>
       <c r="H682" t="n">
         <v>344165</v>
@@ -20205,7 +20205,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G684" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H684" t="n">
         <v>156997</v>
@@ -20263,7 +20263,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G686" t="n">
-        <v>4.56151914596558</v>
+        <v>4.56151819229126</v>
       </c>
       <c r="H686" t="n">
         <v>236154</v>
@@ -20321,7 +20321,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44391107559204</v>
+        <v>4.44391059875488</v>
       </c>
       <c r="H688" t="n">
         <v>234396</v>
@@ -20350,7 +20350,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271463394165</v>
+        <v>4.50271511077881</v>
       </c>
       <c r="H689" t="n">
         <v>161397</v>
@@ -20379,7 +20379,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G690" t="n">
-        <v>4.46911239624023</v>
+        <v>4.46911287307739</v>
       </c>
       <c r="H690" t="n">
         <v>256912</v>
@@ -20408,7 +20408,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350748062134</v>
+        <v>4.39350700378418</v>
       </c>
       <c r="H691" t="n">
         <v>319589</v>
@@ -20437,7 +20437,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>4.3347020149231</v>
+        <v>4.33470249176025</v>
       </c>
       <c r="H692" t="n">
         <v>263689</v>
@@ -20466,7 +20466,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749849319458</v>
       </c>
       <c r="H693" t="n">
         <v>130168</v>
@@ -20495,7 +20495,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>4.05328321456909</v>
+        <v>4.05328273773193</v>
       </c>
       <c r="H694" t="n">
         <v>499614</v>
@@ -20553,7 +20553,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10788679122925</v>
+        <v>4.10788726806641</v>
       </c>
       <c r="H696" t="n">
         <v>268352</v>
@@ -20611,7 +20611,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.80546641349792</v>
+        <v>3.8054666519165</v>
       </c>
       <c r="H698" t="n">
         <v>372911</v>
@@ -20669,7 +20669,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.73826122283936</v>
+        <v>3.73826098442078</v>
       </c>
       <c r="H700" t="n">
         <v>569444</v>
@@ -20698,7 +20698,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.6626558303833</v>
+        <v>3.66265606880188</v>
       </c>
       <c r="H701" t="n">
         <v>726054</v>
@@ -20756,7 +20756,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G703" t="n">
-        <v>3.51144552230835</v>
+        <v>3.51144528388977</v>
       </c>
       <c r="H703" t="n">
         <v>923184</v>
@@ -20785,7 +20785,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H704" t="n">
         <v>848630</v>
@@ -20843,7 +20843,7 @@
         <v>3.625</v>
       </c>
       <c r="G706" t="n">
-        <v>3.04521250724792</v>
+        <v>3.0452127456665</v>
       </c>
       <c r="H706" t="n">
         <v>384688</v>
@@ -20872,7 +20872,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H707" t="n">
         <v>426984</v>
@@ -20901,7 +20901,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.99480938911438</v>
+        <v>2.9948091506958</v>
       </c>
       <c r="H708" t="n">
         <v>295472</v>
@@ -20930,7 +20930,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H709" t="n">
         <v>375579</v>
@@ -20959,7 +20959,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G710" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H710" t="n">
         <v>559647</v>
@@ -21017,7 +21017,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.95280647277832</v>
+        <v>2.95280623435974</v>
       </c>
       <c r="H712" t="n">
         <v>247551</v>
@@ -21046,7 +21046,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.98220825195312</v>
+        <v>2.9822084903717</v>
       </c>
       <c r="H713" t="n">
         <v>188189</v>
@@ -21104,7 +21104,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G715" t="n">
-        <v>2.80579614639282</v>
+        <v>2.8057963848114</v>
       </c>
       <c r="H715" t="n">
         <v>252342</v>
@@ -21220,7 +21220,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G719" t="n">
-        <v>2.66718649864197</v>
+        <v>2.66718626022339</v>
       </c>
       <c r="H719" t="n">
         <v>464448</v>
@@ -21365,7 +21365,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G724" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H724" t="n">
         <v>1093352</v>
@@ -21394,7 +21394,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H725" t="n">
         <v>454214</v>
@@ -21423,7 +21423,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.14181923866272</v>
+        <v>3.1418194770813</v>
       </c>
       <c r="H726" t="n">
         <v>367513</v>
@@ -21481,7 +21481,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G728" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H728" t="n">
         <v>411240</v>
@@ -21510,7 +21510,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G729" t="n">
-        <v>3.31823182106018</v>
+        <v>3.31823205947876</v>
       </c>
       <c r="H729" t="n">
         <v>295648</v>
@@ -21713,7 +21713,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="n">
-        <v>3.09141635894775</v>
+        <v>3.09141612052917</v>
       </c>
       <c r="H736" t="n">
         <v>239182</v>
@@ -21742,7 +21742,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380757331848</v>
       </c>
       <c r="H737" t="n">
         <v>226777</v>
@@ -21800,7 +21800,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.84779906272888</v>
+        <v>2.84779930114746</v>
       </c>
       <c r="H739" t="n">
         <v>272198</v>
@@ -21829,7 +21829,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>2.79319524765015</v>
+        <v>2.79319500923157</v>
       </c>
       <c r="H740" t="n">
         <v>100946</v>
@@ -21858,7 +21858,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>2.83939838409424</v>
+        <v>2.83939862251282</v>
       </c>
       <c r="H741" t="n">
         <v>67826</v>
@@ -21916,7 +21916,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92760467529297</v>
+        <v>2.92760443687439</v>
       </c>
       <c r="H743" t="n">
         <v>213240</v>
@@ -21945,7 +21945,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>3.20902442932129</v>
+        <v>3.20902419090271</v>
       </c>
       <c r="H744" t="n">
         <v>370069</v>
@@ -21974,7 +21974,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G745" t="n">
-        <v>3.17542171478271</v>
+        <v>3.17542195320129</v>
       </c>
       <c r="H745" t="n">
         <v>579265</v>
@@ -22090,7 +22090,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H749" t="n">
         <v>224963</v>
@@ -22119,7 +22119,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781412124634</v>
+        <v>3.05781364440918</v>
       </c>
       <c r="H750" t="n">
         <v>147033</v>
@@ -22148,7 +22148,7 @@
         <v>3.625</v>
       </c>
       <c r="G751" t="n">
-        <v>3.04521250724792</v>
+        <v>3.0452127456665</v>
       </c>
       <c r="H751" t="n">
         <v>315691</v>
@@ -22177,7 +22177,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.98220825195312</v>
+        <v>2.9822084903717</v>
       </c>
       <c r="H752" t="n">
         <v>253493</v>
@@ -22206,7 +22206,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380805015564</v>
+        <v>2.97380757331848</v>
       </c>
       <c r="H753" t="n">
         <v>142456</v>
@@ -22235,7 +22235,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G754" t="n">
-        <v>3.02001094818115</v>
+        <v>3.02001118659973</v>
       </c>
       <c r="H754" t="n">
         <v>82541</v>
@@ -22264,7 +22264,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G755" t="n">
-        <v>2.99060916900635</v>
+        <v>2.99060893058777</v>
       </c>
       <c r="H755" t="n">
         <v>113781</v>
@@ -22351,7 +22351,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418200492859</v>
+        <v>2.60418224334717</v>
       </c>
       <c r="H758" t="n">
         <v>295455</v>
@@ -22438,7 +22438,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G761" t="n">
-        <v>2.64618515968323</v>
+        <v>2.64618492126465</v>
       </c>
       <c r="H761" t="n">
         <v>124988</v>
@@ -22525,7 +22525,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G764" t="n">
-        <v>2.84779906272888</v>
+        <v>2.84779930114746</v>
       </c>
       <c r="H764" t="n">
         <v>321253</v>
@@ -22554,7 +22554,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>2.91500377655029</v>
+        <v>2.91500401496887</v>
       </c>
       <c r="H765" t="n">
         <v>153244</v>
@@ -22612,7 +22612,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G767" t="n">
-        <v>2.89400243759155</v>
+        <v>2.89400219917297</v>
       </c>
       <c r="H767" t="n">
         <v>120075</v>
@@ -22728,7 +22728,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15862059593201</v>
+        <v>3.15862083435059</v>
       </c>
       <c r="H771" t="n">
         <v>105311</v>
@@ -22815,7 +22815,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.06201386451721</v>
+        <v>3.06201410293579</v>
       </c>
       <c r="H774" t="n">
         <v>67584</v>
@@ -22873,7 +22873,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.22582530975342</v>
+        <v>3.225825548172</v>
       </c>
       <c r="H776" t="n">
         <v>234308</v>
@@ -22989,7 +22989,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026390075684</v>
+        <v>3.78026461601257</v>
       </c>
       <c r="H780" t="n">
         <v>599313</v>
@@ -23047,7 +23047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226729393005</v>
+        <v>3.82226777076721</v>
       </c>
       <c r="H782" t="n">
         <v>469438</v>
@@ -23076,7 +23076,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.9860782623291</v>
+        <v>3.98607850074768</v>
       </c>
       <c r="H783" t="n">
         <v>485114</v>
@@ -23105,7 +23105,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148855209351</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H784" t="n">
         <v>562311</v>
@@ -23134,7 +23134,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G785" t="n">
-        <v>4.11628818511963</v>
+        <v>4.11628770828247</v>
       </c>
       <c r="H785" t="n">
         <v>283610</v>
@@ -23221,7 +23221,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H788" t="n">
         <v>224507</v>
@@ -23308,7 +23308,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486819267273</v>
+        <v>3.83486771583557</v>
       </c>
       <c r="H791" t="n">
         <v>191763</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.70465898513794</v>
+        <v>3.70465874671936</v>
       </c>
       <c r="H792" t="n">
         <v>292131</v>
@@ -23366,7 +23366,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G793" t="n">
-        <v>3.84326839447021</v>
+        <v>3.84326863288879</v>
       </c>
       <c r="H793" t="n">
         <v>223832</v>
@@ -23424,7 +23424,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G795" t="n">
-        <v>3.87267112731934</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H795" t="n">
         <v>114469</v>
@@ -23482,7 +23482,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H797" t="n">
         <v>63961</v>
@@ -23540,7 +23540,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827580451965</v>
+        <v>3.94827556610107</v>
       </c>
       <c r="H799" t="n">
         <v>128867</v>
@@ -23569,7 +23569,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147468566895</v>
+        <v>3.93147444725037</v>
       </c>
       <c r="H800" t="n">
         <v>132720</v>
@@ -23598,7 +23598,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88947200775146</v>
+        <v>3.88947176933289</v>
       </c>
       <c r="H801" t="n">
         <v>39567</v>
@@ -23656,7 +23656,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.96507692337036</v>
+        <v>3.96507716178894</v>
       </c>
       <c r="H803" t="n">
         <v>122911</v>
@@ -23685,7 +23685,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H804" t="n">
         <v>63625</v>
@@ -23714,7 +23714,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427068710327</v>
       </c>
       <c r="H805" t="n">
         <v>135123</v>
@@ -23801,7 +23801,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165472984314</v>
+        <v>3.64165449142456</v>
       </c>
       <c r="H808" t="n">
         <v>150135</v>
@@ -23830,7 +23830,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G809" t="n">
-        <v>3.62905359268188</v>
+        <v>3.62905383110046</v>
       </c>
       <c r="H809" t="n">
         <v>170209</v>
@@ -23917,7 +23917,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>3.74666213989258</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H812" t="n">
         <v>387155</v>
@@ -23946,7 +23946,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845584869385</v>
+        <v>3.65845561027527</v>
       </c>
       <c r="H813" t="n">
         <v>431429</v>
@@ -23975,7 +23975,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>3.74666213989258</v>
+        <v>3.746661901474</v>
       </c>
       <c r="H814" t="n">
         <v>334266</v>
@@ -24033,7 +24033,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>4.11208772659302</v>
+        <v>4.11208724975586</v>
       </c>
       <c r="H816" t="n">
         <v>491127</v>
@@ -24062,7 +24062,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>4.04068231582642</v>
+        <v>4.04068279266357</v>
       </c>
       <c r="H817" t="n">
         <v>212730</v>
@@ -24120,7 +24120,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H819" t="n">
         <v>214808</v>
@@ -24178,7 +24178,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.86426997184753</v>
+        <v>3.86427068710327</v>
       </c>
       <c r="H821" t="n">
         <v>245208</v>
@@ -24265,7 +24265,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H824" t="n">
         <v>280086</v>
@@ -24323,7 +24323,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>4.08688545227051</v>
+        <v>4.08688592910767</v>
       </c>
       <c r="H826" t="n">
         <v>196766</v>
@@ -24381,7 +24381,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008504867554</v>
+        <v>4.07008409500122</v>
       </c>
       <c r="H828" t="n">
         <v>111313</v>
@@ -24410,7 +24410,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148855209351</v>
+        <v>4.14148902893066</v>
       </c>
       <c r="H829" t="n">
         <v>178794</v>
@@ -24439,7 +24439,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>4.53631687164307</v>
+        <v>4.53631734848022</v>
       </c>
       <c r="H830" t="n">
         <v>1165706</v>
@@ -24497,7 +24497,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G832" t="n">
-        <v>4.61192178726196</v>
+        <v>4.61192226409912</v>
       </c>
       <c r="H832" t="n">
         <v>446862</v>
@@ -24526,7 +24526,7 @@
         <v>5.5</v>
       </c>
       <c r="G833" t="n">
-        <v>4.62032318115234</v>
+        <v>4.62032270431519</v>
       </c>
       <c r="H833" t="n">
         <v>457602</v>
@@ -24613,7 +24613,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030836105347</v>
+        <v>4.41030883789062</v>
       </c>
       <c r="H836" t="n">
         <v>161740</v>
@@ -24700,7 +24700,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749801635742</v>
+        <v>4.26749849319458</v>
       </c>
       <c r="H839" t="n">
         <v>229262</v>
@@ -24758,7 +24758,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228235244751</v>
+        <v>4.03228187561035</v>
       </c>
       <c r="H841" t="n">
         <v>258680</v>
@@ -24787,7 +24787,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627312660217</v>
+        <v>3.90627288818359</v>
       </c>
       <c r="H842" t="n">
         <v>193026</v>
@@ -24816,7 +24816,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746861457825</v>
+        <v>3.84746885299683</v>
       </c>
       <c r="H843" t="n">
         <v>134136</v>
@@ -24845,7 +24845,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866505622864</v>
+        <v>3.78866481781006</v>
       </c>
       <c r="H844" t="n">
         <v>180317</v>
@@ -24874,7 +24874,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.973477602005</v>
+        <v>3.97347807884216</v>
       </c>
       <c r="H845" t="n">
         <v>787756</v>
@@ -24903,7 +24903,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>3.92307424545288</v>
+        <v>3.92307448387146</v>
       </c>
       <c r="H846" t="n">
         <v>609683</v>
@@ -24932,7 +24932,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>3.87267112731934</v>
+        <v>3.87267065048218</v>
       </c>
       <c r="H847" t="n">
         <v>424574</v>
@@ -25019,7 +25019,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H850" t="n">
         <v>352449</v>
@@ -25048,7 +25048,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H851" t="n">
         <v>279899</v>
@@ -25077,7 +25077,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G852" t="n">
-        <v>4.09310150146484</v>
+        <v>4.09310245513916</v>
       </c>
       <c r="H852" t="n">
         <v>823655</v>
@@ -25135,7 +25135,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71275019645691</v>
+        <v>3.71275043487549</v>
       </c>
       <c r="H854" t="n">
         <v>237445</v>
@@ -25164,7 +25164,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.73436093330383</v>
+        <v>3.73436117172241</v>
       </c>
       <c r="H855" t="n">
         <v>240038</v>
@@ -25193,7 +25193,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868274688721</v>
+        <v>3.73868298530579</v>
       </c>
       <c r="H856" t="n">
         <v>149487</v>
@@ -25280,7 +25280,7 @@
         <v>4.5</v>
       </c>
       <c r="G859" t="n">
-        <v>3.88995909690857</v>
+        <v>3.88995933532715</v>
       </c>
       <c r="H859" t="n">
         <v>350261</v>
@@ -25309,7 +25309,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157054901123</v>
+        <v>3.91157031059265</v>
       </c>
       <c r="H860" t="n">
         <v>222935</v>
@@ -25367,7 +25367,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385077476501</v>
       </c>
       <c r="H862" t="n">
         <v>185171</v>
@@ -25454,7 +25454,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359545707703</v>
+        <v>3.64359521865845</v>
       </c>
       <c r="H865" t="n">
         <v>139539</v>
@@ -25483,7 +25483,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>3.50096368789673</v>
+        <v>3.50096344947815</v>
       </c>
       <c r="H866" t="n">
         <v>230177</v>
@@ -25541,7 +25541,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G868" t="n">
-        <v>3.41019773483276</v>
+        <v>3.41019749641418</v>
       </c>
       <c r="H868" t="n">
         <v>168875</v>
@@ -25657,7 +25657,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503042221069</v>
+        <v>3.47503018379211</v>
       </c>
       <c r="H872" t="n">
         <v>217721</v>
@@ -25715,7 +25715,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>3.52689647674561</v>
+        <v>3.52689623832703</v>
       </c>
       <c r="H874" t="n">
         <v>98751</v>
@@ -25744,7 +25744,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G875" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H875" t="n">
         <v>71123</v>
@@ -25773,7 +25773,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.4015531539917</v>
+        <v>3.40155363082886</v>
       </c>
       <c r="H876" t="n">
         <v>185268</v>
@@ -25918,7 +25918,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>3.31510972976685</v>
+        <v>3.31510996818542</v>
       </c>
       <c r="H881" t="n">
         <v>112761</v>
@@ -25976,7 +25976,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G883" t="n">
-        <v>3.39723134040833</v>
+        <v>3.39723110198975</v>
       </c>
       <c r="H883" t="n">
         <v>257002</v>
@@ -26005,7 +26005,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646562576294</v>
+        <v>3.30646538734436</v>
       </c>
       <c r="H884" t="n">
         <v>244267</v>
@@ -26063,7 +26063,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>3.26324391365051</v>
+        <v>3.26324367523193</v>
       </c>
       <c r="H886" t="n">
         <v>143035</v>
@@ -26092,7 +26092,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163293838501</v>
+        <v>3.24163269996643</v>
       </c>
       <c r="H887" t="n">
         <v>163491</v>
@@ -26150,7 +26150,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.22434401512146</v>
+        <v>3.22434425354004</v>
       </c>
       <c r="H889" t="n">
         <v>96520</v>
@@ -26179,7 +26179,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>3.2589213848114</v>
+        <v>3.25892162322998</v>
       </c>
       <c r="H890" t="n">
         <v>91110</v>
@@ -26208,7 +26208,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646562576294</v>
+        <v>3.30646538734436</v>
       </c>
       <c r="H891" t="n">
         <v>200140</v>
@@ -26266,7 +26266,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H893" t="n">
         <v>139091</v>
@@ -26295,7 +26295,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H894" t="n">
         <v>85735</v>
@@ -26324,7 +26324,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.17680025100708</v>
+        <v>3.1768000125885</v>
       </c>
       <c r="H895" t="n">
         <v>103388</v>
@@ -26353,7 +26353,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H896" t="n">
         <v>119831</v>
@@ -26382,7 +26382,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756572723389</v>
+        <v>3.26756596565247</v>
       </c>
       <c r="H897" t="n">
         <v>379211</v>
@@ -26440,7 +26440,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>3.2589213848114</v>
+        <v>3.25892162322998</v>
       </c>
       <c r="H899" t="n">
         <v>114743</v>
@@ -26469,7 +26469,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.25027704238892</v>
+        <v>3.2502772808075</v>
       </c>
       <c r="H900" t="n">
         <v>76009</v>
@@ -26614,7 +26614,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G905" t="n">
-        <v>3.22866630554199</v>
+        <v>3.22866606712341</v>
       </c>
       <c r="H905" t="n">
         <v>85073</v>
@@ -26643,7 +26643,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H906" t="n">
         <v>93066</v>
@@ -26672,7 +26672,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>3.20705533027649</v>
+        <v>3.20705556869507</v>
       </c>
       <c r="H907" t="n">
         <v>135848</v>
@@ -26846,7 +26846,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H913" t="n">
         <v>826164</v>
@@ -26991,7 +26991,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385053634644</v>
+        <v>3.67385077476501</v>
       </c>
       <c r="H918" t="n">
         <v>412035</v>
@@ -27020,7 +27020,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H919" t="n">
         <v>281614</v>
@@ -27049,7 +27049,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G920" t="n">
-        <v>3.44477486610413</v>
+        <v>3.44477510452271</v>
       </c>
       <c r="H920" t="n">
         <v>529420</v>
@@ -27136,7 +27136,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H923" t="n">
         <v>275779</v>
@@ -27165,7 +27165,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H924" t="n">
         <v>233109</v>
@@ -27223,7 +27223,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444071769714</v>
+        <v>3.57444047927856</v>
       </c>
       <c r="H926" t="n">
         <v>367003</v>
@@ -27252,7 +27252,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G927" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H927" t="n">
         <v>182647</v>
@@ -27310,7 +27310,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G929" t="n">
-        <v>3.62198424339294</v>
+        <v>3.62198448181152</v>
       </c>
       <c r="H929" t="n">
         <v>169327</v>
@@ -27339,7 +27339,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.57011818885803</v>
+        <v>3.57011842727661</v>
       </c>
       <c r="H930" t="n">
         <v>221733</v>
@@ -27368,7 +27368,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>3.55282950401306</v>
+        <v>3.55282926559448</v>
       </c>
       <c r="H931" t="n">
         <v>92909</v>
@@ -27397,7 +27397,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>3.58308458328247</v>
+        <v>3.58308482170105</v>
       </c>
       <c r="H932" t="n">
         <v>271781</v>
@@ -27542,7 +27542,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960803031921</v>
+        <v>3.50960779190063</v>
       </c>
       <c r="H937" t="n">
         <v>213268</v>
@@ -27629,7 +27629,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H940" t="n">
         <v>107731</v>
@@ -27658,7 +27658,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>3.51393008232117</v>
+        <v>3.51392984390259</v>
       </c>
       <c r="H941" t="n">
         <v>236550</v>
@@ -27745,7 +27745,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487156867981</v>
+        <v>3.79487133026123</v>
       </c>
       <c r="H944" t="n">
         <v>271076</v>
@@ -27774,7 +27774,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H945" t="n">
         <v>315309</v>
@@ -27803,7 +27803,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.61766242980957</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H946" t="n">
         <v>539098</v>
@@ -27861,7 +27861,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>3.59605145454407</v>
+        <v>3.59605121612549</v>
       </c>
       <c r="H948" t="n">
         <v>88816</v>
@@ -27919,7 +27919,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G950" t="n">
-        <v>3.587406873703</v>
+        <v>3.58740711212158</v>
       </c>
       <c r="H950" t="n">
         <v>137894</v>
@@ -27977,7 +27977,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G952" t="n">
-        <v>3.62198424339294</v>
+        <v>3.62198448181152</v>
       </c>
       <c r="H952" t="n">
         <v>64199</v>
@@ -28006,7 +28006,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>3.61766242980957</v>
+        <v>3.61766219139099</v>
       </c>
       <c r="H953" t="n">
         <v>46261</v>
@@ -28064,7 +28064,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774173736572</v>
+        <v>3.45774149894714</v>
       </c>
       <c r="H955" t="n">
         <v>118165</v>
@@ -28122,7 +28122,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G957" t="n">
-        <v>3.48799657821655</v>
+        <v>3.48799681663513</v>
       </c>
       <c r="H957" t="n">
         <v>73213</v>
@@ -28209,7 +28209,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638607978821</v>
+        <v>3.46638631820679</v>
       </c>
       <c r="H960" t="n">
         <v>67763</v>
@@ -28238,7 +28238,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>3.45341920852661</v>
+        <v>3.45341944694519</v>
       </c>
       <c r="H961" t="n">
         <v>86978</v>
@@ -28296,7 +28296,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G963" t="n">
-        <v>3.57011818885803</v>
+        <v>3.57011842727661</v>
       </c>
       <c r="H963" t="n">
         <v>60156</v>
@@ -28325,7 +28325,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>3.53554081916809</v>
+        <v>3.53554105758667</v>
       </c>
       <c r="H964" t="n">
         <v>125810</v>
@@ -28383,7 +28383,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>3.81648254394531</v>
+        <v>3.81648230552673</v>
       </c>
       <c r="H966" t="n">
         <v>901832</v>
@@ -28412,7 +28412,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H967" t="n">
         <v>671393</v>
@@ -28441,7 +28441,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054951667786</v>
+        <v>3.79054975509644</v>
       </c>
       <c r="H968" t="n">
         <v>389865</v>
@@ -28470,7 +28470,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402630805969</v>
+        <v>3.86402606964111</v>
       </c>
       <c r="H969" t="n">
         <v>302156</v>
@@ -28528,7 +28528,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="n">
-        <v>3.99801397323608</v>
+        <v>3.9980137348175</v>
       </c>
       <c r="H971" t="n">
         <v>284989</v>
@@ -28586,7 +28586,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343636512756</v>
+        <v>3.96343660354614</v>
       </c>
       <c r="H973" t="n">
         <v>108809</v>
@@ -28615,7 +28615,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724802017212</v>
+        <v>3.90724778175354</v>
       </c>
       <c r="H974" t="n">
         <v>225485</v>
@@ -28673,7 +28673,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.78622698783875</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H976" t="n">
         <v>109461</v>
@@ -28702,7 +28702,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="n">
-        <v>3.78190493583679</v>
+        <v>3.78190445899963</v>
       </c>
       <c r="H977" t="n">
         <v>66712</v>
@@ -28789,7 +28789,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241533279419</v>
+        <v>3.84241557121277</v>
       </c>
       <c r="H980" t="n">
         <v>205384</v>
@@ -28818,7 +28818,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>3.81216025352478</v>
+        <v>3.81216049194336</v>
       </c>
       <c r="H981" t="n">
         <v>426008</v>
@@ -28847,7 +28847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893830299377</v>
+        <v>3.76893854141235</v>
       </c>
       <c r="H982" t="n">
         <v>188043</v>
@@ -28905,7 +28905,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.9504702091217</v>
+        <v>3.95046997070312</v>
       </c>
       <c r="H984" t="n">
         <v>655591</v>
@@ -28963,7 +28963,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H986" t="n">
         <v>720957</v>
@@ -29050,7 +29050,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911383628845</v>
+        <v>3.95911407470703</v>
       </c>
       <c r="H989" t="n">
         <v>256400</v>
@@ -29079,7 +29079,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318128585815</v>
+        <v>3.93318104743958</v>
       </c>
       <c r="H990" t="n">
         <v>214631</v>
@@ -29108,7 +29108,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.88563704490662</v>
+        <v>3.8856372833252</v>
       </c>
       <c r="H991" t="n">
         <v>325475</v>
@@ -29137,7 +29137,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G992" t="n">
-        <v>4.09310150146484</v>
+        <v>4.09310245513916</v>
       </c>
       <c r="H992" t="n">
         <v>539029</v>
@@ -29166,7 +29166,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445739746094</v>
+        <v>4.08445692062378</v>
       </c>
       <c r="H993" t="n">
         <v>676881</v>
@@ -29195,7 +29195,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="n">
-        <v>4.32217741012573</v>
+        <v>4.32217693328857</v>
       </c>
       <c r="H994" t="n">
         <v>1100977</v>
@@ -29398,7 +29398,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337421417236</v>
       </c>
       <c r="H1001" t="n">
         <v>803711</v>
@@ -29543,7 +29543,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337373733521</v>
+        <v>4.63337421417236</v>
       </c>
       <c r="H1006" t="n">
         <v>237220</v>
@@ -29601,7 +29601,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.75439500808716</v>
+        <v>4.75439453125</v>
       </c>
       <c r="H1008" t="n">
         <v>249523</v>
@@ -29833,7 +29833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1016" t="n">
         <v>142573</v>
@@ -29920,7 +29920,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659568786621</v>
+        <v>4.67659521102905</v>
       </c>
       <c r="H1019" t="n">
         <v>318021</v>
@@ -30094,7 +30094,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1025" t="n">
         <v>190180</v>
@@ -30152,7 +30152,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1027" t="n">
         <v>362151</v>
@@ -30181,7 +30181,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761648178101</v>
+        <v>4.79761695861816</v>
       </c>
       <c r="H1028" t="n">
         <v>190796</v>
@@ -30268,7 +30268,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.2817006111145</v>
+        <v>5.28170013427734</v>
       </c>
       <c r="H1031" t="n">
         <v>1366658</v>
@@ -30297,7 +30297,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340805053711</v>
+        <v>5.65340709686279</v>
       </c>
       <c r="H1032" t="n">
         <v>1195444</v>
@@ -30355,7 +30355,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.2817006111145</v>
+        <v>5.28170013427734</v>
       </c>
       <c r="H1034" t="n">
         <v>955078</v>
@@ -30413,7 +30413,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.99643707275391</v>
+        <v>4.99643754959106</v>
       </c>
       <c r="H1036" t="n">
         <v>781150</v>
@@ -30500,7 +30500,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.72846174240112</v>
+        <v>4.72846126556396</v>
       </c>
       <c r="H1039" t="n">
         <v>544285</v>
@@ -30645,7 +30645,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.59015226364136</v>
+        <v>4.5901517868042</v>
       </c>
       <c r="H1044" t="n">
         <v>169114</v>
@@ -30674,7 +30674,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48642015457153</v>
+        <v>4.48641967773438</v>
       </c>
       <c r="H1045" t="n">
         <v>723012</v>
@@ -30703,7 +30703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.52964115142822</v>
+        <v>4.52964162826538</v>
       </c>
       <c r="H1046" t="n">
         <v>233413</v>
@@ -30761,7 +30761,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.41726541519165</v>
+        <v>4.41726493835449</v>
       </c>
       <c r="H1048" t="n">
         <v>203223</v>
@@ -30935,7 +30935,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428162574768</v>
+        <v>3.89428186416626</v>
       </c>
       <c r="H1054" t="n">
         <v>573847</v>
@@ -30964,7 +30964,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970425605774</v>
+        <v>3.85970401763916</v>
       </c>
       <c r="H1055" t="n">
         <v>847899</v>
@@ -30993,7 +30993,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.78622698783875</v>
+        <v>3.78622722625732</v>
       </c>
       <c r="H1056" t="n">
         <v>469309</v>
@@ -31022,7 +31022,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.8251268863678</v>
+        <v>3.82512664794922</v>
       </c>
       <c r="H1057" t="n">
         <v>541802</v>
@@ -31109,7 +31109,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59172940254211</v>
+        <v>3.59172916412354</v>
       </c>
       <c r="H1060" t="n">
         <v>379798</v>
@@ -31138,7 +31138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503042221069</v>
+        <v>3.47503018379211</v>
       </c>
       <c r="H1061" t="n">
         <v>283526</v>
@@ -31167,7 +31167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.39723134040833</v>
+        <v>3.39723110198975</v>
       </c>
       <c r="H1062" t="n">
         <v>449166</v>
@@ -31196,7 +31196,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.02984619140625</v>
+        <v>3.02984642982483</v>
       </c>
       <c r="H1063" t="n">
         <v>357198</v>
@@ -31225,7 +31225,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.06010150909424</v>
+        <v>3.06010127067566</v>
       </c>
       <c r="H1064" t="n">
         <v>505917</v>
@@ -31283,7 +31283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085030555725</v>
+        <v>2.64085006713867</v>
       </c>
       <c r="H1066" t="n">
         <v>650023</v>
@@ -31370,7 +31370,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.38151931762695</v>
+        <v>2.38151955604553</v>
       </c>
       <c r="H1069" t="n">
         <v>130604</v>
@@ -31399,7 +31399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.07464528083801</v>
+        <v>2.07464504241943</v>
       </c>
       <c r="H1070" t="n">
         <v>262247</v>
@@ -31602,7 +31602,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.32533144950867</v>
+        <v>2.32533121109009</v>
       </c>
       <c r="H1077" t="n">
         <v>581790</v>
@@ -31631,7 +31631,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.32533144950867</v>
+        <v>2.32533121109009</v>
       </c>
       <c r="H1078" t="n">
         <v>244777</v>
@@ -31689,7 +31689,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.37719750404358</v>
+        <v>2.377197265625</v>
       </c>
       <c r="H1080" t="n">
         <v>322998</v>
@@ -31718,7 +31718,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584184646606</v>
+        <v>2.38584160804749</v>
       </c>
       <c r="H1081" t="n">
         <v>211093</v>
@@ -31805,7 +31805,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.65381646156311</v>
+        <v>2.65381669998169</v>
       </c>
       <c r="H1084" t="n">
         <v>782496</v>
@@ -31834,7 +31834,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.13790082931519</v>
+        <v>3.13790059089661</v>
       </c>
       <c r="H1085" t="n">
         <v>743640</v>
@@ -31892,7 +31892,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.01255750656128</v>
+        <v>3.0125572681427</v>
       </c>
       <c r="H1087" t="n">
         <v>431366</v>
@@ -31921,7 +31921,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.82670402526855</v>
+        <v>2.8267035484314</v>
       </c>
       <c r="H1088" t="n">
         <v>426909</v>
@@ -31979,7 +31979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.90450263023376</v>
+        <v>2.90450286865234</v>
       </c>
       <c r="H1090" t="n">
         <v>520138</v>
@@ -32008,7 +32008,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.84399271011353</v>
+        <v>2.84399247169495</v>
       </c>
       <c r="H1091" t="n">
         <v>383489</v>
@@ -32095,7 +32095,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.88289189338684</v>
+        <v>2.88289213180542</v>
       </c>
       <c r="H1094" t="n">
         <v>580788</v>
@@ -32472,7 +32472,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1107" t="n">
         <v>185508</v>
@@ -32617,7 +32617,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1112" t="n">
         <v>799814</v>
@@ -32675,7 +32675,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1114" t="n">
         <v>623601</v>
@@ -32733,7 +32733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1116" t="n">
         <v>711582</v>
@@ -32820,7 +32820,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232954025269</v>
+        <v>3.05232930183411</v>
       </c>
       <c r="H1119" t="n">
         <v>598569</v>
@@ -33139,7 +33139,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1130" t="n">
         <v>551818</v>
@@ -33255,7 +33255,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1134" t="n">
         <v>282817</v>
@@ -33284,7 +33284,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1135" t="n">
         <v>201971</v>
@@ -33429,7 +33429,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1140" t="n">
         <v>299367</v>
@@ -33516,7 +33516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1143" t="n">
         <v>886339</v>
@@ -33574,7 +33574,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1145" t="n">
         <v>572690</v>
@@ -33603,7 +33603,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1146" t="n">
         <v>308166</v>
@@ -33690,7 +33690,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1149" t="n">
         <v>745765</v>
@@ -33864,7 +33864,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1155" t="n">
         <v>470106</v>
@@ -33951,7 +33951,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1158" t="n">
         <v>245795</v>
@@ -33980,7 +33980,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1159" t="n">
         <v>285234</v>
@@ -34328,7 +34328,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1171" t="n">
         <v>1662260</v>
@@ -34357,7 +34357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1172" t="n">
         <v>666452</v>
@@ -34473,7 +34473,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1176" t="n">
         <v>577466</v>
@@ -34531,7 +34531,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.28362774848938</v>
+        <v>2.28362798690796</v>
       </c>
       <c r="H1178" t="n">
         <v>281450</v>
@@ -34676,7 +34676,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.36903929710388</v>
+        <v>2.36903953552246</v>
       </c>
       <c r="H1183" t="n">
         <v>325503</v>
@@ -34995,7 +34995,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1194" t="n">
         <v>412501</v>
@@ -35169,7 +35169,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1200" t="n">
         <v>293884</v>
@@ -35227,7 +35227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1202" t="n">
         <v>270880</v>
@@ -35517,7 +35517,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1212" t="n">
         <v>93722</v>
@@ -35575,7 +35575,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1214" t="n">
         <v>83174</v>
@@ -35604,7 +35604,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.12629127502441</v>
+        <v>2.12629151344299</v>
       </c>
       <c r="H1215" t="n">
         <v>55817</v>
@@ -35720,7 +35720,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1219" t="n">
         <v>149277</v>
@@ -35836,7 +35836,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1223" t="n">
         <v>120064</v>
@@ -35865,7 +35865,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.88354349136353</v>
+        <v>1.88354361057281</v>
       </c>
       <c r="H1224" t="n">
         <v>220159</v>
@@ -35923,7 +35923,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620689868927</v>
+        <v>1.72620701789856</v>
       </c>
       <c r="H1226" t="n">
         <v>214567</v>
@@ -35981,7 +35981,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.76037156581879</v>
+        <v>1.7603714466095</v>
       </c>
       <c r="H1228" t="n">
         <v>328193</v>
@@ -36213,7 +36213,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H1236" t="n">
         <v>923518</v>
@@ -36677,7 +36677,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1252" t="n">
         <v>102114</v>
@@ -36938,7 +36938,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1261" t="n">
         <v>239717</v>
@@ -37170,7 +37170,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1269" t="n">
         <v>42041</v>
@@ -37373,7 +37373,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1276" t="n">
         <v>70248</v>
@@ -37634,7 +37634,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408595085144</v>
+        <v>2.32408618927002</v>
       </c>
       <c r="H1285" t="n">
         <v>150077</v>
@@ -37663,7 +37663,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1286" t="n">
         <v>215584</v>
@@ -37692,7 +37692,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1287" t="n">
         <v>225233</v>
@@ -37779,7 +37779,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1290" t="n">
         <v>119725</v>
@@ -37808,7 +37808,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1291" t="n">
         <v>77258</v>
@@ -37837,7 +37837,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.279132604599</v>
+        <v>2.27913284301758</v>
       </c>
       <c r="H1292" t="n">
         <v>82580</v>
@@ -38301,7 +38301,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1308" t="n">
         <v>456363</v>
@@ -38504,7 +38504,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1315" t="n">
         <v>125058</v>
@@ -38707,7 +38707,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1322" t="n">
         <v>502079</v>
@@ -38823,7 +38823,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1326" t="n">
         <v>387648</v>
@@ -38997,7 +38997,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.14223623275757</v>
+        <v>3.14223599433899</v>
       </c>
       <c r="H1332" t="n">
         <v>318860</v>
@@ -39026,7 +39026,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1333" t="n">
         <v>253289</v>
@@ -39055,7 +39055,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1334" t="n">
         <v>268572</v>
@@ -39200,7 +39200,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1339" t="n">
         <v>288534</v>
@@ -39258,7 +39258,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1341" t="n">
         <v>201348</v>
@@ -39287,7 +39287,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1342" t="n">
         <v>144840</v>
@@ -39374,7 +39374,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.38947916030884</v>
+        <v>3.38947939872742</v>
       </c>
       <c r="H1345" t="n">
         <v>658939</v>
@@ -39403,7 +39403,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.51534867286682</v>
+        <v>3.5153489112854</v>
       </c>
       <c r="H1346" t="n">
         <v>761891</v>
@@ -39490,7 +39490,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1349" t="n">
         <v>969567</v>
@@ -39809,7 +39809,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1360" t="n">
         <v>491649</v>
@@ -39896,7 +39896,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1363" t="n">
         <v>209513</v>
@@ -39983,7 +39983,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.15122675895691</v>
+        <v>3.15122699737549</v>
       </c>
       <c r="H1366" t="n">
         <v>382149</v>
@@ -40012,7 +40012,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1367" t="n">
         <v>279630</v>
@@ -40041,7 +40041,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1368" t="n">
         <v>97665</v>
@@ -40244,7 +40244,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406808853149</v>
+        <v>3.30406785011292</v>
       </c>
       <c r="H1375" t="n">
         <v>235034</v>
@@ -40273,7 +40273,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.32654500007629</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H1376" t="n">
         <v>116449</v>
@@ -40331,7 +40331,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1378" t="n">
         <v>431404</v>
@@ -40505,7 +40505,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.58277821540833</v>
+        <v>3.5827784538269</v>
       </c>
       <c r="H1384" t="n">
         <v>1125475</v>
@@ -40563,7 +40563,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.42544174194336</v>
+        <v>3.42544198036194</v>
       </c>
       <c r="H1386" t="n">
         <v>241060</v>
@@ -40592,7 +40592,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.42544174194336</v>
+        <v>3.42544198036194</v>
       </c>
       <c r="H1387" t="n">
         <v>434151</v>
@@ -40621,7 +40621,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1388" t="n">
         <v>540008</v>
@@ -40708,7 +40708,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.35351657867432</v>
+        <v>3.3535168170929</v>
       </c>
       <c r="H1391" t="n">
         <v>370117</v>
@@ -40737,7 +40737,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1392" t="n">
         <v>238167</v>
@@ -40766,7 +40766,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.39397478103638</v>
+        <v>3.3939745426178</v>
       </c>
       <c r="H1393" t="n">
         <v>143579</v>
@@ -40853,7 +40853,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1396" t="n">
         <v>334946</v>
@@ -41085,7 +41085,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1404" t="n">
         <v>316463</v>
@@ -41143,7 +41143,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1406" t="n">
         <v>110251</v>
@@ -41172,7 +41172,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1407" t="n">
         <v>191794</v>
@@ -41288,7 +41288,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1411" t="n">
         <v>178077</v>
@@ -41433,7 +41433,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1416" t="n">
         <v>191622</v>
@@ -41462,7 +41462,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1417" t="n">
         <v>162161</v>
@@ -41665,7 +41665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875008583069</v>
+        <v>3.12875032424927</v>
       </c>
       <c r="H1424" t="n">
         <v>691356</v>
@@ -41781,7 +41781,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673137664795</v>
+        <v>3.14673161506653</v>
       </c>
       <c r="H1428" t="n">
         <v>105063</v>
@@ -41868,7 +41868,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1431" t="n">
         <v>170331</v>
@@ -41926,7 +41926,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1433" t="n">
         <v>93109</v>
@@ -41955,7 +41955,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1434" t="n">
         <v>227674</v>
@@ -42013,7 +42013,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.14223623275757</v>
+        <v>3.14223599433899</v>
       </c>
       <c r="H1436" t="n">
         <v>94110</v>
@@ -42071,7 +42071,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920804977417</v>
+        <v>3.16920828819275</v>
       </c>
       <c r="H1438" t="n">
         <v>343066</v>
@@ -42129,7 +42129,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1440" t="n">
         <v>1135545</v>
@@ -42187,7 +42187,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1442" t="n">
         <v>387928</v>
@@ -42622,7 +42622,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1457" t="n">
         <v>305835</v>
@@ -42680,7 +42680,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1459" t="n">
         <v>136550</v>
@@ -42825,7 +42825,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.3445258140564</v>
+        <v>3.34452605247498</v>
       </c>
       <c r="H1464" t="n">
         <v>707977</v>
@@ -43028,7 +43028,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.4074604511261</v>
+        <v>3.40746068954468</v>
       </c>
       <c r="H1471" t="n">
         <v>889735</v>
@@ -43057,7 +43057,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1472" t="n">
         <v>551128</v>
@@ -43086,7 +43086,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H1473" t="n">
         <v>386644</v>
@@ -43434,7 +43434,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39846992492676</v>
+        <v>3.39847016334534</v>
       </c>
       <c r="H1485" t="n">
         <v>895572</v>
@@ -43463,7 +43463,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.33553528785706</v>
+        <v>3.33553552627563</v>
       </c>
       <c r="H1486" t="n">
         <v>279033</v>
@@ -43840,7 +43840,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.08379673957825</v>
+        <v>3.08379697799683</v>
       </c>
       <c r="H1499" t="n">
         <v>272379</v>
@@ -43869,7 +43869,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1500" t="n">
         <v>282544</v>
@@ -43898,7 +43898,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1501" t="n">
         <v>271139</v>
@@ -44130,7 +44130,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1509" t="n">
         <v>68109</v>
@@ -44159,7 +44159,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1510" t="n">
         <v>454951</v>
@@ -44188,7 +44188,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.11526417732239</v>
+        <v>3.11526393890381</v>
       </c>
       <c r="H1511" t="n">
         <v>105392</v>
@@ -44246,7 +44246,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H1513" t="n">
         <v>64236</v>
@@ -44333,7 +44333,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1516" t="n">
         <v>46706</v>
@@ -44391,7 +44391,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1518" t="n">
         <v>80257</v>
@@ -44449,7 +44449,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1520" t="n">
         <v>272492</v>
@@ -44507,7 +44507,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.10177803039551</v>
+        <v>3.10177826881409</v>
       </c>
       <c r="H1522" t="n">
         <v>117521</v>
@@ -44594,7 +44594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1525" t="n">
         <v>203308</v>
@@ -44623,7 +44623,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1526" t="n">
         <v>73450</v>
@@ -44739,7 +44739,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1530" t="n">
         <v>198774</v>
@@ -44797,7 +44797,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1532" t="n">
         <v>305086</v>
@@ -44826,7 +44826,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.01187133789062</v>
+        <v>3.0118715763092</v>
       </c>
       <c r="H1533" t="n">
         <v>98457</v>
@@ -44884,7 +44884,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.02086186408997</v>
+        <v>3.02086210250854</v>
       </c>
       <c r="H1535" t="n">
         <v>208506</v>
@@ -44942,7 +44942,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728288650513</v>
+        <v>3.09728264808655</v>
       </c>
       <c r="H1537" t="n">
         <v>333813</v>
@@ -45058,7 +45058,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.02535772323608</v>
+        <v>3.0253574848175</v>
       </c>
       <c r="H1541" t="n">
         <v>78472</v>
@@ -45174,7 +45174,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1545" t="n">
         <v>356062</v>
@@ -45290,7 +45290,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H1549" t="n">
         <v>129232</v>
@@ -45319,7 +45319,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1550" t="n">
         <v>95039</v>
@@ -45348,7 +45348,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1551" t="n">
         <v>58369</v>
@@ -45377,7 +45377,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.02535772323608</v>
+        <v>3.0253574848175</v>
       </c>
       <c r="H1552" t="n">
         <v>43531</v>
@@ -45522,7 +45522,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1557" t="n">
         <v>197235</v>
@@ -45638,7 +45638,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.95792770385742</v>
+        <v>2.95792746543884</v>
       </c>
       <c r="H1561" t="n">
         <v>99789</v>
@@ -45870,7 +45870,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1569" t="n">
         <v>254117</v>
@@ -45928,7 +45928,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1571" t="n">
         <v>363249</v>
@@ -45986,7 +45986,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H1573" t="n">
         <v>183733</v>
@@ -46015,7 +46015,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1574" t="n">
         <v>252389</v>
@@ -46102,7 +46102,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1577" t="n">
         <v>267897</v>
@@ -46798,7 +46798,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H1601" t="n">
         <v>81169</v>
@@ -46856,7 +46856,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682492256165</v>
+        <v>3.05682516098022</v>
       </c>
       <c r="H1603" t="n">
         <v>48152</v>
@@ -46885,7 +46885,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737619400024</v>
+        <v>3.00737595558167</v>
       </c>
       <c r="H1604" t="n">
         <v>37041</v>
@@ -47030,7 +47030,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.93994641304016</v>
+        <v>2.93994617462158</v>
       </c>
       <c r="H1609" t="n">
         <v>26440</v>
@@ -47262,7 +47262,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1617" t="n">
         <v>40710</v>
@@ -47320,7 +47320,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1619" t="n">
         <v>90747</v>
@@ -47436,7 +47436,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1623" t="n">
         <v>34309</v>
@@ -47465,7 +47465,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1624" t="n">
         <v>55517</v>
@@ -47523,7 +47523,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1626" t="n">
         <v>42334</v>
@@ -47639,7 +47639,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96242308616638</v>
+        <v>2.9624228477478</v>
       </c>
       <c r="H1630" t="n">
         <v>32369</v>
@@ -47668,7 +47668,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.9354510307312</v>
+        <v>2.93545079231262</v>
       </c>
       <c r="H1631" t="n">
         <v>36859</v>
@@ -47813,7 +47813,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.99389004707336</v>
+        <v>2.99389028549194</v>
       </c>
       <c r="H1636" t="n">
         <v>22683</v>
@@ -47929,7 +47929,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1640" t="n">
         <v>49301</v>
@@ -48016,7 +48016,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1643" t="n">
         <v>56599</v>
@@ -48045,7 +48045,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1644" t="n">
         <v>97311</v>
@@ -48132,7 +48132,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1647" t="n">
         <v>12343</v>
@@ -48161,7 +48161,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1648" t="n">
         <v>9398</v>
@@ -48190,7 +48190,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1649" t="n">
         <v>11528</v>
@@ -48335,7 +48335,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1654" t="n">
         <v>61583</v>
@@ -48422,7 +48422,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1657" t="n">
         <v>67892</v>
@@ -48567,7 +48567,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H1662" t="n">
         <v>16043</v>
@@ -48683,7 +48683,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1666" t="n">
         <v>17974</v>
@@ -48741,7 +48741,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1668" t="n">
         <v>19913</v>
@@ -48770,7 +48770,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1669" t="n">
         <v>22730</v>
@@ -48857,7 +48857,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1672" t="n">
         <v>79322</v>
@@ -48915,7 +48915,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1674" t="n">
         <v>24683</v>
@@ -48944,7 +48944,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1675" t="n">
         <v>21274</v>
@@ -48973,7 +48973,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1676" t="n">
         <v>7623</v>
@@ -49002,7 +49002,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1677" t="n">
         <v>20070</v>
@@ -49060,7 +49060,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1679" t="n">
         <v>31702</v>
@@ -49089,7 +49089,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1680" t="n">
         <v>7884</v>
@@ -49263,7 +49263,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.80059099197388</v>
+        <v>2.8005907535553</v>
       </c>
       <c r="H1686" t="n">
         <v>19617</v>
@@ -49321,7 +49321,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160046577454</v>
+        <v>2.79160022735596</v>
       </c>
       <c r="H1688" t="n">
         <v>42783</v>
@@ -49350,7 +49350,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1689" t="n">
         <v>16051</v>
@@ -49408,7 +49408,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1691" t="n">
         <v>5289</v>
@@ -49553,7 +49553,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1696" t="n">
         <v>6294</v>
@@ -49640,7 +49640,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1699" t="n">
         <v>16843</v>
@@ -49669,7 +49669,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1700" t="n">
         <v>7315</v>
@@ -49698,7 +49698,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1701" t="n">
         <v>5896</v>
@@ -49727,7 +49727,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1702" t="n">
         <v>82780</v>
@@ -50133,7 +50133,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1716" t="n">
         <v>50428</v>
@@ -50191,7 +50191,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1718" t="n">
         <v>6099</v>
@@ -50220,7 +50220,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1719" t="n">
         <v>17415</v>
@@ -50249,7 +50249,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.8095817565918</v>
+        <v>2.80958151817322</v>
       </c>
       <c r="H1720" t="n">
         <v>4689</v>
@@ -50307,7 +50307,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1722" t="n">
         <v>7432</v>
@@ -50481,7 +50481,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1728" t="n">
         <v>183991</v>
@@ -50597,7 +50597,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.77361917495728</v>
+        <v>2.7736189365387</v>
       </c>
       <c r="H1732" t="n">
         <v>9042</v>
@@ -50742,7 +50742,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1737" t="n">
         <v>18546</v>
@@ -50887,7 +50887,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1742" t="n">
         <v>5442</v>
@@ -50916,7 +50916,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1743" t="n">
         <v>33930</v>
@@ -51119,7 +51119,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.76462864875793</v>
+        <v>2.76462841033936</v>
       </c>
       <c r="H1750" t="n">
         <v>39529</v>
@@ -51235,7 +51235,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1754" t="n">
         <v>5581</v>
@@ -51264,7 +51264,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1755" t="n">
         <v>35299</v>
@@ -51293,7 +51293,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1756" t="n">
         <v>5803</v>
@@ -51351,7 +51351,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1758" t="n">
         <v>6307</v>
@@ -51409,7 +51409,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1760" t="n">
         <v>40934</v>
@@ -51525,7 +51525,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1764" t="n">
         <v>12378</v>
@@ -51554,7 +51554,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1765" t="n">
         <v>5013</v>
@@ -51583,7 +51583,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866582870483</v>
+        <v>2.72866559028625</v>
       </c>
       <c r="H1766" t="n">
         <v>806</v>
@@ -51612,7 +51612,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1767" t="n">
         <v>6388</v>
@@ -51670,7 +51670,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517968177795</v>
+        <v>2.71517992019653</v>
       </c>
       <c r="H1769" t="n">
         <v>6051</v>
@@ -51757,7 +51757,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H1772" t="n">
         <v>34016</v>
@@ -51902,7 +51902,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325428009033</v>
+        <v>2.64325451850891</v>
       </c>
       <c r="H1777" t="n">
         <v>6473</v>
@@ -51931,7 +51931,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1778" t="n">
         <v>3334</v>
@@ -51960,7 +51960,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875913619995</v>
+        <v>2.63875889778137</v>
       </c>
       <c r="H1779" t="n">
         <v>10239</v>
@@ -51989,7 +51989,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1780" t="n">
         <v>5480</v>
@@ -52018,7 +52018,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1781" t="n">
         <v>5433</v>
@@ -52076,7 +52076,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1783" t="n">
         <v>21408</v>
@@ -52105,7 +52105,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1784" t="n">
         <v>29962</v>
@@ -52134,7 +52134,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1785" t="n">
         <v>32553</v>
@@ -52366,7 +52366,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.76013278961182</v>
+        <v>2.7601330280304</v>
       </c>
       <c r="H1793" t="n">
         <v>25504</v>
@@ -52453,7 +52453,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1796" t="n">
         <v>9888</v>
@@ -52482,7 +52482,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664711952209</v>
+        <v>2.74664688110352</v>
       </c>
       <c r="H1797" t="n">
         <v>11787</v>
@@ -52540,7 +52540,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.75563788414001</v>
+        <v>2.75563764572144</v>
       </c>
       <c r="H1799" t="n">
         <v>10358</v>
@@ -52685,7 +52685,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967530250549</v>
+        <v>2.71967506408691</v>
       </c>
       <c r="H1804" t="n">
         <v>38789</v>
@@ -52801,7 +52801,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224504470825</v>
+        <v>2.65224528312683</v>
       </c>
       <c r="H1808" t="n">
         <v>57535</v>
@@ -52830,7 +52830,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1809" t="n">
         <v>43213</v>
@@ -52975,7 +52975,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1814" t="n">
         <v>42615</v>
@@ -53004,7 +53004,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1815" t="n">
         <v>45668</v>
@@ -53033,7 +53033,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178708076477</v>
+        <v>2.61178684234619</v>
       </c>
       <c r="H1816" t="n">
         <v>61184</v>
@@ -53062,7 +53062,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H1817" t="n">
         <v>33665</v>
@@ -53120,7 +53120,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674042701721</v>
+        <v>2.65674018859863</v>
       </c>
       <c r="H1819" t="n">
         <v>41062</v>
@@ -53178,7 +53178,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.68371248245239</v>
+        <v>2.68371224403381</v>
       </c>
       <c r="H1821" t="n">
         <v>92970</v>
@@ -53410,7 +53410,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.71068453788757</v>
+        <v>2.71068429946899</v>
       </c>
       <c r="H1829" t="n">
         <v>102497</v>
@@ -53526,7 +53526,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169401168823</v>
+        <v>2.70169377326965</v>
       </c>
       <c r="H1833" t="n">
         <v>141369</v>
@@ -53700,7 +53700,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H1839" t="n">
         <v>33738</v>
@@ -53729,7 +53729,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H1840" t="n">
         <v>52048</v>
@@ -53787,7 +53787,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1842" t="n">
         <v>78570</v>
@@ -53874,7 +53874,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1845" t="n">
         <v>50260</v>
@@ -53903,7 +53903,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.47692704200745</v>
+        <v>2.47692728042603</v>
       </c>
       <c r="H1846" t="n">
         <v>66625</v>
@@ -53961,7 +53961,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399240493774</v>
+        <v>2.41399264335632</v>
       </c>
       <c r="H1848" t="n">
         <v>92588</v>
@@ -54193,7 +54193,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1856" t="n">
         <v>62589</v>
@@ -54251,7 +54251,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142266273499</v>
+        <v>2.48142242431641</v>
       </c>
       <c r="H1858" t="n">
         <v>34367</v>
@@ -54280,7 +54280,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1859" t="n">
         <v>16373</v>
@@ -54309,7 +54309,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.45894598960876</v>
+        <v>2.45894575119019</v>
       </c>
       <c r="H1860" t="n">
         <v>34753</v>
@@ -54367,7 +54367,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.46793627738953</v>
+        <v>2.46793651580811</v>
       </c>
       <c r="H1862" t="n">
         <v>13603</v>
@@ -55063,7 +55063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.28362774848938</v>
+        <v>2.28362798690796</v>
       </c>
       <c r="H1886" t="n">
         <v>49671</v>
@@ -55121,7 +55121,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H1888" t="n">
         <v>42331</v>
@@ -55208,7 +55208,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H1891" t="n">
         <v>27810</v>
@@ -55295,7 +55295,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H1894" t="n">
         <v>68275</v>
@@ -55324,7 +55324,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H1895" t="n">
         <v>232762</v>
@@ -55353,7 +55353,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1896" t="n">
         <v>155188</v>
@@ -55382,7 +55382,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.26115131378174</v>
+        <v>2.26115155220032</v>
       </c>
       <c r="H1897" t="n">
         <v>299620</v>
@@ -55411,7 +55411,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.26564693450928</v>
+        <v>2.2656466960907</v>
       </c>
       <c r="H1898" t="n">
         <v>84602</v>
@@ -55469,7 +55469,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.26564693450928</v>
+        <v>2.2656466960907</v>
       </c>
       <c r="H1900" t="n">
         <v>31948</v>
@@ -55498,7 +55498,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1901" t="n">
         <v>35105</v>
@@ -55527,7 +55527,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417925834656</v>
+        <v>2.23417949676514</v>
       </c>
       <c r="H1902" t="n">
         <v>24904</v>
@@ -55614,7 +55614,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.18922591209412</v>
+        <v>2.1892261505127</v>
       </c>
       <c r="H1905" t="n">
         <v>43527</v>
@@ -55701,7 +55701,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473076820374</v>
+        <v>2.18473052978516</v>
       </c>
       <c r="H1908" t="n">
         <v>23797</v>
@@ -55730,7 +55730,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H1909" t="n">
         <v>32256</v>
@@ -55817,7 +55817,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.15775895118713</v>
+        <v>2.15775871276855</v>
       </c>
       <c r="H1912" t="n">
         <v>60529</v>
@@ -55875,7 +55875,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1914" t="n">
         <v>32974</v>
@@ -55904,7 +55904,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977766036987</v>
+        <v>2.13977742195129</v>
       </c>
       <c r="H1915" t="n">
         <v>39294</v>
@@ -55962,7 +55962,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1917" t="n">
         <v>66793</v>
@@ -55991,7 +55991,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1918" t="n">
         <v>162703</v>
@@ -56020,7 +56020,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1919" t="n">
         <v>31507</v>
@@ -56049,7 +56049,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1920" t="n">
         <v>54591</v>
@@ -56078,7 +56078,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H1921" t="n">
         <v>23738</v>
@@ -56107,7 +56107,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15326309204102</v>
+        <v>2.15326333045959</v>
       </c>
       <c r="H1922" t="n">
         <v>17858</v>
@@ -56194,7 +56194,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280536651611</v>
+        <v>2.11280512809753</v>
       </c>
       <c r="H1925" t="n">
         <v>50158</v>
@@ -56223,7 +56223,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H1926" t="n">
         <v>73983</v>
@@ -56252,7 +56252,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1927" t="n">
         <v>488603</v>
@@ -56281,7 +56281,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H1928" t="n">
         <v>188271</v>
@@ -56339,7 +56339,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.12629127502441</v>
+        <v>2.12629151344299</v>
       </c>
       <c r="H1930" t="n">
         <v>119506</v>
@@ -56368,7 +56368,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.10830998420715</v>
+        <v>2.10831022262573</v>
       </c>
       <c r="H1931" t="n">
         <v>87426</v>
@@ -56629,7 +56629,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143147468567</v>
+        <v>1.99143135547638</v>
       </c>
       <c r="H1940" t="n">
         <v>43318</v>
@@ -56658,7 +56658,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1941" t="n">
         <v>91732</v>
@@ -56687,7 +56687,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1942" t="n">
         <v>38211</v>
@@ -56774,7 +56774,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501092910767</v>
+        <v>1.91501080989838</v>
       </c>
       <c r="H1945" t="n">
         <v>34096</v>
@@ -56832,7 +56832,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1947" t="n">
         <v>69631</v>
@@ -56890,7 +56890,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H1949" t="n">
         <v>42050</v>
@@ -57035,7 +57035,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.98693597316742</v>
+        <v>1.98693609237671</v>
       </c>
       <c r="H1954" t="n">
         <v>36120</v>
@@ -57064,7 +57064,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1955" t="n">
         <v>23899</v>
@@ -57093,7 +57093,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.97345018386841</v>
+        <v>1.97345006465912</v>
       </c>
       <c r="H1956" t="n">
         <v>33630</v>
@@ -57122,7 +57122,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299233913422</v>
+        <v>1.93299221992493</v>
       </c>
       <c r="H1957" t="n">
         <v>28970</v>
@@ -57238,7 +57238,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996415615082</v>
+        <v>1.95996427536011</v>
       </c>
       <c r="H1961" t="n">
         <v>18238</v>
@@ -57354,7 +57354,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1965" t="n">
         <v>34147</v>
@@ -57383,7 +57383,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1966" t="n">
         <v>38443</v>
@@ -57412,7 +57412,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702939987183</v>
+        <v>1.89702951908112</v>
       </c>
       <c r="H1967" t="n">
         <v>37018</v>
@@ -57441,7 +57441,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602004528046</v>
+        <v>1.90602016448975</v>
       </c>
       <c r="H1968" t="n">
         <v>36266</v>
@@ -57499,7 +57499,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.85207617282867</v>
+        <v>1.85207629203796</v>
       </c>
       <c r="H1970" t="n">
         <v>26752</v>
@@ -57557,7 +57557,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262768268585</v>
+        <v>1.80262780189514</v>
       </c>
       <c r="H1972" t="n">
         <v>64312</v>
@@ -57673,7 +57673,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923496246338</v>
+        <v>1.69923508167267</v>
       </c>
       <c r="H1976" t="n">
         <v>117309</v>
@@ -57702,7 +57702,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.68125355243683</v>
+        <v>1.68125367164612</v>
       </c>
       <c r="H1977" t="n">
         <v>85454</v>
@@ -57847,7 +57847,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879396915436</v>
+        <v>1.73879384994507</v>
       </c>
       <c r="H1982" t="n">
         <v>22757</v>
@@ -57876,7 +57876,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.71361994743347</v>
+        <v>1.71362006664276</v>
       </c>
       <c r="H1983" t="n">
         <v>21437</v>
@@ -57934,7 +57934,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.69563889503479</v>
+        <v>1.6956387758255</v>
       </c>
       <c r="H1985" t="n">
         <v>50617</v>
@@ -57963,7 +57963,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.7351975440979</v>
+        <v>1.73519766330719</v>
       </c>
       <c r="H1986" t="n">
         <v>29283</v>
@@ -58079,7 +58079,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406117916107</v>
+        <v>1.67406105995178</v>
       </c>
       <c r="H1990" t="n">
         <v>102289</v>
@@ -58108,7 +58108,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1991" t="n">
         <v>48919</v>
@@ -58137,7 +58137,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.62910783290863</v>
+        <v>1.62910795211792</v>
       </c>
       <c r="H1992" t="n">
         <v>49727</v>
@@ -58311,7 +58311,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794544696808</v>
+        <v>1.97794532775879</v>
       </c>
       <c r="H1998" t="n">
         <v>498538</v>
@@ -58369,7 +58369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198286533356</v>
+        <v>1.94198298454285</v>
       </c>
       <c r="H2000" t="n">
         <v>116001</v>
@@ -58398,7 +58398,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546877384186</v>
+        <v>1.95546865463257</v>
       </c>
       <c r="H2001" t="n">
         <v>126955</v>
@@ -58514,7 +58514,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.11730074882507</v>
+        <v>2.11730098724365</v>
       </c>
       <c r="H2005" t="n">
         <v>360092</v>
@@ -58601,7 +58601,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124462127686</v>
+        <v>2.17124485969543</v>
       </c>
       <c r="H2008" t="n">
         <v>108999</v>
@@ -58717,7 +58717,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.14427256584167</v>
+        <v>2.14427280426025</v>
       </c>
       <c r="H2012" t="n">
         <v>86443</v>
@@ -58833,7 +58833,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.20271229743958</v>
+        <v>2.202712059021</v>
       </c>
       <c r="H2016" t="n">
         <v>120482</v>
@@ -58862,7 +58862,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2017" t="n">
-        <v>2.21619772911072</v>
+        <v>2.2161979675293</v>
       </c>
       <c r="H2017" t="n">
         <v>110558</v>
@@ -58891,7 +58891,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2018" t="n">
         <v>141366</v>
@@ -58920,7 +58920,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.22069358825684</v>
+        <v>2.22069334983826</v>
       </c>
       <c r="H2019" t="n">
         <v>87674</v>
@@ -58949,7 +58949,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.22968411445618</v>
+        <v>2.2296838760376</v>
       </c>
       <c r="H2020" t="n">
         <v>31700</v>
@@ -59036,7 +59036,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2023" t="n">
         <v>74875</v>
@@ -59123,7 +59123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2026" t="n">
         <v>69262</v>
@@ -59181,7 +59181,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.30160903930664</v>
+        <v>2.30160927772522</v>
       </c>
       <c r="H2028" t="n">
         <v>97929</v>
@@ -59210,7 +59210,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463746070862</v>
+        <v>2.27463722229004</v>
       </c>
       <c r="H2029" t="n">
         <v>51922</v>
@@ -59355,7 +59355,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.34656238555908</v>
+        <v>2.34656262397766</v>
       </c>
       <c r="H2034" t="n">
         <v>73184</v>
@@ -59558,7 +59558,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2041" t="n">
         <v>283736</v>
@@ -59587,7 +59587,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.61628270149231</v>
+        <v>2.61628246307373</v>
       </c>
       <c r="H2042" t="n">
         <v>217481</v>
@@ -59703,7 +59703,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.52637600898743</v>
+        <v>2.52637577056885</v>
       </c>
       <c r="H2046" t="n">
         <v>237419</v>
@@ -59848,7 +59848,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.52188038825989</v>
+        <v>2.52188062667847</v>
       </c>
       <c r="H2051" t="n">
         <v>243372</v>
@@ -59906,7 +59906,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986167907715</v>
+        <v>2.53986191749573</v>
       </c>
       <c r="H2053" t="n">
         <v>97873</v>
@@ -59993,7 +59993,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2056" t="n">
         <v>80880</v>
@@ -60283,7 +60283,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.67022633552551</v>
+        <v>2.67022657394409</v>
       </c>
       <c r="H2066" t="n">
         <v>341329</v>
@@ -60457,7 +60457,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132911682129</v>
+        <v>2.57132887840271</v>
       </c>
       <c r="H2072" t="n">
         <v>36049</v>
@@ -60689,7 +60689,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.98040437698364</v>
+        <v>2.98040413856506</v>
       </c>
       <c r="H2080" t="n">
         <v>774198</v>
@@ -60950,7 +60950,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="n">
-        <v>3.03884339332581</v>
+        <v>3.03884363174438</v>
       </c>
       <c r="H2089" t="n">
         <v>358716</v>
@@ -60979,7 +60979,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031083106995</v>
+        <v>3.07031059265137</v>
       </c>
       <c r="H2090" t="n">
         <v>607275</v>
@@ -61124,7 +61124,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241379737854</v>
+        <v>3.45241403579712</v>
       </c>
       <c r="H2095" t="n">
         <v>913593</v>
@@ -61211,7 +61211,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2098" t="n">
-        <v>3.465900182724</v>
+        <v>3.46589994430542</v>
       </c>
       <c r="H2098" t="n">
         <v>292062</v>
@@ -61269,7 +61269,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2100" t="n">
-        <v>3.465900182724</v>
+        <v>3.46589994430542</v>
       </c>
       <c r="H2100" t="n">
         <v>226182</v>
@@ -61414,7 +61414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.32654500007629</v>
+        <v>3.32654476165771</v>
       </c>
       <c r="H2105" t="n">
         <v>1383823</v>
@@ -61501,7 +61501,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="n">
-        <v>3.34902143478394</v>
+        <v>3.34902119636536</v>
       </c>
       <c r="H2108" t="n">
         <v>322890</v>
@@ -61530,7 +61530,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2109" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H2109" t="n">
         <v>150313</v>
@@ -61675,7 +61675,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.36250710487366</v>
+        <v>3.36250734329224</v>
       </c>
       <c r="H2114" t="n">
         <v>208158</v>
@@ -80067,6 +80067,35 @@
         <v>25918</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>7.15999984741211</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>31826</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349234104156</v>
+        <v>1.89349257946014</v>
       </c>
       <c r="H2" t="n">
         <v>142675</v>
@@ -514,7 +514,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H5" t="n">
         <v>122356</v>
@@ -543,7 +543,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612647533417</v>
+        <v>1.80612635612488</v>
       </c>
       <c r="H6" t="n">
         <v>149442</v>
@@ -659,7 +659,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64231491088867</v>
+        <v>1.64231479167938</v>
       </c>
       <c r="H10" t="n">
         <v>209029</v>
@@ -746,7 +746,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43314003944397</v>
+        <v>1.43314015865326</v>
       </c>
       <c r="H13" t="n">
         <v>146017</v>
@@ -775,7 +775,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H14" t="n">
         <v>179103</v>
@@ -833,7 +833,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>1.50370514392853</v>
+        <v>1.50370502471924</v>
       </c>
       <c r="H16" t="n">
         <v>387378</v>
@@ -862,7 +862,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44322085380554</v>
+        <v>1.44322097301483</v>
       </c>
       <c r="H17" t="n">
         <v>299127</v>
@@ -949,7 +949,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H20" t="n">
         <v>164363</v>
@@ -1007,7 +1007,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4852237701416</v>
+        <v>1.48522388935089</v>
       </c>
       <c r="H22" t="n">
         <v>52912</v>
@@ -1036,7 +1036,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G23" t="n">
-        <v>1.45246160030365</v>
+        <v>1.45246136188507</v>
       </c>
       <c r="H23" t="n">
         <v>58814</v>
@@ -1065,7 +1065,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H24" t="n">
         <v>64863</v>
@@ -1094,7 +1094,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H25" t="n">
         <v>50052</v>
@@ -1181,7 +1181,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>1.13995957374573</v>
+        <v>1.13995969295502</v>
       </c>
       <c r="H28" t="n">
         <v>177163</v>
@@ -1210,7 +1210,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G29" t="n">
-        <v>1.20296406745911</v>
+        <v>1.2029641866684</v>
       </c>
       <c r="H29" t="n">
         <v>181158</v>
@@ -1239,7 +1239,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G30" t="n">
-        <v>1.1693617105484</v>
+        <v>1.16936159133911</v>
       </c>
       <c r="H30" t="n">
         <v>95012</v>
@@ -1326,7 +1326,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35333454608917</v>
+        <v>1.35333466529846</v>
       </c>
       <c r="H33" t="n">
         <v>210586</v>
@@ -1355,7 +1355,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H34" t="n">
         <v>136172</v>
@@ -1413,7 +1413,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.41969931125641</v>
+        <v>1.4196994304657</v>
       </c>
       <c r="H36" t="n">
         <v>50293</v>
@@ -1442,7 +1442,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346293926239</v>
+        <v>1.47346305847168</v>
       </c>
       <c r="H37" t="n">
         <v>122783</v>
@@ -1471,7 +1471,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926248073578</v>
       </c>
       <c r="H38" t="n">
         <v>41622</v>
@@ -1500,7 +1500,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G39" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742107391357</v>
       </c>
       <c r="H39" t="n">
         <v>101588</v>
@@ -1529,7 +1529,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G40" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742107391357</v>
       </c>
       <c r="H40" t="n">
         <v>57255</v>
@@ -1587,7 +1587,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42893993854523</v>
+        <v>1.42893981933594</v>
       </c>
       <c r="H42" t="n">
         <v>25450</v>
@@ -1616,7 +1616,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254241466522</v>
       </c>
       <c r="H43" t="n">
         <v>49994</v>
@@ -1819,7 +1819,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H50" t="n">
         <v>34548</v>
@@ -1848,7 +1848,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G51" t="n">
-        <v>1.46506226062775</v>
+        <v>1.46506237983704</v>
       </c>
       <c r="H51" t="n">
         <v>36075</v>
@@ -1877,7 +1877,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G52" t="n">
-        <v>1.50286507606506</v>
+        <v>1.50286519527435</v>
       </c>
       <c r="H52" t="n">
         <v>58786</v>
@@ -1906,7 +1906,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586945056915</v>
+        <v>1.56586933135986</v>
       </c>
       <c r="H53" t="n">
         <v>235408</v>
@@ -2080,7 +2080,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G59" t="n">
-        <v>1.55578875541687</v>
+        <v>1.55578863620758</v>
       </c>
       <c r="H59" t="n">
         <v>177054</v>
@@ -2109,7 +2109,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H60" t="n">
         <v>70797</v>
@@ -2138,7 +2138,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H61" t="n">
         <v>52361</v>
@@ -2167,7 +2167,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926248073578</v>
       </c>
       <c r="H62" t="n">
         <v>74998</v>
@@ -2225,7 +2225,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994127750397</v>
+        <v>1.44994115829468</v>
       </c>
       <c r="H64" t="n">
         <v>18558</v>
@@ -2254,7 +2254,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G65" t="n">
-        <v>1.43482029438019</v>
+        <v>1.4348201751709</v>
       </c>
       <c r="H65" t="n">
         <v>95844</v>
@@ -2341,7 +2341,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30965161323547</v>
+        <v>1.30965149402618</v>
       </c>
       <c r="H68" t="n">
         <v>60442</v>
@@ -2370,7 +2370,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H69" t="n">
         <v>97298</v>
@@ -2428,7 +2428,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742107391357</v>
       </c>
       <c r="H71" t="n">
         <v>100585</v>
@@ -2515,7 +2515,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847034931183</v>
+        <v>1.57847023010254</v>
       </c>
       <c r="H74" t="n">
         <v>128291</v>
@@ -2573,7 +2573,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830895900726</v>
+        <v>1.55830883979797</v>
       </c>
       <c r="H76" t="n">
         <v>60173</v>
@@ -2776,7 +2776,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G83" t="n">
-        <v>1.55074822902679</v>
+        <v>1.55074834823608</v>
       </c>
       <c r="H83" t="n">
         <v>74710</v>
@@ -2834,7 +2834,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>1.50370514392853</v>
+        <v>1.50370502471924</v>
       </c>
       <c r="H85" t="n">
         <v>62878</v>
@@ -2863,7 +2863,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H86" t="n">
         <v>72814</v>
@@ -2892,7 +2892,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H87" t="n">
         <v>10859</v>
@@ -2950,7 +2950,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G89" t="n">
-        <v>1.41213858127594</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H89" t="n">
         <v>42036</v>
@@ -3037,7 +3037,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809975147247</v>
       </c>
       <c r="H92" t="n">
         <v>40091</v>
@@ -3211,7 +3211,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H98" t="n">
         <v>24454</v>
@@ -3269,7 +3269,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.4827036857605</v>
+        <v>1.48270356655121</v>
       </c>
       <c r="H100" t="n">
         <v>26242</v>
@@ -3327,7 +3327,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G102" t="n">
-        <v>1.52050626277924</v>
+        <v>1.52050614356995</v>
       </c>
       <c r="H102" t="n">
         <v>40357</v>
@@ -3530,7 +3530,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H109" t="n">
         <v>38996</v>
@@ -3617,7 +3617,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>1.51210570335388</v>
+        <v>1.51210558414459</v>
       </c>
       <c r="H112" t="n">
         <v>28155</v>
@@ -3646,7 +3646,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G113" t="n">
-        <v>1.49614453315735</v>
+        <v>1.49614465236664</v>
       </c>
       <c r="H113" t="n">
         <v>17040</v>
@@ -3675,7 +3675,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G114" t="n">
-        <v>1.44322085380554</v>
+        <v>1.44322097301483</v>
       </c>
       <c r="H114" t="n">
         <v>56900</v>
@@ -3704,7 +3704,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457832813263</v>
+        <v>1.40457820892334</v>
       </c>
       <c r="H115" t="n">
         <v>72247</v>
@@ -3733,7 +3733,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G116" t="n">
-        <v>1.34577393531799</v>
+        <v>1.34577417373657</v>
       </c>
       <c r="H116" t="n">
         <v>70118</v>
@@ -3762,7 +3762,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G117" t="n">
-        <v>1.35669481754303</v>
+        <v>1.35669493675232</v>
       </c>
       <c r="H117" t="n">
         <v>31255</v>
@@ -3820,7 +3820,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G119" t="n">
-        <v>1.40205812454224</v>
+        <v>1.40205800533295</v>
       </c>
       <c r="H119" t="n">
         <v>39107</v>
@@ -3849,7 +3849,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G120" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809975147247</v>
       </c>
       <c r="H120" t="n">
         <v>68309</v>
@@ -3878,7 +3878,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G121" t="n">
-        <v>1.45246160030365</v>
+        <v>1.45246136188507</v>
       </c>
       <c r="H121" t="n">
         <v>39896</v>
@@ -3965,7 +3965,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28192961215973</v>
+        <v>1.28192973136902</v>
       </c>
       <c r="H124" t="n">
         <v>145528</v>
@@ -4110,7 +4110,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H129" t="n">
         <v>34201</v>
@@ -4139,7 +4139,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G130" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H130" t="n">
         <v>59203</v>
@@ -4168,7 +4168,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537045955658</v>
+        <v>1.29537057876587</v>
       </c>
       <c r="H131" t="n">
         <v>29496</v>
@@ -4371,7 +4371,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G138" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H138" t="n">
         <v>37733</v>
@@ -4458,7 +4458,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H141" t="n">
         <v>14979</v>
@@ -4516,7 +4516,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G143" t="n">
-        <v>1.36089527606964</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H143" t="n">
         <v>14444</v>
@@ -4574,7 +4574,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>1.36005520820618</v>
+        <v>1.3600549697876</v>
       </c>
       <c r="H145" t="n">
         <v>15215</v>
@@ -4603,7 +4603,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34997451305389</v>
+        <v>1.34997427463531</v>
       </c>
       <c r="H146" t="n">
         <v>25885</v>
@@ -4632,7 +4632,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769627571106</v>
+        <v>1.37769639492035</v>
       </c>
       <c r="H147" t="n">
         <v>103585</v>
@@ -4661,7 +4661,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.36089527606964</v>
+        <v>1.36089503765106</v>
       </c>
       <c r="H148" t="n">
         <v>48909</v>
@@ -4748,7 +4748,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569359779358</v>
       </c>
       <c r="H151" t="n">
         <v>35803</v>
@@ -4777,7 +4777,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H152" t="n">
         <v>12097</v>
@@ -4893,7 +4893,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.31385183334351</v>
+        <v>1.3138519525528</v>
       </c>
       <c r="H156" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H157" t="n">
         <v>6004</v>
@@ -4951,7 +4951,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H158" t="n">
         <v>35138</v>
@@ -4980,7 +4980,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125117301941</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H159" t="n">
         <v>15586</v>
@@ -5009,7 +5009,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28948998451233</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H160" t="n">
         <v>3220</v>
@@ -5038,7 +5038,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H161" t="n">
         <v>8206</v>
@@ -5125,7 +5125,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680850982666</v>
+        <v>1.26680862903595</v>
       </c>
       <c r="H164" t="n">
         <v>13879</v>
@@ -5154,7 +5154,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545127391815</v>
+        <v>1.30545139312744</v>
       </c>
       <c r="H165" t="n">
         <v>18762</v>
@@ -5183,7 +5183,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30293118953705</v>
+        <v>1.30293107032776</v>
       </c>
       <c r="H166" t="n">
         <v>20085</v>
@@ -5212,7 +5212,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29201018810272</v>
+        <v>1.29201030731201</v>
       </c>
       <c r="H167" t="n">
         <v>8138</v>
@@ -5241,7 +5241,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G168" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H168" t="n">
         <v>9419</v>
@@ -5270,7 +5270,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H169" t="n">
         <v>8043</v>
@@ -5299,7 +5299,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H170" t="n">
         <v>9592</v>
@@ -5328,7 +5328,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.32813286781311</v>
+        <v>1.3281329870224</v>
       </c>
       <c r="H171" t="n">
         <v>34956</v>
@@ -5357,7 +5357,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301176548004</v>
+        <v>1.31301188468933</v>
       </c>
       <c r="H172" t="n">
         <v>47662</v>
@@ -5386,7 +5386,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713152885437</v>
+        <v>1.30713129043579</v>
       </c>
       <c r="H173" t="n">
         <v>6108</v>
@@ -5444,7 +5444,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30629146099091</v>
+        <v>1.30629134178162</v>
       </c>
       <c r="H175" t="n">
         <v>84071</v>
@@ -5473,7 +5473,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G176" t="n">
-        <v>1.30629146099091</v>
+        <v>1.30629134178162</v>
       </c>
       <c r="H176" t="n">
         <v>23238</v>
@@ -5560,7 +5560,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569359779358</v>
       </c>
       <c r="H179" t="n">
         <v>49524</v>
@@ -5589,7 +5589,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G180" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H180" t="n">
         <v>25966</v>
@@ -5821,7 +5821,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417473316193</v>
+        <v>1.35417461395264</v>
       </c>
       <c r="H188" t="n">
         <v>58082</v>
@@ -5850,7 +5850,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G189" t="n">
-        <v>1.33905363082886</v>
+        <v>1.33905351161957</v>
       </c>
       <c r="H189" t="n">
         <v>17138</v>
@@ -5879,7 +5879,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149313926697</v>
+        <v>1.33149302005768</v>
       </c>
       <c r="H190" t="n">
         <v>47211</v>
@@ -5966,7 +5966,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.37685632705688</v>
+        <v>1.3768562078476</v>
       </c>
       <c r="H193" t="n">
         <v>34278</v>
@@ -5995,7 +5995,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G194" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H194" t="n">
         <v>9694</v>
@@ -6024,7 +6024,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G195" t="n">
-        <v>1.35165452957153</v>
+        <v>1.35165441036224</v>
       </c>
       <c r="H195" t="n">
         <v>42844</v>
@@ -6053,7 +6053,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525676727295</v>
+        <v>1.38525688648224</v>
       </c>
       <c r="H196" t="n">
         <v>26702</v>
@@ -6111,7 +6111,7 @@
         <v>1.625</v>
       </c>
       <c r="G198" t="n">
-        <v>1.36509549617767</v>
+        <v>1.36509537696838</v>
       </c>
       <c r="H198" t="n">
         <v>76726</v>
@@ -6169,7 +6169,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G200" t="n">
-        <v>1.38105666637421</v>
+        <v>1.38105654716492</v>
       </c>
       <c r="H200" t="n">
         <v>116025</v>
@@ -6198,7 +6198,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569359779358</v>
       </c>
       <c r="H201" t="n">
         <v>114562</v>
@@ -6285,7 +6285,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G204" t="n">
-        <v>1.30461120605469</v>
+        <v>1.3046110868454</v>
       </c>
       <c r="H204" t="n">
         <v>24915</v>
@@ -6314,7 +6314,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31721210479736</v>
+        <v>1.31721198558807</v>
       </c>
       <c r="H205" t="n">
         <v>18321</v>
@@ -6343,7 +6343,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G206" t="n">
-        <v>1.32141220569611</v>
+        <v>1.3214123249054</v>
       </c>
       <c r="H206" t="n">
         <v>16873</v>
@@ -6401,7 +6401,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217181682587</v>
+        <v>1.31217169761658</v>
       </c>
       <c r="H208" t="n">
         <v>31170</v>
@@ -6430,7 +6430,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125117301941</v>
+        <v>1.30125105381012</v>
       </c>
       <c r="H209" t="n">
         <v>107376</v>
@@ -6459,7 +6459,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G210" t="n">
-        <v>1.28865003585815</v>
+        <v>1.28865015506744</v>
       </c>
       <c r="H210" t="n">
         <v>21941</v>
@@ -6488,7 +6488,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G211" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H211" t="n">
         <v>25428</v>
@@ -6517,7 +6517,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H212" t="n">
         <v>16453</v>
@@ -6546,7 +6546,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28948998451233</v>
+        <v>1.28949010372162</v>
       </c>
       <c r="H213" t="n">
         <v>13131</v>
@@ -6575,7 +6575,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27940940856934</v>
+        <v>1.27940952777863</v>
       </c>
       <c r="H214" t="n">
         <v>23612</v>
@@ -6778,7 +6778,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G221" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H221" t="n">
         <v>120506</v>
@@ -6836,7 +6836,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G223" t="n">
-        <v>1.20968472957611</v>
+        <v>1.20968461036682</v>
       </c>
       <c r="H223" t="n">
         <v>40673</v>
@@ -6865,7 +6865,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H224" t="n">
         <v>38946</v>
@@ -6894,7 +6894,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H225" t="n">
         <v>27800</v>
@@ -6923,7 +6923,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G226" t="n">
-        <v>1.14836037158966</v>
+        <v>1.14836025238037</v>
       </c>
       <c r="H226" t="n">
         <v>42201</v>
@@ -7010,7 +7010,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G229" t="n">
-        <v>1.09543669223785</v>
+        <v>1.09543657302856</v>
       </c>
       <c r="H229" t="n">
         <v>28645</v>
@@ -7126,7 +7126,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G233" t="n">
-        <v>1.07947528362274</v>
+        <v>1.07947552204132</v>
       </c>
       <c r="H233" t="n">
         <v>22285</v>
@@ -7155,7 +7155,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G234" t="n">
-        <v>1.08115541934967</v>
+        <v>1.08115553855896</v>
       </c>
       <c r="H234" t="n">
         <v>38205</v>
@@ -7184,7 +7184,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.0803154706955</v>
+        <v>1.08031535148621</v>
       </c>
       <c r="H235" t="n">
         <v>47088</v>
@@ -7213,7 +7213,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G236" t="n">
-        <v>1.06351447105408</v>
+        <v>1.06351435184479</v>
       </c>
       <c r="H236" t="n">
         <v>37238</v>
@@ -7329,7 +7329,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939482688904</v>
+        <v>1.06939470767975</v>
       </c>
       <c r="H240" t="n">
         <v>41501</v>
@@ -7358,7 +7358,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G241" t="n">
-        <v>1.11811816692352</v>
+        <v>1.11811804771423</v>
       </c>
       <c r="H241" t="n">
         <v>72092</v>
@@ -7416,7 +7416,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H243" t="n">
         <v>24746</v>
@@ -7445,7 +7445,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.1256787776947</v>
+        <v>1.12567865848541</v>
       </c>
       <c r="H244" t="n">
         <v>42995</v>
@@ -7474,7 +7474,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G245" t="n">
-        <v>1.14163970947266</v>
+        <v>1.14163982868195</v>
       </c>
       <c r="H245" t="n">
         <v>77628</v>
@@ -7503,7 +7503,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584016799927</v>
+        <v>1.14584004878998</v>
       </c>
       <c r="H246" t="n">
         <v>30733</v>
@@ -7561,7 +7561,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G248" t="n">
-        <v>1.19624352455139</v>
+        <v>1.19624364376068</v>
       </c>
       <c r="H248" t="n">
         <v>64262</v>
@@ -7619,7 +7619,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G250" t="n">
-        <v>1.19624352455139</v>
+        <v>1.19624364376068</v>
       </c>
       <c r="H250" t="n">
         <v>149793</v>
@@ -7648,7 +7648,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18028259277344</v>
+        <v>1.18028247356415</v>
       </c>
       <c r="H251" t="n">
         <v>48253</v>
@@ -7735,7 +7735,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H254" t="n">
         <v>38587</v>
@@ -7764,7 +7764,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G255" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H255" t="n">
         <v>58672</v>
@@ -7793,7 +7793,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H256" t="n">
         <v>13371</v>
@@ -7851,7 +7851,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G258" t="n">
-        <v>1.19792366027832</v>
+        <v>1.1979238986969</v>
       </c>
       <c r="H258" t="n">
         <v>50093</v>
@@ -7880,7 +7880,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952322006226</v>
+        <v>1.18952310085297</v>
       </c>
       <c r="H259" t="n">
         <v>167866</v>
@@ -7909,7 +7909,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900581359863</v>
       </c>
       <c r="H260" t="n">
         <v>166425</v>
@@ -7967,7 +7967,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501480102539</v>
+        <v>1.35501492023468</v>
       </c>
       <c r="H262" t="n">
         <v>277449</v>
@@ -7996,7 +7996,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3432537317276</v>
+        <v>1.34325397014618</v>
       </c>
       <c r="H263" t="n">
         <v>158414</v>
@@ -8025,7 +8025,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G264" t="n">
-        <v>1.31469190120697</v>
+        <v>1.31469202041626</v>
       </c>
       <c r="H264" t="n">
         <v>94734</v>
@@ -8112,7 +8112,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>1.29117012023926</v>
+        <v>1.29117023944855</v>
       </c>
       <c r="H267" t="n">
         <v>22423</v>
@@ -8141,7 +8141,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G268" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H268" t="n">
         <v>271352</v>
@@ -8199,7 +8199,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832725524902</v>
+        <v>1.24832713603973</v>
       </c>
       <c r="H270" t="n">
         <v>55365</v>
@@ -8228,7 +8228,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H271" t="n">
         <v>103512</v>
@@ -8315,7 +8315,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H274" t="n">
         <v>53621</v>
@@ -8344,7 +8344,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548439025879</v>
       </c>
       <c r="H275" t="n">
         <v>109224</v>
@@ -8431,7 +8431,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H278" t="n">
         <v>152723</v>
@@ -8518,7 +8518,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>1.18028259277344</v>
+        <v>1.18028247356415</v>
       </c>
       <c r="H281" t="n">
         <v>29155</v>
@@ -8547,7 +8547,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G282" t="n">
-        <v>1.19792366027832</v>
+        <v>1.1979238986969</v>
       </c>
       <c r="H282" t="n">
         <v>19778</v>
@@ -8576,7 +8576,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H283" t="n">
         <v>60336</v>
@@ -8634,7 +8634,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H285" t="n">
         <v>42766</v>
@@ -8663,7 +8663,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17104184627533</v>
+        <v>1.17104196548462</v>
       </c>
       <c r="H286" t="n">
         <v>21577</v>
@@ -8692,7 +8692,7 @@
         <v>1.38900005817413</v>
       </c>
       <c r="G287" t="n">
-        <v>1.1668416261673</v>
+        <v>1.16684150695801</v>
       </c>
       <c r="H287" t="n">
         <v>29558</v>
@@ -8721,7 +8721,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.18028259277344</v>
+        <v>1.18028247356415</v>
       </c>
       <c r="H288" t="n">
         <v>17766</v>
@@ -8779,7 +8779,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G290" t="n">
-        <v>1.1693617105484</v>
+        <v>1.16936159133911</v>
       </c>
       <c r="H290" t="n">
         <v>53137</v>
@@ -8808,7 +8808,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G291" t="n">
-        <v>1.17860245704651</v>
+        <v>1.17860233783722</v>
       </c>
       <c r="H291" t="n">
         <v>29246</v>
@@ -8866,7 +8866,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H293" t="n">
         <v>25900</v>
@@ -8895,7 +8895,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G294" t="n">
-        <v>1.1643214225769</v>
+        <v>1.16432130336761</v>
       </c>
       <c r="H294" t="n">
         <v>36944</v>
@@ -8953,7 +8953,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524206638336</v>
+        <v>1.17524230480194</v>
       </c>
       <c r="H296" t="n">
         <v>39885</v>
@@ -9040,7 +9040,7 @@
         <v>1.375</v>
       </c>
       <c r="G299" t="n">
-        <v>1.1550806760788</v>
+        <v>1.15508079528809</v>
       </c>
       <c r="H299" t="n">
         <v>27476</v>
@@ -9069,7 +9069,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G300" t="n">
-        <v>1.19540345668793</v>
+        <v>1.19540357589722</v>
       </c>
       <c r="H300" t="n">
         <v>61794</v>
@@ -9098,7 +9098,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900581359863</v>
       </c>
       <c r="H301" t="n">
         <v>112526</v>
@@ -9214,7 +9214,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900593280792</v>
+        <v>1.22900581359863</v>
       </c>
       <c r="H305" t="n">
         <v>29402</v>
@@ -9272,7 +9272,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.2054842710495</v>
+        <v>1.20548439025879</v>
       </c>
       <c r="H307" t="n">
         <v>124489</v>
@@ -9301,7 +9301,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G308" t="n">
-        <v>1.19288325309753</v>
+        <v>1.19288337230682</v>
       </c>
       <c r="H308" t="n">
         <v>29585</v>
@@ -9330,7 +9330,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20380413532257</v>
+        <v>1.20380425453186</v>
       </c>
       <c r="H309" t="n">
         <v>25149</v>
@@ -9417,7 +9417,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H312" t="n">
         <v>169466</v>
@@ -9475,7 +9475,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19540345668793</v>
+        <v>1.19540357589722</v>
       </c>
       <c r="H314" t="n">
         <v>51473</v>
@@ -9504,7 +9504,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036328792572</v>
+        <v>1.19036340713501</v>
       </c>
       <c r="H315" t="n">
         <v>26439</v>
@@ -9533,7 +9533,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G316" t="n">
-        <v>1.17860245704651</v>
+        <v>1.17860233783722</v>
       </c>
       <c r="H316" t="n">
         <v>36707</v>
@@ -9591,7 +9591,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H318" t="n">
         <v>363589</v>
@@ -9620,7 +9620,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884454250336</v>
+        <v>1.20884442329407</v>
       </c>
       <c r="H319" t="n">
         <v>228508</v>
@@ -9707,7 +9707,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.21052479743958</v>
+        <v>1.210524559021</v>
       </c>
       <c r="H322" t="n">
         <v>15835</v>
@@ -9765,7 +9765,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252771377563</v>
+        <v>1.25252747535706</v>
       </c>
       <c r="H324" t="n">
         <v>69914</v>
@@ -9881,7 +9881,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.2659684419632</v>
+        <v>1.26596856117249</v>
       </c>
       <c r="H328" t="n">
         <v>28100</v>
@@ -9939,7 +9939,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320627212524</v>
+        <v>1.23320615291595</v>
       </c>
       <c r="H330" t="n">
         <v>59512</v>
@@ -9968,7 +9968,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808516979218</v>
+        <v>1.21808505058289</v>
       </c>
       <c r="H331" t="n">
         <v>30919</v>
@@ -10084,7 +10084,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.20968472957611</v>
+        <v>1.20968461036682</v>
       </c>
       <c r="H335" t="n">
         <v>28289</v>
@@ -10113,7 +10113,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.21724510192871</v>
+        <v>1.217245221138</v>
       </c>
       <c r="H336" t="n">
         <v>36491</v>
@@ -10142,7 +10142,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G337" t="n">
-        <v>1.22564554214478</v>
+        <v>1.22564566135406</v>
       </c>
       <c r="H337" t="n">
         <v>21126</v>
@@ -10171,7 +10171,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.2441269159317</v>
+        <v>1.24412703514099</v>
       </c>
       <c r="H338" t="n">
         <v>121442</v>
@@ -10229,7 +10229,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.22480547428131</v>
+        <v>1.22480571269989</v>
       </c>
       <c r="H340" t="n">
         <v>28390</v>
@@ -10258,7 +10258,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388494968414</v>
+        <v>1.21388483047485</v>
       </c>
       <c r="H341" t="n">
         <v>33517</v>
@@ -10345,7 +10345,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G344" t="n">
-        <v>1.24664700031281</v>
+        <v>1.24664711952209</v>
       </c>
       <c r="H344" t="n">
         <v>72151</v>
@@ -10374,7 +10374,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G345" t="n">
-        <v>1.30293118953705</v>
+        <v>1.30293107032776</v>
       </c>
       <c r="H345" t="n">
         <v>228591</v>
@@ -10403,7 +10403,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H346" t="n">
         <v>142637</v>
@@ -10432,7 +10432,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G347" t="n">
-        <v>1.29789066314697</v>
+        <v>1.29789078235626</v>
       </c>
       <c r="H347" t="n">
         <v>47509</v>
@@ -10461,7 +10461,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G348" t="n">
-        <v>1.2777293920517</v>
+        <v>1.27772927284241</v>
       </c>
       <c r="H348" t="n">
         <v>58888</v>
@@ -10490,7 +10490,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>1.28528988361359</v>
+        <v>1.2852897644043</v>
       </c>
       <c r="H349" t="n">
         <v>56577</v>
@@ -10548,7 +10548,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H351" t="n">
         <v>99220</v>
@@ -10577,7 +10577,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30209112167358</v>
+        <v>1.302090883255</v>
       </c>
       <c r="H352" t="n">
         <v>134003</v>
@@ -10606,7 +10606,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301176548004</v>
+        <v>1.31301188468933</v>
       </c>
       <c r="H353" t="n">
         <v>99196</v>
@@ -10664,7 +10664,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G355" t="n">
-        <v>1.52890682220459</v>
+        <v>1.52890694141388</v>
       </c>
       <c r="H355" t="n">
         <v>875535</v>
@@ -10722,7 +10722,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194431304932</v>
+        <v>1.49194419384003</v>
       </c>
       <c r="H357" t="n">
         <v>183588</v>
@@ -10751,7 +10751,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690378665924</v>
+        <v>1.48690402507782</v>
       </c>
       <c r="H358" t="n">
         <v>214405</v>
@@ -10838,7 +10838,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G361" t="n">
-        <v>1.46506226062775</v>
+        <v>1.46506237983704</v>
       </c>
       <c r="H361" t="n">
         <v>61803</v>
@@ -10983,7 +10983,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G366" t="n">
-        <v>1.38861691951752</v>
+        <v>1.38861703872681</v>
       </c>
       <c r="H366" t="n">
         <v>69743</v>
@@ -11012,7 +11012,7 @@
         <v>1.625</v>
       </c>
       <c r="G367" t="n">
-        <v>1.36509549617767</v>
+        <v>1.36509537696838</v>
       </c>
       <c r="H367" t="n">
         <v>124404</v>
@@ -11070,7 +11070,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173534393311</v>
+        <v>1.36173510551453</v>
       </c>
       <c r="H369" t="n">
         <v>94755</v>
@@ -11099,7 +11099,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G370" t="n">
-        <v>1.36845552921295</v>
+        <v>1.36845564842224</v>
       </c>
       <c r="H370" t="n">
         <v>29886</v>
@@ -11157,7 +11157,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G372" t="n">
-        <v>1.36341536045074</v>
+        <v>1.36341524124146</v>
       </c>
       <c r="H372" t="n">
         <v>45469</v>
@@ -11186,7 +11186,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G373" t="n">
-        <v>1.34829413890839</v>
+        <v>1.34829425811768</v>
       </c>
       <c r="H373" t="n">
         <v>39211</v>
@@ -11215,7 +11215,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.335693359375</v>
+        <v>1.33569359779358</v>
       </c>
       <c r="H374" t="n">
         <v>54288</v>
@@ -11244,7 +11244,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G375" t="n">
-        <v>1.34157371520996</v>
+        <v>1.34157383441925</v>
       </c>
       <c r="H375" t="n">
         <v>67186</v>
@@ -11302,7 +11302,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.3432537317276</v>
+        <v>1.34325397014618</v>
       </c>
       <c r="H377" t="n">
         <v>25858</v>
@@ -11389,7 +11389,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G380" t="n">
-        <v>1.36005520820618</v>
+        <v>1.3600549697876</v>
       </c>
       <c r="H380" t="n">
         <v>53916</v>
@@ -11534,7 +11534,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G385" t="n">
-        <v>1.42557978630066</v>
+        <v>1.42557954788208</v>
       </c>
       <c r="H385" t="n">
         <v>153814</v>
@@ -11563,7 +11563,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>1.44070065021515</v>
+        <v>1.44070076942444</v>
       </c>
       <c r="H386" t="n">
         <v>56358</v>
@@ -11592,7 +11592,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G387" t="n">
-        <v>1.42978000640869</v>
+        <v>1.4297798871994</v>
       </c>
       <c r="H387" t="n">
         <v>25887</v>
@@ -11621,7 +11621,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G388" t="n">
-        <v>1.41129851341248</v>
+        <v>1.41129863262177</v>
       </c>
       <c r="H388" t="n">
         <v>61575</v>
@@ -11650,7 +11650,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.42221939563751</v>
+        <v>1.4222195148468</v>
       </c>
       <c r="H389" t="n">
         <v>26833</v>
@@ -11679,7 +11679,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.41297876834869</v>
+        <v>1.4129786491394</v>
       </c>
       <c r="H390" t="n">
         <v>62429</v>
@@ -11708,7 +11708,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G391" t="n">
-        <v>1.41129851341248</v>
+        <v>1.41129863262177</v>
       </c>
       <c r="H391" t="n">
         <v>38374</v>
@@ -11795,7 +11795,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G394" t="n">
-        <v>1.44406080245972</v>
+        <v>1.4440610408783</v>
       </c>
       <c r="H394" t="n">
         <v>54757</v>
@@ -11853,7 +11853,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809975147247</v>
       </c>
       <c r="H396" t="n">
         <v>24332</v>
@@ -11882,7 +11882,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>1.41213858127594</v>
+        <v>1.41213870048523</v>
       </c>
       <c r="H397" t="n">
         <v>64069</v>
@@ -11911,7 +11911,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.42809987068176</v>
+        <v>1.42809975147247</v>
       </c>
       <c r="H398" t="n">
         <v>43866</v>
@@ -11940,7 +11940,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G399" t="n">
-        <v>1.42978000640869</v>
+        <v>1.4297798871994</v>
       </c>
       <c r="H399" t="n">
         <v>73782</v>
@@ -11969,7 +11969,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H400" t="n">
         <v>136155</v>
@@ -11998,7 +11998,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102343082428</v>
+        <v>1.48102366924286</v>
       </c>
       <c r="H401" t="n">
         <v>80507</v>
@@ -12027,7 +12027,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>1.4852237701416</v>
+        <v>1.48522388935089</v>
       </c>
       <c r="H402" t="n">
         <v>69708</v>
@@ -12056,7 +12056,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H403" t="n">
         <v>39945</v>
@@ -12201,7 +12201,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>1.52050626277924</v>
+        <v>1.52050614356995</v>
       </c>
       <c r="H408" t="n">
         <v>200957</v>
@@ -12259,7 +12259,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.53310716152191</v>
+        <v>1.5331072807312</v>
       </c>
       <c r="H410" t="n">
         <v>122279</v>
@@ -12288,7 +12288,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H411" t="n">
         <v>96313</v>
@@ -12346,7 +12346,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G413" t="n">
-        <v>1.45246160030365</v>
+        <v>1.45246136188507</v>
       </c>
       <c r="H413" t="n">
         <v>73244</v>
@@ -12375,7 +12375,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>1.44742119312286</v>
+        <v>1.44742107391357</v>
       </c>
       <c r="H414" t="n">
         <v>58941</v>
@@ -12433,7 +12433,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H416" t="n">
         <v>30670</v>
@@ -12520,7 +12520,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H419" t="n">
         <v>24016</v>
@@ -12549,7 +12549,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G420" t="n">
-        <v>1.44322085380554</v>
+        <v>1.44322097301483</v>
       </c>
       <c r="H420" t="n">
         <v>20737</v>
@@ -12607,7 +12607,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G422" t="n">
-        <v>1.44070065021515</v>
+        <v>1.44070076942444</v>
       </c>
       <c r="H422" t="n">
         <v>8832</v>
@@ -12665,7 +12665,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422231197357</v>
+        <v>1.46422243118286</v>
       </c>
       <c r="H424" t="n">
         <v>83230</v>
@@ -12810,7 +12810,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.44154071807861</v>
+        <v>1.4415408372879</v>
       </c>
       <c r="H429" t="n">
         <v>13399</v>
@@ -12868,7 +12868,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G431" t="n">
-        <v>1.46842277050018</v>
+        <v>1.46842265129089</v>
       </c>
       <c r="H431" t="n">
         <v>38166</v>
@@ -12897,7 +12897,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926271915436</v>
+        <v>1.46926248073578</v>
       </c>
       <c r="H432" t="n">
         <v>101212</v>
@@ -12926,7 +12926,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.4659024477005</v>
+        <v>1.46590256690979</v>
       </c>
       <c r="H433" t="n">
         <v>23096</v>
@@ -12955,7 +12955,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254229545593</v>
+        <v>1.46254241466522</v>
       </c>
       <c r="H434" t="n">
         <v>24018</v>
@@ -12984,7 +12984,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>1.45330166816711</v>
+        <v>1.45330154895782</v>
       </c>
       <c r="H435" t="n">
         <v>34256</v>
@@ -13042,7 +13042,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422231197357</v>
+        <v>1.46422243118286</v>
       </c>
       <c r="H437" t="n">
         <v>60693</v>
@@ -13100,7 +13100,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294577121735</v>
+        <v>1.51294565200806</v>
       </c>
       <c r="H439" t="n">
         <v>106284</v>
@@ -13129,7 +13129,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G440" t="n">
-        <v>1.52134644985199</v>
+        <v>1.5213463306427</v>
       </c>
       <c r="H440" t="n">
         <v>37061</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052072525024</v>
       </c>
       <c r="H442" t="n">
         <v>1415394</v>
@@ -13245,7 +13245,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.8010858297348</v>
+        <v>1.80108594894409</v>
       </c>
       <c r="H444" t="n">
         <v>1350440</v>
@@ -13303,7 +13303,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G446" t="n">
-        <v>1.78428471088409</v>
+        <v>1.78428483009338</v>
       </c>
       <c r="H446" t="n">
         <v>238019</v>
@@ -13361,7 +13361,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717551231384</v>
+        <v>1.93717527389526</v>
       </c>
       <c r="H448" t="n">
         <v>1651667</v>
@@ -13390,7 +13390,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G449" t="n">
-        <v>1.99429965019226</v>
+        <v>1.99429953098297</v>
       </c>
       <c r="H449" t="n">
         <v>1092117</v>
@@ -13419,7 +13419,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>1.94053566455841</v>
+        <v>1.94053554534912</v>
       </c>
       <c r="H450" t="n">
         <v>303798</v>
@@ -13448,7 +13448,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.89013230800629</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H451" t="n">
         <v>274964</v>
@@ -13477,7 +13477,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757922649384</v>
+        <v>1.98757874965668</v>
       </c>
       <c r="H452" t="n">
         <v>517407</v>
@@ -13535,7 +13535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G454" t="n">
-        <v>1.91869401931763</v>
+        <v>1.91869413852692</v>
       </c>
       <c r="H454" t="n">
         <v>179721</v>
@@ -13564,7 +13564,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476888179779</v>
+        <v>1.84476923942566</v>
       </c>
       <c r="H455" t="n">
         <v>293919</v>
@@ -13651,7 +13651,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>1.85652959346771</v>
+        <v>1.85652983188629</v>
       </c>
       <c r="H458" t="n">
         <v>69006</v>
@@ -13680,7 +13680,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G459" t="n">
-        <v>1.84644901752472</v>
+        <v>1.84644889831543</v>
       </c>
       <c r="H459" t="n">
         <v>64839</v>
@@ -13767,7 +13767,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420389652252</v>
+        <v>1.77420401573181</v>
       </c>
       <c r="H462" t="n">
         <v>87616</v>
@@ -13796,7 +13796,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H463" t="n">
         <v>100739</v>
@@ -13825,7 +13825,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87165081501007</v>
+        <v>1.87165093421936</v>
       </c>
       <c r="H464" t="n">
         <v>216656</v>
@@ -13883,7 +13883,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.86493039131165</v>
+        <v>1.86493027210236</v>
       </c>
       <c r="H466" t="n">
         <v>336610</v>
@@ -13912,7 +13912,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173139095306</v>
       </c>
       <c r="H467" t="n">
         <v>129153</v>
@@ -14028,7 +14028,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.94893610477448</v>
+        <v>1.9489358663559</v>
       </c>
       <c r="H471" t="n">
         <v>119724</v>
@@ -14057,7 +14057,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581791877747</v>
+        <v>1.97581803798676</v>
       </c>
       <c r="H472" t="n">
         <v>124221</v>
@@ -14086,7 +14086,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061635971069</v>
+        <v>1.95061647891998</v>
       </c>
       <c r="H473" t="n">
         <v>90920</v>
@@ -14173,7 +14173,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.88341164588928</v>
+        <v>1.88341176509857</v>
       </c>
       <c r="H476" t="n">
         <v>139588</v>
@@ -14202,7 +14202,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308874607086</v>
+        <v>1.84308886528015</v>
       </c>
       <c r="H477" t="n">
         <v>210138</v>
@@ -14231,7 +14231,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H478" t="n">
         <v>93091</v>
@@ -14260,7 +14260,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316944122314</v>
+        <v>1.85316967964172</v>
       </c>
       <c r="H479" t="n">
         <v>100214</v>
@@ -14318,7 +14318,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879324913025</v>
+        <v>1.61879336833954</v>
       </c>
       <c r="H481" t="n">
         <v>205479</v>
@@ -14347,7 +14347,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G482" t="n">
-        <v>1.64651501178741</v>
+        <v>1.6465151309967</v>
       </c>
       <c r="H482" t="n">
         <v>88167</v>
@@ -14405,7 +14405,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G484" t="n">
-        <v>1.62635362148285</v>
+        <v>1.62635374069214</v>
       </c>
       <c r="H484" t="n">
         <v>43159</v>
@@ -14434,7 +14434,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G485" t="n">
-        <v>1.5885511636734</v>
+        <v>1.58855104446411</v>
       </c>
       <c r="H485" t="n">
         <v>80862</v>
@@ -14463,7 +14463,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H486" t="n">
         <v>179687</v>
@@ -14492,7 +14492,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763028144836</v>
+        <v>1.57763016223907</v>
       </c>
       <c r="H487" t="n">
         <v>65136</v>
@@ -14550,7 +14550,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G489" t="n">
-        <v>1.55326867103577</v>
+        <v>1.55326855182648</v>
       </c>
       <c r="H489" t="n">
         <v>75040</v>
@@ -14695,7 +14695,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G494" t="n">
-        <v>1.58771097660065</v>
+        <v>1.58771085739136</v>
       </c>
       <c r="H494" t="n">
         <v>65464</v>
@@ -14724,7 +14724,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>1.59695160388947</v>
+        <v>1.59695172309875</v>
       </c>
       <c r="H495" t="n">
         <v>68871</v>
@@ -14753,7 +14753,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.612912774086</v>
+        <v>1.61291265487671</v>
       </c>
       <c r="H496" t="n">
         <v>81035</v>
@@ -14782,7 +14782,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H497" t="n">
         <v>118911</v>
@@ -15014,7 +15014,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459290981293</v>
+        <v>1.61459279060364</v>
       </c>
       <c r="H505" t="n">
         <v>51477</v>
@@ -15043,7 +15043,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811457157135</v>
+        <v>1.63811469078064</v>
       </c>
       <c r="H506" t="n">
         <v>34414</v>
@@ -15072,7 +15072,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G507" t="n">
-        <v>1.62887382507324</v>
+        <v>1.62887394428253</v>
       </c>
       <c r="H507" t="n">
         <v>38889</v>
@@ -15130,7 +15130,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62467348575592</v>
+        <v>1.62467360496521</v>
       </c>
       <c r="H509" t="n">
         <v>66555</v>
@@ -15188,7 +15188,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090973854065</v>
+        <v>1.57090985774994</v>
       </c>
       <c r="H511" t="n">
         <v>27246</v>
@@ -15217,7 +15217,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535228252411</v>
+        <v>1.60535216331482</v>
       </c>
       <c r="H512" t="n">
         <v>44066</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.596111536026</v>
+        <v>1.59611165523529</v>
       </c>
       <c r="H513" t="n">
         <v>14563</v>
@@ -15304,7 +15304,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G515" t="n">
-        <v>1.62635362148285</v>
+        <v>1.62635374069214</v>
       </c>
       <c r="H515" t="n">
         <v>91898</v>
@@ -15362,7 +15362,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>1.6633163690567</v>
+        <v>1.66331624984741</v>
       </c>
       <c r="H517" t="n">
         <v>95411</v>
@@ -15391,7 +15391,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G518" t="n">
-        <v>1.65323555469513</v>
+        <v>1.65323567390442</v>
       </c>
       <c r="H518" t="n">
         <v>361901</v>
@@ -15420,7 +15420,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H519" t="n">
         <v>148709</v>
@@ -15478,7 +15478,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G521" t="n">
-        <v>1.65827596187592</v>
+        <v>1.65827584266663</v>
       </c>
       <c r="H521" t="n">
         <v>58377</v>
@@ -15565,7 +15565,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G524" t="n">
-        <v>1.71792018413544</v>
+        <v>1.71792006492615</v>
       </c>
       <c r="H524" t="n">
         <v>107099</v>
@@ -15594,7 +15594,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H525" t="n">
         <v>105751</v>
@@ -15623,7 +15623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H526" t="n">
         <v>208108</v>
@@ -15710,7 +15710,7 @@
         <v>2.25</v>
       </c>
       <c r="G529" t="n">
-        <v>1.89013230800629</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H529" t="n">
         <v>236640</v>
@@ -15739,7 +15739,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G530" t="n">
-        <v>1.86493039131165</v>
+        <v>1.86493027210236</v>
       </c>
       <c r="H530" t="n">
         <v>144381</v>
@@ -15797,7 +15797,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G532" t="n">
-        <v>1.89433240890503</v>
+        <v>1.89433264732361</v>
       </c>
       <c r="H532" t="n">
         <v>278860</v>
@@ -15884,7 +15884,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82712769508362</v>
+        <v>1.82712757587433</v>
       </c>
       <c r="H535" t="n">
         <v>146091</v>
@@ -15913,7 +15913,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G536" t="n">
-        <v>1.7599231004715</v>
+        <v>1.75992298126221</v>
       </c>
       <c r="H536" t="n">
         <v>155319</v>
@@ -15942,7 +15942,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052072525024</v>
       </c>
       <c r="H537" t="n">
         <v>208037</v>
@@ -15971,7 +15971,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>1.83552825450897</v>
+        <v>1.83552837371826</v>
       </c>
       <c r="H538" t="n">
         <v>97475</v>
@@ -16000,7 +16000,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H539" t="n">
         <v>120622</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.74732208251953</v>
+        <v>1.74732220172882</v>
       </c>
       <c r="H540" t="n">
         <v>87173</v>
@@ -16145,7 +16145,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G544" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H544" t="n">
         <v>60876</v>
@@ -16174,7 +16174,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G545" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H545" t="n">
         <v>35103</v>
@@ -16203,7 +16203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G546" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H546" t="n">
         <v>61265</v>
@@ -16232,7 +16232,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H547" t="n">
         <v>34436</v>
@@ -16261,7 +16261,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H548" t="n">
         <v>27650</v>
@@ -16319,7 +16319,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632074356079</v>
       </c>
       <c r="H550" t="n">
         <v>29238</v>
@@ -16435,7 +16435,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>1.7263206243515</v>
+        <v>1.72632074356079</v>
       </c>
       <c r="H554" t="n">
         <v>38189</v>
@@ -16464,7 +16464,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67171692848206</v>
+        <v>1.67171680927277</v>
       </c>
       <c r="H555" t="n">
         <v>54253</v>
@@ -16493,7 +16493,7 @@
         <v>2</v>
       </c>
       <c r="G556" t="n">
-        <v>1.68011736869812</v>
+        <v>1.68011748790741</v>
       </c>
       <c r="H556" t="n">
         <v>110142</v>
@@ -16522,7 +16522,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>1.73052096366882</v>
+        <v>1.73052072525024</v>
       </c>
       <c r="H557" t="n">
         <v>86536</v>
@@ -16609,7 +16609,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79772555828094</v>
+        <v>1.79772567749023</v>
       </c>
       <c r="H560" t="n">
         <v>124459</v>
@@ -16812,7 +16812,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173139095306</v>
       </c>
       <c r="H567" t="n">
         <v>123060</v>
@@ -16841,7 +16841,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173139095306</v>
       </c>
       <c r="H568" t="n">
         <v>60488</v>
@@ -16928,7 +16928,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>1.77672433853149</v>
+        <v>1.7767242193222</v>
       </c>
       <c r="H571" t="n">
         <v>49826</v>
@@ -16957,7 +16957,7 @@
         <v>2.125</v>
       </c>
       <c r="G572" t="n">
-        <v>1.78512477874756</v>
+        <v>1.78512465953827</v>
       </c>
       <c r="H572" t="n">
         <v>93097</v>
@@ -16986,7 +16986,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>1.76832354068756</v>
+        <v>1.76832365989685</v>
       </c>
       <c r="H573" t="n">
         <v>87580</v>
@@ -17044,7 +17044,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H575" t="n">
         <v>126706</v>
@@ -17073,7 +17073,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G576" t="n">
-        <v>1.76412332057953</v>
+        <v>1.76412320137024</v>
       </c>
       <c r="H576" t="n">
         <v>42580</v>
@@ -17102,7 +17102,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>1.79352533817291</v>
+        <v>1.7935254573822</v>
       </c>
       <c r="H577" t="n">
         <v>101629</v>
@@ -17160,7 +17160,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G579" t="n">
-        <v>1.78932511806488</v>
+        <v>1.78932523727417</v>
       </c>
       <c r="H579" t="n">
         <v>43108</v>
@@ -17218,7 +17218,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>1.80192589759827</v>
+        <v>1.80192601680756</v>
       </c>
       <c r="H581" t="n">
         <v>72182</v>
@@ -17305,7 +17305,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>1.91113388538361</v>
+        <v>1.91113376617432</v>
       </c>
       <c r="H584" t="n">
         <v>252203</v>
@@ -17363,7 +17363,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>1.88173151016235</v>
+        <v>1.88173139095306</v>
       </c>
       <c r="H586" t="n">
         <v>107760</v>
@@ -17392,7 +17392,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86913049221039</v>
+        <v>1.86913061141968</v>
       </c>
       <c r="H587" t="n">
         <v>102743</v>
@@ -17450,7 +17450,7 @@
         <v>2.25</v>
       </c>
       <c r="G589" t="n">
-        <v>1.89013230800629</v>
+        <v>1.890132188797</v>
       </c>
       <c r="H589" t="n">
         <v>435390</v>
@@ -17479,7 +17479,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G590" t="n">
-        <v>1.94893610477448</v>
+        <v>1.9489358663559</v>
       </c>
       <c r="H590" t="n">
         <v>669252</v>
@@ -17537,7 +17537,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>1.92373442649841</v>
+        <v>1.9237345457077</v>
       </c>
       <c r="H592" t="n">
         <v>234946</v>
@@ -17566,7 +17566,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.92373442649841</v>
+        <v>1.9237345457077</v>
       </c>
       <c r="H593" t="n">
         <v>139281</v>
@@ -17624,7 +17624,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G595" t="n">
-        <v>1.96993768215179</v>
+        <v>1.96993780136108</v>
       </c>
       <c r="H595" t="n">
         <v>316600</v>
@@ -17711,7 +17711,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.01614093780518</v>
+        <v>2.01614117622375</v>
       </c>
       <c r="H598" t="n">
         <v>203153</v>
@@ -17798,7 +17798,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>1.99093925952911</v>
+        <v>1.99093890190125</v>
       </c>
       <c r="H601" t="n">
         <v>580375</v>
@@ -17856,7 +17856,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.2639582157135</v>
+        <v>2.26395797729492</v>
       </c>
       <c r="H603" t="n">
         <v>1308900</v>
@@ -17914,7 +17914,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.20935463905334</v>
+        <v>2.20935416221619</v>
       </c>
       <c r="H605" t="n">
         <v>545260</v>
@@ -17943,7 +17943,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.20935463905334</v>
+        <v>2.20935416221619</v>
       </c>
       <c r="H606" t="n">
         <v>207664</v>
@@ -18059,7 +18059,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>2.37316560745239</v>
+        <v>2.37316608428955</v>
       </c>
       <c r="H610" t="n">
         <v>1841688</v>
@@ -18088,7 +18088,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>2.410968542099</v>
+        <v>2.41096878051758</v>
       </c>
       <c r="H611" t="n">
         <v>984452</v>
@@ -18117,7 +18117,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>2.51177573204041</v>
+        <v>2.51177525520325</v>
       </c>
       <c r="H612" t="n">
         <v>948656</v>
@@ -18175,7 +18175,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41936945915222</v>
+        <v>2.41936922073364</v>
       </c>
       <c r="H614" t="n">
         <v>1222010</v>
@@ -18262,7 +18262,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>2.62938380241394</v>
+        <v>2.62938404083252</v>
       </c>
       <c r="H617" t="n">
         <v>902836</v>
@@ -18349,7 +18349,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>2.82259702682495</v>
+        <v>2.82259726524353</v>
       </c>
       <c r="H620" t="n">
         <v>680598</v>
@@ -18407,7 +18407,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>2.83939862251282</v>
+        <v>2.8393988609314</v>
       </c>
       <c r="H622" t="n">
         <v>500692</v>
@@ -18436,7 +18436,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>2.78059411048889</v>
+        <v>2.78059434890747</v>
       </c>
       <c r="H623" t="n">
         <v>401592</v>
@@ -18465,7 +18465,7 @@
         <v>3.375</v>
       </c>
       <c r="G624" t="n">
-        <v>2.83519816398621</v>
+        <v>2.83519792556763</v>
       </c>
       <c r="H624" t="n">
         <v>415404</v>
@@ -18494,7 +18494,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.00321006774902</v>
+        <v>3.00320982933044</v>
       </c>
       <c r="H625" t="n">
         <v>870894</v>
@@ -18552,7 +18552,7 @@
         <v>3.75</v>
       </c>
       <c r="G627" t="n">
-        <v>3.15022039413452</v>
+        <v>3.15022015571594</v>
       </c>
       <c r="H627" t="n">
         <v>455671</v>
@@ -18581,7 +18581,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>3.11661791801453</v>
+        <v>3.11661767959595</v>
       </c>
       <c r="H628" t="n">
         <v>314606</v>
@@ -18697,7 +18697,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.26362824440002</v>
+        <v>3.26362800598145</v>
       </c>
       <c r="H632" t="n">
         <v>485085</v>
@@ -18726,7 +18726,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16282105445862</v>
+        <v>3.1628212928772</v>
       </c>
       <c r="H633" t="n">
         <v>315758</v>
@@ -18813,7 +18813,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G636" t="n">
-        <v>3.17542195320129</v>
+        <v>3.17542171478271</v>
       </c>
       <c r="H636" t="n">
         <v>267220</v>
@@ -18900,7 +18900,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>3.39803743362427</v>
+        <v>3.39803767204285</v>
       </c>
       <c r="H639" t="n">
         <v>640363</v>
@@ -19045,7 +19045,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>3.51564598083496</v>
+        <v>3.5156455039978</v>
       </c>
       <c r="H644" t="n">
         <v>443924</v>
@@ -19103,7 +19103,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G646" t="n">
-        <v>3.61645245552063</v>
+        <v>3.61645269393921</v>
       </c>
       <c r="H646" t="n">
         <v>320057</v>
@@ -19161,7 +19161,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>3.78446483612061</v>
+        <v>3.78446459770203</v>
       </c>
       <c r="H648" t="n">
         <v>331005</v>
@@ -19190,7 +19190,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H649" t="n">
         <v>536313</v>
@@ -19219,7 +19219,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>3.91887402534485</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H650" t="n">
         <v>324176</v>
@@ -19248,7 +19248,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>3.96927738189697</v>
+        <v>3.96927714347839</v>
       </c>
       <c r="H651" t="n">
         <v>414943</v>
@@ -19277,7 +19277,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>3.91887402534485</v>
+        <v>3.91887426376343</v>
       </c>
       <c r="H652" t="n">
         <v>229460</v>
@@ -19364,7 +19364,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G655" t="n">
-        <v>3.82226777076721</v>
+        <v>3.82226753234863</v>
       </c>
       <c r="H655" t="n">
         <v>304092</v>
@@ -19393,7 +19393,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.84746885299683</v>
+        <v>3.84746909141541</v>
       </c>
       <c r="H656" t="n">
         <v>309751</v>
@@ -19422,7 +19422,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G657" t="n">
-        <v>3.59545111656189</v>
+        <v>3.59545135498047</v>
       </c>
       <c r="H657" t="n">
         <v>526354</v>
@@ -19596,7 +19596,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>4.14989042282104</v>
+        <v>4.14988994598389</v>
       </c>
       <c r="H663" t="n">
         <v>316961</v>
@@ -19625,7 +19625,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>4.47751235961914</v>
+        <v>4.4775128364563</v>
       </c>
       <c r="H664" t="n">
         <v>885590</v>
@@ -19683,7 +19683,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G666" t="n">
-        <v>4.59512138366699</v>
+        <v>4.59512090682983</v>
       </c>
       <c r="H666" t="n">
         <v>607583</v>
@@ -19741,7 +19741,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.89754247665405</v>
+        <v>4.89754199981689</v>
       </c>
       <c r="H668" t="n">
         <v>626116</v>
@@ -19799,7 +19799,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>4.7967357635498</v>
+        <v>4.79673528671265</v>
       </c>
       <c r="H670" t="n">
         <v>250557</v>
@@ -19828,7 +19828,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G671" t="n">
-        <v>4.72113037109375</v>
+        <v>4.72112989425659</v>
       </c>
       <c r="H671" t="n">
         <v>193001</v>
@@ -19857,7 +19857,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G672" t="n">
-        <v>4.18349266052246</v>
+        <v>4.1834921836853</v>
       </c>
       <c r="H672" t="n">
         <v>1024929</v>
@@ -19915,7 +19915,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G674" t="n">
-        <v>4.821937084198</v>
+        <v>4.82193756103516</v>
       </c>
       <c r="H674" t="n">
         <v>840694</v>
@@ -19944,7 +19944,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G675" t="n">
-        <v>4.85553979873657</v>
+        <v>4.85553932189941</v>
       </c>
       <c r="H675" t="n">
         <v>602751</v>
@@ -20089,7 +20089,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.7043285369873</v>
+        <v>4.70432901382446</v>
       </c>
       <c r="H680" t="n">
         <v>305866</v>
@@ -20147,7 +20147,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>4.67912769317627</v>
+        <v>4.67912721633911</v>
       </c>
       <c r="H682" t="n">
         <v>344165</v>
@@ -20263,7 +20263,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G686" t="n">
-        <v>4.56151819229126</v>
+        <v>4.56151866912842</v>
       </c>
       <c r="H686" t="n">
         <v>236154</v>
@@ -20321,7 +20321,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>4.44391059875488</v>
+        <v>4.44391012191772</v>
       </c>
       <c r="H688" t="n">
         <v>234396</v>
@@ -20350,7 +20350,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G689" t="n">
-        <v>4.50271511077881</v>
+        <v>4.50271463394165</v>
       </c>
       <c r="H689" t="n">
         <v>161397</v>
@@ -20408,7 +20408,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>4.39350700378418</v>
+        <v>4.39350748062134</v>
       </c>
       <c r="H691" t="n">
         <v>319589</v>
@@ -20466,7 +20466,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H693" t="n">
         <v>130168</v>
@@ -20495,7 +20495,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>4.05328273773193</v>
+        <v>4.05328321456909</v>
       </c>
       <c r="H694" t="n">
         <v>499614</v>
@@ -20524,7 +20524,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>4.0574836730957</v>
+        <v>4.05748414993286</v>
       </c>
       <c r="H695" t="n">
         <v>282929</v>
@@ -20611,7 +20611,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G698" t="n">
-        <v>3.8054666519165</v>
+        <v>3.80546593666077</v>
       </c>
       <c r="H698" t="n">
         <v>372911</v>
@@ -20640,7 +20640,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.79286479949951</v>
+        <v>3.79286503791809</v>
       </c>
       <c r="H699" t="n">
         <v>286966</v>
@@ -20669,7 +20669,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>3.73826098442078</v>
+        <v>3.73826122283936</v>
       </c>
       <c r="H700" t="n">
         <v>569444</v>
@@ -20727,7 +20727,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G702" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H702" t="n">
         <v>914925</v>
@@ -20814,7 +20814,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>3.18382239341736</v>
+        <v>3.18382263183594</v>
       </c>
       <c r="H705" t="n">
         <v>692837</v>
@@ -20843,7 +20843,7 @@
         <v>3.625</v>
       </c>
       <c r="G706" t="n">
-        <v>3.0452127456665</v>
+        <v>3.04521250724792</v>
       </c>
       <c r="H706" t="n">
         <v>384688</v>
@@ -20872,7 +20872,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H707" t="n">
         <v>426984</v>
@@ -20901,7 +20901,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.9948091506958</v>
+        <v>2.99480962753296</v>
       </c>
       <c r="H708" t="n">
         <v>295472</v>
@@ -20930,7 +20930,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H709" t="n">
         <v>375579</v>
@@ -20959,7 +20959,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G710" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H710" t="n">
         <v>559647</v>
@@ -21017,7 +21017,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.95280623435974</v>
+        <v>2.9528067111969</v>
       </c>
       <c r="H712" t="n">
         <v>247551</v>
@@ -21104,7 +21104,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G715" t="n">
-        <v>2.8057963848114</v>
+        <v>2.80579590797424</v>
       </c>
       <c r="H715" t="n">
         <v>252342</v>
@@ -21162,7 +21162,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G717" t="n">
-        <v>2.931804895401</v>
+        <v>2.93180513381958</v>
       </c>
       <c r="H717" t="n">
         <v>318723</v>
@@ -21220,7 +21220,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G719" t="n">
-        <v>2.66718626022339</v>
+        <v>2.66718649864197</v>
       </c>
       <c r="H719" t="n">
         <v>464448</v>
@@ -21336,7 +21336,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>2.94860601425171</v>
+        <v>2.94860577583313</v>
       </c>
       <c r="H723" t="n">
         <v>797687</v>
@@ -21423,7 +21423,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G726" t="n">
-        <v>3.1418194770813</v>
+        <v>3.14181971549988</v>
       </c>
       <c r="H726" t="n">
         <v>367513</v>
@@ -21568,7 +21568,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>3.2888298034668</v>
+        <v>3.28883004188538</v>
       </c>
       <c r="H731" t="n">
         <v>228748</v>
@@ -21626,7 +21626,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>3.18382239341736</v>
+        <v>3.18382263183594</v>
       </c>
       <c r="H733" t="n">
         <v>160282</v>
@@ -21684,7 +21684,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G735" t="n">
-        <v>3.10401678085327</v>
+        <v>3.10401701927185</v>
       </c>
       <c r="H735" t="n">
         <v>209920</v>
@@ -21742,7 +21742,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97380757331848</v>
+        <v>2.97380805015564</v>
       </c>
       <c r="H737" t="n">
         <v>226777</v>
@@ -21800,7 +21800,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H739" t="n">
         <v>272198</v>
@@ -21858,7 +21858,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>2.83939862251282</v>
+        <v>2.8393988609314</v>
       </c>
       <c r="H741" t="n">
         <v>67826</v>
@@ -21887,7 +21887,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G742" t="n">
-        <v>2.8814013004303</v>
+        <v>2.88140153884888</v>
       </c>
       <c r="H742" t="n">
         <v>137508</v>
@@ -21974,7 +21974,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G745" t="n">
-        <v>3.17542195320129</v>
+        <v>3.17542171478271</v>
       </c>
       <c r="H745" t="n">
         <v>579265</v>
@@ -22003,7 +22003,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.2762291431427</v>
+        <v>3.27622938156128</v>
       </c>
       <c r="H746" t="n">
         <v>277360</v>
@@ -22119,7 +22119,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05781364440918</v>
+        <v>3.05781388282776</v>
       </c>
       <c r="H750" t="n">
         <v>147033</v>
@@ -22148,7 +22148,7 @@
         <v>3.625</v>
       </c>
       <c r="G751" t="n">
-        <v>3.0452127456665</v>
+        <v>3.04521250724792</v>
       </c>
       <c r="H751" t="n">
         <v>315691</v>
@@ -22206,7 +22206,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>2.97380757331848</v>
+        <v>2.97380805015564</v>
       </c>
       <c r="H753" t="n">
         <v>142456</v>
@@ -22235,7 +22235,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G754" t="n">
-        <v>3.02001118659973</v>
+        <v>3.02001094818115</v>
       </c>
       <c r="H754" t="n">
         <v>82541</v>
@@ -22322,7 +22322,7 @@
         <v>3.25</v>
       </c>
       <c r="G757" t="n">
-        <v>2.73019099235535</v>
+        <v>2.73019075393677</v>
       </c>
       <c r="H757" t="n">
         <v>316158</v>
@@ -22351,7 +22351,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60418224334717</v>
+        <v>2.60418176651001</v>
       </c>
       <c r="H758" t="n">
         <v>295455</v>
@@ -22525,7 +22525,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G764" t="n">
-        <v>2.84779930114746</v>
+        <v>2.84779906272888</v>
       </c>
       <c r="H764" t="n">
         <v>321253</v>
@@ -22554,7 +22554,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>2.91500401496887</v>
+        <v>2.91500377655029</v>
       </c>
       <c r="H765" t="n">
         <v>153244</v>
@@ -22670,7 +22670,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G769" t="n">
-        <v>3.20062351226807</v>
+        <v>3.20062375068665</v>
       </c>
       <c r="H769" t="n">
         <v>257121</v>
@@ -22699,7 +22699,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G770" t="n">
-        <v>3.20482397079468</v>
+        <v>3.20482420921326</v>
       </c>
       <c r="H770" t="n">
         <v>144368</v>
@@ -22757,7 +22757,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>3.07881498336792</v>
+        <v>3.0788152217865</v>
       </c>
       <c r="H772" t="n">
         <v>84601</v>
@@ -22786,7 +22786,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.00741028785706</v>
+        <v>3.00741004943848</v>
       </c>
       <c r="H773" t="n">
         <v>71849</v>
@@ -22873,7 +22873,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G776" t="n">
-        <v>3.225825548172</v>
+        <v>3.22582530975342</v>
       </c>
       <c r="H776" t="n">
         <v>234308</v>
@@ -22902,7 +22902,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>3.35183429718018</v>
+        <v>3.35183453559875</v>
       </c>
       <c r="H777" t="n">
         <v>316364</v>
@@ -22960,7 +22960,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>3.76346302032471</v>
+        <v>3.76346278190613</v>
       </c>
       <c r="H779" t="n">
         <v>689270</v>
@@ -22989,7 +22989,7 @@
         <v>4.5</v>
       </c>
       <c r="G780" t="n">
-        <v>3.78026461601257</v>
+        <v>3.78026437759399</v>
       </c>
       <c r="H780" t="n">
         <v>599313</v>
@@ -23018,7 +23018,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>3.73406100273132</v>
+        <v>3.73406147956848</v>
       </c>
       <c r="H781" t="n">
         <v>247790</v>
@@ -23047,7 +23047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>3.82226777076721</v>
+        <v>3.82226753234863</v>
       </c>
       <c r="H782" t="n">
         <v>469438</v>
@@ -23076,7 +23076,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98607850074768</v>
+        <v>3.98607873916626</v>
       </c>
       <c r="H783" t="n">
         <v>485114</v>
@@ -23105,7 +23105,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H784" t="n">
         <v>562311</v>
@@ -23192,7 +23192,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>4.01128005981445</v>
+        <v>4.01128053665161</v>
       </c>
       <c r="H787" t="n">
         <v>326238</v>
@@ -23221,7 +23221,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H788" t="n">
         <v>224507</v>
@@ -23279,7 +23279,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G790" t="n">
-        <v>4.00288009643555</v>
+        <v>4.00287961959839</v>
       </c>
       <c r="H790" t="n">
         <v>220886</v>
@@ -23308,7 +23308,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83486771583557</v>
+        <v>3.83486819267273</v>
       </c>
       <c r="H791" t="n">
         <v>191763</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.70465874671936</v>
+        <v>3.70465898513794</v>
       </c>
       <c r="H792" t="n">
         <v>292131</v>
@@ -23366,7 +23366,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G793" t="n">
-        <v>3.84326863288879</v>
+        <v>3.84326815605164</v>
       </c>
       <c r="H793" t="n">
         <v>223832</v>
@@ -23453,7 +23453,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>3.88107132911682</v>
+        <v>3.88107109069824</v>
       </c>
       <c r="H796" t="n">
         <v>95197</v>
@@ -23482,7 +23482,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H797" t="n">
         <v>63961</v>
@@ -23511,7 +23511,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>3.93567514419556</v>
+        <v>3.93567490577698</v>
       </c>
       <c r="H798" t="n">
         <v>68505</v>
@@ -23540,7 +23540,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>3.94827556610107</v>
+        <v>3.94827604293823</v>
       </c>
       <c r="H799" t="n">
         <v>128867</v>
@@ -23569,7 +23569,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>3.93147444725037</v>
+        <v>3.93147492408752</v>
       </c>
       <c r="H800" t="n">
         <v>132720</v>
@@ -23598,7 +23598,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88947176933289</v>
+        <v>3.88947224617004</v>
       </c>
       <c r="H801" t="n">
         <v>39567</v>
@@ -23685,7 +23685,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H804" t="n">
         <v>63625</v>
@@ -23743,7 +23743,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>3.80126595497131</v>
+        <v>3.80126571655273</v>
       </c>
       <c r="H806" t="n">
         <v>74797</v>
@@ -23772,7 +23772,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>3.70885944366455</v>
+        <v>3.70885896682739</v>
       </c>
       <c r="H807" t="n">
         <v>145265</v>
@@ -23801,7 +23801,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.64165449142456</v>
+        <v>3.64165496826172</v>
       </c>
       <c r="H808" t="n">
         <v>150135</v>
@@ -23859,7 +23859,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.51564598083496</v>
+        <v>3.5156455039978</v>
       </c>
       <c r="H810" t="n">
         <v>155696</v>
@@ -23946,7 +23946,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>3.65845561027527</v>
+        <v>3.65845608711243</v>
       </c>
       <c r="H813" t="n">
         <v>431429</v>
@@ -24062,7 +24062,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>4.04068279266357</v>
+        <v>4.04068231582642</v>
       </c>
       <c r="H817" t="n">
         <v>212730</v>
@@ -24120,7 +24120,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H819" t="n">
         <v>214808</v>
@@ -24149,7 +24149,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G820" t="n">
-        <v>3.93987536430359</v>
+        <v>3.93987560272217</v>
       </c>
       <c r="H820" t="n">
         <v>315880</v>
@@ -24207,7 +24207,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G822" t="n">
-        <v>3.93567514419556</v>
+        <v>3.93567490577698</v>
       </c>
       <c r="H822" t="n">
         <v>180007</v>
@@ -24265,7 +24265,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>4.03228187561035</v>
+        <v>4.03228235244751</v>
       </c>
       <c r="H824" t="n">
         <v>280086</v>
@@ -24381,7 +24381,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07008409500122</v>
+        <v>4.07008457183838</v>
       </c>
       <c r="H828" t="n">
         <v>111313</v>
@@ -24410,7 +24410,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G829" t="n">
-        <v>4.14148902893066</v>
+        <v>4.14148950576782</v>
       </c>
       <c r="H829" t="n">
         <v>178794</v>
@@ -24468,7 +24468,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G831" t="n">
-        <v>4.72953033447266</v>
+        <v>4.72953081130981</v>
       </c>
       <c r="H831" t="n">
         <v>734870</v>
@@ -24526,7 +24526,7 @@
         <v>5.5</v>
       </c>
       <c r="G833" t="n">
-        <v>4.62032270431519</v>
+        <v>4.62032318115234</v>
       </c>
       <c r="H833" t="n">
         <v>457602</v>
@@ -24555,7 +24555,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.57832002639771</v>
+        <v>4.57832050323486</v>
       </c>
       <c r="H834" t="n">
         <v>153136</v>
@@ -24613,7 +24613,7 @@
         <v>5.25</v>
       </c>
       <c r="G836" t="n">
-        <v>4.41030883789062</v>
+        <v>4.41030836105347</v>
       </c>
       <c r="H836" t="n">
         <v>161740</v>
@@ -24642,7 +24642,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G837" t="n">
-        <v>4.30950117111206</v>
+        <v>4.30950164794922</v>
       </c>
       <c r="H837" t="n">
         <v>277391</v>
@@ -24671,7 +24671,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>4.25909757614136</v>
+        <v>4.25909805297852</v>
       </c>
       <c r="H838" t="n">
         <v>581777</v>
@@ -24700,7 +24700,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>4.26749849319458</v>
+        <v>4.26749801635742</v>
       </c>
       <c r="H839" t="n">
         <v>229262</v>
@@ -24729,7 +24729,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G840" t="n">
-        <v>4.14989042282104</v>
+        <v>4.14988994598389</v>
       </c>
       <c r="H840" t="n">
         <v>190949</v>
@@ -24758,7 +24758,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>4.03228187561035</v>
+        <v>4.03228235244751</v>
       </c>
       <c r="H841" t="n">
         <v>258680</v>
@@ -24787,7 +24787,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.90627288818359</v>
+        <v>3.90627336502075</v>
       </c>
       <c r="H842" t="n">
         <v>193026</v>
@@ -24816,7 +24816,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.84746885299683</v>
+        <v>3.84746909141541</v>
       </c>
       <c r="H843" t="n">
         <v>134136</v>
@@ -24845,7 +24845,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>3.78866481781006</v>
+        <v>3.78866529464722</v>
       </c>
       <c r="H844" t="n">
         <v>180317</v>
@@ -24874,7 +24874,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>3.97347807884216</v>
+        <v>3.973477602005</v>
       </c>
       <c r="H845" t="n">
         <v>787756</v>
@@ -24903,7 +24903,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>3.92307448387146</v>
+        <v>3.9230740070343</v>
       </c>
       <c r="H846" t="n">
         <v>609683</v>
@@ -24961,7 +24961,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G848" t="n">
-        <v>4.13632345199585</v>
+        <v>4.13632297515869</v>
       </c>
       <c r="H848" t="n">
         <v>225108</v>
@@ -25019,7 +25019,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G850" t="n">
-        <v>3.8856372833252</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H850" t="n">
         <v>352449</v>
@@ -25048,7 +25048,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487156867981</v>
       </c>
       <c r="H851" t="n">
         <v>279899</v>
@@ -25077,7 +25077,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G852" t="n">
-        <v>4.09310245513916</v>
+        <v>4.09310150146484</v>
       </c>
       <c r="H852" t="n">
         <v>823655</v>
@@ -25135,7 +25135,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>3.71275043487549</v>
+        <v>3.71275019645691</v>
       </c>
       <c r="H854" t="n">
         <v>237445</v>
@@ -25164,7 +25164,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.73436117172241</v>
+        <v>3.73436093330383</v>
       </c>
       <c r="H855" t="n">
         <v>240038</v>
@@ -25193,7 +25193,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>3.73868298530579</v>
+        <v>3.73868322372437</v>
       </c>
       <c r="H856" t="n">
         <v>149487</v>
@@ -25251,7 +25251,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G858" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707201004028</v>
       </c>
       <c r="H858" t="n">
         <v>143919</v>
@@ -25280,7 +25280,7 @@
         <v>4.5</v>
       </c>
       <c r="G859" t="n">
-        <v>3.88995933532715</v>
+        <v>3.88995909690857</v>
       </c>
       <c r="H859" t="n">
         <v>350261</v>
@@ -25309,7 +25309,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>3.91157031059265</v>
+        <v>3.91157054901123</v>
       </c>
       <c r="H860" t="n">
         <v>222935</v>
@@ -25338,7 +25338,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>3.83377122879028</v>
+        <v>3.83377075195312</v>
       </c>
       <c r="H861" t="n">
         <v>131749</v>
@@ -25367,7 +25367,7 @@
         <v>4.25</v>
       </c>
       <c r="G862" t="n">
-        <v>3.67385077476501</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H862" t="n">
         <v>185171</v>
@@ -25425,7 +25425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.71707248687744</v>
+        <v>3.71707201004028</v>
       </c>
       <c r="H864" t="n">
         <v>92135</v>
@@ -25454,7 +25454,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G865" t="n">
-        <v>3.64359521865845</v>
+        <v>3.64359569549561</v>
       </c>
       <c r="H865" t="n">
         <v>139539</v>
@@ -25541,7 +25541,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G868" t="n">
-        <v>3.41019749641418</v>
+        <v>3.41019797325134</v>
       </c>
       <c r="H868" t="n">
         <v>168875</v>
@@ -25657,7 +25657,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H872" t="n">
         <v>217721</v>
@@ -25773,7 +25773,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G876" t="n">
-        <v>3.40155363082886</v>
+        <v>3.4015531539917</v>
       </c>
       <c r="H876" t="n">
         <v>185268</v>
@@ -25860,7 +25860,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>3.31078767776489</v>
+        <v>3.31078743934631</v>
       </c>
       <c r="H879" t="n">
         <v>368060</v>
@@ -25889,7 +25889,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H880" t="n">
         <v>312709</v>
@@ -25918,7 +25918,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G881" t="n">
-        <v>3.31510996818542</v>
+        <v>3.31510972976685</v>
       </c>
       <c r="H881" t="n">
         <v>112761</v>
@@ -25976,7 +25976,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G883" t="n">
-        <v>3.39723110198975</v>
+        <v>3.39723134040833</v>
       </c>
       <c r="H883" t="n">
         <v>257002</v>
@@ -26005,7 +26005,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H884" t="n">
         <v>244267</v>
@@ -26063,7 +26063,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>3.26324367523193</v>
+        <v>3.26324391365051</v>
       </c>
       <c r="H886" t="n">
         <v>143035</v>
@@ -26092,7 +26092,7 @@
         <v>3.75</v>
       </c>
       <c r="G887" t="n">
-        <v>3.24163269996643</v>
+        <v>3.24163293838501</v>
       </c>
       <c r="H887" t="n">
         <v>163491</v>
@@ -26121,7 +26121,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G888" t="n">
-        <v>3.21137762069702</v>
+        <v>3.21137738227844</v>
       </c>
       <c r="H888" t="n">
         <v>151557</v>
@@ -26150,7 +26150,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.22434425354004</v>
+        <v>3.22434401512146</v>
       </c>
       <c r="H889" t="n">
         <v>96520</v>
@@ -26208,7 +26208,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G891" t="n">
-        <v>3.30646538734436</v>
+        <v>3.30646562576294</v>
       </c>
       <c r="H891" t="n">
         <v>200140</v>
@@ -26237,7 +26237,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G892" t="n">
-        <v>3.28917694091797</v>
+        <v>3.28917670249939</v>
       </c>
       <c r="H892" t="n">
         <v>176202</v>
@@ -26266,7 +26266,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G893" t="n">
-        <v>3.2502772808075</v>
+        <v>3.25027704238892</v>
       </c>
       <c r="H893" t="n">
         <v>139091</v>
@@ -26324,7 +26324,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>3.1768000125885</v>
+        <v>3.17680025100708</v>
       </c>
       <c r="H895" t="n">
         <v>103388</v>
@@ -26382,7 +26382,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G897" t="n">
-        <v>3.26756596565247</v>
+        <v>3.26756572723389</v>
       </c>
       <c r="H897" t="n">
         <v>379211</v>
@@ -26469,7 +26469,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>3.2502772808075</v>
+        <v>3.25027704238892</v>
       </c>
       <c r="H900" t="n">
         <v>76009</v>
@@ -26527,7 +26527,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>3.29349875450134</v>
+        <v>3.29349899291992</v>
       </c>
       <c r="H902" t="n">
         <v>199685</v>
@@ -26585,7 +26585,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>3.18112254142761</v>
+        <v>3.18112230300903</v>
       </c>
       <c r="H904" t="n">
         <v>64399</v>
@@ -26614,7 +26614,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G905" t="n">
-        <v>3.22866606712341</v>
+        <v>3.22866630554199</v>
       </c>
       <c r="H905" t="n">
         <v>85073</v>
@@ -26846,7 +26846,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.59605121612549</v>
+        <v>3.59605145454407</v>
       </c>
       <c r="H913" t="n">
         <v>826164</v>
@@ -26875,7 +26875,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113898277283</v>
       </c>
       <c r="H914" t="n">
         <v>612221</v>
@@ -26904,7 +26904,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113898277283</v>
       </c>
       <c r="H915" t="n">
         <v>650236</v>
@@ -26933,7 +26933,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>3.68681693077087</v>
+        <v>3.68681716918945</v>
       </c>
       <c r="H916" t="n">
         <v>212057</v>
@@ -26991,7 +26991,7 @@
         <v>4.25</v>
       </c>
       <c r="G918" t="n">
-        <v>3.67385077476501</v>
+        <v>3.67385029792786</v>
       </c>
       <c r="H918" t="n">
         <v>412035</v>
@@ -27020,7 +27020,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.48799681663513</v>
+        <v>3.48799657821655</v>
       </c>
       <c r="H919" t="n">
         <v>281614</v>
@@ -27107,7 +27107,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G922" t="n">
-        <v>3.34104299545288</v>
+        <v>3.3410427570343</v>
       </c>
       <c r="H922" t="n">
         <v>177144</v>
@@ -27136,7 +27136,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.51392984390259</v>
+        <v>3.51393008232117</v>
       </c>
       <c r="H923" t="n">
         <v>275779</v>
@@ -27223,7 +27223,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>3.57444047927856</v>
+        <v>3.57444071769714</v>
       </c>
       <c r="H926" t="n">
         <v>367003</v>
@@ -27281,7 +27281,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>3.56147384643555</v>
+        <v>3.56147408485413</v>
       </c>
       <c r="H928" t="n">
         <v>76058</v>
@@ -27339,7 +27339,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.57011842727661</v>
+        <v>3.57011818885803</v>
       </c>
       <c r="H930" t="n">
         <v>221733</v>
@@ -27368,7 +27368,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>3.55282926559448</v>
+        <v>3.55282974243164</v>
       </c>
       <c r="H931" t="n">
         <v>92909</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.56147384643555</v>
+        <v>3.56147408485413</v>
       </c>
       <c r="H935" t="n">
         <v>352848</v>
@@ -27542,7 +27542,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>3.50960779190063</v>
+        <v>3.50960803031921</v>
       </c>
       <c r="H937" t="n">
         <v>213268</v>
@@ -27571,7 +27571,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>3.4966413974762</v>
+        <v>3.49664163589478</v>
       </c>
       <c r="H938" t="n">
         <v>211590</v>
@@ -27629,7 +27629,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H940" t="n">
         <v>107731</v>
@@ -27658,7 +27658,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G941" t="n">
-        <v>3.51392984390259</v>
+        <v>3.51393008232117</v>
       </c>
       <c r="H941" t="n">
         <v>236550</v>
@@ -27687,7 +27687,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>3.69113922119141</v>
+        <v>3.69113898277283</v>
       </c>
       <c r="H942" t="n">
         <v>945235</v>
@@ -27745,7 +27745,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G944" t="n">
-        <v>3.79487133026123</v>
+        <v>3.79487156867981</v>
       </c>
       <c r="H944" t="n">
         <v>271076</v>
@@ -27774,7 +27774,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H945" t="n">
         <v>315309</v>
@@ -27803,7 +27803,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.61766219139099</v>
+        <v>3.61766195297241</v>
       </c>
       <c r="H946" t="n">
         <v>539098</v>
@@ -27861,7 +27861,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>3.59605121612549</v>
+        <v>3.59605145454407</v>
       </c>
       <c r="H948" t="n">
         <v>88816</v>
@@ -27919,7 +27919,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G950" t="n">
-        <v>3.58740711212158</v>
+        <v>3.587406873703</v>
       </c>
       <c r="H950" t="n">
         <v>137894</v>
@@ -28006,7 +28006,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>3.61766219139099</v>
+        <v>3.61766195297241</v>
       </c>
       <c r="H953" t="n">
         <v>46261</v>
@@ -28064,7 +28064,7 @@
         <v>4</v>
       </c>
       <c r="G955" t="n">
-        <v>3.45774149894714</v>
+        <v>3.45774173736572</v>
       </c>
       <c r="H955" t="n">
         <v>118165</v>
@@ -28093,7 +28093,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H956" t="n">
         <v>153789</v>
@@ -28122,7 +28122,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G957" t="n">
-        <v>3.48799681663513</v>
+        <v>3.48799657821655</v>
       </c>
       <c r="H957" t="n">
         <v>73213</v>
@@ -28151,7 +28151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H958" t="n">
         <v>64692</v>
@@ -28180,7 +28180,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>3.49231934547424</v>
+        <v>3.49231910705566</v>
       </c>
       <c r="H959" t="n">
         <v>94617</v>
@@ -28209,7 +28209,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="n">
-        <v>3.46638631820679</v>
+        <v>3.46638607978821</v>
       </c>
       <c r="H960" t="n">
         <v>67763</v>
@@ -28296,7 +28296,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G963" t="n">
-        <v>3.57011842727661</v>
+        <v>3.57011818885803</v>
       </c>
       <c r="H963" t="n">
         <v>60156</v>
@@ -28383,7 +28383,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>3.81648230552673</v>
+        <v>3.81648254394531</v>
       </c>
       <c r="H966" t="n">
         <v>901832</v>
@@ -28412,7 +28412,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="n">
-        <v>3.93318104743958</v>
+        <v>3.933180809021</v>
       </c>
       <c r="H967" t="n">
         <v>671393</v>
@@ -28441,7 +28441,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79054975509644</v>
+        <v>3.79054951667786</v>
       </c>
       <c r="H968" t="n">
         <v>389865</v>
@@ -28470,7 +28470,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.86402606964111</v>
+        <v>3.86402630805969</v>
       </c>
       <c r="H969" t="n">
         <v>302156</v>
@@ -28586,7 +28586,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>3.96343660354614</v>
+        <v>3.96343636512756</v>
       </c>
       <c r="H973" t="n">
         <v>108809</v>
@@ -28615,7 +28615,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>3.90724778175354</v>
+        <v>3.90724802017212</v>
       </c>
       <c r="H974" t="n">
         <v>225485</v>
@@ -28673,7 +28673,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="n">
-        <v>3.78622722625732</v>
+        <v>3.7862274646759</v>
       </c>
       <c r="H976" t="n">
         <v>109461</v>
@@ -28702,7 +28702,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="n">
-        <v>3.78190445899963</v>
+        <v>3.78190493583679</v>
       </c>
       <c r="H977" t="n">
         <v>66712</v>
@@ -28789,7 +28789,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="n">
-        <v>3.84241557121277</v>
+        <v>3.84241580963135</v>
       </c>
       <c r="H980" t="n">
         <v>205384</v>
@@ -28818,7 +28818,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="n">
-        <v>3.81216049194336</v>
+        <v>3.81216025352478</v>
       </c>
       <c r="H981" t="n">
         <v>426008</v>
@@ -28847,7 +28847,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="n">
-        <v>3.76893854141235</v>
+        <v>3.76893877983093</v>
       </c>
       <c r="H982" t="n">
         <v>188043</v>
@@ -28905,7 +28905,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="n">
-        <v>3.95046997070312</v>
+        <v>3.95046973228455</v>
       </c>
       <c r="H984" t="n">
         <v>655591</v>
@@ -28963,7 +28963,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="n">
-        <v>3.93318104743958</v>
+        <v>3.933180809021</v>
       </c>
       <c r="H986" t="n">
         <v>720957</v>
@@ -28992,7 +28992,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>3.87699317932129</v>
+        <v>3.87699270248413</v>
       </c>
       <c r="H987" t="n">
         <v>315026</v>
@@ -29021,7 +29021,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="n">
-        <v>4.04555749893188</v>
+        <v>4.04555797576904</v>
       </c>
       <c r="H988" t="n">
         <v>382155</v>
@@ -29050,7 +29050,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>3.95911407470703</v>
+        <v>3.95911431312561</v>
       </c>
       <c r="H989" t="n">
         <v>256400</v>
@@ -29079,7 +29079,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>3.93318104743958</v>
+        <v>3.933180809021</v>
       </c>
       <c r="H990" t="n">
         <v>214631</v>
@@ -29108,7 +29108,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>3.8856372833252</v>
+        <v>3.88563704490662</v>
       </c>
       <c r="H991" t="n">
         <v>325475</v>
@@ -29137,7 +29137,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G992" t="n">
-        <v>4.09310245513916</v>
+        <v>4.09310150146484</v>
       </c>
       <c r="H992" t="n">
         <v>539029</v>
@@ -29166,7 +29166,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.08445692062378</v>
+        <v>4.08445739746094</v>
       </c>
       <c r="H993" t="n">
         <v>676881</v>
@@ -29195,7 +29195,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="n">
-        <v>4.32217693328857</v>
+        <v>4.32217741012573</v>
       </c>
       <c r="H994" t="n">
         <v>1100977</v>
@@ -29282,7 +29282,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.44319772720337</v>
+        <v>4.44319820404053</v>
       </c>
       <c r="H997" t="n">
         <v>239472</v>
@@ -29398,7 +29398,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1001" t="n">
         <v>803711</v>
@@ -29485,7 +29485,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1004" t="n">
         <v>150662</v>
@@ -29543,7 +29543,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.63337421417236</v>
+        <v>4.63337373733521</v>
       </c>
       <c r="H1006" t="n">
         <v>237220</v>
@@ -29630,7 +29630,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.84948253631592</v>
+        <v>4.84948301315308</v>
       </c>
       <c r="H1009" t="n">
         <v>507158</v>
@@ -29659,7 +29659,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1010" t="n">
         <v>284503</v>
@@ -29717,7 +29717,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.82354974746704</v>
+        <v>4.8235502243042</v>
       </c>
       <c r="H1012" t="n">
         <v>550061</v>
@@ -29833,7 +29833,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1016" t="n">
         <v>142573</v>
@@ -29920,7 +29920,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.67659521102905</v>
+        <v>4.67659568786621</v>
       </c>
       <c r="H1019" t="n">
         <v>318021</v>
@@ -29949,7 +29949,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1020" t="n">
         <v>296001</v>
@@ -30065,7 +30065,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84083843231201</v>
+        <v>4.84083795547485</v>
       </c>
       <c r="H1024" t="n">
         <v>111612</v>
@@ -30094,7 +30094,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1025" t="n">
         <v>190180</v>
@@ -30123,7 +30123,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1026" t="n">
         <v>196836</v>
@@ -30152,7 +30152,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1027" t="n">
         <v>362151</v>
@@ -30181,7 +30181,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.79761695861816</v>
+        <v>4.79761648178101</v>
       </c>
       <c r="H1028" t="n">
         <v>190796</v>
@@ -30268,7 +30268,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.28170013427734</v>
+        <v>5.28170108795166</v>
       </c>
       <c r="H1031" t="n">
         <v>1366658</v>
@@ -30297,7 +30297,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.65340709686279</v>
+        <v>5.65340805053711</v>
       </c>
       <c r="H1032" t="n">
         <v>1195444</v>
@@ -30355,7 +30355,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.28170013427734</v>
+        <v>5.28170108795166</v>
       </c>
       <c r="H1034" t="n">
         <v>955078</v>
@@ -30413,7 +30413,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.99643754959106</v>
+        <v>4.99643659591675</v>
       </c>
       <c r="H1036" t="n">
         <v>781150</v>
@@ -30442,7 +30442,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.74574995040894</v>
+        <v>4.74575042724609</v>
       </c>
       <c r="H1037" t="n">
         <v>327363</v>
@@ -30558,7 +30558,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.55557489395142</v>
+        <v>4.55557441711426</v>
       </c>
       <c r="H1041" t="n">
         <v>544975</v>
@@ -30587,7 +30587,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.56421899795532</v>
+        <v>4.56421947479248</v>
       </c>
       <c r="H1042" t="n">
         <v>640983</v>
@@ -30616,7 +30616,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1043" t="n">
         <v>234871</v>
@@ -30645,7 +30645,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.5901517868042</v>
+        <v>4.59015226364136</v>
       </c>
       <c r="H1044" t="n">
         <v>169114</v>
@@ -30674,7 +30674,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.48641967773438</v>
+        <v>4.48642015457153</v>
       </c>
       <c r="H1045" t="n">
         <v>723012</v>
@@ -30703,7 +30703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.52964162826538</v>
+        <v>4.52964115142822</v>
       </c>
       <c r="H1046" t="n">
         <v>233413</v>
@@ -30761,7 +30761,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.41726493835449</v>
+        <v>4.41726541519165</v>
       </c>
       <c r="H1048" t="n">
         <v>203223</v>
@@ -30790,7 +30790,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.27895545959473</v>
+        <v>4.27895498275757</v>
       </c>
       <c r="H1049" t="n">
         <v>418848</v>
@@ -30819,7 +30819,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.65930700302124</v>
+        <v>4.65930652618408</v>
       </c>
       <c r="H1050" t="n">
         <v>1026582</v>
@@ -30877,7 +30877,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.53828620910645</v>
+        <v>4.53828573226929</v>
       </c>
       <c r="H1052" t="n">
         <v>475739</v>
@@ -30935,7 +30935,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.89428186416626</v>
+        <v>3.89428162574768</v>
       </c>
       <c r="H1054" t="n">
         <v>573847</v>
@@ -30964,7 +30964,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.85970401763916</v>
+        <v>3.8597047328949</v>
       </c>
       <c r="H1055" t="n">
         <v>847899</v>
@@ -30993,7 +30993,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.78622722625732</v>
+        <v>3.7862274646759</v>
       </c>
       <c r="H1056" t="n">
         <v>469309</v>
@@ -31022,7 +31022,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.82512664794922</v>
+        <v>3.8251268863678</v>
       </c>
       <c r="H1057" t="n">
         <v>541802</v>
@@ -31080,7 +31080,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.68249487876892</v>
+        <v>3.6824951171875</v>
       </c>
       <c r="H1059" t="n">
         <v>261182</v>
@@ -31138,7 +31138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.47503018379211</v>
+        <v>3.47503042221069</v>
       </c>
       <c r="H1061" t="n">
         <v>283526</v>
@@ -31167,7 +31167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.39723110198975</v>
+        <v>3.39723134040833</v>
       </c>
       <c r="H1062" t="n">
         <v>449166</v>
@@ -31196,7 +31196,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.02984642982483</v>
+        <v>3.02984619140625</v>
       </c>
       <c r="H1063" t="n">
         <v>357198</v>
@@ -31283,7 +31283,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.64085006713867</v>
+        <v>2.64085054397583</v>
       </c>
       <c r="H1066" t="n">
         <v>650023</v>
@@ -31312,7 +31312,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.67110538482666</v>
+        <v>2.67110514640808</v>
       </c>
       <c r="H1067" t="n">
         <v>618359</v>
@@ -31341,7 +31341,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.37287497520447</v>
+        <v>2.37287521362305</v>
       </c>
       <c r="H1068" t="n">
         <v>448476</v>
@@ -31515,7 +31515,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.27346515655518</v>
+        <v>2.27346539497375</v>
       </c>
       <c r="H1074" t="n">
         <v>1007522</v>
@@ -31602,7 +31602,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.32533121109009</v>
+        <v>2.32533168792725</v>
       </c>
       <c r="H1077" t="n">
         <v>581790</v>
@@ -31631,7 +31631,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.32533121109009</v>
+        <v>2.32533168792725</v>
       </c>
       <c r="H1078" t="n">
         <v>244777</v>
@@ -31718,7 +31718,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.38584160804749</v>
+        <v>2.38584184646606</v>
       </c>
       <c r="H1081" t="n">
         <v>211093</v>
@@ -31892,7 +31892,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.0125572681427</v>
+        <v>3.01255750656128</v>
       </c>
       <c r="H1087" t="n">
         <v>431366</v>
@@ -31921,7 +31921,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.8267035484314</v>
+        <v>2.82670402526855</v>
       </c>
       <c r="H1088" t="n">
         <v>426909</v>
@@ -31950,7 +31950,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76187109947205</v>
+        <v>2.76187133789062</v>
       </c>
       <c r="H1089" t="n">
         <v>247451</v>
@@ -32066,7 +32066,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.80077075958252</v>
+        <v>2.80077052116394</v>
       </c>
       <c r="H1093" t="n">
         <v>653210</v>
@@ -32095,7 +32095,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.88289213180542</v>
+        <v>2.88289189338684</v>
       </c>
       <c r="H1094" t="n">
         <v>580788</v>
@@ -32182,7 +32182,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.90882539749146</v>
+        <v>2.90882515907288</v>
       </c>
       <c r="H1097" t="n">
         <v>933770</v>
@@ -32414,7 +32414,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1105" t="n">
         <v>296647</v>
@@ -32530,7 +32530,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H1109" t="n">
         <v>419779</v>
@@ -32559,7 +32559,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1110" t="n">
         <v>406018</v>
@@ -32617,7 +32617,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1112" t="n">
         <v>799814</v>
@@ -32675,7 +32675,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1114" t="n">
         <v>623601</v>
@@ -32733,7 +32733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1116" t="n">
         <v>711582</v>
@@ -32820,7 +32820,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.05232930183411</v>
+        <v>3.05232954025269</v>
       </c>
       <c r="H1119" t="n">
         <v>598569</v>
@@ -32907,7 +32907,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H1122" t="n">
         <v>416689</v>
@@ -32965,7 +32965,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1124" t="n">
         <v>865712</v>
@@ -32994,7 +32994,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1125" t="n">
         <v>737644</v>
@@ -33081,7 +33081,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1128" t="n">
         <v>1437783</v>
@@ -33139,7 +33139,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1130" t="n">
         <v>551818</v>
@@ -33197,7 +33197,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1132" t="n">
         <v>457229</v>
@@ -33284,7 +33284,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1135" t="n">
         <v>201971</v>
@@ -33342,7 +33342,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1137" t="n">
         <v>340693</v>
@@ -33574,7 +33574,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1145" t="n">
         <v>572690</v>
@@ -33603,7 +33603,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1146" t="n">
         <v>308166</v>
@@ -33661,7 +33661,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1148" t="n">
         <v>421416</v>
@@ -33690,7 +33690,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1149" t="n">
         <v>745765</v>
@@ -33806,7 +33806,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1153" t="n">
         <v>652281</v>
@@ -33864,7 +33864,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1155" t="n">
         <v>470106</v>
@@ -33980,7 +33980,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1159" t="n">
         <v>285234</v>
@@ -34009,7 +34009,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1160" t="n">
         <v>357619</v>
@@ -34212,7 +34212,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.06785202026367</v>
+        <v>2.06785178184509</v>
       </c>
       <c r="H1167" t="n">
         <v>769684</v>
@@ -34299,7 +34299,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1170" t="n">
         <v>1304798</v>
@@ -34386,7 +34386,7 @@
         <v>2.75</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1173" t="n">
         <v>558370</v>
@@ -34473,7 +34473,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1176" t="n">
         <v>577466</v>
@@ -34589,7 +34589,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1180" t="n">
         <v>786080</v>
@@ -34676,7 +34676,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.36903953552246</v>
+        <v>2.3690390586853</v>
       </c>
       <c r="H1183" t="n">
         <v>325503</v>
@@ -34821,7 +34821,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.41848802566528</v>
+        <v>2.41848826408386</v>
       </c>
       <c r="H1188" t="n">
         <v>545716</v>
@@ -34937,7 +34937,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1192" t="n">
         <v>185231</v>
@@ -34966,7 +34966,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1193" t="n">
         <v>83712</v>
@@ -34995,7 +34995,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1194" t="n">
         <v>412501</v>
@@ -35082,7 +35082,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1197" t="n">
         <v>313243</v>
@@ -35111,7 +35111,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.44995522499084</v>
+        <v>2.44995498657227</v>
       </c>
       <c r="H1198" t="n">
         <v>176835</v>
@@ -35169,7 +35169,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1200" t="n">
         <v>293884</v>
@@ -35198,7 +35198,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.22518873214722</v>
+        <v>2.22518849372864</v>
       </c>
       <c r="H1201" t="n">
         <v>531852</v>
@@ -35227,7 +35227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H1202" t="n">
         <v>270880</v>
@@ -35314,7 +35314,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1205" t="n">
         <v>348143</v>
@@ -35401,7 +35401,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.10381460189819</v>
+        <v>2.10381484031677</v>
       </c>
       <c r="H1208" t="n">
         <v>107234</v>
@@ -35517,7 +35517,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1212" t="n">
         <v>93722</v>
@@ -35662,7 +35662,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.05886125564575</v>
+        <v>2.05886149406433</v>
       </c>
       <c r="H1217" t="n">
         <v>224414</v>
@@ -35720,7 +35720,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1219" t="n">
         <v>149277</v>
@@ -35807,7 +35807,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1222" t="n">
         <v>485043</v>
@@ -35836,7 +35836,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1223" t="n">
         <v>120064</v>
@@ -35923,7 +35923,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.72620701789856</v>
+        <v>1.72620689868927</v>
       </c>
       <c r="H1226" t="n">
         <v>214567</v>
@@ -35981,7 +35981,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.7603714466095</v>
+        <v>1.76037156581879</v>
       </c>
       <c r="H1228" t="n">
         <v>328193</v>
@@ -36010,7 +36010,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.74059200286865</v>
+        <v>1.74059212207794</v>
       </c>
       <c r="H1229" t="n">
         <v>153292</v>
@@ -36097,7 +36097,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.96895480155945</v>
+        <v>1.96895503997803</v>
       </c>
       <c r="H1232" t="n">
         <v>500133</v>
@@ -36155,7 +36155,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.05886125564575</v>
+        <v>2.05886149406433</v>
       </c>
       <c r="H1234" t="n">
         <v>1282814</v>
@@ -36213,7 +36213,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H1236" t="n">
         <v>923518</v>
@@ -36242,7 +36242,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1237" t="n">
         <v>825488</v>
@@ -36474,7 +36474,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1245" t="n">
         <v>271716</v>
@@ -36532,7 +36532,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1247" t="n">
         <v>342197</v>
@@ -36619,7 +36619,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.63426375389099</v>
+        <v>2.63426399230957</v>
       </c>
       <c r="H1250" t="n">
         <v>225910</v>
@@ -36648,7 +36648,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1251" t="n">
         <v>180457</v>
@@ -36677,7 +36677,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1252" t="n">
         <v>102114</v>
@@ -36793,7 +36793,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1256" t="n">
         <v>104313</v>
@@ -36909,7 +36909,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H1260" t="n">
         <v>135727</v>
@@ -36938,7 +36938,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1261" t="n">
         <v>239717</v>
@@ -36967,7 +36967,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.67921710014343</v>
+        <v>2.67921733856201</v>
       </c>
       <c r="H1262" t="n">
         <v>314028</v>
@@ -37025,7 +37025,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1264" t="n">
         <v>175562</v>
@@ -37054,7 +37054,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H1265" t="n">
         <v>386859</v>
@@ -37170,7 +37170,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1269" t="n">
         <v>42041</v>
@@ -37257,7 +37257,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1272" t="n">
         <v>37811</v>
@@ -37315,7 +37315,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H1274" t="n">
         <v>258847</v>
@@ -37373,7 +37373,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1276" t="n">
         <v>70248</v>
@@ -37431,7 +37431,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1278" t="n">
         <v>47586</v>
@@ -37518,7 +37518,7 @@
         <v>2.75</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1281" t="n">
         <v>93460</v>
@@ -37605,7 +37605,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1284" t="n">
         <v>177140</v>
@@ -37634,7 +37634,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.32408618927002</v>
+        <v>2.32408595085144</v>
       </c>
       <c r="H1285" t="n">
         <v>150077</v>
@@ -37692,7 +37692,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1287" t="n">
         <v>225233</v>
@@ -37721,7 +37721,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1288" t="n">
         <v>121175</v>
@@ -37750,7 +37750,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.25665616989136</v>
+        <v>2.25665593147278</v>
       </c>
       <c r="H1289" t="n">
         <v>176074</v>
@@ -37808,7 +37808,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H1291" t="n">
         <v>77258</v>
@@ -37837,7 +37837,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.27913284301758</v>
+        <v>2.279132604599</v>
       </c>
       <c r="H1292" t="n">
         <v>82580</v>
@@ -37866,7 +37866,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1293" t="n">
         <v>141021</v>
@@ -37924,7 +37924,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1295" t="n">
         <v>330093</v>
@@ -37982,7 +37982,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1297" t="n">
         <v>315280</v>
@@ -38359,7 +38359,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1310" t="n">
         <v>245602</v>
@@ -38388,7 +38388,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.62077784538269</v>
+        <v>2.62077760696411</v>
       </c>
       <c r="H1311" t="n">
         <v>260834</v>
@@ -38620,7 +38620,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1319" t="n">
         <v>494591</v>
@@ -38823,7 +38823,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1326" t="n">
         <v>387648</v>
@@ -38852,7 +38852,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1327" t="n">
         <v>290870</v>
@@ -38910,7 +38910,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1329" t="n">
         <v>270547</v>
@@ -39084,7 +39084,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1335" t="n">
         <v>570248</v>
@@ -39142,7 +39142,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1337" t="n">
         <v>421991</v>
@@ -39200,7 +39200,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1339" t="n">
         <v>288534</v>
@@ -39258,7 +39258,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1341" t="n">
         <v>201348</v>
@@ -39403,7 +39403,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.5153489112854</v>
+        <v>3.51534867286682</v>
       </c>
       <c r="H1346" t="n">
         <v>761891</v>
@@ -39490,7 +39490,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.30406785011292</v>
+        <v>3.30406808853149</v>
       </c>
       <c r="H1349" t="n">
         <v>969567</v>
@@ -39519,7 +39519,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1350" t="n">
         <v>373273</v>
@@ -39577,7 +39577,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.34003067016602</v>
+        <v>3.34003043174744</v>
       </c>
       <c r="H1352" t="n">
         <v>697789</v>
@@ -39635,7 +39635,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1354" t="n">
         <v>211729</v>
@@ -39780,7 +39780,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1359" t="n">
         <v>259201</v>
@@ -39809,7 +39809,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1360" t="n">
         <v>491649</v>
@@ -39896,7 +39896,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1363" t="n">
         <v>209513</v>
@@ -39925,7 +39925,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1364" t="n">
         <v>149981</v>
@@ -39954,7 +39954,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.18718934059143</v>
+        <v>3.18718957901001</v>
       </c>
       <c r="H1365" t="n">
         <v>312867</v>
@@ -40041,7 +40041,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1368" t="n">
         <v>97665</v>
@@ -40070,7 +40070,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1369" t="n">
         <v>201385</v>
@@ -40128,7 +40128,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1371" t="n">
         <v>103425</v>
@@ -40186,7 +40186,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1373" t="n">
         <v>376159</v>
@@ -40215,7 +40215,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1374" t="n">
         <v>159196</v>
@@ -40244,7 +40244,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.30406785011292</v>
+        <v>3.30406808853149</v>
       </c>
       <c r="H1375" t="n">
         <v>235034</v>
@@ -40331,7 +40331,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.39847016334534</v>
+        <v>3.39846992492676</v>
       </c>
       <c r="H1378" t="n">
         <v>431404</v>
@@ -40534,7 +40534,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.4434232711792</v>
+        <v>3.44342303276062</v>
       </c>
       <c r="H1385" t="n">
         <v>452765</v>
@@ -40679,7 +40679,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.4299373626709</v>
+        <v>3.42993712425232</v>
       </c>
       <c r="H1390" t="n">
         <v>179232</v>
@@ -40708,7 +40708,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.3535168170929</v>
+        <v>3.35351657867432</v>
       </c>
       <c r="H1391" t="n">
         <v>370117</v>
@@ -40766,7 +40766,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.3939745426178</v>
+        <v>3.39397478103638</v>
       </c>
       <c r="H1393" t="n">
         <v>143579</v>
@@ -40853,7 +40853,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.12875032424927</v>
+        <v>3.12875008583069</v>
       </c>
       <c r="H1396" t="n">
         <v>334946</v>
@@ -40882,7 +40882,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1397" t="n">
         <v>144695</v>
@@ -40940,7 +40940,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1399" t="n">
         <v>485206</v>
@@ -40969,7 +40969,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1400" t="n">
         <v>282685</v>
@@ -41085,7 +41085,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.14673161506653</v>
+        <v>3.14673137664795</v>
       </c>
       <c r="H1404" t="n">
         <v>316463</v>
@@ -41172,7 +41172,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1407" t="n">
         <v>191794</v>
@@ -41288,7 +41288,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1411" t="n">
         <v>178077</v>
@@ -41375,7 +41375,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.06132006645203</v>
+        <v>3.06132030487061</v>
       </c>
       <c r="H1414" t="n">
         <v>102936</v>
@@ -41491,7 +41491,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H1418" t="n">
         <v>281418</v>
@@ -41607,7 +41607,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1422" t="n">
         <v>157214</v>
@@ -41665,7 +41665,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12875032424927</v>
+        <v>3.12875008583069</v>
       </c>
       <c r="H1424" t="n">
         <v>691356</v>
@@ -41723,7 +41723,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1426" t="n">
         <v>186710</v>
@@ -41781,7 +41781,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.14673161506653</v>
+        <v>3.14673137664795</v>
       </c>
       <c r="H1428" t="n">
         <v>105063</v>
@@ -41839,7 +41839,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1430" t="n">
         <v>78000</v>
@@ -41955,7 +41955,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1434" t="n">
         <v>227674</v>
@@ -42071,7 +42071,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.16920828819275</v>
+        <v>3.16920804977417</v>
       </c>
       <c r="H1438" t="n">
         <v>343066</v>
@@ -42129,7 +42129,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.40746068954468</v>
+        <v>3.4074604511261</v>
       </c>
       <c r="H1440" t="n">
         <v>1135545</v>
@@ -42245,7 +42245,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1444" t="n">
         <v>270255</v>
@@ -42274,7 +42274,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.19618010520935</v>
+        <v>3.19618034362793</v>
       </c>
       <c r="H1445" t="n">
         <v>323942</v>
@@ -42303,7 +42303,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.17819881439209</v>
+        <v>3.17819905281067</v>
       </c>
       <c r="H1446" t="n">
         <v>179701</v>
@@ -42361,7 +42361,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1448" t="n">
         <v>105950</v>
@@ -42506,7 +42506,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1453" t="n">
         <v>77312</v>
@@ -42593,7 +42593,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1456" t="n">
         <v>259895</v>
@@ -42738,7 +42738,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1461" t="n">
         <v>224339</v>
@@ -42854,7 +42854,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.31755423545837</v>
+        <v>3.31755399703979</v>
       </c>
       <c r="H1465" t="n">
         <v>566409</v>
@@ -42941,7 +42941,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.21865677833557</v>
+        <v>3.21865701675415</v>
       </c>
       <c r="H1468" t="n">
         <v>194799</v>
@@ -42999,7 +42999,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H1470" t="n">
         <v>332426</v>
@@ -43028,7 +43028,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.40746068954468</v>
+        <v>3.4074604511261</v>
       </c>
       <c r="H1471" t="n">
         <v>889735</v>
@@ -43173,7 +43173,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1476" t="n">
         <v>261906</v>
@@ -43202,7 +43202,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.30856370925903</v>
+        <v>3.30856347084045</v>
       </c>
       <c r="H1477" t="n">
         <v>707219</v>
@@ -43231,7 +43231,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1478" t="n">
         <v>216638</v>
@@ -43434,7 +43434,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.39847016334534</v>
+        <v>3.39846992492676</v>
       </c>
       <c r="H1485" t="n">
         <v>895572</v>
@@ -43579,7 +43579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.23663806915283</v>
+        <v>3.23663783073425</v>
       </c>
       <c r="H1490" t="n">
         <v>563647</v>
@@ -43608,7 +43608,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.26361036300659</v>
+        <v>3.26361012458801</v>
       </c>
       <c r="H1491" t="n">
         <v>317811</v>
@@ -43637,7 +43637,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1492" t="n">
         <v>136121</v>
@@ -43666,7 +43666,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.27260088920593</v>
+        <v>3.27260065078735</v>
       </c>
       <c r="H1493" t="n">
         <v>520926</v>
@@ -43724,7 +43724,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.26810526847839</v>
+        <v>3.26810550689697</v>
       </c>
       <c r="H1495" t="n">
         <v>216431</v>
@@ -43782,7 +43782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.16471266746521</v>
+        <v>3.16471290588379</v>
       </c>
       <c r="H1497" t="n">
         <v>299328</v>
@@ -43869,7 +43869,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1500" t="n">
         <v>282544</v>
@@ -43927,7 +43927,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1502" t="n">
         <v>157789</v>
@@ -44072,7 +44072,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1507" t="n">
         <v>146234</v>
@@ -44159,7 +44159,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1510" t="n">
         <v>454951</v>
@@ -44217,7 +44217,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.07930159568787</v>
+        <v>3.07930135726929</v>
       </c>
       <c r="H1512" t="n">
         <v>70420</v>
@@ -44246,7 +44246,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.07031059265137</v>
+        <v>3.07031083106995</v>
       </c>
       <c r="H1513" t="n">
         <v>64236</v>
@@ -44333,7 +44333,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1516" t="n">
         <v>46706</v>
@@ -44391,7 +44391,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1518" t="n">
         <v>80257</v>
@@ -44420,7 +44420,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.92646026611328</v>
+        <v>2.92646050453186</v>
       </c>
       <c r="H1519" t="n">
         <v>260816</v>
@@ -44507,7 +44507,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.10177826881409</v>
+        <v>3.10177803039551</v>
       </c>
       <c r="H1522" t="n">
         <v>117521</v>
@@ -44594,7 +44594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.05682516098022</v>
+        <v>3.05682492256165</v>
       </c>
       <c r="H1525" t="n">
         <v>203308</v>
@@ -44681,7 +44681,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.18269419670105</v>
+        <v>3.18269395828247</v>
       </c>
       <c r="H1528" t="n">
         <v>282637</v>
@@ -44739,7 +44739,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1530" t="n">
         <v>198774</v>
@@ -44768,7 +44768,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1531" t="n">
         <v>108386</v>
@@ -44797,7 +44797,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1532" t="n">
         <v>305086</v>
@@ -44826,7 +44826,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.0118715763092</v>
+        <v>3.01187133789062</v>
       </c>
       <c r="H1533" t="n">
         <v>98457</v>
@@ -44942,7 +44942,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09728264808655</v>
+        <v>3.09728288650513</v>
       </c>
       <c r="H1537" t="n">
         <v>333813</v>
@@ -45029,7 +45029,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.02985262870789</v>
+        <v>3.02985286712646</v>
       </c>
       <c r="H1540" t="n">
         <v>325007</v>
@@ -45087,7 +45087,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1542" t="n">
         <v>171004</v>
@@ -45174,7 +45174,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1545" t="n">
         <v>356062</v>
@@ -45319,7 +45319,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1550" t="n">
         <v>95039</v>
@@ -45348,7 +45348,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1551" t="n">
         <v>58369</v>
@@ -45667,7 +45667,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.9219651222229</v>
+        <v>2.92196488380432</v>
       </c>
       <c r="H1562" t="n">
         <v>221866</v>
@@ -45783,7 +45783,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1566" t="n">
         <v>252910</v>
@@ -45870,7 +45870,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1569" t="n">
         <v>254117</v>
@@ -45899,7 +45899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1570" t="n">
         <v>191841</v>
@@ -45928,7 +45928,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1571" t="n">
         <v>363249</v>
@@ -45957,7 +45957,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H1572" t="n">
         <v>482762</v>
@@ -45986,7 +45986,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H1573" t="n">
         <v>183733</v>
@@ -46015,7 +46015,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1574" t="n">
         <v>252389</v>
@@ -46160,7 +46160,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1579" t="n">
         <v>233943</v>
@@ -46363,7 +46363,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1586" t="n">
         <v>52574</v>
@@ -46479,7 +46479,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.93095564842224</v>
+        <v>2.93095541000366</v>
       </c>
       <c r="H1590" t="n">
         <v>139047</v>
@@ -46798,7 +46798,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H1601" t="n">
         <v>81169</v>
@@ -46856,7 +46856,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05682516098022</v>
+        <v>3.05682492256165</v>
       </c>
       <c r="H1603" t="n">
         <v>48152</v>
@@ -46885,7 +46885,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.00737595558167</v>
+        <v>3.00737643241882</v>
       </c>
       <c r="H1604" t="n">
         <v>37041</v>
@@ -46972,7 +46972,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1607" t="n">
         <v>75556</v>
@@ -47001,7 +47001,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1608" t="n">
         <v>68959</v>
@@ -47030,7 +47030,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.93994617462158</v>
+        <v>2.93994641304016</v>
       </c>
       <c r="H1609" t="n">
         <v>26440</v>
@@ -47059,7 +47059,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>2.91746950149536</v>
+        <v>2.91746973991394</v>
       </c>
       <c r="H1610" t="n">
         <v>39637</v>
@@ -47088,7 +47088,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H1611" t="n">
         <v>30490</v>
@@ -47262,7 +47262,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1617" t="n">
         <v>40710</v>
@@ -47378,7 +47378,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.8365535736084</v>
+        <v>2.83655381202698</v>
       </c>
       <c r="H1621" t="n">
         <v>41778</v>
@@ -47552,7 +47552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1627" t="n">
         <v>22631</v>
@@ -47639,7 +47639,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.9624228477478</v>
+        <v>2.96242308616638</v>
       </c>
       <c r="H1630" t="n">
         <v>32369</v>
@@ -47668,7 +47668,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.93545079231262</v>
+        <v>2.9354510307312</v>
       </c>
       <c r="H1631" t="n">
         <v>36859</v>
@@ -47726,7 +47726,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.97590899467468</v>
+        <v>2.9759087562561</v>
       </c>
       <c r="H1633" t="n">
         <v>30711</v>
@@ -47929,7 +47929,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1640" t="n">
         <v>49301</v>
@@ -48016,7 +48016,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1643" t="n">
         <v>56599</v>
@@ -48045,7 +48045,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1644" t="n">
         <v>97311</v>
@@ -48132,7 +48132,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1647" t="n">
         <v>12343</v>
@@ -48161,7 +48161,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1648" t="n">
         <v>9398</v>
@@ -48190,7 +48190,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1649" t="n">
         <v>11528</v>
@@ -48277,7 +48277,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1652" t="n">
         <v>23575</v>
@@ -48335,7 +48335,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.61178684234619</v>
+        <v>2.61178731918335</v>
       </c>
       <c r="H1654" t="n">
         <v>61583</v>
@@ -48393,7 +48393,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1656" t="n">
         <v>57134</v>
@@ -48422,7 +48422,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1657" t="n">
         <v>67892</v>
@@ -48538,7 +48538,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H1661" t="n">
         <v>11843</v>
@@ -48741,7 +48741,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H1668" t="n">
         <v>19913</v>
@@ -48770,7 +48770,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1669" t="n">
         <v>22730</v>
@@ -48799,7 +48799,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H1670" t="n">
         <v>30918</v>
@@ -48973,7 +48973,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1676" t="n">
         <v>7623</v>
@@ -49002,7 +49002,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1677" t="n">
         <v>20070</v>
@@ -49118,7 +49118,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1681" t="n">
         <v>7460</v>
@@ -49292,7 +49292,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1687" t="n">
         <v>16114</v>
@@ -49321,7 +49321,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.79160022735596</v>
+        <v>2.79160046577454</v>
       </c>
       <c r="H1688" t="n">
         <v>42783</v>
@@ -49350,7 +49350,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1689" t="n">
         <v>16051</v>
@@ -49553,7 +49553,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.80958151817322</v>
+        <v>2.8095817565918</v>
       </c>
       <c r="H1696" t="n">
         <v>6294</v>
@@ -49669,7 +49669,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1700" t="n">
         <v>7315</v>
@@ -49959,7 +49959,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1710" t="n">
         <v>25283</v>
@@ -50075,7 +50075,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.87251615524292</v>
+        <v>2.8725163936615</v>
       </c>
       <c r="H1714" t="n">
         <v>12820</v>
@@ -50104,7 +50104,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1715" t="n">
         <v>7468</v>
@@ -50191,7 +50191,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1718" t="n">
         <v>6099</v>
@@ -50249,7 +50249,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.80958151817322</v>
+        <v>2.8095817565918</v>
       </c>
       <c r="H1720" t="n">
         <v>4689</v>
@@ -50365,7 +50365,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1724" t="n">
         <v>2572</v>
@@ -50423,7 +50423,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1726" t="n">
         <v>6840</v>
@@ -50452,7 +50452,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1727" t="n">
         <v>6948</v>
@@ -50510,7 +50510,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1729" t="n">
         <v>2431</v>
@@ -50771,7 +50771,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1738" t="n">
         <v>8892</v>
@@ -50800,7 +50800,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1739" t="n">
         <v>31663</v>
@@ -50829,7 +50829,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1740" t="n">
         <v>6242</v>
@@ -50974,7 +50974,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.863525390625</v>
+        <v>2.86352562904358</v>
       </c>
       <c r="H1745" t="n">
         <v>39405</v>
@@ -51003,7 +51003,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.86802101135254</v>
+        <v>2.86802077293396</v>
       </c>
       <c r="H1746" t="n">
         <v>144199</v>
@@ -51090,7 +51090,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.78710508346558</v>
+        <v>2.787104845047</v>
       </c>
       <c r="H1749" t="n">
         <v>32195</v>
@@ -51264,7 +51264,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1755" t="n">
         <v>35299</v>
@@ -51322,7 +51322,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1757" t="n">
         <v>803</v>
@@ -51351,7 +51351,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1758" t="n">
         <v>6307</v>
@@ -51409,7 +51409,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1760" t="n">
         <v>40934</v>
@@ -51438,7 +51438,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.77811431884766</v>
+        <v>2.77811408042908</v>
       </c>
       <c r="H1761" t="n">
         <v>129660</v>
@@ -51583,7 +51583,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72866559028625</v>
+        <v>2.72866582870483</v>
       </c>
       <c r="H1766" t="n">
         <v>806</v>
@@ -51612,7 +51612,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1767" t="n">
         <v>6388</v>
@@ -51670,7 +51670,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.71517992019653</v>
+        <v>2.71517968177795</v>
       </c>
       <c r="H1769" t="n">
         <v>6051</v>
@@ -51728,7 +51728,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1771" t="n">
         <v>5520</v>
@@ -51757,7 +51757,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H1772" t="n">
         <v>34016</v>
@@ -51786,7 +51786,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1773" t="n">
         <v>53791</v>
@@ -51844,7 +51844,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1775" t="n">
         <v>16855</v>
@@ -51902,7 +51902,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.64325451850891</v>
+        <v>2.64325428009033</v>
       </c>
       <c r="H1777" t="n">
         <v>6473</v>
@@ -51960,7 +51960,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.63875889778137</v>
+        <v>2.63875913619995</v>
       </c>
       <c r="H1779" t="n">
         <v>10239</v>
@@ -52047,7 +52047,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.60729193687439</v>
+        <v>2.60729169845581</v>
       </c>
       <c r="H1782" t="n">
         <v>24341</v>
@@ -52076,7 +52076,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1783" t="n">
         <v>21408</v>
@@ -52105,7 +52105,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1784" t="n">
         <v>29962</v>
@@ -52134,7 +52134,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1785" t="n">
         <v>32553</v>
@@ -52163,7 +52163,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1786" t="n">
         <v>40368</v>
@@ -52395,7 +52395,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.76912355422974</v>
+        <v>2.76912379264832</v>
       </c>
       <c r="H1794" t="n">
         <v>11490</v>
@@ -52482,7 +52482,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.74664688110352</v>
+        <v>2.74664735794067</v>
       </c>
       <c r="H1797" t="n">
         <v>11787</v>
@@ -52598,7 +52598,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.67921710014343</v>
+        <v>2.67921733856201</v>
       </c>
       <c r="H1801" t="n">
         <v>87935</v>
@@ -52627,7 +52627,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1802" t="n">
         <v>28436</v>
@@ -52656,7 +52656,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1803" t="n">
         <v>33741</v>
@@ -52685,7 +52685,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.71967506408691</v>
+        <v>2.71967530250549</v>
       </c>
       <c r="H1804" t="n">
         <v>38789</v>
@@ -52801,7 +52801,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.65224528312683</v>
+        <v>2.65224504470825</v>
       </c>
       <c r="H1808" t="n">
         <v>57535</v>
@@ -52830,7 +52830,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.65674018859863</v>
+        <v>2.65674042701721</v>
       </c>
       <c r="H1809" t="n">
         <v>43213</v>
@@ -52888,7 +52888,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.63426375389099</v>
+        <v>2.63426399230957</v>
       </c>
       <c r="H1811" t="n">
         <v>109757</v>
@@ -53033,7 +53033,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.61178684234619</v>
+        <v>2.61178731918335</v>
       </c>
       <c r="H1816" t="n">
         <v>61184</v>
@@ -53120,7 +53120,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.65674018859863</v>
+        <v>2.65674042701721</v>
       </c>
       <c r="H1819" t="n">
         <v>41062</v>
@@ -53439,7 +53439,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1830" t="n">
         <v>33338</v>
@@ -53468,7 +53468,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.70618891716003</v>
+        <v>2.70618915557861</v>
       </c>
       <c r="H1831" t="n">
         <v>16249</v>
@@ -53526,7 +53526,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.70169377326965</v>
+        <v>2.70169401168823</v>
       </c>
       <c r="H1833" t="n">
         <v>141369</v>
@@ -53613,7 +53613,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.60279631614685</v>
+        <v>2.60279655456543</v>
       </c>
       <c r="H1836" t="n">
         <v>20616</v>
@@ -53671,7 +53671,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H1838" t="n">
         <v>16332</v>
@@ -53700,7 +53700,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H1839" t="n">
         <v>33738</v>
@@ -53729,7 +53729,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H1840" t="n">
         <v>52048</v>
@@ -53787,7 +53787,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1842" t="n">
         <v>78570</v>
@@ -53816,7 +53816,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.42298340797424</v>
+        <v>2.42298316955566</v>
       </c>
       <c r="H1843" t="n">
         <v>16387</v>
@@ -53845,7 +53845,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.41848802566528</v>
+        <v>2.41848826408386</v>
       </c>
       <c r="H1844" t="n">
         <v>24792</v>
@@ -53874,7 +53874,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1845" t="n">
         <v>50260</v>
@@ -53961,7 +53961,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.41399264335632</v>
+        <v>2.41399240493774</v>
       </c>
       <c r="H1848" t="n">
         <v>92588</v>
@@ -54077,7 +54077,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H1852" t="n">
         <v>30308</v>
@@ -54251,7 +54251,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.48142242431641</v>
+        <v>2.48142266273499</v>
       </c>
       <c r="H1858" t="n">
         <v>34367</v>
@@ -54338,7 +54338,7 @@
         <v>2.75</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H1861" t="n">
         <v>22492</v>
@@ -54541,7 +54541,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1868" t="n">
         <v>30523</v>
@@ -54570,7 +54570,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1869" t="n">
         <v>46271</v>
@@ -54628,7 +54628,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H1871" t="n">
         <v>64411</v>
@@ -54715,7 +54715,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1874" t="n">
         <v>35540</v>
@@ -54889,7 +54889,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1880" t="n">
         <v>25387</v>
@@ -54918,7 +54918,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.37353467941284</v>
+        <v>2.37353491783142</v>
       </c>
       <c r="H1881" t="n">
         <v>10834</v>
@@ -54947,7 +54947,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36004877090454</v>
+        <v>2.36004853248596</v>
       </c>
       <c r="H1882" t="n">
         <v>12443</v>
@@ -55034,7 +55034,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H1885" t="n">
         <v>15478</v>
@@ -55121,7 +55121,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H1888" t="n">
         <v>42331</v>
@@ -55208,7 +55208,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H1891" t="n">
         <v>27810</v>
@@ -55237,7 +55237,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1892" t="n">
         <v>91013</v>
@@ -55266,7 +55266,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.21170282363892</v>
+        <v>2.21170258522034</v>
       </c>
       <c r="H1893" t="n">
         <v>79197</v>
@@ -55353,7 +55353,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.1892261505127</v>
+        <v>2.18922591209412</v>
       </c>
       <c r="H1896" t="n">
         <v>155188</v>
@@ -55498,7 +55498,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.23417949676514</v>
+        <v>2.23417925834656</v>
       </c>
       <c r="H1901" t="n">
         <v>35105</v>
@@ -55527,7 +55527,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.23417949676514</v>
+        <v>2.23417925834656</v>
       </c>
       <c r="H1902" t="n">
         <v>24904</v>
@@ -55556,7 +55556,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H1903" t="n">
         <v>26567</v>
@@ -55614,7 +55614,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.1892261505127</v>
+        <v>2.18922591209412</v>
       </c>
       <c r="H1905" t="n">
         <v>43527</v>
@@ -55701,7 +55701,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18473052978516</v>
+        <v>2.18473076820374</v>
       </c>
       <c r="H1908" t="n">
         <v>23797</v>
@@ -55875,7 +55875,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13977742195129</v>
+        <v>2.13977766036987</v>
       </c>
       <c r="H1914" t="n">
         <v>32974</v>
@@ -55904,7 +55904,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.13977742195129</v>
+        <v>2.13977766036987</v>
       </c>
       <c r="H1915" t="n">
         <v>39294</v>
@@ -55962,7 +55962,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10831022262573</v>
+        <v>2.10830998420715</v>
       </c>
       <c r="H1917" t="n">
         <v>66793</v>
@@ -55991,7 +55991,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1918" t="n">
         <v>162703</v>
@@ -56020,7 +56020,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1919" t="n">
         <v>31507</v>
@@ -56049,7 +56049,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.11280512809753</v>
+        <v>2.11280536651611</v>
       </c>
       <c r="H1920" t="n">
         <v>54591</v>
@@ -56078,7 +56078,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H1921" t="n">
         <v>23738</v>
@@ -56194,7 +56194,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.11280512809753</v>
+        <v>2.11280536651611</v>
       </c>
       <c r="H1925" t="n">
         <v>50158</v>
@@ -56252,7 +56252,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1927" t="n">
         <v>488603</v>
@@ -56281,7 +56281,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H1928" t="n">
         <v>188271</v>
@@ -56368,7 +56368,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.10831022262573</v>
+        <v>2.10830998420715</v>
       </c>
       <c r="H1931" t="n">
         <v>87426</v>
@@ -56426,7 +56426,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H1933" t="n">
         <v>149266</v>
@@ -56455,7 +56455,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H1934" t="n">
         <v>41591</v>
@@ -56629,7 +56629,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.99143135547638</v>
+        <v>1.99143147468567</v>
       </c>
       <c r="H1940" t="n">
         <v>43318</v>
@@ -56658,7 +56658,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.97794532775879</v>
+        <v>1.97794544696808</v>
       </c>
       <c r="H1941" t="n">
         <v>91732</v>
@@ -56687,7 +56687,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.95996427536011</v>
+        <v>1.9599643945694</v>
       </c>
       <c r="H1942" t="n">
         <v>38211</v>
@@ -56745,7 +56745,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1944" t="n">
-        <v>1.91950619220734</v>
+        <v>1.91950607299805</v>
       </c>
       <c r="H1944" t="n">
         <v>83068</v>
@@ -56774,7 +56774,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.91501080989838</v>
+        <v>1.91501104831696</v>
       </c>
       <c r="H1945" t="n">
         <v>34096</v>
@@ -56832,7 +56832,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.93299221992493</v>
+        <v>1.93299210071564</v>
       </c>
       <c r="H1947" t="n">
         <v>69631</v>
@@ -56861,7 +56861,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.91950619220734</v>
+        <v>1.91950607299805</v>
       </c>
       <c r="H1948" t="n">
         <v>33793</v>
@@ -56890,7 +56890,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.94198298454285</v>
+        <v>1.94198286533356</v>
       </c>
       <c r="H1949" t="n">
         <v>42050</v>
@@ -57035,7 +57035,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.98693609237671</v>
+        <v>1.98693597316742</v>
       </c>
       <c r="H1954" t="n">
         <v>36120</v>
@@ -57064,7 +57064,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1955" t="n">
         <v>23899</v>
@@ -57093,7 +57093,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.97345006465912</v>
+        <v>1.97345018386841</v>
       </c>
       <c r="H1956" t="n">
         <v>33630</v>
@@ -57122,7 +57122,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.93299221992493</v>
+        <v>1.93299210071564</v>
       </c>
       <c r="H1957" t="n">
         <v>28970</v>
@@ -57151,7 +57151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.94647812843323</v>
+        <v>1.94647836685181</v>
       </c>
       <c r="H1958" t="n">
         <v>84119</v>
@@ -57238,7 +57238,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.95996427536011</v>
+        <v>1.9599643945694</v>
       </c>
       <c r="H1961" t="n">
         <v>18238</v>
@@ -57296,7 +57296,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.96445953845978</v>
+        <v>1.9644593000412</v>
       </c>
       <c r="H1963" t="n">
         <v>12830</v>
@@ -57325,7 +57325,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.91051554679871</v>
+        <v>1.91051542758942</v>
       </c>
       <c r="H1964" t="n">
         <v>69130</v>
@@ -57354,7 +57354,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1965" t="n">
         <v>34147</v>
@@ -57383,7 +57383,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1966" t="n">
         <v>38443</v>
@@ -57412,7 +57412,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.89702951908112</v>
+        <v>1.89702939987183</v>
       </c>
       <c r="H1967" t="n">
         <v>37018</v>
@@ -57441,7 +57441,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.90602016448975</v>
+        <v>1.90602004528046</v>
       </c>
       <c r="H1968" t="n">
         <v>36266</v>
@@ -57557,7 +57557,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.80262780189514</v>
+        <v>1.80262768268585</v>
       </c>
       <c r="H1972" t="n">
         <v>64312</v>
@@ -57673,7 +57673,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.69923508167267</v>
+        <v>1.69923496246338</v>
       </c>
       <c r="H1976" t="n">
         <v>117309</v>
@@ -57789,7 +57789,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.7208126783371</v>
+        <v>1.72081255912781</v>
       </c>
       <c r="H1980" t="n">
         <v>87294</v>
@@ -57818,7 +57818,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.73699569702148</v>
+        <v>1.73699581623077</v>
       </c>
       <c r="H1981" t="n">
         <v>34395</v>
@@ -57847,7 +57847,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.73879384994507</v>
+        <v>1.73879396915436</v>
       </c>
       <c r="H1982" t="n">
         <v>22757</v>
@@ -57905,7 +57905,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.7208126783371</v>
+        <v>1.72081255912781</v>
       </c>
       <c r="H1984" t="n">
         <v>28300</v>
@@ -57934,7 +57934,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.6956387758255</v>
+        <v>1.69563889503479</v>
       </c>
       <c r="H1985" t="n">
         <v>50617</v>
@@ -57963,7 +57963,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.73519766330719</v>
+        <v>1.7351975440979</v>
       </c>
       <c r="H1986" t="n">
         <v>29283</v>
@@ -58079,7 +58079,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.67406105995178</v>
+        <v>1.67406117916107</v>
       </c>
       <c r="H1990" t="n">
         <v>102289</v>
@@ -58108,7 +58108,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.62910795211792</v>
+        <v>1.62910783290863</v>
       </c>
       <c r="H1991" t="n">
         <v>48919</v>
@@ -58137,7 +58137,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.62910795211792</v>
+        <v>1.62910783290863</v>
       </c>
       <c r="H1992" t="n">
         <v>49727</v>
@@ -58282,7 +58282,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.76576590538025</v>
+        <v>1.76576578617096</v>
       </c>
       <c r="H1997" t="n">
         <v>189034</v>
@@ -58311,7 +58311,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.97794532775879</v>
+        <v>1.97794544696808</v>
       </c>
       <c r="H1998" t="n">
         <v>498538</v>
@@ -58369,7 +58369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.94198298454285</v>
+        <v>1.94198286533356</v>
       </c>
       <c r="H2000" t="n">
         <v>116001</v>
@@ -58398,7 +58398,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.95546865463257</v>
+        <v>1.95546877384186</v>
       </c>
       <c r="H2001" t="n">
         <v>126955</v>
@@ -58427,7 +58427,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.04987072944641</v>
+        <v>2.04987096786499</v>
       </c>
       <c r="H2002" t="n">
         <v>631965</v>
@@ -58543,7 +58543,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.20720720291138</v>
+        <v>2.20720744132996</v>
       </c>
       <c r="H2006" t="n">
         <v>357320</v>
@@ -58601,7 +58601,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.17124485969543</v>
+        <v>2.17124462127686</v>
       </c>
       <c r="H2008" t="n">
         <v>108999</v>
@@ -58717,7 +58717,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.14427280426025</v>
+        <v>2.14427256584167</v>
       </c>
       <c r="H2012" t="n">
         <v>86443</v>
@@ -58891,7 +58891,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H2018" t="n">
         <v>141366</v>
@@ -58920,7 +58920,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.22069334983826</v>
+        <v>2.22069358825684</v>
       </c>
       <c r="H2019" t="n">
         <v>87674</v>
@@ -58949,7 +58949,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.2296838760376</v>
+        <v>2.22968411445618</v>
       </c>
       <c r="H2020" t="n">
         <v>31700</v>
@@ -59036,7 +59036,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.30160927772522</v>
+        <v>2.30160903930664</v>
       </c>
       <c r="H2023" t="n">
         <v>74875</v>
@@ -59094,7 +59094,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.31059980392456</v>
+        <v>2.31060004234314</v>
       </c>
       <c r="H2025" t="n">
         <v>147807</v>
@@ -59123,7 +59123,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H2026" t="n">
         <v>69262</v>
@@ -59152,7 +59152,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2027" t="n">
         <v>94806</v>
@@ -59181,7 +59181,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.30160927772522</v>
+        <v>2.30160903930664</v>
       </c>
       <c r="H2028" t="n">
         <v>97929</v>
@@ -59210,7 +59210,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.27463722229004</v>
+        <v>2.27463746070862</v>
       </c>
       <c r="H2029" t="n">
         <v>51922</v>
@@ -59268,7 +59268,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H2031" t="n">
         <v>46955</v>
@@ -59297,7 +59297,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.3150954246521</v>
+        <v>2.31509518623352</v>
       </c>
       <c r="H2032" t="n">
         <v>153650</v>
@@ -59326,7 +59326,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.3195903301239</v>
+        <v>2.31959056854248</v>
       </c>
       <c r="H2033" t="n">
         <v>278546</v>
@@ -59355,7 +59355,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.34656262397766</v>
+        <v>2.34656238555908</v>
       </c>
       <c r="H2034" t="n">
         <v>73184</v>
@@ -59384,7 +59384,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.36454391479492</v>
+        <v>2.3645441532135</v>
       </c>
       <c r="H2035" t="n">
         <v>142671</v>
@@ -59413,7 +59413,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.48591804504395</v>
+        <v>2.48591780662537</v>
       </c>
       <c r="H2036" t="n">
         <v>796398</v>
@@ -59442,7 +59442,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H2037" t="n">
         <v>644230</v>
@@ -59471,7 +59471,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H2038" t="n">
         <v>348092</v>
@@ -59529,7 +59529,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.54885244369507</v>
+        <v>2.54885268211365</v>
       </c>
       <c r="H2040" t="n">
         <v>161510</v>
@@ -59616,7 +59616,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H2043" t="n">
         <v>255174</v>
@@ -59790,7 +59790,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.51738524436951</v>
+        <v>2.51738500595093</v>
       </c>
       <c r="H2049" t="n">
         <v>219618</v>
@@ -59819,7 +59819,7 @@
         <v>2.75</v>
       </c>
       <c r="G2050" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H2050" t="n">
         <v>184251</v>
@@ -59906,7 +59906,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.53986191749573</v>
+        <v>2.53986167907715</v>
       </c>
       <c r="H2053" t="n">
         <v>97873</v>
@@ -59964,7 +59964,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.59830141067505</v>
+        <v>2.59830117225647</v>
       </c>
       <c r="H2055" t="n">
         <v>128780</v>
@@ -59993,7 +59993,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2056" t="n">
         <v>80880</v>
@@ -60080,7 +60080,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.50839447975159</v>
+        <v>2.50839471817017</v>
       </c>
       <c r="H2059" t="n">
         <v>66825</v>
@@ -60109,7 +60109,7 @@
         <v>2.75</v>
       </c>
       <c r="G2060" t="n">
-        <v>2.47243189811707</v>
+        <v>2.47243165969849</v>
       </c>
       <c r="H2060" t="n">
         <v>68284</v>
@@ -60283,7 +60283,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.67022657394409</v>
+        <v>2.67022633552551</v>
       </c>
       <c r="H2066" t="n">
         <v>341329</v>
@@ -60312,7 +60312,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.62976837158203</v>
+        <v>2.62976813316345</v>
       </c>
       <c r="H2067" t="n">
         <v>158873</v>
@@ -60457,7 +60457,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.57132887840271</v>
+        <v>2.57132911682129</v>
       </c>
       <c r="H2072" t="n">
         <v>36049</v>
@@ -60689,7 +60689,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.98040413856506</v>
+        <v>2.98040437698364</v>
       </c>
       <c r="H2080" t="n">
         <v>774198</v>
@@ -60718,7 +60718,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H2081" t="n">
         <v>408063</v>
@@ -60747,7 +60747,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.90398359298706</v>
+        <v>2.90398383140564</v>
       </c>
       <c r="H2082" t="n">
         <v>119791</v>
@@ -60805,7 +60805,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.94444179534912</v>
+        <v>2.94444155693054</v>
       </c>
       <c r="H2084" t="n">
         <v>128118</v>
@@ -60979,7 +60979,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.07031059265137</v>
+        <v>3.07031083106995</v>
       </c>
       <c r="H2090" t="n">
         <v>607275</v>
@@ -61095,7 +61095,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.24562883377075</v>
+        <v>3.24562859535217</v>
       </c>
       <c r="H2094" t="n">
         <v>470642</v>
@@ -61124,7 +61124,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.45241403579712</v>
+        <v>3.45241379737854</v>
       </c>
       <c r="H2095" t="n">
         <v>913593</v>
@@ -61182,7 +61182,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="n">
-        <v>3.52883434295654</v>
+        <v>3.52883458137512</v>
       </c>
       <c r="H2097" t="n">
         <v>297741</v>
@@ -61327,7 +61327,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.78506827354431</v>
+        <v>3.78506851196289</v>
       </c>
       <c r="H2102" t="n">
         <v>666236</v>
@@ -61385,7 +61385,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.69516181945801</v>
+        <v>3.69516205787659</v>
       </c>
       <c r="H2104" t="n">
         <v>1859332</v>
@@ -61472,7 +61472,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.32204914093018</v>
+        <v>3.32204937934875</v>
       </c>
       <c r="H2107" t="n">
         <v>603946</v>
@@ -61501,7 +61501,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="n">
-        <v>3.34902119636536</v>
+        <v>3.34902143478394</v>
       </c>
       <c r="H2108" t="n">
         <v>322890</v>
@@ -61559,7 +61559,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="n">
-        <v>3.28608679771423</v>
+        <v>3.28608655929565</v>
       </c>
       <c r="H2110" t="n">
         <v>240394</v>
@@ -61704,7 +61704,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.47489070892334</v>
+        <v>3.47489047050476</v>
       </c>
       <c r="H2115" t="n">
         <v>312158</v>
@@ -61762,7 +61762,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2117" t="n">
-        <v>3.4434232711792</v>
+        <v>3.44342303276062</v>
       </c>
       <c r="H2117" t="n">
         <v>82941</v>
@@ -80096,6 +80096,35 @@
         <v>31826</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>7.1100001335144</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>7.34000015258789</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>7.1100001335144</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>27226</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89349257946014</v>
+        <v>1.89349222183228</v>
       </c>
       <c r="H2" t="n">
         <v>142675</v>
@@ -485,7 +485,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H4" t="n">
         <v>96004</v>
@@ -514,7 +514,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79772567749023</v>
+        <v>1.79772591590881</v>
       </c>
       <c r="H5" t="n">
         <v>122356</v>
@@ -543,7 +543,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80612635612488</v>
+        <v>1.80612623691559</v>
       </c>
       <c r="H6" t="n">
         <v>149442</v>
@@ -659,7 +659,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64231479167938</v>
+        <v>1.64231491088867</v>
       </c>
       <c r="H10" t="n">
         <v>209029</v>
@@ -688,7 +688,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G11" t="n">
-        <v>1.56754970550537</v>
+        <v>1.56754958629608</v>
       </c>
       <c r="H11" t="n">
         <v>152370</v>
@@ -862,7 +862,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H17" t="n">
         <v>299127</v>
@@ -949,7 +949,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H20" t="n">
         <v>164363</v>
@@ -1036,7 +1036,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G23" t="n">
-        <v>1.45246136188507</v>
+        <v>1.45246160030365</v>
       </c>
       <c r="H23" t="n">
         <v>58814</v>
@@ -1065,7 +1065,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525700569153</v>
       </c>
       <c r="H24" t="n">
         <v>64863</v>
@@ -1123,7 +1123,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G26" t="n">
-        <v>1.34241378307343</v>
+        <v>1.34241390228271</v>
       </c>
       <c r="H26" t="n">
         <v>105494</v>
@@ -1152,7 +1152,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>1.24328696727753</v>
+        <v>1.24328684806824</v>
       </c>
       <c r="H27" t="n">
         <v>162847</v>
@@ -1239,7 +1239,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G30" t="n">
-        <v>1.16936159133911</v>
+        <v>1.16936182975769</v>
       </c>
       <c r="H30" t="n">
         <v>95012</v>
@@ -1268,7 +1268,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G31" t="n">
-        <v>1.19204330444336</v>
+        <v>1.19204354286194</v>
       </c>
       <c r="H31" t="n">
         <v>55919</v>
@@ -1297,7 +1297,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G32" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H32" t="n">
         <v>226070</v>
@@ -1326,7 +1326,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35333466529846</v>
+        <v>1.35333454608917</v>
       </c>
       <c r="H33" t="n">
         <v>210586</v>
@@ -1442,7 +1442,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G37" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H37" t="n">
         <v>122783</v>
@@ -1471,7 +1471,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G38" t="n">
-        <v>1.46926248073578</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H38" t="n">
         <v>41622</v>
@@ -1500,7 +1500,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G39" t="n">
-        <v>1.44742107391357</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H39" t="n">
         <v>101588</v>
@@ -1529,7 +1529,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G40" t="n">
-        <v>1.44742107391357</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H40" t="n">
         <v>57255</v>
@@ -1558,7 +1558,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G41" t="n">
-        <v>1.43061995506287</v>
+        <v>1.43061983585358</v>
       </c>
       <c r="H41" t="n">
         <v>35142</v>
@@ -1616,7 +1616,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46254241466522</v>
+        <v>1.46254217624664</v>
       </c>
       <c r="H43" t="n">
         <v>49994</v>
@@ -1645,7 +1645,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H44" t="n">
         <v>126947</v>
@@ -1761,7 +1761,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G48" t="n">
-        <v>1.48018336296082</v>
+        <v>1.4801834821701</v>
       </c>
       <c r="H48" t="n">
         <v>31572</v>
@@ -1906,7 +1906,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56586933135986</v>
+        <v>1.56586945056915</v>
       </c>
       <c r="H53" t="n">
         <v>235408</v>
@@ -1993,7 +1993,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>1.62551355361938</v>
+        <v>1.62551367282867</v>
       </c>
       <c r="H56" t="n">
         <v>112057</v>
@@ -2022,7 +2022,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>1.60283195972443</v>
+        <v>1.60283207893372</v>
       </c>
       <c r="H57" t="n">
         <v>64816</v>
@@ -2080,7 +2080,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G59" t="n">
-        <v>1.55578863620758</v>
+        <v>1.55578875541687</v>
       </c>
       <c r="H59" t="n">
         <v>177054</v>
@@ -2109,7 +2109,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H60" t="n">
         <v>70797</v>
@@ -2138,7 +2138,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G61" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H61" t="n">
         <v>52361</v>
@@ -2167,7 +2167,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46926248073578</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H62" t="n">
         <v>74998</v>
@@ -2225,7 +2225,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G64" t="n">
-        <v>1.44994115829468</v>
+        <v>1.44994127750397</v>
       </c>
       <c r="H64" t="n">
         <v>18558</v>
@@ -2254,7 +2254,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G65" t="n">
-        <v>1.4348201751709</v>
+        <v>1.43482029438019</v>
       </c>
       <c r="H65" t="n">
         <v>95844</v>
@@ -2341,7 +2341,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30965149402618</v>
+        <v>1.30965161323547</v>
       </c>
       <c r="H68" t="n">
         <v>60442</v>
@@ -2428,7 +2428,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>1.44742107391357</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H71" t="n">
         <v>100585</v>
@@ -2515,7 +2515,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G74" t="n">
-        <v>1.57847023010254</v>
+        <v>1.57847034931183</v>
       </c>
       <c r="H74" t="n">
         <v>128291</v>
@@ -2544,7 +2544,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G75" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H75" t="n">
         <v>74007</v>
@@ -2573,7 +2573,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>1.55830883979797</v>
+        <v>1.55830895900726</v>
       </c>
       <c r="H76" t="n">
         <v>60173</v>
@@ -2631,7 +2631,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.6078724861145</v>
+        <v>1.60787236690521</v>
       </c>
       <c r="H78" t="n">
         <v>161214</v>
@@ -2660,7 +2660,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H79" t="n">
         <v>123106</v>
@@ -2689,7 +2689,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G80" t="n">
-        <v>1.53646731376648</v>
+        <v>1.53646743297577</v>
       </c>
       <c r="H80" t="n">
         <v>8803</v>
@@ -2776,7 +2776,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G83" t="n">
-        <v>1.55074834823608</v>
+        <v>1.55074822902679</v>
       </c>
       <c r="H83" t="n">
         <v>74710</v>
@@ -2805,7 +2805,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.53898751735687</v>
+        <v>1.53898775577545</v>
       </c>
       <c r="H84" t="n">
         <v>87212</v>
@@ -3124,7 +3124,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55410873889923</v>
+        <v>1.55410861968994</v>
       </c>
       <c r="H95" t="n">
         <v>124547</v>
@@ -3269,7 +3269,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G100" t="n">
-        <v>1.48270356655121</v>
+        <v>1.4827036857605</v>
       </c>
       <c r="H100" t="n">
         <v>26242</v>
@@ -3298,7 +3298,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G101" t="n">
-        <v>1.49278438091278</v>
+        <v>1.4927841424942</v>
       </c>
       <c r="H101" t="n">
         <v>25555</v>
@@ -3356,7 +3356,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G103" t="n">
-        <v>1.49866473674774</v>
+        <v>1.49866485595703</v>
       </c>
       <c r="H103" t="n">
         <v>83894</v>
@@ -3385,7 +3385,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.5020250082016</v>
+        <v>1.50202512741089</v>
       </c>
       <c r="H104" t="n">
         <v>14686</v>
@@ -3443,7 +3443,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G106" t="n">
-        <v>1.52470672130585</v>
+        <v>1.52470660209656</v>
       </c>
       <c r="H106" t="n">
         <v>85536</v>
@@ -3472,7 +3472,7 @@
         <v>1.79900002479553</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51126563549042</v>
+        <v>1.51126575469971</v>
       </c>
       <c r="H107" t="n">
         <v>33834</v>
@@ -3530,7 +3530,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H109" t="n">
         <v>38996</v>
@@ -3588,7 +3588,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H111" t="n">
         <v>68477</v>
@@ -3675,7 +3675,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G114" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H114" t="n">
         <v>56900</v>
@@ -3704,7 +3704,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G115" t="n">
-        <v>1.40457820892334</v>
+        <v>1.40457832813263</v>
       </c>
       <c r="H115" t="n">
         <v>72247</v>
@@ -3791,7 +3791,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H118" t="n">
         <v>57849</v>
@@ -3878,7 +3878,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G121" t="n">
-        <v>1.45246136188507</v>
+        <v>1.45246160030365</v>
       </c>
       <c r="H121" t="n">
         <v>39896</v>
@@ -3907,7 +3907,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H122" t="n">
         <v>57149</v>
@@ -3936,7 +3936,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G123" t="n">
-        <v>1.43734037876129</v>
+        <v>1.43734061717987</v>
       </c>
       <c r="H123" t="n">
         <v>46115</v>
@@ -4023,7 +4023,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H126" t="n">
         <v>40738</v>
@@ -4168,7 +4168,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G131" t="n">
-        <v>1.29537057876587</v>
+        <v>1.29537069797516</v>
       </c>
       <c r="H131" t="n">
         <v>29496</v>
@@ -4226,7 +4226,7 @@
         <v>1.5</v>
       </c>
       <c r="G133" t="n">
-        <v>1.26008808612823</v>
+        <v>1.26008796691895</v>
       </c>
       <c r="H133" t="n">
         <v>69851</v>
@@ -4255,7 +4255,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G134" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H134" t="n">
         <v>18189</v>
@@ -4284,7 +4284,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G135" t="n">
-        <v>1.31889224052429</v>
+        <v>1.318892121315</v>
       </c>
       <c r="H135" t="n">
         <v>36849</v>
@@ -4342,7 +4342,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.31889224052429</v>
+        <v>1.318892121315</v>
       </c>
       <c r="H137" t="n">
         <v>23614</v>
@@ -4632,7 +4632,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G147" t="n">
-        <v>1.37769639492035</v>
+        <v>1.37769627571106</v>
       </c>
       <c r="H147" t="n">
         <v>103585</v>
@@ -4748,7 +4748,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G151" t="n">
-        <v>1.33569359779358</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H151" t="n">
         <v>35803</v>
@@ -4806,7 +4806,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G153" t="n">
-        <v>1.33737337589264</v>
+        <v>1.33737361431122</v>
       </c>
       <c r="H153" t="n">
         <v>11912</v>
@@ -4835,7 +4835,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G154" t="n">
-        <v>1.32309246063232</v>
+        <v>1.32309257984161</v>
       </c>
       <c r="H154" t="n">
         <v>23094</v>
@@ -4864,7 +4864,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.32309246063232</v>
+        <v>1.32309257984161</v>
       </c>
       <c r="H155" t="n">
         <v>19485</v>
@@ -4893,7 +4893,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3138519525528</v>
+        <v>1.31385183334351</v>
       </c>
       <c r="H156" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G157" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H157" t="n">
         <v>6004</v>
@@ -4980,7 +4980,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G159" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125093460083</v>
       </c>
       <c r="H159" t="n">
         <v>15586</v>
@@ -5009,7 +5009,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28949022293091</v>
       </c>
       <c r="H160" t="n">
         <v>3220</v>
@@ -5038,7 +5038,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H161" t="n">
         <v>8206</v>
@@ -5125,7 +5125,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G164" t="n">
-        <v>1.26680862903595</v>
+        <v>1.26680850982666</v>
       </c>
       <c r="H164" t="n">
         <v>13879</v>
@@ -5154,7 +5154,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30545139312744</v>
+        <v>1.30545127391815</v>
       </c>
       <c r="H165" t="n">
         <v>18762</v>
@@ -5212,7 +5212,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29201030731201</v>
+        <v>1.2920104265213</v>
       </c>
       <c r="H167" t="n">
         <v>8138</v>
@@ -5241,7 +5241,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G168" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H168" t="n">
         <v>9419</v>
@@ -5270,7 +5270,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H169" t="n">
         <v>8043</v>
@@ -5328,7 +5328,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G171" t="n">
-        <v>1.3281329870224</v>
+        <v>1.32813274860382</v>
       </c>
       <c r="H171" t="n">
         <v>34956</v>
@@ -5357,7 +5357,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H172" t="n">
         <v>47662</v>
@@ -5386,7 +5386,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G173" t="n">
-        <v>1.30713129043579</v>
+        <v>1.30713140964508</v>
       </c>
       <c r="H173" t="n">
         <v>6108</v>
@@ -5415,7 +5415,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29621052742004</v>
+        <v>1.29621064662933</v>
       </c>
       <c r="H174" t="n">
         <v>15271</v>
@@ -5444,7 +5444,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30629134178162</v>
+        <v>1.30629122257233</v>
       </c>
       <c r="H175" t="n">
         <v>84071</v>
@@ -5473,7 +5473,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G176" t="n">
-        <v>1.30629134178162</v>
+        <v>1.30629122257233</v>
       </c>
       <c r="H176" t="n">
         <v>23238</v>
@@ -5502,7 +5502,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G177" t="n">
-        <v>1.37265598773956</v>
+        <v>1.37265586853027</v>
       </c>
       <c r="H177" t="n">
         <v>159638</v>
@@ -5560,7 +5560,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33569359779358</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H179" t="n">
         <v>49524</v>
@@ -5647,7 +5647,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G182" t="n">
-        <v>1.36677551269531</v>
+        <v>1.36677539348602</v>
       </c>
       <c r="H182" t="n">
         <v>13176</v>
@@ -5763,7 +5763,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33821356296539</v>
+        <v>1.3382134437561</v>
       </c>
       <c r="H186" t="n">
         <v>23249</v>
@@ -5792,7 +5792,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G187" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H187" t="n">
         <v>16776</v>
@@ -5821,7 +5821,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.35417461395264</v>
+        <v>1.35417473316193</v>
       </c>
       <c r="H188" t="n">
         <v>58082</v>
@@ -5879,7 +5879,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.33149302005768</v>
+        <v>1.33149313926697</v>
       </c>
       <c r="H190" t="n">
         <v>47211</v>
@@ -5966,7 +5966,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3768562078476</v>
+        <v>1.37685644626617</v>
       </c>
       <c r="H193" t="n">
         <v>34278</v>
@@ -6053,7 +6053,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G196" t="n">
-        <v>1.38525688648224</v>
+        <v>1.38525700569153</v>
       </c>
       <c r="H196" t="n">
         <v>26702</v>
@@ -6082,7 +6082,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G197" t="n">
-        <v>1.39365744590759</v>
+        <v>1.39365756511688</v>
       </c>
       <c r="H197" t="n">
         <v>31070</v>
@@ -6198,7 +6198,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G201" t="n">
-        <v>1.33569359779358</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H201" t="n">
         <v>114562</v>
@@ -6227,7 +6227,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G202" t="n">
-        <v>1.30881154537201</v>
+        <v>1.30881142616272</v>
       </c>
       <c r="H202" t="n">
         <v>85287</v>
@@ -6256,7 +6256,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G203" t="n">
-        <v>1.3163720369339</v>
+        <v>1.31637215614319</v>
       </c>
       <c r="H203" t="n">
         <v>55079</v>
@@ -6372,7 +6372,7 @@
         <v>1.57099997997284</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31973218917847</v>
+        <v>1.31973230838776</v>
       </c>
       <c r="H207" t="n">
         <v>19744</v>
@@ -6401,7 +6401,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31217169761658</v>
+        <v>1.31217181682587</v>
       </c>
       <c r="H208" t="n">
         <v>31170</v>
@@ -6430,7 +6430,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30125105381012</v>
+        <v>1.30125093460083</v>
       </c>
       <c r="H209" t="n">
         <v>107376</v>
@@ -6488,7 +6488,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G211" t="n">
-        <v>1.27940952777863</v>
+        <v>1.27940940856934</v>
       </c>
       <c r="H211" t="n">
         <v>25428</v>
@@ -6546,7 +6546,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28949010372162</v>
+        <v>1.28949022293091</v>
       </c>
       <c r="H213" t="n">
         <v>13131</v>
@@ -6575,7 +6575,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27940952777863</v>
+        <v>1.27940940856934</v>
       </c>
       <c r="H214" t="n">
         <v>23612</v>
@@ -6604,7 +6604,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G215" t="n">
-        <v>1.27856934070587</v>
+        <v>1.27856945991516</v>
       </c>
       <c r="H215" t="n">
         <v>5900</v>
@@ -6633,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.26008808612823</v>
+        <v>1.26008796691895</v>
       </c>
       <c r="H216" t="n">
         <v>157616</v>
@@ -6865,7 +6865,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G224" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H224" t="n">
         <v>38946</v>
@@ -6894,7 +6894,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H225" t="n">
         <v>27800</v>
@@ -7039,7 +7039,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G230" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H230" t="n">
         <v>21769</v>
@@ -7068,7 +7068,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G231" t="n">
-        <v>1.08787596225739</v>
+        <v>1.08787608146667</v>
       </c>
       <c r="H231" t="n">
         <v>21196</v>
@@ -7097,7 +7097,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G232" t="n">
-        <v>1.09795677661896</v>
+        <v>1.09795665740967</v>
       </c>
       <c r="H232" t="n">
         <v>29928</v>
@@ -7184,7 +7184,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>1.08031535148621</v>
+        <v>1.0803154706955</v>
       </c>
       <c r="H235" t="n">
         <v>47088</v>
@@ -7300,7 +7300,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>1.0391526222229</v>
+        <v>1.03915250301361</v>
       </c>
       <c r="H239" t="n">
         <v>11183</v>
@@ -7329,7 +7329,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G240" t="n">
-        <v>1.06939470767975</v>
+        <v>1.06939482688904</v>
       </c>
       <c r="H240" t="n">
         <v>41501</v>
@@ -7503,7 +7503,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G246" t="n">
-        <v>1.14584004878998</v>
+        <v>1.14583992958069</v>
       </c>
       <c r="H246" t="n">
         <v>30733</v>
@@ -7648,7 +7648,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G251" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028235435486</v>
       </c>
       <c r="H251" t="n">
         <v>48253</v>
@@ -7677,7 +7677,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G252" t="n">
-        <v>1.16180121898651</v>
+        <v>1.1618013381958</v>
       </c>
       <c r="H252" t="n">
         <v>24822</v>
@@ -7706,7 +7706,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.16348135471344</v>
+        <v>1.16348123550415</v>
       </c>
       <c r="H253" t="n">
         <v>60273</v>
@@ -7793,7 +7793,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G256" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H256" t="n">
         <v>13371</v>
@@ -7851,7 +7851,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G258" t="n">
-        <v>1.1979238986969</v>
+        <v>1.19792366027832</v>
       </c>
       <c r="H258" t="n">
         <v>50093</v>
@@ -7880,7 +7880,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G259" t="n">
-        <v>1.18952310085297</v>
+        <v>1.18952322006226</v>
       </c>
       <c r="H259" t="n">
         <v>167866</v>
@@ -7909,7 +7909,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G260" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H260" t="n">
         <v>166425</v>
@@ -7938,7 +7938,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G261" t="n">
-        <v>1.3407336473465</v>
+        <v>1.34073376655579</v>
       </c>
       <c r="H261" t="n">
         <v>560773</v>
@@ -7967,7 +7967,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.35501492023468</v>
+        <v>1.3550146818161</v>
       </c>
       <c r="H262" t="n">
         <v>277449</v>
@@ -7996,7 +7996,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>1.34325397014618</v>
+        <v>1.34325385093689</v>
       </c>
       <c r="H263" t="n">
         <v>158414</v>
@@ -8054,7 +8054,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33821356296539</v>
+        <v>1.3382134437561</v>
       </c>
       <c r="H265" t="n">
         <v>71239</v>
@@ -8083,7 +8083,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G266" t="n">
-        <v>1.30377125740051</v>
+        <v>1.30377113819122</v>
       </c>
       <c r="H266" t="n">
         <v>53629</v>
@@ -8112,7 +8112,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>1.29117023944855</v>
+        <v>1.29117012023926</v>
       </c>
       <c r="H267" t="n">
         <v>22423</v>
@@ -8170,7 +8170,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G269" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H269" t="n">
         <v>175414</v>
@@ -8199,7 +8199,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G270" t="n">
-        <v>1.24832713603973</v>
+        <v>1.24832737445831</v>
       </c>
       <c r="H270" t="n">
         <v>55365</v>
@@ -8228,7 +8228,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G271" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H271" t="n">
         <v>103512</v>
@@ -8315,7 +8315,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G274" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H274" t="n">
         <v>53621</v>
@@ -8344,7 +8344,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G275" t="n">
-        <v>1.20548439025879</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H275" t="n">
         <v>109224</v>
@@ -8402,7 +8402,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>1.1886830329895</v>
+        <v>1.18868315219879</v>
       </c>
       <c r="H277" t="n">
         <v>23809</v>
@@ -8431,7 +8431,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G278" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H278" t="n">
         <v>152723</v>
@@ -8460,7 +8460,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G279" t="n">
-        <v>1.18532288074493</v>
+        <v>1.18532299995422</v>
       </c>
       <c r="H279" t="n">
         <v>48771</v>
@@ -8489,7 +8489,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G280" t="n">
-        <v>1.18448281288147</v>
+        <v>1.18448269367218</v>
       </c>
       <c r="H280" t="n">
         <v>20220</v>
@@ -8518,7 +8518,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028235435486</v>
       </c>
       <c r="H281" t="n">
         <v>29155</v>
@@ -8547,7 +8547,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G282" t="n">
-        <v>1.1979238986969</v>
+        <v>1.19792366027832</v>
       </c>
       <c r="H282" t="n">
         <v>19778</v>
@@ -8576,7 +8576,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G283" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H283" t="n">
         <v>60336</v>
@@ -8634,7 +8634,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G285" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H285" t="n">
         <v>42766</v>
@@ -8692,7 +8692,7 @@
         <v>1.38900005817413</v>
       </c>
       <c r="G287" t="n">
-        <v>1.16684150695801</v>
+        <v>1.1668416261673</v>
       </c>
       <c r="H287" t="n">
         <v>29558</v>
@@ -8721,7 +8721,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.18028247356415</v>
+        <v>1.18028235435486</v>
       </c>
       <c r="H288" t="n">
         <v>17766</v>
@@ -8779,7 +8779,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G290" t="n">
-        <v>1.16936159133911</v>
+        <v>1.16936182975769</v>
       </c>
       <c r="H290" t="n">
         <v>53137</v>
@@ -8866,7 +8866,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G293" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H293" t="n">
         <v>25900</v>
@@ -8895,7 +8895,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G294" t="n">
-        <v>1.16432130336761</v>
+        <v>1.16432154178619</v>
       </c>
       <c r="H294" t="n">
         <v>36944</v>
@@ -8953,7 +8953,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G296" t="n">
-        <v>1.17524230480194</v>
+        <v>1.17524218559265</v>
       </c>
       <c r="H296" t="n">
         <v>39885</v>
@@ -9098,7 +9098,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G301" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H301" t="n">
         <v>112526</v>
@@ -9156,7 +9156,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.23236620426178</v>
+        <v>1.23236608505249</v>
       </c>
       <c r="H303" t="n">
         <v>66001</v>
@@ -9214,7 +9214,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G305" t="n">
-        <v>1.22900581359863</v>
+        <v>1.22900593280792</v>
       </c>
       <c r="H305" t="n">
         <v>29402</v>
@@ -9272,7 +9272,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>1.20548439025879</v>
+        <v>1.2054842710495</v>
       </c>
       <c r="H307" t="n">
         <v>124489</v>
@@ -9417,7 +9417,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H312" t="n">
         <v>169466</v>
@@ -9504,7 +9504,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19036340713501</v>
+        <v>1.19036328792572</v>
       </c>
       <c r="H315" t="n">
         <v>26439</v>
@@ -9562,7 +9562,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18196260929108</v>
+        <v>1.18196249008179</v>
       </c>
       <c r="H317" t="n">
         <v>15234</v>
@@ -9591,7 +9591,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G318" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H318" t="n">
         <v>363589</v>
@@ -9620,7 +9620,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G319" t="n">
-        <v>1.20884442329407</v>
+        <v>1.20884454250336</v>
       </c>
       <c r="H319" t="n">
         <v>228508</v>
@@ -9707,7 +9707,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G322" t="n">
-        <v>1.210524559021</v>
+        <v>1.21052467823029</v>
       </c>
       <c r="H322" t="n">
         <v>15835</v>
@@ -9765,7 +9765,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G324" t="n">
-        <v>1.25252747535706</v>
+        <v>1.25252759456635</v>
       </c>
       <c r="H324" t="n">
         <v>69914</v>
@@ -9794,7 +9794,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>1.27688932418823</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H325" t="n">
         <v>165501</v>
@@ -9823,7 +9823,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>1.27688932418823</v>
+        <v>1.27688920497894</v>
       </c>
       <c r="H326" t="n">
         <v>59125</v>
@@ -9881,7 +9881,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>1.26596856117249</v>
+        <v>1.2659684419632</v>
       </c>
       <c r="H328" t="n">
         <v>28100</v>
@@ -9939,7 +9939,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G330" t="n">
-        <v>1.23320615291595</v>
+        <v>1.23320639133453</v>
       </c>
       <c r="H330" t="n">
         <v>59512</v>
@@ -9968,7 +9968,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G331" t="n">
-        <v>1.21808505058289</v>
+        <v>1.21808516979218</v>
       </c>
       <c r="H331" t="n">
         <v>30919</v>
@@ -9997,7 +9997,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>1.20128393173218</v>
+        <v>1.20128381252289</v>
       </c>
       <c r="H332" t="n">
         <v>77707</v>
@@ -10026,7 +10026,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G333" t="n">
-        <v>1.23908662796021</v>
+        <v>1.23908650875092</v>
       </c>
       <c r="H333" t="n">
         <v>107368</v>
@@ -10113,7 +10113,7 @@
         <v>1.44900000095367</v>
       </c>
       <c r="G336" t="n">
-        <v>1.217245221138</v>
+        <v>1.21724510192871</v>
       </c>
       <c r="H336" t="n">
         <v>36491</v>
@@ -10171,7 +10171,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.24412703514099</v>
+        <v>1.2441269159317</v>
       </c>
       <c r="H338" t="n">
         <v>121442</v>
@@ -10200,7 +10200,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.23488628864288</v>
+        <v>1.23488616943359</v>
       </c>
       <c r="H339" t="n">
         <v>28767</v>
@@ -10229,7 +10229,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G340" t="n">
-        <v>1.22480571269989</v>
+        <v>1.2248055934906</v>
       </c>
       <c r="H340" t="n">
         <v>28390</v>
@@ -10258,7 +10258,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G341" t="n">
-        <v>1.21388483047485</v>
+        <v>1.21388494968414</v>
       </c>
       <c r="H341" t="n">
         <v>33517</v>
@@ -10287,7 +10287,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G342" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H342" t="n">
         <v>37872</v>
@@ -10316,7 +10316,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G343" t="n">
-        <v>1.24496698379517</v>
+        <v>1.24496710300446</v>
       </c>
       <c r="H343" t="n">
         <v>29781</v>
@@ -10432,7 +10432,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G347" t="n">
-        <v>1.29789078235626</v>
+        <v>1.29789054393768</v>
       </c>
       <c r="H347" t="n">
         <v>47509</v>
@@ -10490,7 +10490,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>1.2852897644043</v>
+        <v>1.28528988361359</v>
       </c>
       <c r="H349" t="n">
         <v>56577</v>
@@ -10606,7 +10606,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G353" t="n">
-        <v>1.31301188468933</v>
+        <v>1.31301176548004</v>
       </c>
       <c r="H353" t="n">
         <v>99196</v>
@@ -10635,7 +10635,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G354" t="n">
-        <v>1.36761558055878</v>
+        <v>1.36761569976807</v>
       </c>
       <c r="H354" t="n">
         <v>285211</v>
@@ -10722,7 +10722,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>1.49194419384003</v>
+        <v>1.49194431304932</v>
       </c>
       <c r="H357" t="n">
         <v>183588</v>
@@ -10751,7 +10751,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.48690402507782</v>
+        <v>1.48690390586853</v>
       </c>
       <c r="H358" t="n">
         <v>214405</v>
@@ -10780,7 +10780,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G359" t="n">
-        <v>1.45162153244019</v>
+        <v>1.4516214132309</v>
       </c>
       <c r="H359" t="n">
         <v>145364</v>
@@ -10954,7 +10954,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G365" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H365" t="n">
         <v>28050</v>
@@ -11041,7 +11041,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G368" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H368" t="n">
         <v>187011</v>
@@ -11070,7 +11070,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G369" t="n">
-        <v>1.36173510551453</v>
+        <v>1.36173522472382</v>
       </c>
       <c r="H369" t="n">
         <v>94755</v>
@@ -11215,7 +11215,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G374" t="n">
-        <v>1.33569359779358</v>
+        <v>1.335693359375</v>
       </c>
       <c r="H374" t="n">
         <v>54288</v>
@@ -11244,7 +11244,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G375" t="n">
-        <v>1.34157383441925</v>
+        <v>1.34157371520996</v>
       </c>
       <c r="H375" t="n">
         <v>67186</v>
@@ -11273,7 +11273,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G376" t="n">
-        <v>1.34409391880035</v>
+        <v>1.34409403800964</v>
       </c>
       <c r="H376" t="n">
         <v>41045</v>
@@ -11302,7 +11302,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>1.34325397014618</v>
+        <v>1.34325385093689</v>
       </c>
       <c r="H377" t="n">
         <v>25858</v>
@@ -11592,7 +11592,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G387" t="n">
-        <v>1.4297798871994</v>
+        <v>1.42978000640869</v>
       </c>
       <c r="H387" t="n">
         <v>25887</v>
@@ -11650,7 +11650,7 @@
         <v>1.692999958992</v>
       </c>
       <c r="G389" t="n">
-        <v>1.4222195148468</v>
+        <v>1.42221927642822</v>
       </c>
       <c r="H389" t="n">
         <v>26833</v>
@@ -11679,7 +11679,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G390" t="n">
-        <v>1.4129786491394</v>
+        <v>1.41297888755798</v>
       </c>
       <c r="H390" t="n">
         <v>62429</v>
@@ -11737,7 +11737,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G392" t="n">
-        <v>1.41381883621216</v>
+        <v>1.41381871700287</v>
       </c>
       <c r="H392" t="n">
         <v>37725</v>
@@ -11824,7 +11824,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G395" t="n">
-        <v>1.4272598028183</v>
+        <v>1.42725968360901</v>
       </c>
       <c r="H395" t="n">
         <v>31306</v>
@@ -11940,7 +11940,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G399" t="n">
-        <v>1.4297798871994</v>
+        <v>1.42978000640869</v>
       </c>
       <c r="H399" t="n">
         <v>73782</v>
@@ -11969,7 +11969,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G400" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H400" t="n">
         <v>136155</v>
@@ -11998,7 +11998,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>1.48102366924286</v>
+        <v>1.48102355003357</v>
       </c>
       <c r="H401" t="n">
         <v>80507</v>
@@ -12056,7 +12056,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G403" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H403" t="n">
         <v>39945</v>
@@ -12114,7 +12114,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G405" t="n">
-        <v>1.43734037876129</v>
+        <v>1.43734061717987</v>
       </c>
       <c r="H405" t="n">
         <v>108082</v>
@@ -12230,7 +12230,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G409" t="n">
-        <v>1.52554666996002</v>
+        <v>1.52554655075073</v>
       </c>
       <c r="H409" t="n">
         <v>131979</v>
@@ -12288,7 +12288,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G411" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H411" t="n">
         <v>96313</v>
@@ -12346,7 +12346,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G413" t="n">
-        <v>1.45246136188507</v>
+        <v>1.45246160030365</v>
       </c>
       <c r="H413" t="n">
         <v>73244</v>
@@ -12375,7 +12375,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>1.44742107391357</v>
+        <v>1.44742119312286</v>
       </c>
       <c r="H414" t="n">
         <v>58941</v>
@@ -12404,7 +12404,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G415" t="n">
-        <v>1.43986058235168</v>
+        <v>1.43986070156097</v>
       </c>
       <c r="H415" t="n">
         <v>5593</v>
@@ -12549,7 +12549,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G420" t="n">
-        <v>1.44322097301483</v>
+        <v>1.44322085380554</v>
       </c>
       <c r="H420" t="n">
         <v>20737</v>
@@ -12636,7 +12636,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>1.44490098953247</v>
+        <v>1.44490087032318</v>
       </c>
       <c r="H423" t="n">
         <v>14289</v>
@@ -12665,7 +12665,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H424" t="n">
         <v>83230</v>
@@ -12810,7 +12810,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G429" t="n">
-        <v>1.4415408372879</v>
+        <v>1.44154071807861</v>
       </c>
       <c r="H429" t="n">
         <v>13399</v>
@@ -12897,7 +12897,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G432" t="n">
-        <v>1.46926248073578</v>
+        <v>1.46926259994507</v>
       </c>
       <c r="H432" t="n">
         <v>101212</v>
@@ -12926,7 +12926,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G433" t="n">
-        <v>1.46590256690979</v>
+        <v>1.4659024477005</v>
       </c>
       <c r="H433" t="n">
         <v>23096</v>
@@ -12955,7 +12955,7 @@
         <v>1.74100005626678</v>
       </c>
       <c r="G434" t="n">
-        <v>1.46254241466522</v>
+        <v>1.46254217624664</v>
       </c>
       <c r="H434" t="n">
         <v>24018</v>
@@ -13013,7 +13013,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45162153244019</v>
+        <v>1.4516214132309</v>
       </c>
       <c r="H436" t="n">
         <v>40612</v>
@@ -13042,7 +13042,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G437" t="n">
-        <v>1.46422243118286</v>
+        <v>1.46422231197357</v>
       </c>
       <c r="H437" t="n">
         <v>60693</v>
@@ -13071,7 +13071,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G438" t="n">
-        <v>1.51966631412506</v>
+        <v>1.51966643333435</v>
       </c>
       <c r="H438" t="n">
         <v>231891</v>
@@ -13100,7 +13100,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G439" t="n">
-        <v>1.51294565200806</v>
+        <v>1.51294577121735</v>
       </c>
       <c r="H439" t="n">
         <v>106284</v>
@@ -13158,7 +13158,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G441" t="n">
-        <v>1.59527146816254</v>
+        <v>1.59527158737183</v>
       </c>
       <c r="H441" t="n">
         <v>630947</v>
@@ -13187,7 +13187,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G442" t="n">
-        <v>1.73052072525024</v>
+        <v>1.73052096366882</v>
       </c>
       <c r="H442" t="n">
         <v>1415394</v>
@@ -13216,7 +13216,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>1.70531928539276</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H443" t="n">
         <v>662645</v>
@@ -13245,7 +13245,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G444" t="n">
-        <v>1.80108594894409</v>
+        <v>1.80108606815338</v>
       </c>
       <c r="H444" t="n">
         <v>1350440</v>
@@ -13361,7 +13361,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93717527389526</v>
+        <v>1.93717539310455</v>
       </c>
       <c r="H448" t="n">
         <v>1651667</v>
@@ -13448,7 +13448,7 @@
         <v>2.25</v>
       </c>
       <c r="G451" t="n">
-        <v>1.890132188797</v>
+        <v>1.89013206958771</v>
       </c>
       <c r="H451" t="n">
         <v>274964</v>
@@ -13477,7 +13477,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G452" t="n">
-        <v>1.98757874965668</v>
+        <v>1.98757898807526</v>
       </c>
       <c r="H452" t="n">
         <v>517407</v>
@@ -13506,7 +13506,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G453" t="n">
-        <v>1.95229625701904</v>
+        <v>1.95229637622833</v>
       </c>
       <c r="H453" t="n">
         <v>344440</v>
@@ -13564,7 +13564,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G455" t="n">
-        <v>1.84476923942566</v>
+        <v>1.84476912021637</v>
       </c>
       <c r="H455" t="n">
         <v>293919</v>
@@ -13593,7 +13593,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G456" t="n">
-        <v>1.84812927246094</v>
+        <v>1.84812915325165</v>
       </c>
       <c r="H456" t="n">
         <v>118562</v>
@@ -13622,7 +13622,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>1.84980916976929</v>
+        <v>1.84980928897858</v>
       </c>
       <c r="H457" t="n">
         <v>133644</v>
@@ -13709,7 +13709,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>1.79100513458252</v>
+        <v>1.7910053730011</v>
       </c>
       <c r="H460" t="n">
         <v>175490</v>
@@ -13767,7 +13767,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G462" t="n">
-        <v>1.77420401573181</v>
+        <v>1.77420389652252</v>
       </c>
       <c r="H462" t="n">
         <v>87616</v>
@@ -13854,7 +13854,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G465" t="n">
-        <v>1.87669110298157</v>
+        <v>1.87669134140015</v>
       </c>
       <c r="H465" t="n">
         <v>93915</v>
@@ -13912,7 +13912,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G467" t="n">
-        <v>1.88173139095306</v>
+        <v>1.88173162937164</v>
       </c>
       <c r="H467" t="n">
         <v>129153</v>
@@ -13941,7 +13941,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.91533374786377</v>
+        <v>1.91533398628235</v>
       </c>
       <c r="H468" t="n">
         <v>291840</v>
@@ -13999,7 +13999,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G470" t="n">
-        <v>2.00437998771667</v>
+        <v>2.00438022613525</v>
       </c>
       <c r="H470" t="n">
         <v>330066</v>
@@ -14028,7 +14028,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G471" t="n">
-        <v>1.9489358663559</v>
+        <v>1.94893610477448</v>
       </c>
       <c r="H471" t="n">
         <v>119724</v>
@@ -14057,7 +14057,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G472" t="n">
-        <v>1.97581803798676</v>
+        <v>1.97581815719604</v>
       </c>
       <c r="H472" t="n">
         <v>124221</v>
@@ -14086,7 +14086,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G473" t="n">
-        <v>1.95061647891998</v>
+        <v>1.95061635971069</v>
       </c>
       <c r="H473" t="n">
         <v>90920</v>
@@ -14144,7 +14144,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93213534355164</v>
+        <v>1.93213486671448</v>
       </c>
       <c r="H475" t="n">
         <v>75301</v>
@@ -14202,7 +14202,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G477" t="n">
-        <v>1.84308886528015</v>
+        <v>1.84308910369873</v>
       </c>
       <c r="H477" t="n">
         <v>210138</v>
@@ -14231,7 +14231,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>1.76412320137024</v>
+        <v>1.76412296295166</v>
       </c>
       <c r="H478" t="n">
         <v>93091</v>
@@ -14260,7 +14260,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G479" t="n">
-        <v>1.85316967964172</v>
+        <v>1.85316944122314</v>
       </c>
       <c r="H479" t="n">
         <v>100214</v>
@@ -14318,7 +14318,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>1.61879336833954</v>
+        <v>1.61879312992096</v>
       </c>
       <c r="H481" t="n">
         <v>205479</v>
@@ -14376,7 +14376,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63475430011749</v>
+        <v>1.6347541809082</v>
       </c>
       <c r="H483" t="n">
         <v>59107</v>
@@ -14405,7 +14405,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G484" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H484" t="n">
         <v>43159</v>
@@ -14434,7 +14434,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G485" t="n">
-        <v>1.58855104446411</v>
+        <v>1.58855092525482</v>
       </c>
       <c r="H485" t="n">
         <v>80862</v>
@@ -14463,7 +14463,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G486" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H486" t="n">
         <v>179687</v>
@@ -14492,7 +14492,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G487" t="n">
-        <v>1.57763016223907</v>
+        <v>1.57763028144836</v>
       </c>
       <c r="H487" t="n">
         <v>65136</v>
@@ -14521,7 +14521,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G488" t="n">
-        <v>1.57595026493073</v>
+        <v>1.57595014572144</v>
       </c>
       <c r="H488" t="n">
         <v>66260</v>
@@ -14637,7 +14637,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G492" t="n">
-        <v>1.54654812812805</v>
+        <v>1.54654800891876</v>
       </c>
       <c r="H492" t="n">
         <v>70153</v>
@@ -14666,7 +14666,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>1.54150772094727</v>
+        <v>1.54150784015656</v>
       </c>
       <c r="H493" t="n">
         <v>23515</v>
@@ -14724,7 +14724,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>1.59695172309875</v>
+        <v>1.59695160388947</v>
       </c>
       <c r="H495" t="n">
         <v>68871</v>
@@ -14782,7 +14782,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H497" t="n">
         <v>118911</v>
@@ -14811,7 +14811,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G498" t="n">
-        <v>1.70531928539276</v>
+        <v>1.70531904697418</v>
       </c>
       <c r="H498" t="n">
         <v>229181</v>
@@ -14869,7 +14869,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G500" t="n">
-        <v>1.67507708072662</v>
+        <v>1.67507696151733</v>
       </c>
       <c r="H500" t="n">
         <v>49637</v>
@@ -14956,7 +14956,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G503" t="n">
-        <v>1.60451209545135</v>
+        <v>1.60451221466064</v>
       </c>
       <c r="H503" t="n">
         <v>18702</v>
@@ -14985,7 +14985,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G504" t="n">
-        <v>1.57931041717529</v>
+        <v>1.579310297966</v>
       </c>
       <c r="H504" t="n">
         <v>91562</v>
@@ -15014,7 +15014,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G505" t="n">
-        <v>1.61459279060364</v>
+        <v>1.61459290981293</v>
       </c>
       <c r="H505" t="n">
         <v>51477</v>
@@ -15043,7 +15043,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G506" t="n">
-        <v>1.63811469078064</v>
+        <v>1.63811445236206</v>
       </c>
       <c r="H506" t="n">
         <v>34414</v>
@@ -15159,7 +15159,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G510" t="n">
-        <v>1.58267045021057</v>
+        <v>1.58267056941986</v>
       </c>
       <c r="H510" t="n">
         <v>44384</v>
@@ -15188,7 +15188,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G511" t="n">
-        <v>1.57090985774994</v>
+        <v>1.57090973854065</v>
       </c>
       <c r="H511" t="n">
         <v>27246</v>
@@ -15217,7 +15217,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G512" t="n">
-        <v>1.60535216331482</v>
+        <v>1.60535228252411</v>
       </c>
       <c r="H512" t="n">
         <v>44066</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.59611165523529</v>
+        <v>1.596111536026</v>
       </c>
       <c r="H513" t="n">
         <v>14563</v>
@@ -15304,7 +15304,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G515" t="n">
-        <v>1.62635374069214</v>
+        <v>1.62635362148285</v>
       </c>
       <c r="H515" t="n">
         <v>91898</v>
@@ -15333,7 +15333,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G516" t="n">
-        <v>1.61627304553986</v>
+        <v>1.6162729263305